--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R27827dfeb933409b"/>
+    <sheet name="Inventarios" sheetId="1" r:id="R2da57ce7b2304384"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -61,10 +61,10 @@
     <t>DO</t>
   </si>
   <si>
-    <t>2013421</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO ALKOSTO CANASTA</t>
+    <t>112268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300.</t>
   </si>
   <si>
     <t>VT1</t>
@@ -76,69 +76,93 @@
     <t>HU</t>
   </si>
   <si>
+    <t>112357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>2110327</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>2110427</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
     <t>2110302</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>2114158</t>
-  </si>
-  <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
     <t>2110317</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
   </si>
   <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>AFSE003</t>
   </si>
   <si>
@@ -157,6 +181,18 @@
     <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
   </si>
   <si>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>152281</t>
   </si>
   <si>
@@ -193,18 +229,6 @@
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>2110403</t>
   </si>
   <si>
@@ -244,12 +268,6 @@
     <t>MD</t>
   </si>
   <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>VT41</t>
   </si>
   <si>
@@ -262,10 +280,34 @@
     <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>112357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>VT43</t>
+  </si>
+  <si>
+    <t>TAT VALLEDUPAR - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT49</t>
+  </si>
+  <si>
+    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>10601</t>
+  </si>
+  <si>
+    <t>HUEVO C X30 CARTON GRIS</t>
   </si>
   <si>
     <t>VT52</t>
@@ -280,91 +322,286 @@
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
     <t>VT59</t>
   </si>
   <si>
     <t>TAT BOGOTA - VT59</t>
   </si>
   <si>
+    <t>VT6</t>
+  </si>
+  <si>
+    <t>TAT PASTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2013322</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
+  </si>
+  <si>
+    <t>VT7</t>
+  </si>
+  <si>
+    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>2013419</t>
   </si>
   <si>
     <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
   </si>
   <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>EMET011</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO AA ROJO X 30 ALAT</t>
+    <t>13358</t>
+  </si>
+  <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTCA</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTDOTH</t>
+  </si>
+  <si>
+    <t>BODEGA DOTACION TH TRANSITO</t>
+  </si>
+  <si>
+    <t>DOTA050</t>
+  </si>
+  <si>
+    <t>TOALLA BLANCA 1.20X0.60X320</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
   </si>
   <si>
     <t>EM</t>
   </si>
   <si>
-    <t>VTALKA2</t>
-  </si>
-  <si>
-    <t>EGIPTO - INVENTARIO TRANSITO ALKA2</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTBC</t>
-  </si>
-  <si>
-    <t>EMPAQUES BELLAVISTA TRANSITO</t>
-  </si>
-  <si>
     <t>EMBA008</t>
   </si>
   <si>
     <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
   </si>
   <si>
-    <t>EMBA025</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
-  </si>
-  <si>
-    <t>EMCA019</t>
-  </si>
-  <si>
-    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
-  </si>
-  <si>
-    <t>EMET014</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
-  </si>
-  <si>
-    <t>EMET03</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO XL X 30 - K</t>
-  </si>
-  <si>
-    <t>EMET031</t>
-  </si>
-  <si>
-    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+    <t>EMES001</t>
+  </si>
+  <si>
+    <t>ESQUINEROS DE CARTON  90X14 CM</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>EMET019</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
+  </si>
+  <si>
+    <t>VTEMBO</t>
+  </si>
+  <si>
+    <t>EMPAQUES BOGOTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET015</t>
+  </si>
+  <si>
+    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>VTEMMO</t>
+  </si>
+  <si>
+    <t>EMPAQUES MONTERIA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>EMTA006</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>DOCL001</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA S</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>DOCL003</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOCL005</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ002</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 30</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>DOPJ004</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 34</t>
+  </si>
+  <si>
+    <t>DOPJ005</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 36</t>
+  </si>
+  <si>
+    <t>DOPJ006</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 38</t>
+  </si>
+  <si>
+    <t>EMCA016</t>
+  </si>
+  <si>
+    <t>CAJA ESTÁNDAR NEUTRA</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
   </si>
   <si>
     <t>EMSU001</t>
@@ -373,223 +610,28 @@
     <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
   </si>
   <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>EMZU004</t>
-  </si>
-  <si>
-    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>13358</t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>VTDOTH</t>
-  </si>
-  <si>
-    <t>BODEGA DOTACION TH TRANSITO</t>
-  </si>
-  <si>
-    <t>DOTA050</t>
-  </si>
-  <si>
-    <t>TOALLA BLANCA 1.20X0.60X320</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EMES001</t>
-  </si>
-  <si>
-    <t>ESQUINEROS DE CARTON  90X14 CM</t>
-  </si>
-  <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>EMET015</t>
-  </si>
-  <si>
-    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>DOCL001</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA S</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>DOCL003</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOCL005</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ002</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 30</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>DOPJ004</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 34</t>
-  </si>
-  <si>
-    <t>DOPJ005</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 36</t>
-  </si>
-  <si>
-    <t>DOPJ006</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 38</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMCA016</t>
-  </si>
-  <si>
-    <t>CAJA ESTÁNDAR NEUTRA</t>
-  </si>
-  <si>
     <t>VTEMT6</t>
   </si>
   <si>
     <t>VIRTUAL EMPAQUE TAT PASTO</t>
   </si>
   <si>
-    <t>VTEMT7</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>DOCL004</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA XL</t>
-  </si>
-  <si>
-    <t>142120</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12</t>
+    <t>100</t>
+  </si>
+  <si>
+    <t>HUEVO SIN CLASIFICAR ROJO</t>
+  </si>
+  <si>
+    <t>VTGRA</t>
+  </si>
+  <si>
+    <t>BODEGA VIRTUAL DE HUEVO EN TRANSITO</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
   </si>
   <si>
     <t>VTKI</t>
@@ -598,21 +640,6 @@
     <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>BP</t>
-  </si>
-  <si>
-    <t>143230</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
     <t>ENES014</t>
   </si>
   <si>
@@ -634,141 +661,36 @@
     <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
   </si>
   <si>
+    <t>13403</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO ALAT</t>
+  </si>
+  <si>
     <t>13419</t>
   </si>
   <si>
     <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
   </si>
   <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
     <t>13524</t>
   </si>
   <si>
     <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
   </si>
   <si>
-    <t>2013322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
-  </si>
-  <si>
     <t>74001</t>
   </si>
   <si>
     <t>HUEVO DE BAJA ROTACION</t>
   </si>
   <si>
-    <t>EECA006</t>
-  </si>
-  <si>
-    <t>CAJA REGULAR X300 EMPAQUE PET</t>
-  </si>
-  <si>
-    <t>VTLZEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES LANZA TRANSITO</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>EMET017</t>
-  </si>
-  <si>
-    <t>ETIQUETA BARRA HUEVO A  X 30 INSUPERABLE EXITO</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>EMET02</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
-  </si>
-  <si>
-    <t>EMET050</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
-  </si>
-  <si>
-    <t>EMTA003</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE DISEÑO KIKES</t>
-  </si>
-  <si>
-    <t>EMTA006</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
-  </si>
-  <si>
-    <t>PTEM029</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>PTEM049</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM050</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM051</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM052</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
-  </si>
-  <si>
     <t>VTME</t>
   </si>
   <si>
     <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>VTPALM</t>
-  </si>
-  <si>
-    <t>EGIPTO - INVENTARIO TRANSITO PALMA</t>
-  </si>
-  <si>
     <t>MA0041</t>
   </si>
   <si>
@@ -851,39 +773,6 @@
   </si>
   <si>
     <t>TRANSITO VIRTUAL PUERTO SANTA MARTA</t>
-  </si>
-  <si>
-    <t>79103</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO GT</t>
-  </si>
-  <si>
-    <t>VTPULV</t>
-  </si>
-  <si>
-    <t>BODEGA TRANSITO HUEVO ROTO PARA PULVERIZADO</t>
-  </si>
-  <si>
-    <t>79111</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO ZF - SANTANDER</t>
-  </si>
-  <si>
-    <t>83118</t>
-  </si>
-  <si>
-    <t>HELP BOLSA POLIETILENO 18 KG CAJA X 1 CORRUGADO</t>
-  </si>
-  <si>
-    <t>VTZ4T3</t>
-  </si>
-  <si>
-    <t>TRANSITO DE CONSERVACION HLP COLFRIGOS BARRANQUILL</t>
-  </si>
-  <si>
-    <t>HL</t>
   </si>
 </sst>
 </file>
@@ -1022,13 +911,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>46295.558182870365</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1040,7 +929,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>5</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="4">
@@ -1054,13 +943,13 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>23040</v>
+        <v>480</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="2">
-        <v>46295.516377314816</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1072,7 +961,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1027</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="5">
@@ -1086,13 +975,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>10200</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="2">
-        <v>46295.558182870365</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1104,7 +993,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>85</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="6">
@@ -1118,145 +1007,145 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>102</v>
+        <v>57600</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="2">
-        <v>46295.558182870365</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>2501</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>28800</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>46295.516377314816</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>1751</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>360</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46296.310763888891</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8">
-        <v>9000</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46294.9765625</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8"/>
+      <c r="I8">
+        <v>440</v>
+      </c>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>1139</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>3360</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2">
-        <v>46294.978310185186</v>
+        <v>46296.310763888891</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9"/>
+        <v>32</v>
+      </c>
+      <c r="I9">
+        <v>250</v>
+      </c>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>547</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D10">
-        <v>7920</v>
+        <v>12000</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2">
-        <v>46294.978310185186</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -1268,27 +1157,27 @@
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2953</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>7920</v>
+        <v>12000</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>46294.978310185186</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -1300,7 +1189,7 @@
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>855</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="12">
@@ -1311,16 +1200,16 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12">
-        <v>10560</v>
+        <v>2400</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>46294.978310185186</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1332,27 +1221,27 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>2429</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>1800</v>
+        <v>24000</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
-        <v>46294.978310185186</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1364,75 +1253,71 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>871</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D14">
-        <v>192</v>
+        <v>3955</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>46294.978310185186</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>4287</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15">
-        <v>26</v>
+        <v>7920</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" s="2">
-        <v>46294.978310185186</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>3729</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="16">
@@ -1443,30 +1328,28 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>15840</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" s="2">
-        <v>46294.978310185186</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>2529</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17">
@@ -1477,16 +1360,16 @@
         <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D17">
-        <v>6000</v>
+        <v>83760</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F17" s="2">
-        <v>46294.869108796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1498,27 +1381,27 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>708</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>2100</v>
+        <v>3960</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F18" s="2">
-        <v>46294.869108796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1530,27 +1413,27 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>185</v>
+        <v>873</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D19">
-        <v>240</v>
+        <v>10560</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>46294.869108796294</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1562,123 +1445,129 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>39</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D20">
-        <v>7500</v>
+        <v>624</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>46294.869108796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20"/>
+        <v>32</v>
+      </c>
+      <c r="I20">
+        <v>440</v>
+      </c>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>233</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D21">
-        <v>5100</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2">
-        <v>46295.30196759259</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21"/>
+        <v>32</v>
+      </c>
+      <c r="I21">
+        <v>250</v>
+      </c>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>1317</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D22">
-        <v>1080</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>46295.30196759259</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22"/>
+        <v>32</v>
+      </c>
+      <c r="I22">
+        <v>250</v>
+      </c>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>560</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>9300</v>
+        <v>6000</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" s="2">
-        <v>46295.30164351852</v>
+        <v>46294.869108796294</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1690,27 +1579,27 @@
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>1344</v>
+        <v>708</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>105600</v>
+        <v>600</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F24" s="2">
-        <v>46295.6721412037</v>
+        <v>46295.691284722219</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1722,27 +1611,27 @@
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>2100</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F25" s="2">
-        <v>46295.303113425922</v>
+        <v>46295.69253472222</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1754,27 +1643,27 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>463</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26">
-        <v>41760</v>
+        <v>2100</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26" s="2">
-        <v>46295.229930555557</v>
+        <v>46294.869108796294</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1786,27 +1675,27 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>2798</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27">
-        <v>3960</v>
+        <v>240</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F27" s="2">
-        <v>46295.303113425922</v>
+        <v>46294.869108796294</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1818,27 +1707,27 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>691</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D28">
-        <v>5580</v>
+        <v>7500</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F28" s="2">
-        <v>46295.30228009259</v>
+        <v>46294.869108796294</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1850,27 +1739,27 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29">
+        <v>5100</v>
+      </c>
+      <c r="E29" t="s">
         <v>70</v>
       </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29">
-        <v>1152</v>
-      </c>
-      <c r="E29" t="s">
-        <v>58</v>
-      </c>
       <c r="F29" s="2">
-        <v>46295.30228009259</v>
+        <v>46295.30196759259</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1882,7 +1771,7 @@
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>79</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="30">
@@ -1893,16 +1782,16 @@
         <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D30">
-        <v>10980</v>
+        <v>1080</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F30" s="2">
-        <v>46295.30228009259</v>
+        <v>46295.30196759259</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1914,27 +1803,27 @@
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>77</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D31">
-        <v>3960</v>
+        <v>9300</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F31" s="2">
-        <v>46295.303113425922</v>
+        <v>46295.30164351852</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1946,58 +1835,56 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>520</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D32">
-        <v>768</v>
+        <v>419040</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F32" s="2">
-        <v>46295.6721412037</v>
+        <v>46295.879189814812</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>3548</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D33">
-        <v>50</v>
+        <v>1800</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2">
         <v>46295.303113425922</v>
@@ -2006,32 +1893,30 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>2776</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D34">
-        <v>16</v>
+        <v>3960</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F34" s="2">
         <v>46295.303113425922</v>
@@ -2040,15 +1925,13 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>2110</v>
+        <v>691</v>
       </c>
     </row>
     <row r="35">
@@ -2059,50 +1942,48 @@
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D35">
-        <v>38</v>
+        <v>5580</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2">
-        <v>46295.303113425922</v>
+        <v>46295.30228009259</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>2174</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D36">
-        <v>9000</v>
+        <v>1152</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F36" s="2">
-        <v>46294.795856481476</v>
+        <v>46295.30228009259</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2114,27 +1995,27 @@
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>1198</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D37">
-        <v>31680</v>
+        <v>10980</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F37" s="2">
-        <v>46294.376215277778</v>
+        <v>46295.30228009259</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -2146,27 +2027,27 @@
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>805</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D38">
-        <v>7920</v>
+        <v>3960</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F38" s="2">
-        <v>46294.795856481476</v>
+        <v>46295.303113425922</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -2178,152 +2059,160 @@
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D39">
-        <v>754080</v>
+        <v>1900</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F39" s="2">
-        <v>46295.3515162037</v>
+        <v>46296.314363425925</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39"/>
+        <v>32</v>
+      </c>
+      <c r="I39">
+        <v>440</v>
+      </c>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>3241</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D40">
-        <v>10260</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F40" s="2">
-        <v>46294.75913194444</v>
+        <v>46296.314363425925</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40"/>
+        <v>32</v>
+      </c>
+      <c r="I40">
+        <v>250</v>
+      </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>69</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
         <v>69</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s">
         <v>70</v>
       </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41">
-        <v>432</v>
-      </c>
-      <c r="E41" t="s">
-        <v>81</v>
-      </c>
       <c r="F41" s="2">
-        <v>46294.75913194444</v>
+        <v>46295.735034722224</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41"/>
+        <v>32</v>
+      </c>
+      <c r="I41">
+        <v>250</v>
+      </c>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>57</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D42">
-        <v>5400</v>
+        <v>98</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F42" s="2">
-        <v>46294.75913194444</v>
+        <v>46296.314363425925</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42"/>
+        <v>85</v>
+      </c>
+      <c r="I42">
+        <v>5000</v>
+      </c>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>65</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D43">
-        <v>7920</v>
+        <v>9000</v>
       </c>
       <c r="E43" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F43" s="2">
         <v>46294.795856481476</v>
@@ -2338,126 +2227,120 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>337</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D44">
-        <v>3452</v>
+        <v>1200</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F44" s="2">
-        <v>46295.3515162037</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>4082</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D45">
-        <v>166</v>
+        <v>480</v>
       </c>
       <c r="E45" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F45" s="2">
-        <v>46295.3515162037</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>3155</v>
+        <v>626</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D46">
-        <v>82</v>
+        <v>8400</v>
       </c>
       <c r="E46" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F46" s="2">
-        <v>46294.795856481476</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>1803</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D47">
-        <v>38</v>
+        <v>7920</v>
       </c>
       <c r="E47" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F47" s="2">
         <v>46294.795856481476</v>
@@ -2466,35 +2349,33 @@
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>2152</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>86</v>
       </c>
       <c r="D48">
-        <v>3600</v>
+        <v>486240</v>
       </c>
       <c r="E48" t="s">
         <v>87</v>
       </c>
       <c r="F48" s="2">
-        <v>46294</v>
+        <v>46295.782233796293</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
@@ -2506,27 +2387,27 @@
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>2433</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
         <v>86</v>
       </c>
       <c r="D49">
-        <v>75000</v>
+        <v>10260</v>
       </c>
       <c r="E49" t="s">
         <v>87</v>
       </c>
       <c r="F49" s="2">
-        <v>46294</v>
+        <v>46294.75913194444</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
@@ -2538,27 +2419,27 @@
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>4766</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C50" t="s">
         <v>86</v>
       </c>
       <c r="D50">
-        <v>6480</v>
+        <v>432</v>
       </c>
       <c r="E50" t="s">
         <v>87</v>
       </c>
       <c r="F50" s="2">
-        <v>46294</v>
+        <v>46294.75913194444</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2570,27 +2451,27 @@
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>1655</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51">
-        <v>105120</v>
+        <v>5400</v>
       </c>
       <c r="E51" t="s">
         <v>87</v>
       </c>
       <c r="F51" s="2">
-        <v>46294</v>
+        <v>46294.75913194444</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2602,27 +2483,27 @@
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>3797</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C52" t="s">
         <v>86</v>
       </c>
       <c r="D52">
-        <v>79200</v>
+        <v>7920</v>
       </c>
       <c r="E52" t="s">
         <v>87</v>
       </c>
       <c r="F52" s="2">
-        <v>46294.726018518515</v>
+        <v>46294.795856481476</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
@@ -2634,291 +2515,291 @@
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>1235</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
         <v>86</v>
       </c>
       <c r="D53">
-        <v>112560</v>
+        <v>2204</v>
       </c>
       <c r="E53" t="s">
         <v>87</v>
       </c>
       <c r="F53" s="2">
-        <v>46294</v>
+        <v>46295.782233796293</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53"/>
+        <v>32</v>
+      </c>
+      <c r="I53">
+        <v>440</v>
+      </c>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>2878</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
         <v>86</v>
       </c>
       <c r="D54">
-        <v>10560</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
         <v>87</v>
       </c>
       <c r="F54" s="2">
-        <v>46295.381018518514</v>
+        <v>46295.782233796293</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54"/>
+        <v>32</v>
+      </c>
+      <c r="I54">
+        <v>250</v>
+      </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>1143</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
         <v>86</v>
       </c>
       <c r="D55">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
         <v>87</v>
       </c>
       <c r="F55" s="2">
-        <v>46294.726018518515</v>
+        <v>46295.782233796293</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55"/>
+        <v>32</v>
+      </c>
+      <c r="I55">
+        <v>250</v>
+      </c>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>213</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
         <v>86</v>
       </c>
       <c r="D56">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
         <v>87</v>
       </c>
       <c r="F56" s="2">
-        <v>46294</v>
+        <v>46294.795856481476</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56"/>
+        <v>85</v>
+      </c>
+      <c r="I56">
+        <v>5000</v>
+      </c>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>205</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D57">
-        <v>1821</v>
+        <v>2400</v>
       </c>
       <c r="E57" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F57" s="2">
-        <v>46295.381018518514</v>
+        <v>46295</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>28</v>
-      </c>
-      <c r="I57">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>5527</v>
+        <v>593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D58">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F58" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>4814</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D59">
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F59" s="2">
-        <v>46294.726018518515</v>
+        <v>46295</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>2739</v>
+        <v>601</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D60">
-        <v>82</v>
+        <v>9000</v>
       </c>
       <c r="E60" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F60" s="2">
-        <v>46294.791817129626</v>
+        <v>46295</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>77</v>
-      </c>
-      <c r="I60">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>3658</v>
+        <v>939</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" t="s">
         <v>90</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61">
+        <v>34560</v>
+      </c>
+      <c r="E61" t="s">
         <v>91</v>
       </c>
-      <c r="C61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61">
-        <v>900</v>
-      </c>
-      <c r="E61" t="s">
-        <v>93</v>
-      </c>
       <c r="F61" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
@@ -2930,27 +2811,27 @@
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>833</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D62">
-        <v>15840</v>
+        <v>150000</v>
       </c>
       <c r="E62" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F62" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
@@ -2962,27 +2843,27 @@
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>1197</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D63">
-        <v>10560</v>
+        <v>2700</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F63" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
@@ -2994,27 +2875,27 @@
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>691</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D64">
-        <v>31680</v>
+        <v>864</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F64" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
@@ -3026,27 +2907,27 @@
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>1013</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D65">
-        <v>900</v>
+        <v>1440</v>
       </c>
       <c r="E65" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F65" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3058,27 +2939,27 @@
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>423</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D66">
-        <v>1200</v>
+        <v>3240</v>
       </c>
       <c r="E66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F66" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -3090,99 +2971,101 @@
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>519</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D67">
-        <v>900</v>
+        <v>816</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F67" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67"/>
+        <v>32</v>
+      </c>
+      <c r="I67">
+        <v>440</v>
+      </c>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>161</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D68">
-        <v>323</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F68" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I68">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>1429</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D69">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F69" s="2">
-        <v>46294.907013888886</v>
+        <v>46295</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I69">
         <v>250</v>
@@ -3190,61 +3073,59 @@
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>1139</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D70">
-        <v>38</v>
+        <v>154800</v>
       </c>
       <c r="E70" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F70" s="2">
-        <v>46294.907013888886</v>
+        <v>46295.790914351848</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>28</v>
-      </c>
-      <c r="I70">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>737</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s">
+        <v>82</v>
+      </c>
+      <c r="C71" t="s">
         <v>94</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71">
+        <v>1800</v>
+      </c>
+      <c r="E71" t="s">
         <v>95</v>
       </c>
-      <c r="C71" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71">
-        <v>86400</v>
-      </c>
-      <c r="E71" t="s">
-        <v>97</v>
-      </c>
       <c r="F71" s="2">
-        <v>46295.660335648143</v>
+        <v>46295.790914351848</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
@@ -3256,33 +3137,33 @@
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>353</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D72">
-        <v>480</v>
+        <v>655</v>
       </c>
       <c r="E72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F72" s="2">
-        <v>46295.660335648143</v>
+        <v>46295.790914351848</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I72">
         <v>440</v>
@@ -3290,33 +3171,33 @@
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>2363</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F73" s="2">
-        <v>46295.660335648143</v>
+        <v>46295.790914351848</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I73">
         <v>250</v>
@@ -3324,571 +3205,549 @@
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>1927</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D74">
-        <v>4000</v>
+        <v>32</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F74" s="2">
-        <v>46276.900914351849</v>
+        <v>46295.790914351848</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I74">
-        <v>70000</v>
+        <v>5000</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>1</v>
+        <v>895</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C75" t="s">
         <v>96</v>
       </c>
       <c r="D75">
-        <v>40</v>
+        <v>3000</v>
       </c>
       <c r="E75" t="s">
         <v>97</v>
       </c>
       <c r="F75" s="2">
-        <v>46295.660335648143</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>77</v>
-      </c>
-      <c r="I75">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>1246</v>
+        <v>331</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D76">
-        <v>2048</v>
+        <v>720</v>
       </c>
       <c r="E76" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F76" s="2">
-        <v>46295.410960648143</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>28</v>
-      </c>
-      <c r="I76">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>2782</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D77">
-        <v>210</v>
+        <v>7800</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F77" s="2">
-        <v>46295.410960648143</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>28</v>
-      </c>
-      <c r="I77">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>2599</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D78">
-        <v>52</v>
+        <v>42240</v>
       </c>
       <c r="E78" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F78" s="2">
-        <v>46295.410960648143</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>28</v>
-      </c>
-      <c r="I78">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>1038</v>
+        <v>465</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D79">
-        <v>106</v>
+        <v>353760</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F79" s="2">
-        <v>46295.410960648143</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>77</v>
-      </c>
-      <c r="I79">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>1100</v>
+        <v>946</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D80">
-        <v>4480</v>
+        <v>3960</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F80" s="2">
-        <v>46295.633564814816</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>100</v>
-      </c>
-      <c r="I80">
-        <v>40320</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>2319</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D81">
-        <v>11520</v>
+        <v>1672</v>
       </c>
       <c r="E81" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F81" s="2">
-        <v>46295.633564814816</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I81">
-        <v>23040</v>
+        <v>440</v>
       </c>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>2394</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D82">
-        <v>21000</v>
+        <v>82</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F82" s="2">
-        <v>46295.633564814816</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I82">
-        <v>25200</v>
+        <v>250</v>
       </c>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>1911</v>
+        <v>884</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D83">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F83" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I83">
-        <v>349</v>
+        <v>250</v>
       </c>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>331</v>
+        <v>673</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C84" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D84">
-        <v>2000</v>
+        <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F84" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.710925925923</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="I84">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>242</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D85">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="E85" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F85" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>100</v>
-      </c>
-      <c r="I85">
-        <v>30000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I85"/>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>59</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="C86" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D86">
-        <v>2500</v>
+        <v>15000</v>
       </c>
       <c r="E86" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F86" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>100</v>
-      </c>
-      <c r="I86">
-        <v>2500</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>619</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D87">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E87" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F87" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>100</v>
-      </c>
-      <c r="I87">
-        <v>100000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I87"/>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>528</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="C88" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D88">
-        <v>17920</v>
+        <v>29100</v>
       </c>
       <c r="E88" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F88" s="2">
-        <v>46295.633564814816</v>
+        <v>46296.313657407409</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>100</v>
-      </c>
-      <c r="I88">
-        <v>55020</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>1068</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>9240</v>
       </c>
       <c r="E89" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F89" s="2">
-        <v>46295.54850694444</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G89" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>100</v>
-      </c>
-      <c r="I89">
-        <v>40</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>450</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D90">
-        <v>73152</v>
+        <v>216142</v>
       </c>
       <c r="E90" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F90" s="2">
-        <v>46294.908101851848</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
@@ -3900,27 +3759,27 @@
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>1568</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D91">
-        <v>230640</v>
+        <v>105600</v>
       </c>
       <c r="E91" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F91" s="2">
-        <v>46294.908101851848</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
@@ -3932,61 +3791,59 @@
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>259</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D92">
-        <v>961</v>
+        <v>110880</v>
       </c>
       <c r="E92" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F92" s="2">
-        <v>46294.908101851848</v>
+        <v>46295.958321759259</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
-      </c>
-      <c r="I92">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>4423</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D93">
-        <v>120</v>
+        <v>15840</v>
       </c>
       <c r="E93" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F93" s="2">
-        <v>46293.94699074074</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
@@ -3998,27 +3855,27 @@
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>914</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D94">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E94" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F94" s="2">
-        <v>46294.997557870367</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
@@ -4030,27 +3887,27 @@
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>1367</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D95">
-        <v>1200</v>
+        <v>49500</v>
       </c>
       <c r="E95" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F95" s="2">
-        <v>46295.682349537034</v>
+        <v>46296.313275462962</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4062,27 +3919,27 @@
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>292</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D96">
-        <v>1200</v>
+        <v>540</v>
       </c>
       <c r="E96" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F96" s="2">
-        <v>46295.682349537034</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
@@ -4094,155 +3951,163 @@
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>270</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D97">
-        <v>300</v>
+        <v>2976</v>
       </c>
       <c r="E97" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F97" s="2">
-        <v>46294.997557870367</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97"/>
+        <v>32</v>
+      </c>
+      <c r="I97">
+        <v>440</v>
+      </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>11</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D98">
-        <v>300</v>
+        <v>134</v>
       </c>
       <c r="E98" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F98" s="2">
-        <v>46295.389479166668</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98"/>
+        <v>32</v>
+      </c>
+      <c r="I98">
+        <v>250</v>
+      </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>303</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D99">
-        <v>72864</v>
+        <v>62</v>
       </c>
       <c r="E99" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F99" s="2">
-        <v>46294.840486111112</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99"/>
+        <v>32</v>
+      </c>
+      <c r="I99">
+        <v>250</v>
+      </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>1867</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D100">
-        <v>306720</v>
+        <v>104</v>
       </c>
       <c r="E100" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F100" s="2">
-        <v>46295.368159722224</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100"/>
+        <v>85</v>
+      </c>
+      <c r="I100">
+        <v>5000</v>
+      </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>5228</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D101">
-        <v>372480</v>
+        <v>1800</v>
       </c>
       <c r="E101" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F101" s="2">
-        <v>46294</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
@@ -4254,2685 +4119,2665 @@
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>152</v>
+        <v>834</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D102">
-        <v>2830</v>
+        <v>59400</v>
       </c>
       <c r="E102" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F102" s="2">
-        <v>46295.368159722224</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>28</v>
-      </c>
-      <c r="I102">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>9235</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D103">
-        <v>144</v>
+        <v>31680</v>
       </c>
       <c r="E103" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F103" s="2">
-        <v>46294</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>28</v>
-      </c>
-      <c r="I103">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I103"/>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>6494</v>
+        <v>692</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C104" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D104">
-        <v>66</v>
+        <v>94080</v>
       </c>
       <c r="E104" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F104" s="2">
-        <v>46294</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>28</v>
-      </c>
-      <c r="I104">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I104"/>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>5261</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B105" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D105">
-        <v>32</v>
+        <v>1980</v>
       </c>
       <c r="E105" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="F105" s="2">
-        <v>46294.36650462963</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>77</v>
-      </c>
-      <c r="I105">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I105"/>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>3019</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>3120</v>
       </c>
       <c r="E106" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="F106" s="2">
-        <v>46290.555405092593</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106">
-        <v>130</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I106"/>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>11</v>
+        <v>520</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D107">
-        <v>6</v>
+        <v>1980</v>
       </c>
       <c r="E107" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="F107" s="2">
-        <v>46290.555405092593</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>16</v>
-      </c>
-      <c r="I107">
-        <v>200</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I107"/>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C108" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D108">
-        <v>840</v>
+        <v>1080</v>
       </c>
       <c r="E108" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="F108" s="2">
-        <v>46294.790335648147</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>100</v>
-      </c>
-      <c r="I108">
-        <v>23040</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I108"/>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>385</v>
+        <v>185</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="C109" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D109">
-        <v>600</v>
+        <v>1027</v>
       </c>
       <c r="E109" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="F109" s="2">
-        <v>46287.95758101852</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I109">
-        <v>660</v>
+        <v>440</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>160</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D110">
-        <v>2000</v>
+        <v>164</v>
       </c>
       <c r="E110" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="F110" s="2">
-        <v>46294.862893518519</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I110">
-        <v>1440</v>
+        <v>250</v>
       </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>420</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C111" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D111">
-        <v>22680</v>
+        <v>82</v>
       </c>
       <c r="E111" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="F111" s="2">
-        <v>46294.862893518519</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I111">
-        <v>55020</v>
+        <v>250</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>2198</v>
+        <v>738</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="D112">
-        <v>4760</v>
+        <v>3600</v>
       </c>
       <c r="E112" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="F112" s="2">
-        <v>46294.861643518518</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>100</v>
-      </c>
-      <c r="I112">
-        <v>35000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>645</v>
+        <v>153</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D113">
-        <v>2380</v>
+        <v>12000</v>
       </c>
       <c r="E113" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="F113" s="2">
-        <v>46294.360497685186</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>100</v>
-      </c>
-      <c r="I113">
-        <v>40320</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>925</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D114">
-        <v>1400</v>
+        <v>95040</v>
       </c>
       <c r="E114" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="F114" s="2">
-        <v>46295.331423611111</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>100</v>
-      </c>
-      <c r="I114">
-        <v>8000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>14</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D115">
-        <v>4000</v>
+        <v>278400</v>
       </c>
       <c r="E115" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="F115" s="2">
-        <v>46294</v>
+        <v>46295.750810185185</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>100</v>
-      </c>
-      <c r="I115">
-        <v>90000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I115"/>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>136</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="B116" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="D116">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="E116" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="F116" s="2">
-        <v>45185</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>100</v>
-      </c>
-      <c r="I116">
-        <v>360</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I116"/>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="B117" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="C117" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>3960</v>
       </c>
       <c r="E117" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="F117" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>16</v>
-      </c>
-      <c r="I117">
-        <v>25</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I117"/>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>9</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="B118" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="C118" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>1720</v>
       </c>
       <c r="E118" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="F118" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I118">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>16</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="C119" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="F119" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I119">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>7</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>168</v>
+        <v>51</v>
       </c>
       <c r="B120" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="C120" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E120" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="F120" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I120">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>7</v>
+        <v>398</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="C121" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>86400</v>
       </c>
       <c r="E121" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F121" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.77244212963</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>16</v>
-      </c>
-      <c r="I121">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I121"/>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>21</v>
+        <v>253</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="B122" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="C122" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>86400</v>
       </c>
       <c r="E122" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F122" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.660335648143</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>16</v>
-      </c>
-      <c r="I122">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I122"/>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>16</v>
+        <v>353</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>174</v>
+        <v>30</v>
       </c>
       <c r="B123" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="C123" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>960</v>
       </c>
       <c r="E123" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F123" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.77244212963</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I123">
-        <v>15</v>
+        <v>440</v>
       </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>20</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>177</v>
+        <v>34</v>
       </c>
       <c r="C124" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E124" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F124" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.77244212963</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I124">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>21</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="B125" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E125" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="F125" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.660335648143</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I125">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>20</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="B126" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>73152</v>
       </c>
       <c r="E126" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F126" s="2">
-        <v>46273.306030092594</v>
+        <v>46294.908101851848</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>16</v>
-      </c>
-      <c r="I126">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I126"/>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>17</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="B127" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D127">
-        <v>1540</v>
+        <v>282240</v>
       </c>
       <c r="E127" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F127" s="2">
-        <v>46293</v>
+        <v>46295.929895833331</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>100</v>
-      </c>
-      <c r="I127">
-        <v>14980</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I127"/>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>258</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="B128" t="s">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D128">
-        <v>120</v>
+        <v>407280</v>
       </c>
       <c r="E128" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F128" s="2">
-        <v>46293</v>
+        <v>46295.929895833331</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>100</v>
-      </c>
-      <c r="I128">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I128"/>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>168</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="C129" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D129">
-        <v>600</v>
+        <v>2873</v>
       </c>
       <c r="E129" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F129" s="2">
-        <v>46293</v>
+        <v>46295.929895833331</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I129">
-        <v>8000</v>
+        <v>440</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>196</v>
+        <v>4426</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="C130" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D130">
-        <v>30000</v>
+        <v>46</v>
       </c>
       <c r="E130" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F130" s="2">
-        <v>46280.943472222221</v>
+        <v>46295.743541666663</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I130">
-        <v>100000</v>
+        <v>250</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>102</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="C131" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E131" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="F131" s="2">
-        <v>46265.788981481477</v>
+        <v>46295.743541666663</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I131">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>14</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="C132" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>128432</v>
       </c>
       <c r="E132" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="F132" s="2">
-        <v>46265.776967592588</v>
+        <v>46295.876770833333</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
-      </c>
-      <c r="I132">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I132"/>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>11</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="B133" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="C133" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>540289</v>
       </c>
       <c r="E133" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="F133" s="2">
-        <v>46265.788981481477</v>
+        <v>46296.305277777778</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>16</v>
-      </c>
-      <c r="I133">
-        <v>15</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I133"/>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>19</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="C134" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>106080</v>
       </c>
       <c r="E134" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F134" s="2">
-        <v>46272.56653935185</v>
+        <v>46296.303877314815</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>16</v>
-      </c>
-      <c r="I134">
-        <v>36</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I134"/>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>3</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="B135" t="s">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="C135" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>3230</v>
       </c>
       <c r="E135" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F135" s="2">
-        <v>46272.56653935185</v>
+        <v>46296.305277777778</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I135">
-        <v>24</v>
+        <v>440</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>3</v>
+        <v>9241</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="C136" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="E136" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F136" s="2">
-        <v>46272.56653935185</v>
+        <v>46296.306354166663</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I136">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>20</v>
+        <v>6501</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="C137" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E137" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F137" s="2">
-        <v>46272.56653935185</v>
+        <v>46296.305277777778</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I137">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>15</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="B138" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="C138" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="E138" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="F138" s="2">
-        <v>46272.56653935185</v>
+        <v>46296.303877314815</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I138">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>17</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="B139" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="C139" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>576</v>
       </c>
       <c r="E139" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="F139" s="2">
-        <v>46272.56653935185</v>
+        <v>46295.805462962962</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>16</v>
-      </c>
-      <c r="I139">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I139"/>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>12</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="B140" t="s">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="C140" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="D140">
-        <v>12</v>
+        <v>900</v>
       </c>
       <c r="E140" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="F140" s="2">
-        <v>46294.93125</v>
+        <v>46295.805462962962</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="I140"/>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>18</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="D141">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="F141" s="2">
-        <v>46294.93125</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>196</v>
-      </c>
-      <c r="I141"/>
+        <v>16</v>
+      </c>
+      <c r="I141">
+        <v>130</v>
+      </c>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="B142" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="C142" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="D142">
-        <v>4602</v>
+        <v>6</v>
       </c>
       <c r="E142" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="F142" s="2">
-        <v>46295.41920138889</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I142">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>11302</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="B143" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="C143" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D143">
-        <v>186</v>
+        <v>840</v>
       </c>
       <c r="E143" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F143" s="2">
-        <v>44946.553055555552</v>
+        <v>46295.896851851852</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I143">
-        <v>20</v>
+        <v>40320</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>2</v>
+        <v>888</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C144" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D144">
-        <v>192</v>
+        <v>840</v>
       </c>
       <c r="E144" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F144" s="2">
-        <v>46295.41920138889</v>
+        <v>46296.161273148144</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I144">
-        <v>250</v>
+        <v>23040</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>8950</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="C145" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D145">
-        <v>94</v>
+        <v>600</v>
       </c>
       <c r="E145" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F145" s="2">
-        <v>46295.41920138889</v>
+        <v>46287.95758101852</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I145">
-        <v>250</v>
+        <v>660</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>4376</v>
+        <v>160</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="B146" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D146">
-        <v>93</v>
+        <v>1000</v>
       </c>
       <c r="E146" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F146" s="2">
-        <v>45777.752291666664</v>
+        <v>46296.161273148144</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="I146">
-        <v>16</v>
+        <v>1440</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>7</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D147">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="E147" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F147" s="2">
-        <v>44426</v>
+        <v>46296.161932870367</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>35000</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>5</v>
+        <v>646</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C148" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="D148">
-        <v>288</v>
+        <v>850</v>
       </c>
       <c r="E148" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="F148" s="2">
-        <v>46295.277013888888</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>21</v>
-      </c>
-      <c r="I148"/>
+        <v>151</v>
+      </c>
+      <c r="I148">
+        <v>5000</v>
+      </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>459</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="B149" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="C149" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="D149">
-        <v>1440</v>
+        <v>980</v>
       </c>
       <c r="E149" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="F149" s="2">
-        <v>46295.668611111112</v>
+        <v>46295.788310185184</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>21</v>
-      </c>
-      <c r="I149"/>
+        <v>138</v>
+      </c>
+      <c r="I149">
+        <v>40320</v>
+      </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>57</v>
+        <v>926</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="B150" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="D150">
-        <v>300</v>
+        <v>24000</v>
       </c>
       <c r="E150" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="F150" s="2">
-        <v>46295.275960648149</v>
+        <v>46295.848576388889</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>21</v>
-      </c>
-      <c r="I150"/>
+        <v>138</v>
+      </c>
+      <c r="I150">
+        <v>90000</v>
+      </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>565</v>
+        <v>137</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="D151">
-        <v>240</v>
+        <v>4000</v>
       </c>
       <c r="E151" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="F151" s="2">
-        <v>46295.684270833328</v>
+        <v>46295.848576388889</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>21</v>
-      </c>
-      <c r="I151"/>
+        <v>138</v>
+      </c>
+      <c r="I151">
+        <v>20000</v>
+      </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>412</v>
+        <v>129</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="C152" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D152">
-        <v>2386</v>
+        <v>560</v>
       </c>
       <c r="E152" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F152" s="2">
-        <v>46295.47378472222</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>21</v>
-      </c>
-      <c r="I152"/>
+        <v>138</v>
+      </c>
+      <c r="I152">
+        <v>5600</v>
+      </c>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="B153" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D153">
-        <v>6330</v>
+        <v>560</v>
       </c>
       <c r="E153" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F153" s="2">
-        <v>46295.47378472222</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>21</v>
-      </c>
-      <c r="I153"/>
+        <v>138</v>
+      </c>
+      <c r="I153">
+        <v>14980</v>
+      </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="B154" t="s">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="C154" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D154">
-        <v>6811</v>
+        <v>200</v>
       </c>
       <c r="E154" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F154" s="2">
-        <v>46295.475601851853</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>21</v>
-      </c>
-      <c r="I154"/>
+        <v>138</v>
+      </c>
+      <c r="I154">
+        <v>660</v>
+      </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>68</v>
+        <v>178</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="B155" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="C155" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D155">
-        <v>309</v>
+        <v>200</v>
       </c>
       <c r="E155" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F155" s="2">
-        <v>46295.475601851853</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I155">
-        <v>440</v>
+        <v>1440</v>
       </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>170</v>
+        <v>127</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="B156" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="C156" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D156">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F156" s="2">
-        <v>46295.480543981481</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I156">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="B157" t="s">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="C157" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D157">
-        <v>14</v>
+        <v>840</v>
       </c>
       <c r="E157" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F157" s="2">
-        <v>46295.480543981481</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="I157">
-        <v>5000</v>
+        <v>3920</v>
       </c>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>59</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="C158" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="D158">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="E158" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="F158" s="2">
-        <v>46295.578587962962</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="I158">
-        <v>875</v>
+        <v>55020</v>
       </c>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>1648</v>
+        <v>263</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="C159" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D159">
-        <v>35840</v>
+        <v>400</v>
       </c>
       <c r="E159" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="F159" s="2">
-        <v>46295.6325</v>
+        <v>45185</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I159">
-        <v>40320</v>
+        <v>360</v>
       </c>
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>3089</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B160" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D160">
-        <v>5600</v>
+        <v>1</v>
       </c>
       <c r="E160" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F160" s="2">
-        <v>46295.6325</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I160">
-        <v>5600</v>
+        <v>25</v>
       </c>
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>2533</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="B161" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="C161" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D161">
-        <v>11520</v>
+        <v>3</v>
       </c>
       <c r="E161" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F161" s="2">
-        <v>46295.6325</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
       </c>
       <c r="H161" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I161">
-        <v>23040</v>
+        <v>50</v>
       </c>
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>2113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C162" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D162">
-        <v>4200</v>
+        <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F162" s="2">
-        <v>46295.6325</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
       </c>
       <c r="H162" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I162">
-        <v>25200</v>
+        <v>36</v>
       </c>
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>2724</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C163" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D163">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F163" s="2">
-        <v>46295.324918981481</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I163">
-        <v>5000</v>
+        <v>8</v>
       </c>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>992</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C164" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D164">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F164" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I164">
-        <v>349</v>
+        <v>43</v>
       </c>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>444</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="B165" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C165" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D165">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F165" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I165">
-        <v>1440</v>
+        <v>2</v>
       </c>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>235</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="B166" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="C166" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D166">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F166" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
       </c>
       <c r="H166" t="s">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c r="I166">
-        <v>5000</v>
+        <v>15</v>
       </c>
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>253</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="B167" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="C167" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D167">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F167" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
       </c>
       <c r="H167" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I167">
-        <v>20000</v>
+        <v>88</v>
       </c>
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>363</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>117</v>
+        <v>190</v>
       </c>
       <c r="B168" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D168">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F168" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G168" t="s">
         <v>15</v>
       </c>
       <c r="H168" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I168">
-        <v>2500</v>
+        <v>5</v>
       </c>
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>842</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="B169" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="C169" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D169">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F169" s="2">
-        <v>46295.578587962962</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G169" t="s">
         <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I169">
-        <v>50000</v>
+        <v>2</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>331</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="B170" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="C170" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D170">
-        <v>3920</v>
+        <v>1540</v>
       </c>
       <c r="E170" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F170" s="2">
-        <v>46295.6325</v>
+        <v>46293</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I170">
-        <v>3920</v>
+        <v>14980</v>
       </c>
       <c r="J170"/>
       <c r="K170"/>
       <c r="L170">
-        <v>704</v>
+        <v>258</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="B171" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C171" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D171">
-        <v>3920</v>
+        <v>120</v>
       </c>
       <c r="E171" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F171" s="2">
-        <v>46295.6325</v>
+        <v>46293</v>
       </c>
       <c r="G171" t="s">
         <v>15</v>
       </c>
       <c r="H171" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I171">
-        <v>3920</v>
+        <v>5000</v>
       </c>
       <c r="J171"/>
       <c r="K171"/>
       <c r="L171">
-        <v>634</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="B172" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="C172" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D172">
-        <v>4480</v>
+        <v>600</v>
       </c>
       <c r="E172" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F172" s="2">
-        <v>46295.6325</v>
+        <v>46293</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I172">
-        <v>55020</v>
+        <v>8000</v>
       </c>
       <c r="J172"/>
       <c r="K172"/>
       <c r="L172">
-        <v>2486</v>
+        <v>196</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="B173" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C173" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D173">
-        <v>4480</v>
+        <v>30000</v>
       </c>
       <c r="E173" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F173" s="2">
-        <v>46295.6325</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G173" t="s">
         <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I173">
-        <v>35000</v>
+        <v>100000</v>
       </c>
       <c r="J173"/>
       <c r="K173"/>
       <c r="L173">
-        <v>865</v>
+        <v>102</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="B174" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="C174" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E174" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F174" s="2">
-        <v>46295.578587962962</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G174" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I174">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J174"/>
       <c r="K174"/>
       <c r="L174">
-        <v>1086</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="C175" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D175">
-        <v>3200</v>
+        <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F175" s="2">
-        <v>46295.324918981481</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>238</v>
+        <v>16</v>
       </c>
       <c r="I175">
-        <v>40000</v>
+        <v>43</v>
       </c>
       <c r="J175"/>
       <c r="K175"/>
       <c r="L175">
-        <v>1214</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="B176" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="C176" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D176">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F176" s="2">
-        <v>46295.578587962962</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>238</v>
-      </c>
-      <c r="I176"/>
+        <v>16</v>
+      </c>
+      <c r="I176">
+        <v>15</v>
+      </c>
       <c r="J176"/>
       <c r="K176"/>
       <c r="L176">
-        <v>143</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="B177" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="C177" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="D177">
-        <v>1400</v>
+        <v>294310</v>
       </c>
       <c r="E177" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F177" s="2">
-        <v>46295.578587962962</v>
+        <v>46295.965694444443</v>
       </c>
       <c r="G177" t="s">
         <v>15</v>
       </c>
       <c r="H177" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="I177"/>
       <c r="J177"/>
       <c r="K177"/>
       <c r="L177">
-        <v>121</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="B178" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="C178" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D178">
-        <v>3200</v>
+        <v>186</v>
       </c>
       <c r="E178" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F178" s="2">
-        <v>46295.578587962962</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
       </c>
       <c r="H178" t="s">
-        <v>238</v>
-      </c>
-      <c r="I178"/>
+        <v>32</v>
+      </c>
+      <c r="I178">
+        <v>20</v>
+      </c>
       <c r="J178"/>
       <c r="K178"/>
       <c r="L178">
-        <v>148</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="B179" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="C179" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D179">
-        <v>300</v>
+        <v>93</v>
       </c>
       <c r="E179" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F179" s="2">
-        <v>46295.578587962962</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
       </c>
       <c r="H179" t="s">
-        <v>238</v>
-      </c>
-      <c r="I179"/>
+        <v>212</v>
+      </c>
+      <c r="I179">
+        <v>16</v>
+      </c>
       <c r="J179"/>
       <c r="K179"/>
       <c r="L179">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="B180" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="C180" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="D180">
-        <v>109728</v>
+        <v>55</v>
       </c>
       <c r="E180" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="F180" s="2">
-        <v>46294.894374999996</v>
+        <v>44426</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
       </c>
       <c r="H180" t="s">
-        <v>21</v>
-      </c>
-      <c r="I180"/>
+        <v>85</v>
+      </c>
+      <c r="I180">
+        <v>2</v>
+      </c>
       <c r="J180"/>
       <c r="K180"/>
       <c r="L180">
-        <v>2415</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="B181" t="s">
-        <v>250</v>
+        <v>99</v>
       </c>
       <c r="C181" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D181">
-        <v>105600</v>
+        <v>32784</v>
       </c>
       <c r="E181" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F181" s="2">
-        <v>46295.1297337963</v>
+        <v>46295.857083333329</v>
       </c>
       <c r="G181" t="s">
         <v>15</v>
@@ -6940,31 +6785,33 @@
       <c r="H181" t="s">
         <v>21</v>
       </c>
-      <c r="I181"/>
+      <c r="I181">
+        <v>0</v>
+      </c>
       <c r="J181"/>
       <c r="K181"/>
       <c r="L181">
-        <v>1839</v>
+        <v>187</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B182" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C182" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D182">
-        <v>316800</v>
+        <v>288</v>
       </c>
       <c r="E182" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F182" s="2">
-        <v>46295.1297337963</v>
+        <v>46295.277013888888</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
@@ -6976,615 +6823,837 @@
       <c r="J182"/>
       <c r="K182"/>
       <c r="L182">
-        <v>277</v>
+        <v>459</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="B183" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="C183" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D183">
-        <v>1760</v>
+        <v>8580</v>
       </c>
       <c r="E183" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F183" s="2">
-        <v>46295.1297337963</v>
+        <v>46295.729444444441</v>
       </c>
       <c r="G183" t="s">
         <v>15</v>
       </c>
       <c r="H183" t="s">
-        <v>28</v>
-      </c>
-      <c r="I183">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I183"/>
       <c r="J183"/>
       <c r="K183"/>
       <c r="L183">
-        <v>5077</v>
+        <v>93</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>29</v>
+        <v>219</v>
       </c>
       <c r="B184" t="s">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="C184" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D184">
-        <v>106</v>
+        <v>1440</v>
       </c>
       <c r="E184" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F184" s="2">
-        <v>46295.1297337963</v>
+        <v>46295.668611111112</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
       </c>
       <c r="H184" t="s">
-        <v>28</v>
-      </c>
-      <c r="I184">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I184"/>
       <c r="J184"/>
       <c r="K184"/>
       <c r="L184">
-        <v>4465</v>
+        <v>57</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="B185" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="C185" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="D185">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="E185" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="F185" s="2">
-        <v>46295.1297337963</v>
+        <v>46295.800960648143</v>
       </c>
       <c r="G185" t="s">
         <v>15</v>
       </c>
       <c r="H185" t="s">
-        <v>28</v>
-      </c>
-      <c r="I185">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I185"/>
       <c r="J185"/>
       <c r="K185"/>
       <c r="L185">
-        <v>2553</v>
+        <v>566</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="B186" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="C186" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D186">
-        <v>1144</v>
+        <v>240</v>
       </c>
       <c r="E186" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F186" s="2">
-        <v>46295.412488425922</v>
+        <v>46295.684270833328</v>
       </c>
       <c r="G186" t="s">
         <v>15</v>
       </c>
       <c r="H186" t="s">
-        <v>28</v>
-      </c>
-      <c r="I186">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I186"/>
       <c r="J186"/>
       <c r="K186"/>
       <c r="L186">
-        <v>3237</v>
+        <v>412</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="B187" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C187" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D187">
-        <v>90</v>
+        <v>2386</v>
       </c>
       <c r="E187" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F187" s="2">
-        <v>46295.412488425922</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
       </c>
       <c r="H187" t="s">
-        <v>28</v>
-      </c>
-      <c r="I187">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I187"/>
       <c r="J187"/>
       <c r="K187"/>
       <c r="L187">
-        <v>2842</v>
+        <v>72</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="B188" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="C188" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D188">
-        <v>49</v>
+        <v>6330</v>
       </c>
       <c r="E188" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F188" s="2">
-        <v>46295.412488425922</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
       </c>
       <c r="H188" t="s">
-        <v>28</v>
-      </c>
-      <c r="I188">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I188"/>
       <c r="J188"/>
       <c r="K188"/>
       <c r="L188">
-        <v>1196</v>
+        <v>97</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="B189" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="C189" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="D189">
-        <v>2439100</v>
+        <v>6811</v>
       </c>
       <c r="E189" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F189" s="2">
-        <v>46266</v>
+        <v>46295.475601851853</v>
       </c>
       <c r="G189" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>258</v>
-      </c>
-      <c r="I189">
-        <v>950000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I189"/>
       <c r="J189"/>
       <c r="K189"/>
       <c r="L189">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>259</v>
+        <v>30</v>
       </c>
       <c r="B190" t="s">
-        <v>260</v>
+        <v>31</v>
       </c>
       <c r="C190" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="D190">
-        <v>2530000</v>
+        <v>309</v>
       </c>
       <c r="E190" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F190" s="2">
-        <v>46266</v>
+        <v>46295.475601851853</v>
       </c>
       <c r="G190" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H190" t="s">
-        <v>258</v>
+        <v>32</v>
       </c>
       <c r="I190">
-        <v>1265000</v>
+        <v>440</v>
       </c>
       <c r="J190"/>
       <c r="K190"/>
       <c r="L190">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>261</v>
+        <v>33</v>
       </c>
       <c r="B191" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="C191" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="D191">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E191" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F191" s="2">
-        <v>46295.485300925924</v>
+        <v>46295.480543981481</v>
       </c>
       <c r="G191" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="H191" t="s">
-        <v>266</v>
+        <v>32</v>
       </c>
       <c r="I191">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="J191"/>
       <c r="K191"/>
       <c r="L191">
-        <v>1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>267</v>
+        <v>83</v>
       </c>
       <c r="B192" t="s">
-        <v>268</v>
+        <v>84</v>
       </c>
       <c r="C192" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="F192" s="2">
-        <v>46293.599965277775</v>
+        <v>46295.480543981481</v>
       </c>
       <c r="G192" t="s">
         <v>15</v>
       </c>
       <c r="H192" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I192">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="J192"/>
       <c r="K192"/>
       <c r="L192">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>269</v>
+        <v>114</v>
       </c>
       <c r="B193" t="s">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="C193" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="D193">
-        <v>2</v>
+        <v>219168</v>
       </c>
       <c r="E193" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="F193" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.092002314814</v>
       </c>
       <c r="G193" t="s">
         <v>15</v>
       </c>
       <c r="H193" t="s">
-        <v>77</v>
-      </c>
-      <c r="I193">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I193"/>
       <c r="J193"/>
       <c r="K193"/>
       <c r="L193">
-        <v>2</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="B194" t="s">
-        <v>272</v>
+        <v>119</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="D194">
-        <v>1</v>
+        <v>105600</v>
       </c>
       <c r="E194" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="F194" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.151446759257</v>
       </c>
       <c r="G194" t="s">
         <v>15</v>
       </c>
       <c r="H194" t="s">
-        <v>77</v>
-      </c>
-      <c r="I194">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I194"/>
       <c r="J194"/>
       <c r="K194"/>
       <c r="L194">
-        <v>1</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
       <c r="B195" t="s">
-        <v>274</v>
+        <v>121</v>
       </c>
       <c r="C195" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>264000</v>
       </c>
       <c r="E195" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="F195" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G195" t="s">
         <v>15</v>
       </c>
       <c r="H195" t="s">
-        <v>77</v>
-      </c>
-      <c r="I195">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I195"/>
       <c r="J195"/>
       <c r="K195"/>
       <c r="L195">
-        <v>1</v>
+        <v>279</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>275</v>
+        <v>30</v>
       </c>
       <c r="B196" t="s">
-        <v>276</v>
+        <v>31</v>
       </c>
       <c r="C196" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="D196">
-        <v>5</v>
+        <v>1540</v>
       </c>
       <c r="E196" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="F196" s="2">
-        <v>46293.594282407408</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="I196">
-        <v>16</v>
+        <v>440</v>
       </c>
       <c r="J196"/>
       <c r="K196"/>
       <c r="L196">
-        <v>1</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
       <c r="B197" t="s">
-        <v>278</v>
+        <v>34</v>
       </c>
       <c r="C197" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="D197">
-        <v>78000</v>
+        <v>118</v>
       </c>
       <c r="E197" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="F197" s="2">
-        <v>46266</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G197" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H197" t="s">
-        <v>258</v>
+        <v>32</v>
       </c>
       <c r="I197">
-        <v>52000</v>
+        <v>250</v>
       </c>
       <c r="J197"/>
       <c r="K197"/>
       <c r="L197">
-        <v>48</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="B198" t="s">
-        <v>282</v>
+        <v>52</v>
       </c>
       <c r="C198" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="D198">
-        <v>684211</v>
+        <v>44</v>
       </c>
       <c r="E198" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="F198" s="2">
-        <v>46295.561736111107</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G198" t="s">
         <v>15</v>
       </c>
       <c r="H198" t="s">
-        <v>21</v>
-      </c>
-      <c r="I198"/>
+        <v>32</v>
+      </c>
+      <c r="I198">
+        <v>250</v>
+      </c>
       <c r="J198"/>
       <c r="K198"/>
       <c r="L198">
-        <v>579</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>285</v>
+        <v>227</v>
       </c>
       <c r="B199" t="s">
-        <v>286</v>
+        <v>228</v>
       </c>
       <c r="C199" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="D199">
-        <v>37500</v>
+        <v>2439100</v>
       </c>
       <c r="E199" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="F199" s="2">
-        <v>46295.394826388889</v>
+        <v>46266</v>
       </c>
       <c r="G199" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
       <c r="H199" t="s">
-        <v>21</v>
-      </c>
-      <c r="I199"/>
+        <v>232</v>
+      </c>
+      <c r="I199">
+        <v>950000</v>
+      </c>
       <c r="J199"/>
       <c r="K199"/>
       <c r="L199">
-        <v>391</v>
+        <v>56</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="B200" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="C200" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="D200">
-        <v>5508</v>
+        <v>2530000</v>
       </c>
       <c r="E200" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="F200" s="2">
-        <v>46294.534918981481</v>
+        <v>46266</v>
       </c>
       <c r="G200" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="H200" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="I200">
-        <v>4104</v>
+        <v>1265000</v>
       </c>
       <c r="J200"/>
       <c r="K200"/>
       <c r="L200">
-        <v>547</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>235</v>
+      </c>
+      <c r="B201" t="s">
+        <v>236</v>
+      </c>
+      <c r="C201" t="s">
+        <v>237</v>
+      </c>
+      <c r="D201">
+        <v>50</v>
+      </c>
+      <c r="E201" t="s">
+        <v>238</v>
+      </c>
+      <c r="F201" s="2">
+        <v>46295.485300925924</v>
+      </c>
+      <c r="G201" t="s">
+        <v>239</v>
+      </c>
+      <c r="H201" t="s">
+        <v>240</v>
+      </c>
+      <c r="I201">
+        <v>50</v>
+      </c>
+      <c r="J201"/>
+      <c r="K201"/>
+      <c r="L201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>241</v>
+      </c>
+      <c r="B202" t="s">
+        <v>242</v>
+      </c>
+      <c r="C202" t="s">
+        <v>237</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
+        <v>238</v>
+      </c>
+      <c r="F202" s="2">
+        <v>46293.599965277775</v>
+      </c>
+      <c r="G202" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" t="s">
+        <v>85</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202"/>
+      <c r="K202"/>
+      <c r="L202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>243</v>
+      </c>
+      <c r="B203" t="s">
+        <v>244</v>
+      </c>
+      <c r="C203" t="s">
+        <v>237</v>
+      </c>
+      <c r="D203">
+        <v>2</v>
+      </c>
+      <c r="E203" t="s">
+        <v>238</v>
+      </c>
+      <c r="F203" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G203" t="s">
+        <v>15</v>
+      </c>
+      <c r="H203" t="s">
+        <v>85</v>
+      </c>
+      <c r="I203">
+        <v>2</v>
+      </c>
+      <c r="J203"/>
+      <c r="K203"/>
+      <c r="L203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>245</v>
+      </c>
+      <c r="B204" t="s">
+        <v>246</v>
+      </c>
+      <c r="C204" t="s">
+        <v>237</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204" t="s">
+        <v>238</v>
+      </c>
+      <c r="F204" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G204" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" t="s">
+        <v>85</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204"/>
+      <c r="K204"/>
+      <c r="L204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>247</v>
+      </c>
+      <c r="B205" t="s">
+        <v>248</v>
+      </c>
+      <c r="C205" t="s">
+        <v>237</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205" t="s">
+        <v>238</v>
+      </c>
+      <c r="F205" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" t="s">
+        <v>85</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205"/>
+      <c r="K205"/>
+      <c r="L205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>249</v>
+      </c>
+      <c r="B206" t="s">
+        <v>250</v>
+      </c>
+      <c r="C206" t="s">
+        <v>237</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+      <c r="E206" t="s">
+        <v>238</v>
+      </c>
+      <c r="F206" s="2">
+        <v>46293.594282407408</v>
+      </c>
+      <c r="G206" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" t="s">
+        <v>85</v>
+      </c>
+      <c r="I206">
+        <v>16</v>
+      </c>
+      <c r="J206"/>
+      <c r="K206"/>
+      <c r="L206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>251</v>
+      </c>
+      <c r="B207" t="s">
+        <v>252</v>
+      </c>
+      <c r="C207" t="s">
+        <v>253</v>
+      </c>
+      <c r="D207">
+        <v>78000</v>
+      </c>
+      <c r="E207" t="s">
+        <v>254</v>
+      </c>
+      <c r="F207" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G207" t="s">
+        <v>231</v>
+      </c>
+      <c r="H207" t="s">
+        <v>232</v>
+      </c>
+      <c r="I207">
+        <v>52000</v>
+      </c>
+      <c r="J207"/>
+      <c r="K207"/>
+      <c r="L207">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R2da57ce7b2304384"/>
+    <sheet name="Inventarios" sheetId="1" r:id="R8695d1628ec64b57"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -61,19 +61,43 @@
     <t>DO</t>
   </si>
   <si>
+    <t>110322</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO - VENTA INTERNA</t>
+  </si>
+  <si>
+    <t>VT1</t>
+  </si>
+  <si>
+    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>110480</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE CAJA X 360 CON ETIQUETA</t>
+  </si>
+  <si>
     <t>112268</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>VT1</t>
-  </si>
-  <si>
-    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>HU</t>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
     <t>112357</t>
@@ -88,16 +112,40 @@
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>2110327</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2110427</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>AFCA022</t>
@@ -115,64 +163,16 @@
     <t>ESTIBAS OVOID 124CM X 65CM</t>
   </si>
   <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>AFSE003</t>
   </si>
   <si>
     <t>SEPARADORES OVOID DE 124CM X 66CM</t>
   </si>
   <si>
-    <t>110316</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>VT36</t>
@@ -181,34 +181,25 @@
     <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
   </si>
   <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>114379</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>152281</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PAGUE 14 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>152381</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PAGUE 11 PET CAJA X 120</t>
-  </si>
-  <si>
-    <t>152382</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
   </si>
   <si>
     <t>114268</t>
@@ -217,10 +208,10 @@
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
   </si>
   <si>
     <t>114357</t>
@@ -229,10 +220,16 @@
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>2110403</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>2114268</t>
@@ -259,45 +256,6 @@
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2110303</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>VT42</t>
-  </si>
-  <si>
-    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>VT43</t>
-  </si>
-  <si>
-    <t>TAT VALLEDUPAR - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>VT49</t>
   </si>
   <si>
@@ -334,357 +292,447 @@
     <t>TAT PASTO - INVENTARIO TRANSITO</t>
   </si>
   <si>
+    <t>EECA006</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X300 EMPAQUE PET</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMES001</t>
+  </si>
+  <si>
+    <t>ESQUINEROS DE CARTON  90X14 CM</t>
+  </si>
+  <si>
+    <t>EMET031</t>
+  </si>
+  <si>
+    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>PTET04</t>
+  </si>
+  <si>
+    <t>ETIQUETA PET X 30 L - ACEBRI</t>
+  </si>
+  <si>
+    <t>UPCI07</t>
+  </si>
+  <si>
+    <t>CINTA EMPAQUE 48MM X 100M REF. 305 3M</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>VTALBKA2</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 2 TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA025</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
+  </si>
+  <si>
+    <t>EMET015</t>
+  </si>
+  <si>
+    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>PTEM049</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM050</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM051</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM052</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM054</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTDOTH</t>
+  </si>
+  <si>
+    <t>BODEGA DOTACION TH TRANSITO</t>
+  </si>
+  <si>
+    <t>DOTA050</t>
+  </si>
+  <si>
+    <t>TOALLA BLANCA 1.20X0.60X320</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>EMET019</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
+  </si>
+  <si>
+    <t>VTEMBO</t>
+  </si>
+  <si>
+    <t>EMPAQUES BOGOTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>VTEMMO</t>
+  </si>
+  <si>
+    <t>EMPAQUES MONTERIA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>EMTA006</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>DOCL001</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA S</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>DOCL003</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOCL005</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ002</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 30</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>DOPJ004</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 34</t>
+  </si>
+  <si>
+    <t>DOPJ005</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 36</t>
+  </si>
+  <si>
+    <t>DOPJ006</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 38</t>
+  </si>
+  <si>
+    <t>EMCA016</t>
+  </si>
+  <si>
+    <t>CAJA ESTÁNDAR NEUTRA</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
+  </si>
+  <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
+    <t>13419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
+  </si>
+  <si>
     <t>2013322</t>
   </si>
   <si>
     <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
   </si>
   <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>2013419</t>
   </si>
   <si>
     <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
   </si>
   <si>
+    <t>74001</t>
+  </si>
+  <si>
+    <t>HUEVO DE BAJA ROTACION</t>
+  </si>
+  <si>
+    <t>VTLZEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES LANZA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMCA019</t>
+  </si>
+  <si>
+    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
+  </si>
+  <si>
+    <t>EMET017</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 INSUPERABLE EXITO</t>
+  </si>
+  <si>
+    <t>EMET03</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO XL X 30 - K</t>
+  </si>
+  <si>
+    <t>EMET050</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
+  </si>
+  <si>
+    <t>PTEM044</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 10 XXL ETIQUETADO</t>
+  </si>
+  <si>
     <t>13358</t>
   </si>
   <si>
     <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
   </si>
   <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTDOTH</t>
-  </si>
-  <si>
-    <t>BODEGA DOTACION TH TRANSITO</t>
-  </si>
-  <si>
-    <t>DOTA050</t>
-  </si>
-  <si>
-    <t>TOALLA BLANCA 1.20X0.60X320</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>EMBA008</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
-  </si>
-  <si>
-    <t>EMES001</t>
-  </si>
-  <si>
-    <t>ESQUINEROS DE CARTON  90X14 CM</t>
-  </si>
-  <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
-    <t>EMET019</t>
-  </si>
-  <si>
-    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
-  </si>
-  <si>
-    <t>VTEMBO</t>
-  </si>
-  <si>
-    <t>EMPAQUES BOGOTA TRANSITO</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMET015</t>
-  </si>
-  <si>
-    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
-  </si>
-  <si>
-    <t>EMET02</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
-  </si>
-  <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>EMTA006</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>DOCL001</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA S</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>DOCL003</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOCL005</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ002</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 30</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>DOPJ004</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 34</t>
-  </si>
-  <si>
-    <t>DOPJ005</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 36</t>
-  </si>
-  <si>
-    <t>DOPJ006</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 38</t>
-  </si>
-  <si>
-    <t>EMCA016</t>
-  </si>
-  <si>
-    <t>CAJA ESTÁNDAR NEUTRA</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>HUEVO SIN CLASIFICAR ROJO</t>
-  </si>
-  <si>
-    <t>VTGRA</t>
-  </si>
-  <si>
-    <t>BODEGA VIRTUAL DE HUEVO EN TRANSITO</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13403</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO ALAT</t>
-  </si>
-  <si>
-    <t>13419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
-  </si>
-  <si>
-    <t>13524</t>
-  </si>
-  <si>
-    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
-  </si>
-  <si>
-    <t>74001</t>
-  </si>
-  <si>
-    <t>HUEVO DE BAJA ROTACION</t>
-  </si>
-  <si>
     <t>VTME</t>
   </si>
   <si>
@@ -773,6 +821,21 @@
   </si>
   <si>
     <t>TRANSITO VIRTUAL PUERTO SANTA MARTA</t>
+  </si>
+  <si>
+    <t>81190</t>
+  </si>
+  <si>
+    <t>HELP BIB BOLSA 1000 KG CONTPR X 1</t>
+  </si>
+  <si>
+    <t>VTZ3T3</t>
+  </si>
+  <si>
+    <t>TRANSITO CONSERVACION HLP COLFRIGOS MEDELLIN</t>
+  </si>
+  <si>
+    <t>HL</t>
   </si>
 </sst>
 </file>
@@ -911,13 +974,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>600</v>
+        <v>23400</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>46296.310763888891</v>
+        <v>46296.385150462964</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -929,7 +992,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>2527</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -943,13 +1006,13 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>480</v>
+        <v>6480</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="2">
-        <v>46296.310763888891</v>
+        <v>46296.659039351849</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -961,7 +1024,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1711</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -972,16 +1035,16 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>10200</v>
+        <v>12000</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2">
-        <v>46296.310763888891</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -993,27 +1056,27 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>2839</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6">
+        <v>12000</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>57600</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
       <c r="F6" s="2">
-        <v>46296.310763888891</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1025,27 +1088,27 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>879</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>28800</v>
+        <v>2400</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2">
-        <v>46296.310763888891</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1057,95 +1120,91 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>881</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>360</v>
+        <v>24000</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>46296.310763888891</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>2504</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>3955</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2">
-        <v>46296.310763888891</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>1753</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>12000</v>
+        <v>7920</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F10" s="2">
-        <v>46295.892233796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -1157,24 +1216,24 @@
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2961</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>12000</v>
+        <v>15840</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2">
         <v>46296.093148148146</v>
@@ -1189,27 +1248,27 @@
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>1141</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>2400</v>
+        <v>83760</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F12" s="2">
-        <v>46295.892233796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1221,27 +1280,27 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>1691</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13">
-        <v>24000</v>
+        <v>3960</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F13" s="2">
-        <v>46295.892233796294</v>
+        <v>46296.093148148146</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1253,27 +1312,27 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>2731</v>
+        <v>873</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14">
-        <v>3955</v>
+        <v>10560</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F14" s="2">
-        <v>46296.093148148146</v>
+        <v>46295.892233796294</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1285,24 +1344,24 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>549</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15">
-        <v>7920</v>
+        <v>624</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2">
         <v>46296.093148148146</v>
@@ -1311,30 +1370,32 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15"/>
+        <v>48</v>
+      </c>
+      <c r="I15">
+        <v>440</v>
+      </c>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2955</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D16">
-        <v>15840</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F16" s="2">
         <v>46296.093148148146</v>
@@ -1343,30 +1404,32 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16"/>
+        <v>48</v>
+      </c>
+      <c r="I16">
+        <v>250</v>
+      </c>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>857</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D17">
-        <v>83760</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2">
         <v>46296.093148148146</v>
@@ -1375,33 +1438,35 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17"/>
+        <v>48</v>
+      </c>
+      <c r="I17">
+        <v>250</v>
+      </c>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>2431</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D18">
-        <v>3960</v>
+        <v>600</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F18" s="2">
-        <v>46296.093148148146</v>
+        <v>46295.691284722219</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1413,27 +1478,27 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>873</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D19">
-        <v>10560</v>
+        <v>600</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F19" s="2">
-        <v>46295.892233796294</v>
+        <v>46295.69253472222</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1445,101 +1510,99 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>1655</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D20">
-        <v>624</v>
+        <v>313440</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2">
-        <v>46296.093148148146</v>
+        <v>46296.571620370371</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>4289</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D21">
-        <v>32</v>
+        <v>1306</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2">
-        <v>46296.093148148146</v>
+        <v>46296.572187499994</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I21">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>3731</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F22" s="2">
-        <v>46296.093148148146</v>
+        <v>46296.571620370371</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I22">
         <v>250</v>
@@ -1547,91 +1610,95 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>2531</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D23">
-        <v>6000</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>46294.869108796294</v>
+        <v>46296.571620370371</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23"/>
+        <v>48</v>
+      </c>
+      <c r="I23">
+        <v>250</v>
+      </c>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>708</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D24">
-        <v>600</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>46295.691284722219</v>
+        <v>46296.571620370371</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24"/>
+        <v>63</v>
+      </c>
+      <c r="I24">
+        <v>5000</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>7</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D25">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F25" s="2">
-        <v>46295.69253472222</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1643,27 +1710,27 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>26</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D26">
-        <v>2100</v>
+        <v>480</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F26" s="2">
-        <v>46294.869108796294</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1675,27 +1742,27 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>185</v>
+        <v>626</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D27">
-        <v>240</v>
+        <v>8400</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2">
-        <v>46294.869108796294</v>
+        <v>46295.780092592591</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1707,27 +1774,27 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>39</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
       <c r="D28">
-        <v>7500</v>
+        <v>103680</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F28" s="2">
-        <v>46294.869108796294</v>
+        <v>46296.614837962959</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1739,123 +1806,129 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>233</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>432</v>
+      </c>
+      <c r="E29" t="s">
         <v>67</v>
       </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29">
-        <v>5100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>70</v>
-      </c>
       <c r="F29" s="2">
-        <v>46295.30196759259</v>
+        <v>46296.614837962959</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29"/>
+        <v>48</v>
+      </c>
+      <c r="I29">
+        <v>440</v>
+      </c>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>1317</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D30">
-        <v>1080</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F30" s="2">
-        <v>46295.30196759259</v>
+        <v>46296.614837962959</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30"/>
+        <v>48</v>
+      </c>
+      <c r="I30">
+        <v>250</v>
+      </c>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>560</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D31">
-        <v>9300</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F31" s="2">
-        <v>46295.30164351852</v>
+        <v>46296.614837962959</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31"/>
+        <v>63</v>
+      </c>
+      <c r="I31">
+        <v>5000</v>
+      </c>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>1344</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32">
-        <v>419040</v>
+        <v>2400</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F32" s="2">
-        <v>46295.879189814812</v>
+        <v>46295</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -1867,27 +1940,27 @@
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>2102</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F33" s="2">
-        <v>46295.303113425922</v>
+        <v>46295</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -1899,27 +1972,27 @@
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>463</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34">
-        <v>3960</v>
+        <v>2400</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F34" s="2">
-        <v>46295.303113425922</v>
+        <v>46295</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1931,27 +2004,27 @@
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>691</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35">
-        <v>5580</v>
+        <v>9000</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F35" s="2">
-        <v>46295.30228009259</v>
+        <v>46295</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -1963,27 +2036,27 @@
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>79</v>
+        <v>939</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D36">
-        <v>1152</v>
+        <v>34560</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F36" s="2">
-        <v>46295.30228009259</v>
+        <v>46295</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -1995,27 +2068,27 @@
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>79</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D37">
-        <v>10980</v>
+        <v>150000</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F37" s="2">
-        <v>46295.30228009259</v>
+        <v>46295</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -2027,27 +2100,27 @@
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>77</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D38">
-        <v>3960</v>
+        <v>2700</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F38" s="2">
-        <v>46295.303113425922</v>
+        <v>46295</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -2059,227 +2132,225 @@
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>520</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D39">
-        <v>1900</v>
+        <v>864</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F39" s="2">
-        <v>46296.314363425925</v>
+        <v>46295</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>3551</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D40">
-        <v>96</v>
+        <v>1440</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F40" s="2">
-        <v>46296.314363425925</v>
+        <v>46295</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>2779</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D41">
-        <v>34</v>
+        <v>3240</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F41" s="2">
-        <v>46295.735034722224</v>
+        <v>46295</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>2111</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D42">
-        <v>98</v>
+        <v>816</v>
       </c>
       <c r="E42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F42" s="2">
-        <v>46296.314363425925</v>
+        <v>46295</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>2176</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D43">
-        <v>9000</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F43" s="2">
-        <v>46294.795856481476</v>
+        <v>46295</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43"/>
+        <v>48</v>
+      </c>
+      <c r="I43">
+        <v>250</v>
+      </c>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>1198</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D44">
-        <v>1200</v>
+        <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F44" s="2">
-        <v>46295.780092592591</v>
+        <v>46295</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44"/>
+        <v>48</v>
+      </c>
+      <c r="I44">
+        <v>250</v>
+      </c>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>1040</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D45">
-        <v>480</v>
+        <v>3000</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F45" s="2">
-        <v>46295.780092592591</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
@@ -2291,27 +2362,27 @@
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>626</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D46">
-        <v>8400</v>
+        <v>720</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F46" s="2">
-        <v>46295.780092592591</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
@@ -2323,27 +2394,27 @@
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>1053</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D47">
-        <v>7920</v>
+        <v>7800</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F47" s="2">
-        <v>46294.795856481476</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
@@ -2355,27 +2426,27 @@
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>515</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D48">
-        <v>486240</v>
+        <v>42240</v>
       </c>
       <c r="E48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F48" s="2">
-        <v>46295.782233796293</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
@@ -2387,27 +2458,27 @@
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>3243</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D49">
-        <v>10260</v>
+        <v>353760</v>
       </c>
       <c r="E49" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F49" s="2">
-        <v>46294.75913194444</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
@@ -2419,27 +2490,27 @@
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>69</v>
+        <v>946</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D50">
-        <v>432</v>
+        <v>3960</v>
       </c>
       <c r="E50" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F50" s="2">
-        <v>46294.75913194444</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2451,227 +2522,227 @@
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>57</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D51">
-        <v>5400</v>
+        <v>1672</v>
       </c>
       <c r="E51" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F51" s="2">
-        <v>46294.75913194444</v>
+        <v>46296.593819444446</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51"/>
+        <v>48</v>
+      </c>
+      <c r="I51">
+        <v>440</v>
+      </c>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>65</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" t="s">
         <v>82</v>
       </c>
-      <c r="C52" t="s">
-        <v>86</v>
-      </c>
       <c r="D52">
-        <v>7920</v>
+        <v>82</v>
       </c>
       <c r="E52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F52" s="2">
-        <v>46294.795856481476</v>
+        <v>46296.593819444446</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52"/>
+        <v>48</v>
+      </c>
+      <c r="I52">
+        <v>250</v>
+      </c>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>337</v>
+        <v>886</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D53">
-        <v>2204</v>
+        <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F53" s="2">
-        <v>46295.782233796293</v>
+        <v>46295.747650462959</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I53">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>4084</v>
+        <v>673</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
         <v>86</v>
       </c>
       <c r="D54">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E54" t="s">
         <v>87</v>
       </c>
       <c r="F54" s="2">
-        <v>46295.782233796293</v>
+        <v>46295.710925925923</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I54">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>3157</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
         <v>86</v>
       </c>
       <c r="D55">
-        <v>40</v>
+        <v>6000</v>
       </c>
       <c r="E55" t="s">
         <v>87</v>
       </c>
       <c r="F55" s="2">
-        <v>46295.782233796293</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>1804</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
         <v>86</v>
       </c>
       <c r="D56">
-        <v>38</v>
+        <v>15000</v>
       </c>
       <c r="E56" t="s">
         <v>87</v>
       </c>
       <c r="F56" s="2">
-        <v>46294.795856481476</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>85</v>
-      </c>
-      <c r="I56">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>2152</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D57">
-        <v>2400</v>
+        <v>24000</v>
       </c>
       <c r="E57" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F57" s="2">
-        <v>46295</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
@@ -2683,27 +2754,27 @@
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>593</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D58">
-        <v>240</v>
+        <v>29100</v>
       </c>
       <c r="E58" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F58" s="2">
-        <v>46295</v>
+        <v>46296.313657407409</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
@@ -2715,27 +2786,27 @@
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>331</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D59">
-        <v>2400</v>
+        <v>9240</v>
       </c>
       <c r="E59" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F59" s="2">
-        <v>46295</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
@@ -2747,27 +2818,27 @@
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>601</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D60">
-        <v>9000</v>
+        <v>216142</v>
       </c>
       <c r="E60" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F60" s="2">
-        <v>46295</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -2779,27 +2850,27 @@
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>939</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D61">
-        <v>34560</v>
+        <v>105600</v>
       </c>
       <c r="E61" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F61" s="2">
-        <v>46295</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
@@ -2811,27 +2882,27 @@
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>1121</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D62">
-        <v>150000</v>
+        <v>110880</v>
       </c>
       <c r="E62" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F62" s="2">
-        <v>46295</v>
+        <v>46295.958321759259</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
@@ -2843,27 +2914,27 @@
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>1773</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D63">
-        <v>2700</v>
+        <v>15840</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F63" s="2">
-        <v>46295</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
@@ -2875,27 +2946,27 @@
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>65</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D64">
-        <v>864</v>
+        <v>1800</v>
       </c>
       <c r="E64" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F64" s="2">
-        <v>46295</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
@@ -2907,27 +2978,27 @@
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>49</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" t="s">
         <v>79</v>
       </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D65">
-        <v>1440</v>
+        <v>49500</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F65" s="2">
-        <v>46295</v>
+        <v>46296.313275462962</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -2939,27 +3010,27 @@
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" t="s">
         <v>81</v>
       </c>
-      <c r="B66" t="s">
-        <v>82</v>
-      </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D66">
-        <v>3240</v>
+        <v>540</v>
       </c>
       <c r="E66" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F66" s="2">
-        <v>46295</v>
+        <v>46295.9137037037</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -2971,33 +3042,33 @@
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>261</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D67">
-        <v>816</v>
+        <v>2976</v>
       </c>
       <c r="E67" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F67" s="2">
-        <v>46295</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I67">
         <v>440</v>
@@ -3005,33 +3076,33 @@
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>2120</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D68">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F68" s="2">
-        <v>46295</v>
+        <v>46296.314166666663</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I68">
         <v>250</v>
@@ -3039,7 +3110,7 @@
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>1755</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="69">
@@ -3050,22 +3121,22 @@
         <v>52</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D69">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E69" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F69" s="2">
-        <v>46295</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I69">
         <v>250</v>
@@ -3073,59 +3144,61 @@
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>1059</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D70">
-        <v>154800</v>
+        <v>104</v>
       </c>
       <c r="E70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F70" s="2">
-        <v>46295.790914351848</v>
+        <v>46296.120555555557</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70"/>
+        <v>63</v>
+      </c>
+      <c r="I70">
+        <v>5000</v>
+      </c>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>1361</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D71">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E71" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F71" s="2">
-        <v>46295.790914351848</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
@@ -3137,129 +3210,123 @@
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>247</v>
+        <v>835</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D72">
-        <v>655</v>
+        <v>43560</v>
       </c>
       <c r="E72" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F72" s="2">
-        <v>46295.790914351848</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>1467</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>21120</v>
       </c>
       <c r="E73" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F73" s="2">
-        <v>46295.790914351848</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>32</v>
-      </c>
-      <c r="I73">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>1246</v>
+        <v>693</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D74">
-        <v>32</v>
+        <v>62400</v>
       </c>
       <c r="E74" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F74" s="2">
-        <v>46295.790914351848</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>85</v>
-      </c>
-      <c r="I74">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>895</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D75">
-        <v>3000</v>
+        <v>1080</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F75" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
@@ -3271,27 +3338,27 @@
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>331</v>
+        <v>425</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D76">
-        <v>720</v>
+        <v>1920</v>
       </c>
       <c r="E76" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
@@ -3303,27 +3370,27 @@
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>233</v>
+        <v>521</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D77">
-        <v>7800</v>
+        <v>1080</v>
       </c>
       <c r="E77" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F77" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
@@ -3335,27 +3402,27 @@
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>323</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D78">
-        <v>42240</v>
+        <v>1080</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F78" s="2">
-        <v>46295.747650462959</v>
+        <v>46295.928888888884</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
@@ -3367,193 +3434,193 @@
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>465</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D79">
-        <v>353760</v>
+        <v>704</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F79" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79"/>
+        <v>48</v>
+      </c>
+      <c r="I79">
+        <v>440</v>
+      </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>946</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D80">
-        <v>3960</v>
+        <v>88</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F80" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80"/>
+        <v>48</v>
+      </c>
+      <c r="I80">
+        <v>250</v>
+      </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>109</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D81">
-        <v>1672</v>
+        <v>44</v>
       </c>
       <c r="E81" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F81" s="2">
-        <v>46295.747650462959</v>
+        <v>46296.399467592593</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I81">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>1048</v>
+        <v>739</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D82">
-        <v>82</v>
+        <v>3600</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F82" s="2">
-        <v>46295.747650462959</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>32</v>
-      </c>
-      <c r="I82">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>884</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D83">
-        <v>36</v>
+        <v>12000</v>
       </c>
       <c r="E83" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F83" s="2">
-        <v>46295.747650462959</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
-      </c>
-      <c r="I83">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>673</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D84">
-        <v>180</v>
+        <v>95040</v>
       </c>
       <c r="E84" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F84" s="2">
-        <v>46295.710925925923</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
@@ -3561,33 +3628,31 @@
       <c r="H84" t="s">
         <v>21</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
+      <c r="I84"/>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>85</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D85">
-        <v>6000</v>
+        <v>278400</v>
       </c>
       <c r="E85" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F85" s="2">
-        <v>46295.9137037037</v>
+        <v>46295.750810185185</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
@@ -3599,27 +3664,27 @@
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>3758</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D86">
-        <v>15000</v>
+        <v>1800</v>
       </c>
       <c r="E86" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F86" s="2">
-        <v>46295.9137037037</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
@@ -3631,27 +3696,27 @@
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>1057</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D87">
-        <v>24000</v>
+        <v>3960</v>
       </c>
       <c r="E87" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F87" s="2">
-        <v>46295.9137037037</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
@@ -3663,969 +3728,1003 @@
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>4769</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>46</v>
+      </c>
+      <c r="B88" t="s">
+        <v>47</v>
+      </c>
+      <c r="C88" t="s">
         <v>92</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88">
+        <v>1720</v>
+      </c>
+      <c r="E88" t="s">
         <v>93</v>
       </c>
-      <c r="C88" t="s">
-        <v>100</v>
-      </c>
-      <c r="D88">
-        <v>29100</v>
-      </c>
-      <c r="E88" t="s">
-        <v>101</v>
-      </c>
       <c r="F88" s="2">
-        <v>46296.313657407409</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88"/>
+        <v>48</v>
+      </c>
+      <c r="I88">
+        <v>440</v>
+      </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>2176</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D89">
-        <v>9240</v>
+        <v>92</v>
       </c>
       <c r="E89" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F89" s="2">
-        <v>46295.9137037037</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89"/>
+        <v>48</v>
+      </c>
+      <c r="I89">
+        <v>250</v>
+      </c>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>1657</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C90" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D90">
-        <v>216142</v>
+        <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F90" s="2">
-        <v>46296.314166666663</v>
+        <v>46295.794895833329</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90"/>
+        <v>48</v>
+      </c>
+      <c r="I90">
+        <v>250</v>
+      </c>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>3801</v>
+        <v>398</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D91">
-        <v>105600</v>
+        <v>500</v>
       </c>
       <c r="E91" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F91" s="2">
-        <v>46296.120555555557</v>
+        <v>46296.332766203705</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91"/>
+        <v>98</v>
+      </c>
+      <c r="I91">
+        <v>875</v>
+      </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>1237</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D92">
-        <v>110880</v>
+        <v>17920</v>
       </c>
       <c r="E92" t="s">
+        <v>97</v>
+      </c>
+      <c r="F92" s="2">
+        <v>46296.602094907408</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
         <v>101</v>
       </c>
-      <c r="F92" s="2">
-        <v>46295.958321759259</v>
-      </c>
-      <c r="G92" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92"/>
+      <c r="I92">
+        <v>31360</v>
+      </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>2881</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D93">
-        <v>15840</v>
+        <v>4480</v>
       </c>
       <c r="E93" t="s">
+        <v>97</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46296.602094907408</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
         <v>101</v>
       </c>
-      <c r="F93" s="2">
-        <v>46296.120555555557</v>
-      </c>
-      <c r="G93" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93"/>
+      <c r="I93">
+        <v>8960</v>
+      </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>1145</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D94">
-        <v>1800</v>
+        <v>7680</v>
       </c>
       <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" s="2">
+        <v>46296.602094907408</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
         <v>101</v>
       </c>
-      <c r="F94" s="2">
-        <v>46296.120555555557</v>
-      </c>
-      <c r="G94" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94"/>
+      <c r="I94">
+        <v>23040</v>
+      </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>215</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D95">
-        <v>49500</v>
+        <v>17920</v>
       </c>
       <c r="E95" t="s">
+        <v>97</v>
+      </c>
+      <c r="F95" s="2">
+        <v>46296.602094907408</v>
+      </c>
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
         <v>101</v>
       </c>
-      <c r="F95" s="2">
-        <v>46296.313275462962</v>
-      </c>
-      <c r="G95" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95"/>
+      <c r="I95">
+        <v>84420</v>
+      </c>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>5</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D96">
-        <v>540</v>
+        <v>2700</v>
       </c>
       <c r="E96" t="s">
+        <v>97</v>
+      </c>
+      <c r="F96" s="2">
+        <v>46296.332766203705</v>
+      </c>
+      <c r="G96" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" t="s">
         <v>101</v>
       </c>
-      <c r="F96" s="2">
-        <v>46295.9137037037</v>
-      </c>
-      <c r="G96" t="s">
-        <v>15</v>
-      </c>
-      <c r="H96" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96"/>
+      <c r="I96">
+        <v>660</v>
+      </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D97">
-        <v>2976</v>
+        <v>5000</v>
       </c>
       <c r="E97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F97" s="2">
+        <v>46296.332766203705</v>
+      </c>
+      <c r="G97" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" t="s">
         <v>101</v>
       </c>
-      <c r="F97" s="2">
-        <v>46296.314166666663</v>
-      </c>
-      <c r="G97" t="s">
-        <v>15</v>
-      </c>
-      <c r="H97" t="s">
-        <v>32</v>
-      </c>
       <c r="I97">
-        <v>440</v>
+        <v>2500</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>5539</v>
+        <v>888</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D98">
-        <v>134</v>
+        <v>8960</v>
       </c>
       <c r="E98" t="s">
+        <v>97</v>
+      </c>
+      <c r="F98" s="2">
+        <v>46296.602094907408</v>
+      </c>
+      <c r="G98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" t="s">
         <v>101</v>
       </c>
-      <c r="F98" s="2">
-        <v>46296.314166666663</v>
-      </c>
-      <c r="G98" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" t="s">
-        <v>32</v>
-      </c>
       <c r="I98">
-        <v>250</v>
+        <v>20160</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>4821</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D99">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="E99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F99" s="2">
+        <v>46296.332766203705</v>
+      </c>
+      <c r="G99" t="s">
+        <v>116</v>
+      </c>
+      <c r="H99" t="s">
         <v>101</v>
       </c>
-      <c r="F99" s="2">
-        <v>46296.120555555557</v>
-      </c>
-      <c r="G99" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s">
-        <v>32</v>
-      </c>
       <c r="I99">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>2743</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D100">
-        <v>104</v>
+        <v>24000</v>
       </c>
       <c r="E100" t="s">
+        <v>97</v>
+      </c>
+      <c r="F100" s="2">
+        <v>46296.332766203705</v>
+      </c>
+      <c r="G100" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" t="s">
         <v>101</v>
       </c>
-      <c r="F100" s="2">
-        <v>46296.120555555557</v>
-      </c>
-      <c r="G100" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" t="s">
-        <v>85</v>
-      </c>
       <c r="I100">
-        <v>5000</v>
+        <v>200000</v>
       </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>3662</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D101">
-        <v>1800</v>
+        <v>132</v>
       </c>
       <c r="E101" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F101" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.332766203705</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101"/>
+        <v>121</v>
+      </c>
+      <c r="I101">
+        <v>600</v>
+      </c>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>834</v>
+        <v>998</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D102">
-        <v>59400</v>
+        <v>22400</v>
       </c>
       <c r="E102" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F102" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102"/>
+        <v>101</v>
+      </c>
+      <c r="I102">
+        <v>31360</v>
+      </c>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>1198</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D103">
-        <v>31680</v>
+        <v>13440</v>
       </c>
       <c r="E103" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F103" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103"/>
+        <v>101</v>
+      </c>
+      <c r="I103">
+        <v>8960</v>
+      </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>692</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D104">
-        <v>94080</v>
+        <v>7680</v>
       </c>
       <c r="E104" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F104" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104"/>
+        <v>101</v>
+      </c>
+      <c r="I104">
+        <v>23040</v>
+      </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>1014</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="C105" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D105">
-        <v>1980</v>
+        <v>8960</v>
       </c>
       <c r="E105" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F105" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105"/>
+        <v>101</v>
+      </c>
+      <c r="I105">
+        <v>84420</v>
+      </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>424</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="B106" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C106" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D106">
-        <v>3120</v>
+        <v>4200</v>
       </c>
       <c r="E106" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F106" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106"/>
+        <v>101</v>
+      </c>
+      <c r="I106">
+        <v>12600</v>
+      </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>520</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D107">
-        <v>1980</v>
+        <v>10000</v>
       </c>
       <c r="E107" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F107" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>21</v>
-      </c>
-      <c r="I107"/>
+        <v>101</v>
+      </c>
+      <c r="I107">
+        <v>90000</v>
+      </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>162</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="B108" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D108">
-        <v>1080</v>
+        <v>5200</v>
       </c>
       <c r="E108" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F108" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>21</v>
-      </c>
-      <c r="I108"/>
+        <v>101</v>
+      </c>
+      <c r="I108">
+        <v>20000</v>
+      </c>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D109">
-        <v>1027</v>
+        <v>4480</v>
       </c>
       <c r="E109" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F109" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.6075</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I109">
-        <v>440</v>
+        <v>20160</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>1430</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D110">
-        <v>164</v>
+        <v>8640</v>
       </c>
       <c r="E110" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F110" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="I110">
-        <v>250</v>
+        <v>4000</v>
       </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>1140</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="B111" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D111">
-        <v>82</v>
+        <v>2400</v>
       </c>
       <c r="E111" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F111" s="2">
-        <v>46295.928888888884</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>32</v>
-      </c>
-      <c r="I111">
-        <v>250</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I111"/>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>738</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D112">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="E112" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F112" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>153</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="C113" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D113">
-        <v>12000</v>
+        <v>1920</v>
       </c>
       <c r="E113" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F113" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>1059</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D114">
-        <v>95040</v>
+        <v>1800</v>
       </c>
       <c r="E114" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F114" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>1181</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C115" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D115">
-        <v>278400</v>
+        <v>1200</v>
       </c>
       <c r="E115" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F115" s="2">
-        <v>46295.750810185185</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I115"/>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>2889</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D116">
-        <v>1800</v>
+        <v>72</v>
       </c>
       <c r="E116" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F116" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.582824074074</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>21</v>
-      </c>
-      <c r="I116"/>
+        <v>121</v>
+      </c>
+      <c r="I116">
+        <v>600</v>
+      </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>169</v>
+        <v>524</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="B117" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="D117">
-        <v>3960</v>
+        <v>282240</v>
       </c>
       <c r="E117" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="F117" s="2">
-        <v>46295.794895833329</v>
+        <v>46295.929895833331</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
@@ -4637,101 +4736,99 @@
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>223</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="D118">
-        <v>1720</v>
+        <v>176640</v>
       </c>
       <c r="E118" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="F118" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.398969907408</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>32</v>
-      </c>
-      <c r="I118">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I118"/>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>3152</v>
+        <v>262</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B119" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C119" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="D119">
-        <v>92</v>
+        <v>1912</v>
       </c>
       <c r="E119" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="F119" s="2">
-        <v>46295.794895833329</v>
+        <v>46296.398969907408</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I119">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>2856</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B120" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C120" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="D120">
         <v>46</v>
       </c>
       <c r="E120" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="F120" s="2">
-        <v>46295.794895833329</v>
+        <v>46295.743541666663</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I120">
         <v>250</v>
@@ -4739,59 +4836,61 @@
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>398</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="B121" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="D121">
-        <v>86400</v>
+        <v>22</v>
       </c>
       <c r="E121" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="F121" s="2">
-        <v>46295.77244212963</v>
+        <v>46295.743541666663</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>21</v>
-      </c>
-      <c r="I121"/>
+        <v>48</v>
+      </c>
+      <c r="I121">
+        <v>250</v>
+      </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>253</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="B122" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="D122">
-        <v>86400</v>
+        <v>128432</v>
       </c>
       <c r="E122" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="F122" s="2">
-        <v>46295.660335648143</v>
+        <v>46295.876770833333</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
@@ -4803,1303 +4902,1317 @@
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>353</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="D123">
-        <v>960</v>
+        <v>393409</v>
       </c>
       <c r="E123" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="F123" s="2">
-        <v>46295.77244212963</v>
+        <v>46296.641747685186</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>32</v>
-      </c>
-      <c r="I123">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I123"/>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>2364</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B124" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="D124">
-        <v>40</v>
+        <v>2176</v>
       </c>
       <c r="E124" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="F124" s="2">
-        <v>46295.77244212963</v>
+        <v>46296.641747685186</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I124">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>1928</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C125" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="D125">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E125" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="F125" s="2">
-        <v>46295.660335648143</v>
+        <v>46296.641747685186</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I125">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>1246</v>
+        <v>6502</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="B126" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="C126" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D126">
-        <v>73152</v>
+        <v>62</v>
       </c>
       <c r="E126" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F126" s="2">
-        <v>46294.908101851848</v>
+        <v>46296.641747685186</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>21</v>
-      </c>
-      <c r="I126"/>
+        <v>48</v>
+      </c>
+      <c r="I126">
+        <v>250</v>
+      </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>1568</v>
+        <v>5268</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="B127" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="C127" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D127">
-        <v>282240</v>
+        <v>128</v>
       </c>
       <c r="E127" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F127" s="2">
-        <v>46295.929895833331</v>
+        <v>46296.303877314815</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>21</v>
-      </c>
-      <c r="I127"/>
+        <v>63</v>
+      </c>
+      <c r="I127">
+        <v>5000</v>
+      </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>1838</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D128">
-        <v>407280</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="F128" s="2">
-        <v>46295.929895833331</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>21</v>
-      </c>
-      <c r="I128"/>
+        <v>16</v>
+      </c>
+      <c r="I128">
+        <v>130</v>
+      </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>261</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="C129" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D129">
-        <v>2873</v>
+        <v>6</v>
       </c>
       <c r="E129" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="F129" s="2">
-        <v>46295.929895833331</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I129">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>4426</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="D130">
-        <v>46</v>
+        <v>840</v>
       </c>
       <c r="E130" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F130" s="2">
-        <v>46295.743541666663</v>
+        <v>46295.896851851852</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I130">
-        <v>250</v>
+        <v>31360</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>4112</v>
+        <v>888</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="B131" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="C131" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="D131">
-        <v>22</v>
+        <v>840</v>
       </c>
       <c r="E131" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F131" s="2">
-        <v>46295.743541666663</v>
+        <v>46296.161273148144</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I131">
-        <v>250</v>
+        <v>23040</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>1479</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B132" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D132">
-        <v>128432</v>
+        <v>600</v>
       </c>
       <c r="E132" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F132" s="2">
-        <v>46295.876770833333</v>
+        <v>46287.95758101852</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>21</v>
-      </c>
-      <c r="I132"/>
+        <v>101</v>
+      </c>
+      <c r="I132">
+        <v>660</v>
+      </c>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>1376</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="B133" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D133">
-        <v>540289</v>
+        <v>1000</v>
       </c>
       <c r="E133" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F133" s="2">
-        <v>46296.305277777778</v>
+        <v>46296.161273148144</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>21</v>
-      </c>
-      <c r="I133"/>
+        <v>101</v>
+      </c>
+      <c r="I133">
+        <v>1440</v>
+      </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>5234</v>
+        <v>423</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C134" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D134">
-        <v>106080</v>
+        <v>280</v>
       </c>
       <c r="E134" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F134" s="2">
-        <v>46296.303877314815</v>
+        <v>46296.161932870367</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>21</v>
-      </c>
-      <c r="I134"/>
+        <v>101</v>
+      </c>
+      <c r="I134">
+        <v>8960</v>
+      </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>153</v>
+        <v>646</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="B135" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="C135" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="D135">
-        <v>3230</v>
+        <v>850</v>
       </c>
       <c r="E135" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="F135" s="2">
-        <v>46296.305277777778</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="I135">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>9241</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B136" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C136" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D136">
-        <v>152</v>
+        <v>980</v>
       </c>
       <c r="E136" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="F136" s="2">
-        <v>46296.306354166663</v>
+        <v>46295.788310185184</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I136">
-        <v>250</v>
+        <v>31360</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>6501</v>
+        <v>926</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="B137" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="C137" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D137">
-        <v>86</v>
+        <v>20000</v>
       </c>
       <c r="E137" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="F137" s="2">
-        <v>46296.305277777778</v>
+        <v>46296.620462962965</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I137">
-        <v>250</v>
+        <v>90000</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>5267</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="B138" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C138" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="D138">
-        <v>128</v>
+        <v>4000</v>
       </c>
       <c r="E138" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="F138" s="2">
-        <v>46296.303877314815</v>
+        <v>46295.848576388889</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="I138">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>3022</v>
+        <v>129</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B139" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C139" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="D139">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E139" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="F139" s="2">
-        <v>46295.805462962962</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>21</v>
-      </c>
-      <c r="I139"/>
+        <v>101</v>
+      </c>
+      <c r="I139">
+        <v>8960</v>
+      </c>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>1163</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B140" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C140" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="D140">
-        <v>900</v>
+        <v>560</v>
       </c>
       <c r="E140" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="F140" s="2">
-        <v>46295.805462962962</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>21</v>
-      </c>
-      <c r="I140"/>
+        <v>101</v>
+      </c>
+      <c r="I140">
+        <v>84420</v>
+      </c>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>1485</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C141" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D141">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="E141" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="F141" s="2">
-        <v>46290.555405092593</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I141">
-        <v>130</v>
+        <v>660</v>
       </c>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>11</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D142">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="E142" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="F142" s="2">
-        <v>46290.555405092593</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I142">
-        <v>200</v>
+        <v>1440</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="B143" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="C143" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="D143">
-        <v>840</v>
+        <v>60</v>
       </c>
       <c r="E143" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F143" s="2">
-        <v>46295.896851851852</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I143">
-        <v>40320</v>
+        <v>255</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>888</v>
+        <v>115</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C144" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="D144">
         <v>840</v>
       </c>
       <c r="E144" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F144" s="2">
-        <v>46296.161273148144</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I144">
-        <v>23040</v>
+        <v>3920</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>387</v>
+        <v>193</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C145" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="D145">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="E145" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="F145" s="2">
-        <v>46287.95758101852</v>
+        <v>46295.742094907408</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I145">
-        <v>660</v>
+        <v>20160</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>160</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D146">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E146" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="F146" s="2">
-        <v>46296.161273148144</v>
+        <v>45185</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I146">
-        <v>1440</v>
+        <v>255</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>423</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="C147" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="D147">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="F147" s="2">
-        <v>46296.161932870367</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I147">
-        <v>35000</v>
+        <v>25</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>646</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="C148" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="D148">
-        <v>850</v>
+        <v>3</v>
       </c>
       <c r="E148" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="F148" s="2">
-        <v>46295.8800462963</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="I148">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B149" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="C149" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D149">
-        <v>980</v>
+        <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="F149" s="2">
-        <v>46295.788310185184</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I149">
-        <v>40320</v>
+        <v>36</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>926</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="B150" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D150">
-        <v>24000</v>
+        <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="F150" s="2">
-        <v>46295.848576388889</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I150">
-        <v>90000</v>
+        <v>8</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="B151" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="C151" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D151">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="F151" s="2">
-        <v>46295.848576388889</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I151">
-        <v>20000</v>
+        <v>43</v>
       </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="C152" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D152">
-        <v>560</v>
+        <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F152" s="2">
-        <v>46295.742094907408</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I152">
-        <v>5600</v>
+        <v>2</v>
       </c>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="C153" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D153">
-        <v>560</v>
+        <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F153" s="2">
-        <v>46295.742094907408</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I153">
-        <v>14980</v>
+        <v>15</v>
       </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="B154" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="C154" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D154">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F154" s="2">
-        <v>46295.742094907408</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I154">
-        <v>660</v>
+        <v>88</v>
       </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="B155" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="C155" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D155">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F155" s="2">
-        <v>46295.742094907408</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I155">
-        <v>1440</v>
+        <v>5</v>
       </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C156" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D156">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F156" s="2">
-        <v>46295.742094907408</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="I156">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>115</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="C157" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D157">
-        <v>840</v>
+        <v>1540</v>
       </c>
       <c r="E157" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F157" s="2">
-        <v>46295.742094907408</v>
+        <v>46293</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I157">
-        <v>3920</v>
+        <v>84420</v>
       </c>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="B158" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C158" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D158">
-        <v>840</v>
+        <v>120</v>
       </c>
       <c r="E158" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F158" s="2">
-        <v>46295.742094907408</v>
+        <v>46293</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I158">
-        <v>55020</v>
+        <v>5000</v>
       </c>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>263</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="C159" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D159">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E159" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="F159" s="2">
-        <v>45185</v>
+        <v>46293</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I159">
-        <v>360</v>
+        <v>8000</v>
       </c>
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>1</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C160" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>30000</v>
       </c>
       <c r="E160" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F160" s="2">
-        <v>46273.306030092594</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I160">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B161" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C161" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F161" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
@@ -6113,27 +6226,27 @@
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B162" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
@@ -6142,32 +6255,32 @@
         <v>16</v>
       </c>
       <c r="I162">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C163" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F163" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
@@ -6176,1484 +6289,1824 @@
         <v>16</v>
       </c>
       <c r="I163">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="B164" t="s">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="C164" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>2079</v>
       </c>
       <c r="E164" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F164" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.407106481478</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I164">
-        <v>43</v>
+        <v>440</v>
       </c>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>21</v>
+        <v>11306</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B165" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C165" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="E165" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F165" s="2">
-        <v>46273.306030092594</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I165">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="B166" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="C166" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="E166" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F166" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.407106481478</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
       </c>
       <c r="H166" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I166">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>20</v>
+        <v>8954</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B167" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C167" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="E167" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F167" s="2">
-        <v>46273.306030092594</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
       </c>
       <c r="H167" t="s">
+        <v>214</v>
+      </c>
+      <c r="I167">
         <v>16</v>
-      </c>
-      <c r="I167">
-        <v>88</v>
       </c>
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B168" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C168" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E168" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F168" s="2">
-        <v>46273.306030092594</v>
+        <v>44426</v>
       </c>
       <c r="G168" t="s">
         <v>15</v>
       </c>
       <c r="H168" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I168">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="B169" t="s">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="C169" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="E169" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="F169" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.407106481478</v>
       </c>
       <c r="G169" t="s">
         <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I169">
-        <v>2</v>
+        <v>5000</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>17</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="B170" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="C170" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="D170">
-        <v>1540</v>
+        <v>32784</v>
       </c>
       <c r="E170" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F170" s="2">
-        <v>46293</v>
+        <v>46295.857083333329</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="I170">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="J170"/>
       <c r="K170"/>
       <c r="L170">
-        <v>258</v>
+        <v>187</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="B171" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C171" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="D171">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="E171" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F171" s="2">
-        <v>46293</v>
+        <v>46295.668611111112</v>
       </c>
       <c r="G171" t="s">
         <v>15</v>
       </c>
       <c r="H171" t="s">
-        <v>138</v>
-      </c>
-      <c r="I171">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I171"/>
       <c r="J171"/>
       <c r="K171"/>
       <c r="L171">
-        <v>168</v>
+        <v>57</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B172" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C172" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="D172">
-        <v>600</v>
+        <v>2386</v>
       </c>
       <c r="E172" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F172" s="2">
-        <v>46293</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>138</v>
-      </c>
-      <c r="I172">
-        <v>8000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I172"/>
       <c r="J172"/>
       <c r="K172"/>
       <c r="L172">
-        <v>196</v>
+        <v>72</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="B173" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C173" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="D173">
-        <v>30000</v>
+        <v>6330</v>
       </c>
       <c r="E173" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F173" s="2">
-        <v>46280.943472222221</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G173" t="s">
         <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>138</v>
-      </c>
-      <c r="I173">
-        <v>100000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I173"/>
       <c r="J173"/>
       <c r="K173"/>
       <c r="L173">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="B174" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="C174" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>6811</v>
       </c>
       <c r="E174" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F174" s="2">
-        <v>46265.788981481477</v>
+        <v>46295.475601851853</v>
       </c>
       <c r="G174" t="s">
         <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>16</v>
-      </c>
-      <c r="I174">
-        <v>50</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I174"/>
       <c r="J174"/>
       <c r="K174"/>
       <c r="L174">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="B175" t="s">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="C175" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>446</v>
       </c>
       <c r="E175" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F175" s="2">
-        <v>46265.776967592588</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I175">
-        <v>43</v>
+        <v>440</v>
       </c>
       <c r="J175"/>
       <c r="K175"/>
       <c r="L175">
-        <v>11</v>
+        <v>171</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="C176" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E176" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F176" s="2">
-        <v>46265.788981481477</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I176">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J176"/>
       <c r="K176"/>
       <c r="L176">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="B177" t="s">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="C177" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D177">
-        <v>294310</v>
+        <v>20</v>
       </c>
       <c r="E177" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F177" s="2">
-        <v>46295.965694444443</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G177" t="s">
         <v>15</v>
       </c>
       <c r="H177" t="s">
-        <v>21</v>
-      </c>
-      <c r="I177"/>
+        <v>63</v>
+      </c>
+      <c r="I177">
+        <v>5000</v>
+      </c>
       <c r="J177"/>
       <c r="K177"/>
       <c r="L177">
-        <v>1364</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>206</v>
+        <v>94</v>
       </c>
       <c r="B178" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="C178" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D178">
-        <v>186</v>
+        <v>1200</v>
       </c>
       <c r="E178" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F178" s="2">
-        <v>44946.553055555552</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
       </c>
       <c r="H178" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="I178">
-        <v>20</v>
+        <v>875</v>
       </c>
       <c r="J178"/>
       <c r="K178"/>
       <c r="L178">
-        <v>2</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="B179" t="s">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="C179" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D179">
-        <v>93</v>
+        <v>31360</v>
       </c>
       <c r="E179" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F179" s="2">
-        <v>45777.752291666664</v>
+        <v>46296.618923611109</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
       </c>
       <c r="H179" t="s">
-        <v>212</v>
+        <v>101</v>
       </c>
       <c r="I179">
-        <v>16</v>
+        <v>31360</v>
       </c>
       <c r="J179"/>
       <c r="K179"/>
       <c r="L179">
-        <v>7</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="B180" t="s">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="C180" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D180">
-        <v>55</v>
+        <v>8960</v>
       </c>
       <c r="E180" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F180" s="2">
-        <v>44426</v>
+        <v>46296.618923611109</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
       </c>
       <c r="H180" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="I180">
-        <v>2</v>
+        <v>8960</v>
       </c>
       <c r="J180"/>
       <c r="K180"/>
       <c r="L180">
-        <v>5</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B181" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D181">
-        <v>32784</v>
+        <v>5600</v>
       </c>
       <c r="E181" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F181" s="2">
-        <v>46295.857083333329</v>
+        <v>46296.618923611109</v>
       </c>
       <c r="G181" t="s">
         <v>15</v>
       </c>
       <c r="H181" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>84420</v>
       </c>
       <c r="J181"/>
       <c r="K181"/>
       <c r="L181">
-        <v>187</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B182" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C182" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D182">
-        <v>288</v>
+        <v>12600</v>
       </c>
       <c r="E182" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F182" s="2">
-        <v>46295.277013888888</v>
+        <v>46296.618923611109</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
       </c>
       <c r="H182" t="s">
-        <v>21</v>
-      </c>
-      <c r="I182"/>
+        <v>101</v>
+      </c>
+      <c r="I182">
+        <v>12600</v>
+      </c>
       <c r="J182"/>
       <c r="K182"/>
       <c r="L182">
-        <v>459</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="B183" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C183" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D183">
-        <v>8580</v>
+        <v>600</v>
       </c>
       <c r="E183" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F183" s="2">
-        <v>46295.729444444441</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G183" t="s">
         <v>15</v>
       </c>
       <c r="H183" t="s">
-        <v>21</v>
-      </c>
-      <c r="I183"/>
+        <v>101</v>
+      </c>
+      <c r="I183">
+        <v>5000</v>
+      </c>
       <c r="J183"/>
       <c r="K183"/>
       <c r="L183">
-        <v>93</v>
+        <v>994</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B184" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C184" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D184">
-        <v>1440</v>
+        <v>600</v>
       </c>
       <c r="E184" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F184" s="2">
-        <v>46295.668611111112</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
       </c>
       <c r="H184" t="s">
-        <v>21</v>
-      </c>
-      <c r="I184"/>
+        <v>101</v>
+      </c>
+      <c r="I184">
+        <v>349</v>
+      </c>
       <c r="J184"/>
       <c r="K184"/>
       <c r="L184">
-        <v>57</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C185" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D185">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E185" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F185" s="2">
-        <v>46295.800960648143</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G185" t="s">
         <v>15</v>
       </c>
       <c r="H185" t="s">
-        <v>21</v>
-      </c>
-      <c r="I185"/>
+        <v>101</v>
+      </c>
+      <c r="I185">
+        <v>660</v>
+      </c>
       <c r="J185"/>
       <c r="K185"/>
       <c r="L185">
-        <v>566</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="B186" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="C186" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D186">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="E186" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F186" s="2">
-        <v>46295.684270833328</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G186" t="s">
         <v>15</v>
       </c>
       <c r="H186" t="s">
-        <v>21</v>
-      </c>
-      <c r="I186"/>
+        <v>101</v>
+      </c>
+      <c r="I186">
+        <v>1440</v>
+      </c>
       <c r="J186"/>
       <c r="K186"/>
       <c r="L186">
-        <v>412</v>
+        <v>237</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="B187" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="C187" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D187">
-        <v>2386</v>
+        <v>2000</v>
       </c>
       <c r="E187" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F187" s="2">
-        <v>46295.47378472222</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
       </c>
       <c r="H187" t="s">
-        <v>21</v>
-      </c>
-      <c r="I187"/>
+        <v>167</v>
+      </c>
+      <c r="I187">
+        <v>5000</v>
+      </c>
       <c r="J187"/>
       <c r="K187"/>
       <c r="L187">
-        <v>72</v>
+        <v>255</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="B188" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C188" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D188">
-        <v>6330</v>
+        <v>8000</v>
       </c>
       <c r="E188" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F188" s="2">
-        <v>46295.47378472222</v>
+        <v>46296.581956018519</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
       </c>
       <c r="H188" t="s">
-        <v>21</v>
-      </c>
-      <c r="I188"/>
+        <v>167</v>
+      </c>
+      <c r="I188">
+        <v>5000</v>
+      </c>
       <c r="J188"/>
       <c r="K188"/>
       <c r="L188">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B189" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C189" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D189">
-        <v>6811</v>
+        <v>2000</v>
       </c>
       <c r="E189" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F189" s="2">
-        <v>46295.475601851853</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G189" t="s">
         <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>21</v>
-      </c>
-      <c r="I189"/>
+        <v>101</v>
+      </c>
+      <c r="I189">
+        <v>30000</v>
+      </c>
       <c r="J189"/>
       <c r="K189"/>
       <c r="L189">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="C190" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D190">
-        <v>309</v>
+        <v>10000</v>
       </c>
       <c r="E190" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F190" s="2">
-        <v>46295.475601851853</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G190" t="s">
         <v>15</v>
       </c>
       <c r="H190" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I190">
-        <v>440</v>
+        <v>2500</v>
       </c>
       <c r="J190"/>
       <c r="K190"/>
       <c r="L190">
-        <v>170</v>
+        <v>844</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>33</v>
+        <v>235</v>
       </c>
       <c r="B191" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="C191" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D191">
-        <v>18</v>
+        <v>9000</v>
       </c>
       <c r="E191" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F191" s="2">
-        <v>46295.480543981481</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G191" t="s">
         <v>15</v>
       </c>
       <c r="H191" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I191">
-        <v>250</v>
+        <v>50000</v>
       </c>
       <c r="J191"/>
       <c r="K191"/>
       <c r="L191">
-        <v>101</v>
+        <v>333</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="B192" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="C192" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D192">
-        <v>14</v>
+        <v>400</v>
       </c>
       <c r="E192" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F192" s="2">
-        <v>46295.480543981481</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G192" t="s">
         <v>15</v>
       </c>
       <c r="H192" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="I192">
-        <v>5000</v>
+        <v>255</v>
       </c>
       <c r="J192"/>
       <c r="K192"/>
       <c r="L192">
-        <v>59</v>
+        <v>703</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="B193" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="C193" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D193">
-        <v>219168</v>
+        <v>20000</v>
       </c>
       <c r="E193" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F193" s="2">
-        <v>46296.092002314814</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G193" t="s">
         <v>15</v>
       </c>
       <c r="H193" t="s">
-        <v>21</v>
-      </c>
-      <c r="I193"/>
+        <v>101</v>
+      </c>
+      <c r="I193">
+        <v>100000</v>
+      </c>
       <c r="J193"/>
       <c r="K193"/>
       <c r="L193">
-        <v>2423</v>
+        <v>993</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B194" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C194" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D194">
-        <v>105600</v>
+        <v>20160</v>
       </c>
       <c r="E194" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F194" s="2">
-        <v>46296.151446759257</v>
+        <v>46296.618923611109</v>
       </c>
       <c r="G194" t="s">
         <v>15</v>
       </c>
       <c r="H194" t="s">
-        <v>21</v>
-      </c>
-      <c r="I194"/>
+        <v>101</v>
+      </c>
+      <c r="I194">
+        <v>20160</v>
+      </c>
       <c r="J194"/>
       <c r="K194"/>
       <c r="L194">
-        <v>1841</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B195" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C195" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D195">
-        <v>264000</v>
+        <v>8</v>
       </c>
       <c r="E195" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F195" s="2">
-        <v>46296.160787037035</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G195" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="H195" t="s">
-        <v>21</v>
-      </c>
-      <c r="I195"/>
+        <v>101</v>
+      </c>
+      <c r="I195">
+        <v>40</v>
+      </c>
       <c r="J195"/>
       <c r="K195"/>
       <c r="L195">
-        <v>279</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="B196" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="C196" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D196">
-        <v>1540</v>
+        <v>3200</v>
       </c>
       <c r="E196" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F196" s="2">
-        <v>46296.160787037035</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="I196">
-        <v>440</v>
+        <v>4000</v>
       </c>
       <c r="J196"/>
       <c r="K196"/>
       <c r="L196">
-        <v>5081</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>33</v>
+        <v>237</v>
       </c>
       <c r="B197" t="s">
-        <v>34</v>
+        <v>238</v>
       </c>
       <c r="C197" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D197">
-        <v>118</v>
+        <v>560</v>
       </c>
       <c r="E197" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F197" s="2">
-        <v>46296.160787037035</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G197" t="s">
         <v>15</v>
       </c>
       <c r="H197" t="s">
-        <v>32</v>
-      </c>
-      <c r="I197">
-        <v>250</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I197"/>
       <c r="J197"/>
       <c r="K197"/>
       <c r="L197">
-        <v>4471</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="B198" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="C198" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D198">
-        <v>44</v>
+        <v>3000</v>
       </c>
       <c r="E198" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F198" s="2">
-        <v>46296.160787037035</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G198" t="s">
         <v>15</v>
       </c>
       <c r="H198" t="s">
-        <v>32</v>
-      </c>
-      <c r="I198">
-        <v>250</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I198"/>
       <c r="J198"/>
       <c r="K198"/>
       <c r="L198">
-        <v>2557</v>
+        <v>145</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>137</v>
+      </c>
+      <c r="B199" t="s">
+        <v>138</v>
+      </c>
+      <c r="C199" t="s">
         <v>227</v>
       </c>
-      <c r="B199" t="s">
+      <c r="D199">
+        <v>4000</v>
+      </c>
+      <c r="E199" t="s">
         <v>228</v>
       </c>
-      <c r="C199" t="s">
-        <v>229</v>
-      </c>
-      <c r="D199">
-        <v>2439100</v>
-      </c>
-      <c r="E199" t="s">
-        <v>230</v>
-      </c>
       <c r="F199" s="2">
-        <v>46266</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G199" t="s">
-        <v>231</v>
+        <v>15</v>
       </c>
       <c r="H199" t="s">
-        <v>232</v>
-      </c>
-      <c r="I199">
-        <v>950000</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I199"/>
       <c r="J199"/>
       <c r="K199"/>
       <c r="L199">
-        <v>56</v>
+        <v>150</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="B200" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="C200" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D200">
-        <v>2530000</v>
+        <v>900</v>
       </c>
       <c r="E200" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F200" s="2">
-        <v>46266</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G200" t="s">
-        <v>231</v>
+        <v>15</v>
       </c>
       <c r="H200" t="s">
-        <v>232</v>
-      </c>
-      <c r="I200">
-        <v>1265000</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I200"/>
       <c r="J200"/>
       <c r="K200"/>
       <c r="L200">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>235</v>
+        <v>141</v>
       </c>
       <c r="B201" t="s">
-        <v>236</v>
+        <v>142</v>
       </c>
       <c r="C201" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D201">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="E201" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F201" s="2">
-        <v>46295.485300925924</v>
+        <v>46296.505486111106</v>
       </c>
       <c r="G201" t="s">
-        <v>239</v>
+        <v>15</v>
       </c>
       <c r="H201" t="s">
-        <v>240</v>
-      </c>
-      <c r="I201">
-        <v>50</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I201"/>
       <c r="J201"/>
       <c r="K201"/>
       <c r="L201">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
+        <v>239</v>
+      </c>
+      <c r="B202" t="s">
+        <v>240</v>
+      </c>
+      <c r="C202" t="s">
         <v>241</v>
       </c>
-      <c r="B202" t="s">
+      <c r="D202">
+        <v>219168</v>
+      </c>
+      <c r="E202" t="s">
         <v>242</v>
       </c>
-      <c r="C202" t="s">
-        <v>237</v>
-      </c>
-      <c r="D202">
-        <v>1</v>
-      </c>
-      <c r="E202" t="s">
-        <v>238</v>
-      </c>
       <c r="F202" s="2">
-        <v>46293.599965277775</v>
+        <v>46296.092002314814</v>
       </c>
       <c r="G202" t="s">
         <v>15</v>
       </c>
       <c r="H202" t="s">
-        <v>85</v>
-      </c>
-      <c r="I202">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I202"/>
       <c r="J202"/>
       <c r="K202"/>
       <c r="L202">
-        <v>1</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>243</v>
+        <v>143</v>
       </c>
       <c r="B203" t="s">
-        <v>244</v>
+        <v>144</v>
       </c>
       <c r="C203" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D203">
-        <v>2</v>
+        <v>105600</v>
       </c>
       <c r="E203" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F203" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.151446759257</v>
       </c>
       <c r="G203" t="s">
         <v>15</v>
       </c>
       <c r="H203" t="s">
-        <v>85</v>
-      </c>
-      <c r="I203">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I203"/>
       <c r="J203"/>
       <c r="K203"/>
       <c r="L203">
-        <v>2</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>245</v>
+        <v>147</v>
       </c>
       <c r="B204" t="s">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="C204" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>264000</v>
       </c>
       <c r="E204" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F204" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G204" t="s">
         <v>15</v>
       </c>
       <c r="H204" t="s">
-        <v>85</v>
-      </c>
-      <c r="I204">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I204"/>
       <c r="J204"/>
       <c r="K204"/>
       <c r="L204">
-        <v>1</v>
+        <v>279</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>247</v>
+        <v>46</v>
       </c>
       <c r="B205" t="s">
-        <v>248</v>
+        <v>47</v>
       </c>
       <c r="C205" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>1540</v>
       </c>
       <c r="E205" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F205" s="2">
-        <v>46293.600868055553</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G205" t="s">
         <v>15</v>
       </c>
       <c r="H205" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="I205">
-        <v>1</v>
+        <v>440</v>
       </c>
       <c r="J205"/>
       <c r="K205"/>
       <c r="L205">
-        <v>1</v>
+        <v>5081</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="B206" t="s">
+        <v>50</v>
+      </c>
+      <c r="C206" t="s">
+        <v>241</v>
+      </c>
+      <c r="D206">
+        <v>118</v>
+      </c>
+      <c r="E206" t="s">
+        <v>242</v>
+      </c>
+      <c r="F206" s="2">
+        <v>46296.160787037035</v>
+      </c>
+      <c r="G206" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" t="s">
+        <v>48</v>
+      </c>
+      <c r="I206">
         <v>250</v>
-      </c>
-      <c r="C206" t="s">
-        <v>237</v>
-      </c>
-      <c r="D206">
-        <v>5</v>
-      </c>
-      <c r="E206" t="s">
-        <v>238</v>
-      </c>
-      <c r="F206" s="2">
-        <v>46293.594282407408</v>
-      </c>
-      <c r="G206" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" t="s">
-        <v>85</v>
-      </c>
-      <c r="I206">
-        <v>16</v>
       </c>
       <c r="J206"/>
       <c r="K206"/>
       <c r="L206">
-        <v>1</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>251</v>
+        <v>51</v>
       </c>
       <c r="B207" t="s">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="C207" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D207">
-        <v>78000</v>
+        <v>44</v>
       </c>
       <c r="E207" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F207" s="2">
-        <v>46266</v>
+        <v>46296.160787037035</v>
       </c>
       <c r="G207" t="s">
-        <v>231</v>
+        <v>15</v>
       </c>
       <c r="H207" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="I207">
-        <v>52000</v>
+        <v>250</v>
       </c>
       <c r="J207"/>
       <c r="K207"/>
       <c r="L207">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>243</v>
+      </c>
+      <c r="B208" t="s">
+        <v>244</v>
+      </c>
+      <c r="C208" t="s">
+        <v>245</v>
+      </c>
+      <c r="D208">
+        <v>2439100</v>
+      </c>
+      <c r="E208" t="s">
+        <v>246</v>
+      </c>
+      <c r="F208" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G208" t="s">
+        <v>247</v>
+      </c>
+      <c r="H208" t="s">
+        <v>248</v>
+      </c>
+      <c r="I208">
+        <v>950000</v>
+      </c>
+      <c r="J208"/>
+      <c r="K208"/>
+      <c r="L208">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>249</v>
+      </c>
+      <c r="B209" t="s">
+        <v>250</v>
+      </c>
+      <c r="C209" t="s">
+        <v>245</v>
+      </c>
+      <c r="D209">
+        <v>2530000</v>
+      </c>
+      <c r="E209" t="s">
+        <v>246</v>
+      </c>
+      <c r="F209" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G209" t="s">
+        <v>247</v>
+      </c>
+      <c r="H209" t="s">
+        <v>248</v>
+      </c>
+      <c r="I209">
+        <v>1265000</v>
+      </c>
+      <c r="J209"/>
+      <c r="K209"/>
+      <c r="L209">
         <v>48</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>251</v>
+      </c>
+      <c r="B210" t="s">
+        <v>252</v>
+      </c>
+      <c r="C210" t="s">
+        <v>253</v>
+      </c>
+      <c r="D210">
+        <v>50</v>
+      </c>
+      <c r="E210" t="s">
+        <v>254</v>
+      </c>
+      <c r="F210" s="2">
+        <v>46295.485300925924</v>
+      </c>
+      <c r="G210" t="s">
+        <v>255</v>
+      </c>
+      <c r="H210" t="s">
+        <v>256</v>
+      </c>
+      <c r="I210">
+        <v>50</v>
+      </c>
+      <c r="J210"/>
+      <c r="K210"/>
+      <c r="L210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>257</v>
+      </c>
+      <c r="B211" t="s">
+        <v>258</v>
+      </c>
+      <c r="C211" t="s">
+        <v>253</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211" t="s">
+        <v>254</v>
+      </c>
+      <c r="F211" s="2">
+        <v>46293.599965277775</v>
+      </c>
+      <c r="G211" t="s">
+        <v>15</v>
+      </c>
+      <c r="H211" t="s">
+        <v>63</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211"/>
+      <c r="K211"/>
+      <c r="L211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>259</v>
+      </c>
+      <c r="B212" t="s">
+        <v>260</v>
+      </c>
+      <c r="C212" t="s">
+        <v>253</v>
+      </c>
+      <c r="D212">
+        <v>2</v>
+      </c>
+      <c r="E212" t="s">
+        <v>254</v>
+      </c>
+      <c r="F212" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G212" t="s">
+        <v>15</v>
+      </c>
+      <c r="H212" t="s">
+        <v>63</v>
+      </c>
+      <c r="I212">
+        <v>2</v>
+      </c>
+      <c r="J212"/>
+      <c r="K212"/>
+      <c r="L212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>261</v>
+      </c>
+      <c r="B213" t="s">
+        <v>262</v>
+      </c>
+      <c r="C213" t="s">
+        <v>253</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213" t="s">
+        <v>254</v>
+      </c>
+      <c r="F213" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G213" t="s">
+        <v>15</v>
+      </c>
+      <c r="H213" t="s">
+        <v>63</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213"/>
+      <c r="K213"/>
+      <c r="L213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>263</v>
+      </c>
+      <c r="B214" t="s">
+        <v>264</v>
+      </c>
+      <c r="C214" t="s">
+        <v>253</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214" t="s">
+        <v>254</v>
+      </c>
+      <c r="F214" s="2">
+        <v>46293.600868055553</v>
+      </c>
+      <c r="G214" t="s">
+        <v>15</v>
+      </c>
+      <c r="H214" t="s">
+        <v>63</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214"/>
+      <c r="K214"/>
+      <c r="L214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>265</v>
+      </c>
+      <c r="B215" t="s">
+        <v>266</v>
+      </c>
+      <c r="C215" t="s">
+        <v>253</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215" t="s">
+        <v>254</v>
+      </c>
+      <c r="F215" s="2">
+        <v>46293.594282407408</v>
+      </c>
+      <c r="G215" t="s">
+        <v>15</v>
+      </c>
+      <c r="H215" t="s">
+        <v>63</v>
+      </c>
+      <c r="I215">
+        <v>16</v>
+      </c>
+      <c r="J215"/>
+      <c r="K215"/>
+      <c r="L215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>267</v>
+      </c>
+      <c r="B216" t="s">
+        <v>268</v>
+      </c>
+      <c r="C216" t="s">
+        <v>269</v>
+      </c>
+      <c r="D216">
+        <v>78000</v>
+      </c>
+      <c r="E216" t="s">
+        <v>270</v>
+      </c>
+      <c r="F216" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G216" t="s">
+        <v>247</v>
+      </c>
+      <c r="H216" t="s">
+        <v>248</v>
+      </c>
+      <c r="I216">
+        <v>52000</v>
+      </c>
+      <c r="J216"/>
+      <c r="K216"/>
+      <c r="L216">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>271</v>
+      </c>
+      <c r="B217" t="s">
+        <v>272</v>
+      </c>
+      <c r="C217" t="s">
+        <v>273</v>
+      </c>
+      <c r="D217">
+        <v>4000</v>
+      </c>
+      <c r="E217" t="s">
+        <v>274</v>
+      </c>
+      <c r="F217" s="2">
+        <v>46296.511597222219</v>
+      </c>
+      <c r="G217" t="s">
+        <v>247</v>
+      </c>
+      <c r="H217" t="s">
+        <v>275</v>
+      </c>
+      <c r="I217">
+        <v>4000</v>
+      </c>
+      <c r="J217"/>
+      <c r="K217"/>
+      <c r="L217">
+        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="Rd5c68847ab694dae"/>
+    <sheet name="Inventarios" sheetId="1" r:id="Rb39ac433831c40dc"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -82,61 +82,166 @@
     <t>HUEVO XL X 15 PET CAJA X 300.</t>
   </si>
   <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>112357</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>2110327</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2110427</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2112207</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>VT2</t>
-  </si>
-  <si>
-    <t>TAT CALI - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>152382</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+    <t>2110403</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
+    <t>2152388</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT49</t>
+  </si>
+  <si>
+    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>VT52</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT52</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
+  </si>
+  <si>
+    <t>2013421</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO ALKOSTO CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>VT59</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT59</t>
   </si>
   <si>
     <t>2110217</t>
@@ -145,151 +250,337 @@
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2152388</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>VT36</t>
-  </si>
-  <si>
-    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2110403</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT42</t>
-  </si>
-  <si>
-    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT49</t>
-  </si>
-  <si>
-    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>10601</t>
-  </si>
-  <si>
-    <t>HUEVO C X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>VT52</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT52</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>2013421</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO ALKOSTO CANASTA</t>
-  </si>
-  <si>
-    <t>VT59</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT59</t>
-  </si>
-  <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
+    <t>EMLA001</t>
+  </si>
+  <si>
+    <t>LAMINA DE CARTON CORRUGADO 88 X 119 CM</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>EMPA007</t>
+  </si>
+  <si>
+    <t>PLASTICO SUPER STRECH 45X10X450 MT SIN CONO</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>142111</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
+  </si>
+  <si>
+    <t>VTALEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES CALOTO TRANSITO</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>142121</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12 CAJA X 48</t>
+  </si>
+  <si>
+    <t>143231</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
+  </si>
+  <si>
+    <t>VTALKA</t>
+  </si>
+  <si>
+    <t>KIKES - EGIPTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>VTBE</t>
+  </si>
+  <si>
+    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>13358</t>
+  </si>
+  <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTCA</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTDOTH</t>
+  </si>
+  <si>
+    <t>BODEGA DOTACION TH TRANSITO</t>
+  </si>
+  <si>
+    <t>DOTA050</t>
+  </si>
+  <si>
+    <t>TOALLA BLANCA 1.20X0.60X320</t>
+  </si>
+  <si>
+    <t>EMES001</t>
+  </si>
+  <si>
+    <t>ESQUINEROS DE CARTON  90X14 CM</t>
+  </si>
+  <si>
+    <t>VTEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES BUCARAMANGA TRANSITO</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>PTEM030</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES TAPA ACEBRI</t>
+  </si>
+  <si>
+    <t>PTEM034</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 TRANSPARENTE ACEBRI</t>
+  </si>
+  <si>
+    <t>PTEM048</t>
+  </si>
+  <si>
+    <t>EMPAQUE PETX12 - ACEBRI</t>
+  </si>
+  <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>EMET019</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
+  </si>
+  <si>
+    <t>VTEMBO</t>
+  </si>
+  <si>
+    <t>EMPAQUES BOGOTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EMET015</t>
+  </si>
+  <si>
+    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>DOCL001</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA S</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>DOCL003</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOCL005</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ002</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 30</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>DOPJ004</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 34</t>
+  </si>
+  <si>
+    <t>DOPJ005</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 36</t>
+  </si>
+  <si>
+    <t>DOPJ006</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 38</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMCA016</t>
+  </si>
+  <si>
+    <t>CAJA ESTÁNDAR NEUTRA</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
   </si>
   <si>
     <t>EECA006</t>
@@ -298,28 +589,112 @@
     <t>CAJA REGULAR X300 EMPAQUE PET</t>
   </si>
   <si>
-    <t>VTAL06</t>
-  </si>
-  <si>
-    <t>EMPAQUES ALKA 1 TRANSITO</t>
+    <t>VTEMT52</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
   </si>
   <si>
     <t>EE</t>
   </si>
   <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>VTEMT7</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
+    <t>13324</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
+    <t>13419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
+  </si>
+  <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
+  </si>
+  <si>
+    <t>2013322</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
+  </si>
+  <si>
+    <t>2013419</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
+  </si>
+  <si>
+    <t>74001</t>
+  </si>
+  <si>
+    <t>HUEVO DE BAJA ROTACION</t>
+  </si>
+  <si>
+    <t>VTLZEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES LANZA TRANSITO</t>
+  </si>
+  <si>
     <t>EMCA019</t>
   </si>
   <si>
     <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
   </si>
   <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>EMET02</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+    <t>EMCA024</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X120 EMPAQUE X12</t>
   </si>
   <si>
     <t>EMET03</t>
@@ -328,10 +703,16 @@
     <t>ETIQUETA COD DE BARRA HUEVO XL X 30 - K</t>
   </si>
   <si>
-    <t>VTALBKA2</t>
-  </si>
-  <si>
-    <t>EMPAQUES ALKA 2 TRANSITO</t>
+    <t>EMET031</t>
+  </si>
+  <si>
+    <t>ETIQUETA ADHESIVA BLANCA 100 MM X 50 MM - ZEBRA</t>
+  </si>
+  <si>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
   </si>
   <si>
     <t>PTEM049</t>
@@ -340,9 +721,6 @@
     <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>PTEM050</t>
   </si>
   <si>
@@ -355,367 +733,10 @@
     <t>EMPAQUE PET X 30 L ETIQUETADO</t>
   </si>
   <si>
-    <t>PTEM054</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 L ETIQUETADO</t>
-  </si>
-  <si>
-    <t>13358</t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>13324</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTDOTH</t>
-  </si>
-  <si>
-    <t>BODEGA DOTACION TH TRANSITO</t>
-  </si>
-  <si>
-    <t>DOTA050</t>
-  </si>
-  <si>
-    <t>TOALLA BLANCA 1.20X0.60X320</t>
-  </si>
-  <si>
-    <t>EMES001</t>
-  </si>
-  <si>
-    <t>ESQUINEROS DE CARTON  90X14 CM</t>
-  </si>
-  <si>
-    <t>VTEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES BUCARAMANGA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA008</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
-    <t>EMET019</t>
-  </si>
-  <si>
-    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
-  </si>
-  <si>
-    <t>VTEMBO</t>
-  </si>
-  <si>
-    <t>EMPAQUES BOGOTA TRANSITO</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>EMET015</t>
-  </si>
-  <si>
-    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMTA006</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>DOCL001</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA S</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>DOCL003</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOCL005</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ002</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 30</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>DOPJ004</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 34</t>
-  </si>
-  <si>
-    <t>DOPJ005</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 36</t>
-  </si>
-  <si>
-    <t>DOPJ006</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 38</t>
-  </si>
-  <si>
-    <t>EMCA016</t>
-  </si>
-  <si>
-    <t>CAJA ESTÁNDAR NEUTRA</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>VTEMT7</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>EMPA007</t>
-  </si>
-  <si>
-    <t>PLASTICO SUPER STRECH 45X10X450 MT SIN CONO</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE.</t>
-  </si>
-  <si>
-    <t>13459</t>
-  </si>
-  <si>
-    <t>HUEVO A X 300 BANDEJA GRIS ALAT CAJA AMARRADO</t>
-  </si>
-  <si>
-    <t>2013322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
-  </si>
-  <si>
-    <t>2013419</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO SOL NACIENTE CANASTA.</t>
-  </si>
-  <si>
-    <t>74001</t>
-  </si>
-  <si>
-    <t>HUEVO DE BAJA ROTACION</t>
-  </si>
-  <si>
-    <t>PTEM029</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
-  </si>
-  <si>
-    <t>VTLZEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES LANZA TRANSITO</t>
+    <t>PTEM052</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
   </si>
   <si>
     <t>VTME</t>
@@ -730,6 +751,12 @@
     <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
   </si>
   <si>
+    <t>VTPALM</t>
+  </si>
+  <si>
+    <t>EGIPTO - INVENTARIO TRANSITO PALMA</t>
+  </si>
+  <si>
     <t>MA0041</t>
   </si>
   <si>
@@ -754,6 +781,18 @@
     <t>TORTA DE SOYA BOLIVIANA</t>
   </si>
   <si>
+    <t>MA0056</t>
+  </si>
+  <si>
+    <t>FRIJOL SOYA AMERICANO CRUDO</t>
+  </si>
+  <si>
+    <t>MI0502</t>
+  </si>
+  <si>
+    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
+  </si>
+  <si>
     <t>EPGU006</t>
   </si>
   <si>
@@ -826,6 +865,12 @@
     <t>BOLSA POLIETILENO TRANSPARENTE 55X76CMS CALIBRE 2.5</t>
   </si>
   <si>
+    <t>EMET014</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
+  </si>
+  <si>
     <t>UPCI07</t>
   </si>
   <si>
@@ -833,12 +878,6 @@
   </si>
   <si>
     <t>UP</t>
-  </si>
-  <si>
-    <t>MI0502</t>
-  </si>
-  <si>
-    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
   </si>
   <si>
     <t>VTPSM</t>
@@ -1039,16 +1078,16 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D4">
-        <v>600</v>
+        <v>21000</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2">
-        <v>46296.902407407404</v>
+        <v>46297.621898148143</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1060,27 +1099,27 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>2529</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5">
+        <v>39000</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="2">
-        <v>46296.902407407404</v>
+        <v>46297.621898148143</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1092,27 +1131,27 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>1713</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>46296.902407407404</v>
+        <v>46297.621898148143</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1124,27 +1163,27 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>2841</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>57600</v>
+        <v>73440</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>46296.902407407404</v>
+        <v>46296.90725694444</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1156,27 +1195,27 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>881</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>23040</v>
+        <v>51840</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2">
-        <v>46296.902407407404</v>
+        <v>46296.90725694444</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -1188,27 +1227,27 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>883</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>360</v>
+        <v>5760</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2">
-        <v>46296.902407407404</v>
+        <v>46296.90725694444</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1220,33 +1259,33 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>115</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>338</v>
+        <v>648</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2">
-        <v>46296.902407407404</v>
+        <v>46296.90725694444</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I10">
         <v>440</v>
@@ -1254,33 +1293,33 @@
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2506</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46296.90725694444</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
         <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2">
-        <v>46296.902407407404</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>36</v>
       </c>
       <c r="I11">
         <v>250</v>
@@ -1288,59 +1327,61 @@
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>1755</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D12">
-        <v>9000</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.90725694444</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12"/>
+        <v>38</v>
+      </c>
+      <c r="I12">
+        <v>250</v>
+      </c>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>2195</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13">
-        <v>36000</v>
+        <v>600</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2">
-        <v>46297.35732638889</v>
+        <v>46295.691284722219</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1352,27 +1393,27 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>505</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D14">
-        <v>15840</v>
+        <v>600</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F14" s="2">
-        <v>46297.35732638889</v>
+        <v>46295.69253472222</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1384,27 +1425,27 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>681</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>72720</v>
+        <v>2400</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1416,27 +1457,27 @@
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2077</v>
+        <v>655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D16">
-        <v>2700</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -1448,27 +1489,27 @@
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>819</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D17">
-        <v>11880</v>
+        <v>3900</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1480,27 +1521,27 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>303</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18">
+        <v>54720</v>
+      </c>
+      <c r="E18" t="s">
         <v>50</v>
       </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>7920</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
-      </c>
       <c r="F18" s="2">
-        <v>46297.35732638889</v>
+        <v>46297.341122685182</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1512,7 +1553,7 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>421</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="19">
@@ -1523,228 +1564,228 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D19">
-        <v>560</v>
+        <v>59520</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>3327</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>3960</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>2885</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>19800</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>46297.35732638889</v>
+        <v>46296.80804398148</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>335</v>
+        <v>523</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>608</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>46297.35732638889</v>
+        <v>46297.341122685182</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I22">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>2025</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>73440</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>46296.90725694444</v>
+        <v>46297.341122685182</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23"/>
+        <v>38</v>
+      </c>
+      <c r="I23">
+        <v>250</v>
+      </c>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>2957</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>51840</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>46296.90725694444</v>
+        <v>46297.341122685182</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24"/>
+        <v>38</v>
+      </c>
+      <c r="I24">
+        <v>250</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>2433</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" s="2">
+        <v>46296.614837962959</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
         <v>61</v>
       </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25">
-        <v>5760</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="2">
-        <v>46296.90725694444</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25"/>
+      <c r="I25">
+        <v>5000</v>
+      </c>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>1657</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="26">
@@ -1755,90 +1796,88 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D26">
-        <v>648</v>
+        <v>211200</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2">
-        <v>46296.90725694444</v>
+        <v>46297.309502314813</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>4291</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
         <v>37</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27">
+        <v>880</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="2">
+        <v>46297.310104166667</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
         <v>38</v>
       </c>
-      <c r="C27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27">
-        <v>36</v>
-      </c>
-      <c r="E27" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="2">
-        <v>46296.90725694444</v>
-      </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>36</v>
-      </c>
       <c r="I27">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>3733</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F28" s="2">
-        <v>46296.90725694444</v>
+        <v>46297.309502314813</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I28">
         <v>250</v>
@@ -1846,91 +1885,95 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>2533</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
         <v>63</v>
       </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29">
-        <v>600</v>
-      </c>
-      <c r="E29" t="s">
-        <v>65</v>
-      </c>
       <c r="F29" s="2">
-        <v>46295.691284722219</v>
+        <v>46297.309502314813</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29"/>
+        <v>38</v>
+      </c>
+      <c r="I29">
+        <v>250</v>
+      </c>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>7</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D30">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F30" s="2">
-        <v>46295.69253472222</v>
+        <v>46296.810150462959</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30"/>
+        <v>61</v>
+      </c>
+      <c r="I30">
+        <v>5000</v>
+      </c>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>26</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D31">
-        <v>2400</v>
+        <v>101760</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F31" s="2">
-        <v>46296.80804398148</v>
+        <v>46297.636331018519</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1942,123 +1985,129 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>655</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D32">
-        <v>240</v>
+        <v>424</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2">
-        <v>46296.80804398148</v>
+        <v>46297.636331018519</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32"/>
+        <v>38</v>
+      </c>
+      <c r="I32">
+        <v>440</v>
+      </c>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>405</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D33">
-        <v>3900</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F33" s="2">
-        <v>46296.80804398148</v>
+        <v>46297.636331018519</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33"/>
+        <v>38</v>
+      </c>
+      <c r="I33">
+        <v>250</v>
+      </c>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>633</v>
+        <v>888</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D34">
-        <v>54720</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2">
-        <v>46297.341122685182</v>
+        <v>46297.636331018519</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34"/>
+        <v>38</v>
+      </c>
+      <c r="I34">
+        <v>250</v>
+      </c>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>2106</v>
+        <v>675</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D35">
-        <v>59520</v>
+        <v>18000</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F35" s="2">
-        <v>46296.80804398148</v>
+        <v>46297.466145833328</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2070,27 +2119,27 @@
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>2800</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D36">
-        <v>3960</v>
+        <v>3000</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F36" s="2">
-        <v>46296.80804398148</v>
+        <v>46296.963854166665</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2102,27 +2151,27 @@
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>693</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D37">
-        <v>19800</v>
+        <v>1200</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F37" s="2">
-        <v>46296.80804398148</v>
+        <v>46297.625034722223</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -2134,129 +2183,123 @@
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>523</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D38">
-        <v>608</v>
+        <v>48000</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F38" s="2">
-        <v>46297.341122685182</v>
+        <v>46297.625034722223</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I38"/>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>3556</v>
+        <v>4771</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D39">
-        <v>66</v>
+        <v>9000</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F39" s="2">
-        <v>46297.341122685182</v>
+        <v>46297.043460648143</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>2783</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D40">
-        <v>32</v>
+        <v>3153</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F40" s="2">
-        <v>46297.341122685182</v>
+        <v>46296.963854166665</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>2114</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D41">
-        <v>103680</v>
+        <v>120060</v>
       </c>
       <c r="E41" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F41" s="2">
-        <v>46296.614837962959</v>
+        <v>46297.286840277775</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -2268,201 +2311,197 @@
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>3244</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D42">
-        <v>432</v>
+        <v>109620</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F42" s="2">
-        <v>46296.614837962959</v>
+        <v>46297.466145833328</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I42"/>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>4086</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>31680</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F43" s="2">
-        <v>46296.614837962959</v>
+        <v>46297.036851851852</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>3158</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>7920</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F44" s="2">
-        <v>46296.614837962959</v>
+        <v>46296.963854166665</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>55</v>
-      </c>
-      <c r="I44">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>2153</v>
+        <v>867</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D45">
-        <v>211200</v>
+        <v>1479</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F45" s="2">
-        <v>46297.309502314813</v>
+        <v>46297.466145833328</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45"/>
+        <v>38</v>
+      </c>
+      <c r="I45">
+        <v>440</v>
+      </c>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>1775</v>
+        <v>5551</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D46">
-        <v>880</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F46" s="2">
-        <v>46297.310104166667</v>
+        <v>46297.466145833328</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>2123</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="2">
+        <v>46297.466145833328</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
         <v>38</v>
-      </c>
-      <c r="C47" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47">
-        <v>40</v>
-      </c>
-      <c r="E47" t="s">
-        <v>75</v>
-      </c>
-      <c r="F47" s="2">
-        <v>46297.309502314813</v>
-      </c>
-      <c r="G47" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" t="s">
-        <v>36</v>
       </c>
       <c r="I47">
         <v>250</v>
@@ -2470,95 +2509,91 @@
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>1757</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>3600</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F48" s="2">
-        <v>46297.309502314813</v>
+        <v>46296.799664351849</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>1061</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D49">
-        <v>40</v>
+        <v>3000</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F49" s="2">
-        <v>46296.810150462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>55</v>
-      </c>
-      <c r="I49">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>1241</v>
+        <v>837</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
         <v>76</v>
       </c>
       <c r="D50">
-        <v>3000</v>
+        <v>23760</v>
       </c>
       <c r="E50" t="s">
         <v>77</v>
       </c>
       <c r="F50" s="2">
-        <v>46295.747650462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2570,27 +2605,27 @@
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>331</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
         <v>76</v>
       </c>
       <c r="D51">
-        <v>720</v>
+        <v>5280</v>
       </c>
       <c r="E51" t="s">
         <v>77</v>
       </c>
       <c r="F51" s="2">
-        <v>46295.747650462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2602,27 +2637,27 @@
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>233</v>
+        <v>695</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
         <v>76</v>
       </c>
       <c r="D52">
-        <v>7800</v>
+        <v>1200</v>
       </c>
       <c r="E52" t="s">
         <v>77</v>
       </c>
       <c r="F52" s="2">
-        <v>46295.747650462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
@@ -2634,27 +2669,27 @@
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>323</v>
+        <v>523</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
         <v>76</v>
       </c>
       <c r="D53">
-        <v>42240</v>
+        <v>900</v>
       </c>
       <c r="E53" t="s">
         <v>77</v>
       </c>
       <c r="F53" s="2">
-        <v>46295.747650462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2666,431 +2701,443 @@
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>465</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C54" t="s">
         <v>76</v>
       </c>
       <c r="D54">
-        <v>455520</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
         <v>77</v>
       </c>
       <c r="F54" s="2">
-        <v>46296.898715277777</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54"/>
+        <v>38</v>
+      </c>
+      <c r="I54">
+        <v>440</v>
+      </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>947</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
         <v>76</v>
       </c>
       <c r="D55">
-        <v>3960</v>
+        <v>90</v>
       </c>
       <c r="E55" t="s">
         <v>77</v>
       </c>
       <c r="F55" s="2">
-        <v>46295.747650462959</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55"/>
+        <v>38</v>
+      </c>
+      <c r="I55">
+        <v>250</v>
+      </c>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>109</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
         <v>76</v>
       </c>
       <c r="D56">
-        <v>2096</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
         <v>77</v>
       </c>
       <c r="F56" s="2">
-        <v>46296.898715277777</v>
+        <v>46297.302974537037</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I56">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>1051</v>
+        <v>741</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D57">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2">
-        <v>46296.898715277777</v>
+        <v>46297.560925925922</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I57">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>887</v>
+        <v>274</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D58">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F58" s="2">
-        <v>46296.898715277777</v>
+        <v>46297.560925925922</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I58">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>674</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D59">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="E59" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F59" s="2">
-        <v>46295.710925925923</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>85</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D60">
-        <v>3000</v>
+        <v>480</v>
       </c>
       <c r="E60" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F60" s="2">
-        <v>46296.963854166665</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>1059</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D61">
-        <v>9000</v>
+        <v>720</v>
       </c>
       <c r="E61" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F61" s="2">
-        <v>46297.043460648143</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>2179</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D62">
-        <v>3153</v>
+        <v>3414</v>
       </c>
       <c r="E62" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F62" s="2">
-        <v>46296.963854166665</v>
+        <v>46297.408437499995</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62"/>
+        <v>38</v>
+      </c>
+      <c r="I62">
+        <v>440</v>
+      </c>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>1659</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D63">
-        <v>120060</v>
+        <v>105</v>
       </c>
       <c r="E63" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F63" s="2">
-        <v>46297.286840277775</v>
+        <v>46297.408437499995</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63"/>
+        <v>38</v>
+      </c>
+      <c r="I63">
+        <v>250</v>
+      </c>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>1</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D64">
-        <v>75960</v>
+        <v>73</v>
       </c>
       <c r="E64" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F64" s="2">
-        <v>46297.197662037033</v>
+        <v>46297.408437499995</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>21</v>
-      </c>
-      <c r="I64"/>
+        <v>38</v>
+      </c>
+      <c r="I64">
+        <v>250</v>
+      </c>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>3804</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>31680</v>
+        <v>3640</v>
       </c>
       <c r="E65" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F65" s="2">
-        <v>46297.036851851852</v>
+        <v>46297.49800925926</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>21</v>
-      </c>
-      <c r="I65"/>
+        <v>84</v>
+      </c>
+      <c r="I65">
+        <v>13440</v>
+      </c>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>2883</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D66">
-        <v>7920</v>
+        <v>108</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F66" s="2">
-        <v>46296.963854166665</v>
+        <v>46297.408437499995</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66"/>
+        <v>61</v>
+      </c>
+      <c r="I66">
+        <v>5000</v>
+      </c>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>867</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="67">
@@ -3101,148 +3148,148 @@
         <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D67">
-        <v>1292</v>
+        <v>680</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="F67" s="2">
-        <v>46297.286840277775</v>
+        <v>46297.439409722218</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>36</v>
-      </c>
-      <c r="I67">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>5550</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D68">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="F68" s="2">
-        <v>46297.286840277775</v>
+        <v>46297.439409722218</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
-      </c>
-      <c r="I68">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>4827</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D69">
-        <v>3600</v>
+        <v>1548</v>
       </c>
       <c r="E69" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F69" s="2">
-        <v>46296.799664351849</v>
+        <v>46297.4146875</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69"/>
+        <v>38</v>
+      </c>
+      <c r="I69">
+        <v>440</v>
+      </c>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>213</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D70">
-        <v>3000</v>
+        <v>129</v>
       </c>
       <c r="E70" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F70" s="2">
-        <v>46297.302974537037</v>
+        <v>46297.4146875</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70"/>
+        <v>38</v>
+      </c>
+      <c r="I70">
+        <v>250</v>
+      </c>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>837</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D71">
-        <v>23760</v>
+        <v>374400</v>
       </c>
       <c r="E71" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F71" s="2">
-        <v>46297.302974537037</v>
+        <v>46297.297546296293</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
@@ -3254,59 +3301,61 @@
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>1201</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D72">
-        <v>5280</v>
+        <v>1560</v>
       </c>
       <c r="E72" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F72" s="2">
-        <v>46297.302974537037</v>
+        <v>46297.297546296293</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72"/>
+        <v>38</v>
+      </c>
+      <c r="I72">
+        <v>440</v>
+      </c>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>695</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D73">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="E73" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F73" s="2">
-        <v>46297.302974537037</v>
+        <v>46296</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
@@ -3318,27 +3367,27 @@
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>523</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D74">
-        <v>900</v>
+        <v>5400</v>
       </c>
       <c r="E74" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F74" s="2">
-        <v>46297.302974537037</v>
+        <v>46296</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
@@ -3350,129 +3399,123 @@
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>187</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D75">
-        <v>186</v>
+        <v>1200</v>
       </c>
       <c r="E75" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F75" s="2">
-        <v>46297.302974537037</v>
+        <v>46296</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>36</v>
-      </c>
-      <c r="I75">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>1433</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D76">
-        <v>90</v>
+        <v>72864</v>
       </c>
       <c r="E76" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F76" s="2">
-        <v>46297.302974537037</v>
+        <v>46297.285555555551</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
-      </c>
-      <c r="I76">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>1143</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D77">
-        <v>48</v>
+        <v>211200</v>
       </c>
       <c r="E77" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F77" s="2">
-        <v>46297.302974537037</v>
+        <v>46297.280555555553</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>36</v>
-      </c>
-      <c r="I77">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>741</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D78">
-        <v>3000</v>
+        <v>511460</v>
       </c>
       <c r="E78" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F78" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.285555555551</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
@@ -3484,155 +3527,163 @@
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>979</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D79">
-        <v>163920</v>
+        <v>3012</v>
       </c>
       <c r="E79" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F79" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.285555555551</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79"/>
+        <v>38</v>
+      </c>
+      <c r="I79">
+        <v>440</v>
+      </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>1677</v>
+        <v>9246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D80">
-        <v>6480</v>
+        <v>129</v>
       </c>
       <c r="E80" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F80" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.285555555551</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80"/>
+        <v>38</v>
+      </c>
+      <c r="I80">
+        <v>250</v>
+      </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>687</v>
+        <v>6505</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C81" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D81">
-        <v>25920</v>
+        <v>64</v>
       </c>
       <c r="E81" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F81" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.285555555551</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>21</v>
-      </c>
-      <c r="I81"/>
+        <v>38</v>
+      </c>
+      <c r="I81">
+        <v>250</v>
+      </c>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>1467</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C82" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D82">
-        <v>900</v>
+        <v>68</v>
       </c>
       <c r="E82" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F82" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.280555555553</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
-      </c>
-      <c r="I82"/>
+        <v>61</v>
+      </c>
+      <c r="I82">
+        <v>5000</v>
+      </c>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>245</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D83">
-        <v>6480</v>
+        <v>69120</v>
       </c>
       <c r="E83" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2">
-        <v>46296.9874074074</v>
+        <v>46297.6674074074</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
@@ -3644,951 +3695,979 @@
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>367</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D84">
-        <v>868</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="F84" s="2">
-        <v>46296.9874074074</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I84">
-        <v>440</v>
+        <v>130</v>
       </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>2367</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D85">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E85" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="F85" s="2">
-        <v>46296.9874074074</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I85">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>1931</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>1380</v>
       </c>
       <c r="E86" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F86" s="2">
-        <v>46296.9874074074</v>
+        <v>46296.9455787037</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I86">
-        <v>250</v>
+        <v>660</v>
       </c>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>971</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D87">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="E87" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F87" s="2">
-        <v>46297.362847222219</v>
+        <v>46297.416145833333</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="I87">
-        <v>875</v>
+        <v>57600</v>
       </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>1904</v>
+        <v>374</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D88">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="E88" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F88" s="2">
-        <v>46297.361481481479</v>
+        <v>46297.416145833333</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I88">
-        <v>349</v>
+        <v>57600</v>
       </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>194</v>
+        <v>474</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="B89" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D89">
-        <v>5200</v>
+        <v>42000</v>
       </c>
       <c r="E89" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F89" s="2">
-        <v>46297.361481481479</v>
+        <v>46297.416145833333</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I89">
-        <v>20000</v>
+        <v>15600</v>
       </c>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>159</v>
+        <v>493</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D90">
-        <v>5200</v>
+        <v>12000</v>
       </c>
       <c r="E90" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F90" s="2">
-        <v>46297.361481481479</v>
+        <v>46297.416145833333</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I90">
-        <v>30000</v>
+        <v>12000</v>
       </c>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D91">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="E91" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F91" s="2">
-        <v>46297.363657407404</v>
+        <v>46296.903240740736</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I91">
-        <v>875</v>
+        <v>11520</v>
       </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>1189</v>
+        <v>389</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B92" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D92">
-        <v>10800</v>
+        <v>600</v>
       </c>
       <c r="E92" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F92" s="2">
-        <v>46297.363657407404</v>
+        <v>46287.95758101852</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>110</v>
-      </c>
-      <c r="I92"/>
+        <v>84</v>
+      </c>
+      <c r="I92">
+        <v>660</v>
+      </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>75</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B93" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D93">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="E93" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F93" s="2">
-        <v>46297.364791666667</v>
+        <v>46297.625902777778</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>110</v>
-      </c>
-      <c r="I93"/>
+        <v>84</v>
+      </c>
+      <c r="I93">
+        <v>8000</v>
+      </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>42</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="B94" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D94">
-        <v>2240</v>
+        <v>160</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F94" s="2">
-        <v>46297.364791666667</v>
+        <v>46297.625902777778</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>110</v>
-      </c>
-      <c r="I94"/>
+        <v>84</v>
+      </c>
+      <c r="I94">
+        <v>133</v>
+      </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>61</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D95">
-        <v>1200</v>
+        <v>6720</v>
       </c>
       <c r="E95" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F95" s="2">
-        <v>46297.364791666667</v>
+        <v>46297.625902777778</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>110</v>
-      </c>
-      <c r="I95"/>
+        <v>84</v>
+      </c>
+      <c r="I95">
+        <v>8960</v>
+      </c>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>45</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D96">
-        <v>109728</v>
+        <v>8960</v>
       </c>
       <c r="E96" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F96" s="2">
-        <v>46296</v>
+        <v>46297.625902777778</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96"/>
+        <v>84</v>
+      </c>
+      <c r="I96">
+        <v>13440</v>
+      </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>1573</v>
+        <v>651</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="D97">
-        <v>374400</v>
+        <v>850</v>
       </c>
       <c r="E97" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="F97" s="2">
-        <v>46297.297546296293</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97"/>
+        <v>146</v>
+      </c>
+      <c r="I97">
+        <v>5000</v>
+      </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>265</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D98">
-        <v>1560</v>
+        <v>2380</v>
       </c>
       <c r="E98" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F98" s="2">
-        <v>46297.297546296293</v>
+        <v>46296.809965277775</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I98">
-        <v>440</v>
+        <v>22400</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>4431</v>
+        <v>927</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D99">
-        <v>18</v>
+        <v>1400</v>
       </c>
       <c r="E99" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F99" s="2">
-        <v>46297.296817129631</v>
+        <v>46296.809965277775</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I99">
-        <v>250</v>
+        <v>17920</v>
       </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>4115</v>
+        <v>280</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D100">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="E100" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F100" s="2">
-        <v>46296</v>
+        <v>46296.809965277775</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100"/>
+        <v>84</v>
+      </c>
+      <c r="I100">
+        <v>1440</v>
+      </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>1364</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D101">
-        <v>5400</v>
+        <v>20000</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F101" s="2">
-        <v>46296</v>
+        <v>46296.620462962965</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101"/>
+        <v>84</v>
+      </c>
+      <c r="I101">
+        <v>90000</v>
+      </c>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>1370</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D102">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F102" s="2">
-        <v>46296</v>
+        <v>46295.848576388889</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102"/>
+        <v>84</v>
+      </c>
+      <c r="I102">
+        <v>20000</v>
+      </c>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>13</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D103">
-        <v>72864</v>
+        <v>600</v>
       </c>
       <c r="E103" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F103" s="2">
-        <v>46297.285555555551</v>
+        <v>46296.809965277775</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103"/>
+        <v>84</v>
+      </c>
+      <c r="I103">
+        <v>359</v>
+      </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>1869</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B104" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D104">
-        <v>211200</v>
+        <v>400</v>
       </c>
       <c r="E104" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="F104" s="2">
-        <v>46297.280555555553</v>
+        <v>45185</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104"/>
+        <v>84</v>
+      </c>
+      <c r="I104">
+        <v>359</v>
+      </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>1379</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B105" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D105">
-        <v>511460</v>
+        <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="F105" s="2">
-        <v>46297.285555555551</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105"/>
+        <v>16</v>
+      </c>
+      <c r="I105">
+        <v>25</v>
+      </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>5238</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="B106" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D106">
-        <v>3012</v>
+        <v>3</v>
       </c>
       <c r="E106" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="F106" s="2">
-        <v>46297.285555555551</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I106">
-        <v>440</v>
+        <v>50</v>
       </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>9246</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D107">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="F107" s="2">
-        <v>46297.285555555551</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107">
         <v>36</v>
-      </c>
-      <c r="I107">
-        <v>250</v>
       </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>6505</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="B108" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D108">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="F108" s="2">
-        <v>46297.285555555551</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I108">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>5271</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D109">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="F109" s="2">
-        <v>46297.280555555553</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="I109">
-        <v>5000</v>
+        <v>43</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>3023</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="B110" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="C110" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="D110">
-        <v>1800</v>
+        <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="F110" s="2">
-        <v>46296.934386574074</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>21</v>
-      </c>
-      <c r="I110"/>
+        <v>16</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>1042</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="B111" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="C111" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="D111">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="F111" s="2">
-        <v>46296.806585648148</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>21</v>
-      </c>
-      <c r="I111"/>
+        <v>16</v>
+      </c>
+      <c r="I111">
+        <v>15</v>
+      </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>1487</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="C112" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D112">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="F112" s="2">
-        <v>46290.555405092593</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
@@ -4597,32 +4676,32 @@
         <v>16</v>
       </c>
       <c r="I112">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="B113" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="C113" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D113">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="F113" s="2">
-        <v>46290.555405092593</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
@@ -4631,7 +4710,7 @@
         <v>16</v>
       </c>
       <c r="I113">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
@@ -4641,1586 +4720,1566 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D114">
-        <v>1380</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="F114" s="2">
-        <v>46296.9455787037</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="I114">
-        <v>660</v>
+        <v>2</v>
       </c>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D115">
-        <v>2400</v>
+        <v>1540</v>
       </c>
       <c r="E115" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="F115" s="2">
-        <v>46296.903240740736</v>
+        <v>46293</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I115">
-        <v>23040</v>
+        <v>17920</v>
       </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>389</v>
+        <v>258</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="C116" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D116">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="E116" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="F116" s="2">
-        <v>46287.95758101852</v>
+        <v>46293</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I116">
-        <v>660</v>
+        <v>5000</v>
       </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C117" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D117">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="E117" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="F117" s="2">
-        <v>46297.357361111106</v>
+        <v>46293</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I117">
-        <v>8960</v>
+        <v>8000</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>648</v>
+        <v>196</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="B118" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D118">
-        <v>850</v>
+        <v>30000</v>
       </c>
       <c r="E118" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F118" s="2">
-        <v>46295.8800462963</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="I118">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="B119" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="C119" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D119">
-        <v>2380</v>
+        <v>300</v>
       </c>
       <c r="E119" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="F119" s="2">
-        <v>46296.809965277775</v>
+        <v>46297.650706018518</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="I119">
-        <v>31360</v>
+        <v>875</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>927</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C120" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D120">
-        <v>1400</v>
+        <v>1080</v>
       </c>
       <c r="E120" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="F120" s="2">
-        <v>46296.809965277775</v>
+        <v>46297.642534722218</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I120">
-        <v>8960</v>
+        <v>11520</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>280</v>
+        <v>446</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B121" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C121" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D121">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="E121" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="F121" s="2">
-        <v>46296.809965277775</v>
+        <v>46297.642534722218</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I121">
-        <v>1440</v>
+        <v>17920</v>
       </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>181</v>
+        <v>448</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B122" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C122" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="D122">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="F122" s="2">
-        <v>46296.620462962965</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="I122">
-        <v>90000</v>
+        <v>50</v>
       </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>138</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="B123" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="D123">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="F123" s="2">
-        <v>46295.848576388889</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="I123">
-        <v>20000</v>
+        <v>43</v>
       </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>129</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C124" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="D124">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="F124" s="2">
-        <v>46296.809965277775</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="I124">
-        <v>255</v>
+        <v>15</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B125" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C125" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D125">
-        <v>560</v>
+        <v>190</v>
       </c>
       <c r="E125" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="F125" s="2">
-        <v>46295.742094907408</v>
+        <v>46296.98773148148</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I125">
-        <v>8960</v>
+        <v>1440</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>55</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C126" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D126">
-        <v>560</v>
+        <v>400</v>
       </c>
       <c r="E126" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="F126" s="2">
-        <v>46295.742094907408</v>
+        <v>46296.98773148148</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I126">
-        <v>84420</v>
+        <v>359</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="C127" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D127">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="E127" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="F127" s="2">
-        <v>46295.742094907408</v>
+        <v>46296.98773148148</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="H127" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I127">
-        <v>660</v>
+        <v>160</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>178</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B128" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="C128" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="D128">
-        <v>200</v>
+        <v>6658</v>
       </c>
       <c r="E128" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F128" s="2">
-        <v>46295.742094907408</v>
+        <v>46297.423749999994</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="I128">
-        <v>1440</v>
+        <v>440</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>127</v>
+        <v>11313</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="C129" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="D129">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="E129" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F129" s="2">
-        <v>46295.742094907408</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="I129">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>115</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="C130" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="D130">
-        <v>840</v>
+        <v>376</v>
       </c>
       <c r="E130" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F130" s="2">
-        <v>46295.742094907408</v>
+        <v>46297.423749999994</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="I130">
-        <v>3920</v>
+        <v>250</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>193</v>
+        <v>8961</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="D131">
-        <v>840</v>
+        <v>131</v>
       </c>
       <c r="E131" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F131" s="2">
-        <v>46295.742094907408</v>
+        <v>46297.423749999994</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="I131">
-        <v>20160</v>
+        <v>250</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>263</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="D132">
-        <v>400</v>
+        <v>93</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="F132" s="2">
-        <v>45185</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="I132">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="B133" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="C133" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E133" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F133" s="2">
-        <v>46273.306030092594</v>
+        <v>44426</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I133">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="B134" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="C134" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>519</v>
       </c>
       <c r="E134" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F134" s="2">
-        <v>46273.306030092594</v>
+        <v>46297.423749999994</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="I134">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>16</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="B135" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C135" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="E135" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F135" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.957384259258</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>16</v>
-      </c>
-      <c r="I135">
-        <v>36</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I135"/>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>7</v>
+        <v>446</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B136" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C136" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>1440</v>
       </c>
       <c r="E136" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F136" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.668611111112</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>16</v>
-      </c>
-      <c r="I136">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I136"/>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="B137" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C137" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="E137" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F137" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.802997685183</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>16</v>
-      </c>
-      <c r="I137">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I137"/>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>21</v>
+        <v>569</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="B138" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="C138" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>2386</v>
       </c>
       <c r="E138" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F138" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
-      </c>
-      <c r="I138">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I138"/>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>16</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="B139" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="C139" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>6330</v>
       </c>
       <c r="E139" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F139" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.47378472222</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>16</v>
-      </c>
-      <c r="I139">
-        <v>15</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I139"/>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>20</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B140" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="C140" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>6811</v>
       </c>
       <c r="E140" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F140" s="2">
-        <v>46273.306030092594</v>
+        <v>46295.475601851853</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>16</v>
-      </c>
-      <c r="I140">
-        <v>88</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I140"/>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="B141" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="C141" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>446</v>
       </c>
       <c r="E141" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F141" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I141">
-        <v>5</v>
+        <v>440</v>
       </c>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>20</v>
+        <v>171</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="B142" t="s">
-        <v>197</v>
+        <v>40</v>
       </c>
       <c r="C142" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E142" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F142" s="2">
-        <v>46273.306030092594</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I142">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="B143" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="C143" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D143">
-        <v>1540</v>
+        <v>20</v>
       </c>
       <c r="E143" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="F143" s="2">
-        <v>46293</v>
+        <v>46296.571886574071</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="I143">
-        <v>84420</v>
+        <v>5000</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>258</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B144" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C144" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="D144">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="E144" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="F144" s="2">
-        <v>46293</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="I144">
-        <v>5000</v>
+        <v>875</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>168</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C145" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="D145">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E145" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="F145" s="2">
-        <v>46293</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I145">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>196</v>
+        <v>996</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B146" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C146" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="D146">
-        <v>30000</v>
+        <v>600</v>
       </c>
       <c r="E146" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="F146" s="2">
-        <v>46280.943472222221</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I146">
-        <v>100000</v>
+        <v>349</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>102</v>
+        <v>448</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="B147" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="E147" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F147" s="2">
-        <v>46265.788981481477</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I147">
-        <v>50</v>
+        <v>2374</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>14</v>
+        <v>672</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>900</v>
       </c>
       <c r="E148" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F148" s="2">
-        <v>46265.776967592588</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I148">
-        <v>43</v>
+        <v>1440</v>
       </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>11</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B149" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="C149" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F149" s="2">
-        <v>46265.788981481477</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I149">
-        <v>15</v>
+        <v>8000</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>19</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B150" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D150">
-        <v>190</v>
+        <v>2000</v>
       </c>
       <c r="E150" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F150" s="2">
-        <v>46296.98773148148</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I150">
-        <v>1440</v>
+        <v>30000</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>121</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="B151" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="C151" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D151">
-        <v>400</v>
+        <v>2500</v>
       </c>
       <c r="E151" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F151" s="2">
-        <v>46296.98773148148</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I151">
-        <v>255</v>
+        <v>2500</v>
       </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>67</v>
+        <v>846</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="C152" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D152">
-        <v>6</v>
+        <v>400</v>
       </c>
       <c r="E152" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F152" s="2">
-        <v>46296.98773148148</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G152" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I152">
-        <v>160</v>
+        <v>359</v>
       </c>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>51</v>
+        <v>705</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="B153" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="C153" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D153">
-        <v>2151</v>
+        <v>10000</v>
       </c>
       <c r="E153" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F153" s="2">
-        <v>46296</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I153">
-        <v>440</v>
+        <v>100000</v>
       </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>11309</v>
+        <v>995</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C154" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D154">
-        <v>186</v>
+        <v>7</v>
       </c>
       <c r="E154" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F154" s="2">
-        <v>44946.553055555552</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G154" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="H154" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I154">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>2</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="B155" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="C155" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D155">
-        <v>75</v>
+        <v>8000</v>
       </c>
       <c r="E155" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F155" s="2">
-        <v>46296</v>
+        <v>46297.359733796293</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="I155">
-        <v>250</v>
+        <v>57600</v>
       </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>8957</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B156" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C156" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D156">
-        <v>93</v>
+        <v>7000</v>
       </c>
       <c r="E156" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F156" s="2">
-        <v>45777.752291666664</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>217</v>
-      </c>
-      <c r="I156">
-        <v>16</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="I156"/>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>7</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B157" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C157" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D157">
-        <v>55</v>
+        <v>4000</v>
       </c>
       <c r="E157" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F157" s="2">
-        <v>44426</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>55</v>
-      </c>
-      <c r="I157">
-        <v>2</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="I157"/>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>53</v>
+        <v>239</v>
       </c>
       <c r="B158" t="s">
-        <v>54</v>
+        <v>240</v>
       </c>
       <c r="C158" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D158">
-        <v>129</v>
+        <v>4800</v>
       </c>
       <c r="E158" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F158" s="2">
-        <v>46296.407106481478</v>
+        <v>46297.359733796293</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>55</v>
-      </c>
-      <c r="I158">
-        <v>5000</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="I158"/>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>2518</v>
+        <v>152</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="B159" t="s">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="C159" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D159">
-        <v>32784</v>
+        <v>1200</v>
       </c>
       <c r="E159" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F159" s="2">
-        <v>46295.857083333329</v>
+        <v>46297.59888888889</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>21</v>
-      </c>
-      <c r="I159">
-        <v>0</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="I159"/>
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>187</v>
+        <v>91</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B160" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C160" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D160">
-        <v>300</v>
+        <v>146304</v>
       </c>
       <c r="E160" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F160" s="2">
-        <v>46296.957384259258</v>
+        <v>46297.666030092594</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
@@ -6232,27 +6291,27 @@
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>446</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="B161" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="C161" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D161">
-        <v>1440</v>
+        <v>371040</v>
       </c>
       <c r="E161" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F161" s="2">
-        <v>46295.668611111112</v>
+        <v>46297.662199074075</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
@@ -6264,27 +6323,27 @@
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>57</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B162" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C162" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D162">
-        <v>300</v>
+        <v>441600</v>
       </c>
       <c r="E162" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F162" s="2">
-        <v>46296.802997685183</v>
+        <v>46297.662199074075</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
@@ -6296,123 +6355,129 @@
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>569</v>
+        <v>282</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>224</v>
+        <v>36</v>
       </c>
       <c r="B163" t="s">
-        <v>225</v>
+        <v>37</v>
       </c>
       <c r="C163" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D163">
-        <v>11400</v>
+        <v>3386</v>
       </c>
       <c r="E163" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F163" s="2">
-        <v>46296.674861111111</v>
+        <v>46297.662199074075</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>21</v>
-      </c>
-      <c r="I163"/>
+        <v>38</v>
+      </c>
+      <c r="I163">
+        <v>440</v>
+      </c>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>3</v>
+        <v>5089</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>226</v>
+        <v>39</v>
       </c>
       <c r="B164" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="C164" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D164">
-        <v>2386</v>
+        <v>206</v>
       </c>
       <c r="E164" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F164" s="2">
-        <v>46295.47378472222</v>
+        <v>46297.666030092594</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>21</v>
-      </c>
-      <c r="I164"/>
+        <v>38</v>
+      </c>
+      <c r="I164">
+        <v>250</v>
+      </c>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>72</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="B165" t="s">
-        <v>229</v>
+        <v>42</v>
       </c>
       <c r="C165" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D165">
-        <v>6330</v>
+        <v>81</v>
       </c>
       <c r="E165" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F165" s="2">
-        <v>46295.47378472222</v>
+        <v>46297.662199074075</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>21</v>
-      </c>
-      <c r="I165"/>
+        <v>38</v>
+      </c>
+      <c r="I165">
+        <v>250</v>
+      </c>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>97</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="B166" t="s">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="C166" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D166">
-        <v>6811</v>
+        <v>105600</v>
       </c>
       <c r="E166" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="F166" s="2">
-        <v>46295.475601851853</v>
+        <v>46296.899398148147</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
@@ -6424,33 +6489,33 @@
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>68</v>
+        <v>375</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C167" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D167">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E167" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="F167" s="2">
-        <v>46296.571886574071</v>
+        <v>46296.899398148147</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
       </c>
       <c r="H167" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I167">
         <v>440</v>
@@ -6458,33 +6523,33 @@
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>171</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B168" t="s">
+        <v>40</v>
+      </c>
+      <c r="C168" t="s">
+        <v>245</v>
+      </c>
+      <c r="D168">
+        <v>26</v>
+      </c>
+      <c r="E168" t="s">
+        <v>246</v>
+      </c>
+      <c r="F168" s="2">
+        <v>46296.899398148147</v>
+      </c>
+      <c r="G168" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" t="s">
         <v>38</v>
-      </c>
-      <c r="C168" t="s">
-        <v>220</v>
-      </c>
-      <c r="D168">
-        <v>24</v>
-      </c>
-      <c r="E168" t="s">
-        <v>221</v>
-      </c>
-      <c r="F168" s="2">
-        <v>46296.571886574071</v>
-      </c>
-      <c r="G168" t="s">
-        <v>15</v>
-      </c>
-      <c r="H168" t="s">
-        <v>36</v>
       </c>
       <c r="I168">
         <v>250</v>
@@ -6492,504 +6557,512 @@
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>102</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B169" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C169" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D169">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E169" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="F169" s="2">
-        <v>46296.571886574071</v>
+        <v>46296.899398148147</v>
       </c>
       <c r="G169" t="s">
         <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I169">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>60</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="B170" t="s">
-        <v>233</v>
+        <v>37</v>
       </c>
       <c r="C170" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D170">
-        <v>8000</v>
+        <v>1152</v>
       </c>
       <c r="E170" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F170" s="2">
-        <v>46297.359733796293</v>
+        <v>46297.421006944445</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="I170">
-        <v>4000</v>
+        <v>440</v>
       </c>
       <c r="J170"/>
       <c r="K170"/>
       <c r="L170">
-        <v>1218</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="B171" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="C171" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D171">
-        <v>4800</v>
+        <v>138</v>
       </c>
       <c r="E171" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F171" s="2">
-        <v>46297.359733796293</v>
+        <v>46297.626030092593</v>
       </c>
       <c r="G171" t="s">
         <v>15</v>
       </c>
       <c r="H171" t="s">
-        <v>110</v>
-      </c>
-      <c r="I171"/>
+        <v>38</v>
+      </c>
+      <c r="I171">
+        <v>250</v>
+      </c>
       <c r="J171"/>
       <c r="K171"/>
       <c r="L171">
-        <v>152</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="B172" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D172">
-        <v>109728</v>
+        <v>51</v>
       </c>
       <c r="E172" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F172" s="2">
-        <v>46297.282037037032</v>
+        <v>46297.421006944445</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>21</v>
-      </c>
-      <c r="I172"/>
+        <v>38</v>
+      </c>
+      <c r="I172">
+        <v>250</v>
+      </c>
       <c r="J172"/>
       <c r="K172"/>
       <c r="L172">
-        <v>2431</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="B173" t="s">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="C173" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D173">
-        <v>207840</v>
+        <v>6</v>
       </c>
       <c r="E173" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F173" s="2">
-        <v>46297.356388888889</v>
+        <v>46297.441203703704</v>
       </c>
       <c r="G173" t="s">
         <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>21</v>
-      </c>
-      <c r="I173"/>
+        <v>61</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
       <c r="J173"/>
       <c r="K173"/>
       <c r="L173">
-        <v>1846</v>
+        <v>37</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B174" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C174" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D174">
-        <v>866</v>
+        <v>240</v>
       </c>
       <c r="E174" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F174" s="2">
-        <v>46297.356388888889</v>
+        <v>46297.421006944445</v>
       </c>
       <c r="G174" t="s">
         <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="I174">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J174"/>
       <c r="K174"/>
       <c r="L174">
-        <v>5087</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="B175" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="C175" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D175">
-        <v>59</v>
+        <v>2439100</v>
       </c>
       <c r="E175" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F175" s="2">
-        <v>46297.356388888889</v>
+        <v>46266</v>
       </c>
       <c r="G175" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H175" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="I175">
-        <v>250</v>
+        <v>950000</v>
       </c>
       <c r="J175"/>
       <c r="K175"/>
       <c r="L175">
-        <v>4479</v>
+        <v>56</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>51</v>
+        <v>255</v>
       </c>
       <c r="B176" t="s">
-        <v>52</v>
+        <v>256</v>
       </c>
       <c r="C176" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D176">
-        <v>15</v>
+        <v>2530000</v>
       </c>
       <c r="E176" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F176" s="2">
-        <v>46297.282037037032</v>
+        <v>46266</v>
       </c>
       <c r="G176" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H176" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="I176">
-        <v>250</v>
+        <v>1265000</v>
       </c>
       <c r="J176"/>
       <c r="K176"/>
       <c r="L176">
-        <v>2560</v>
+        <v>48</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>125</v>
+        <v>257</v>
       </c>
       <c r="B177" t="s">
-        <v>126</v>
+        <v>258</v>
       </c>
       <c r="C177" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D177">
-        <v>105600</v>
+        <v>750000</v>
       </c>
       <c r="E177" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F177" s="2">
-        <v>46296.899398148147</v>
+        <v>46266</v>
       </c>
       <c r="G177" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H177" t="s">
-        <v>21</v>
-      </c>
-      <c r="I177"/>
+        <v>254</v>
+      </c>
+      <c r="I177">
+        <v>750000</v>
+      </c>
       <c r="J177"/>
       <c r="K177"/>
       <c r="L177">
-        <v>375</v>
+        <v>45</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>34</v>
+        <v>259</v>
       </c>
       <c r="B178" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="C178" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D178">
-        <v>440</v>
+        <v>52000</v>
       </c>
       <c r="E178" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F178" s="2">
-        <v>46296.899398148147</v>
+        <v>46294</v>
       </c>
       <c r="G178" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H178" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="I178">
-        <v>440</v>
+        <v>26000</v>
       </c>
       <c r="J178"/>
       <c r="K178"/>
       <c r="L178">
-        <v>1614</v>
+        <v>56</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>37</v>
+        <v>261</v>
       </c>
       <c r="B179" t="s">
-        <v>38</v>
+        <v>262</v>
       </c>
       <c r="C179" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D179">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E179" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="F179" s="2">
-        <v>46296.899398148147</v>
+        <v>46295.485300925924</v>
       </c>
       <c r="G179" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
       <c r="H179" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="I179">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="J179"/>
       <c r="K179"/>
       <c r="L179">
-        <v>1182</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>51</v>
+        <v>267</v>
       </c>
       <c r="B180" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="C180" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D180">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="F180" s="2">
-        <v>46296.899398148147</v>
+        <v>46293.599965277775</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
       </c>
       <c r="H180" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="I180">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="J180"/>
       <c r="K180"/>
       <c r="L180">
-        <v>1053</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="B181" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="C181" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="D181">
-        <v>2439100</v>
+        <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F181" s="2">
-        <v>46266</v>
+        <v>46293.600868055553</v>
       </c>
       <c r="G181" t="s">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="H181" t="s">
-        <v>245</v>
+        <v>61</v>
       </c>
       <c r="I181">
-        <v>950000</v>
+        <v>2</v>
       </c>
       <c r="J181"/>
       <c r="K181"/>
       <c r="L181">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B182" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C182" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="D182">
-        <v>2530000</v>
+        <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F182" s="2">
-        <v>46266</v>
+        <v>46293.600868055553</v>
       </c>
       <c r="G182" t="s">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="H182" t="s">
-        <v>245</v>
+        <v>61</v>
       </c>
       <c r="I182">
-        <v>1265000</v>
+        <v>1</v>
       </c>
       <c r="J182"/>
       <c r="K182"/>
       <c r="L182">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B183" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C183" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D183">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F183" s="2">
-        <v>46295.485300925924</v>
+        <v>46293.600868055553</v>
       </c>
       <c r="G183" t="s">
-        <v>252</v>
+        <v>15</v>
       </c>
       <c r="H183" t="s">
-        <v>253</v>
+        <v>61</v>
       </c>
       <c r="I183">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J183"/>
       <c r="K183"/>
@@ -6999,31 +7072,31 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="B184" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C184" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E184" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F184" s="2">
-        <v>46293.599965277775</v>
+        <v>46293.594282407408</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
       </c>
       <c r="H184" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I184">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J184"/>
       <c r="K184"/>
@@ -7033,223 +7106,223 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="B185" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="C185" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>26880</v>
       </c>
       <c r="E185" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F185" s="2">
-        <v>46293.600868055553</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G185" t="s">
         <v>15</v>
       </c>
       <c r="H185" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="I185">
-        <v>2</v>
+        <v>22400</v>
       </c>
       <c r="J185"/>
       <c r="K185"/>
       <c r="L185">
-        <v>2</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="B186" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="C186" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D186">
-        <v>1</v>
+        <v>8960</v>
       </c>
       <c r="E186" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F186" s="2">
-        <v>46293.600868055553</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G186" t="s">
         <v>15</v>
       </c>
       <c r="H186" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>17920</v>
       </c>
       <c r="J186"/>
       <c r="K186"/>
       <c r="L186">
-        <v>1</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="B187" t="s">
-        <v>261</v>
+        <v>135</v>
       </c>
       <c r="C187" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>15360</v>
       </c>
       <c r="E187" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F187" s="2">
-        <v>46293.600868055553</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
       </c>
       <c r="H187" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="I187">
-        <v>1</v>
+        <v>11520</v>
       </c>
       <c r="J187"/>
       <c r="K187"/>
       <c r="L187">
-        <v>1</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="B188" t="s">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="C188" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>17920</v>
       </c>
       <c r="E188" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F188" s="2">
-        <v>46293.594282407408</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
       </c>
       <c r="H188" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="I188">
-        <v>16</v>
+        <v>17920</v>
       </c>
       <c r="J188"/>
       <c r="K188"/>
       <c r="L188">
-        <v>1</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>154</v>
+        <v>279</v>
       </c>
       <c r="B189" t="s">
-        <v>155</v>
+        <v>280</v>
       </c>
       <c r="C189" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D189">
-        <v>13440</v>
+        <v>7680</v>
       </c>
       <c r="E189" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F189" s="2">
-        <v>46296</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G189" t="s">
         <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I189">
-        <v>31360</v>
+        <v>3840</v>
       </c>
       <c r="J189"/>
       <c r="K189"/>
       <c r="L189">
-        <v>3647</v>
+        <v>414</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>158</v>
+        <v>281</v>
       </c>
       <c r="B190" t="s">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="C190" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D190">
-        <v>4480</v>
+        <v>21000</v>
       </c>
       <c r="E190" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F190" s="2">
-        <v>46296</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G190" t="s">
         <v>15</v>
       </c>
       <c r="H190" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I190">
-        <v>8960</v>
+        <v>31500</v>
       </c>
       <c r="J190"/>
       <c r="K190"/>
       <c r="L190">
-        <v>1799</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>143</v>
+        <v>283</v>
       </c>
       <c r="B191" t="s">
-        <v>144</v>
+        <v>284</v>
       </c>
       <c r="C191" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D191">
-        <v>7680</v>
+        <v>500</v>
       </c>
       <c r="E191" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F191" s="2">
         <v>46296</v>
@@ -7258,100 +7331,100 @@
         <v>15</v>
       </c>
       <c r="H191" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I191">
-        <v>23040</v>
+        <v>2000</v>
       </c>
       <c r="J191"/>
       <c r="K191"/>
       <c r="L191">
-        <v>2392</v>
+        <v>221</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>168</v>
+        <v>285</v>
       </c>
       <c r="B192" t="s">
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D192">
-        <v>8960</v>
+        <v>15000</v>
       </c>
       <c r="E192" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F192" s="2">
-        <v>46296</v>
+        <v>46297.559537037036</v>
       </c>
       <c r="G192" t="s">
         <v>15</v>
       </c>
       <c r="H192" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I192">
-        <v>84420</v>
+        <v>180000</v>
       </c>
       <c r="J192"/>
       <c r="K192"/>
       <c r="L192">
-        <v>3068</v>
+        <v>974</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>266</v>
+        <v>159</v>
       </c>
       <c r="B193" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="C193" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D193">
-        <v>3840</v>
+        <v>1359</v>
       </c>
       <c r="E193" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F193" s="2">
-        <v>46296</v>
+        <v>46297.559537037036</v>
       </c>
       <c r="G193" t="s">
         <v>15</v>
       </c>
       <c r="H193" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I193">
-        <v>3840</v>
+        <v>359</v>
       </c>
       <c r="J193"/>
       <c r="K193"/>
       <c r="L193">
-        <v>413</v>
+        <v>448</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="B194" t="s">
-        <v>269</v>
+        <v>190</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D194">
-        <v>4200</v>
+        <v>50000</v>
       </c>
       <c r="E194" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F194" s="2">
         <v>46296</v>
@@ -7360,66 +7433,66 @@
         <v>15</v>
       </c>
       <c r="H194" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I194">
-        <v>12600</v>
+        <v>100000</v>
       </c>
       <c r="J194"/>
       <c r="K194"/>
       <c r="L194">
-        <v>2217</v>
+        <v>454</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="B195" t="s">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="C195" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D195">
-        <v>500</v>
+        <v>22400</v>
       </c>
       <c r="E195" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F195" s="2">
-        <v>46296</v>
+        <v>46297.575011574074</v>
       </c>
       <c r="G195" t="s">
         <v>15</v>
       </c>
       <c r="H195" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I195">
-        <v>2000</v>
+        <v>8960</v>
       </c>
       <c r="J195"/>
       <c r="K195"/>
       <c r="L195">
-        <v>221</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="B196" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D196">
-        <v>1000</v>
+        <v>8960</v>
       </c>
       <c r="E196" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F196" s="2">
         <v>46296</v>
@@ -7428,32 +7501,32 @@
         <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I196">
-        <v>255</v>
+        <v>13440</v>
       </c>
       <c r="J196"/>
       <c r="K196"/>
       <c r="L196">
-        <v>447</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="B197" t="s">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="C197" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D197">
-        <v>50000</v>
+        <v>36</v>
       </c>
       <c r="E197" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="F197" s="2">
         <v>46296</v>
@@ -7462,66 +7535,66 @@
         <v>15</v>
       </c>
       <c r="H197" t="s">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="I197">
-        <v>100000</v>
+        <v>600</v>
       </c>
       <c r="J197"/>
       <c r="K197"/>
       <c r="L197">
-        <v>454</v>
+        <v>133</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="B198" t="s">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="C198" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="D198">
-        <v>13440</v>
+        <v>104000</v>
       </c>
       <c r="E198" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="F198" s="2">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="G198" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H198" t="s">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="I198">
-        <v>20160</v>
+        <v>26000</v>
       </c>
       <c r="J198"/>
       <c r="K198"/>
       <c r="L198">
-        <v>2766</v>
+        <v>49</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="B199" t="s">
-        <v>148</v>
+        <v>293</v>
       </c>
       <c r="C199" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D199">
-        <v>8960</v>
+        <v>25000</v>
       </c>
       <c r="E199" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="F199" s="2">
         <v>46296</v>
@@ -7530,148 +7603,46 @@
         <v>15</v>
       </c>
       <c r="H199" t="s">
-        <v>101</v>
-      </c>
-      <c r="I199">
-        <v>8960</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I199"/>
       <c r="J199"/>
       <c r="K199"/>
       <c r="L199">
-        <v>1232</v>
+        <v>584</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B200" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C200" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="D200">
-        <v>36</v>
+        <v>4000</v>
       </c>
       <c r="E200" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="F200" s="2">
-        <v>46296</v>
+        <v>46296.511597222219</v>
       </c>
       <c r="G200" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="H200" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="I200">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="J200"/>
       <c r="K200"/>
       <c r="L200">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>275</v>
-      </c>
-      <c r="B201" t="s">
-        <v>276</v>
-      </c>
-      <c r="C201" t="s">
-        <v>277</v>
-      </c>
-      <c r="D201">
-        <v>78000</v>
-      </c>
-      <c r="E201" t="s">
-        <v>278</v>
-      </c>
-      <c r="F201" s="2">
-        <v>46266</v>
-      </c>
-      <c r="G201" t="s">
-        <v>244</v>
-      </c>
-      <c r="H201" t="s">
-        <v>245</v>
-      </c>
-      <c r="I201">
-        <v>52000</v>
-      </c>
-      <c r="J201"/>
-      <c r="K201"/>
-      <c r="L201">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>279</v>
-      </c>
-      <c r="B202" t="s">
-        <v>280</v>
-      </c>
-      <c r="C202" t="s">
-        <v>281</v>
-      </c>
-      <c r="D202">
-        <v>25000</v>
-      </c>
-      <c r="E202" t="s">
-        <v>282</v>
-      </c>
-      <c r="F202" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G202" t="s">
-        <v>15</v>
-      </c>
-      <c r="H202" t="s">
-        <v>21</v>
-      </c>
-      <c r="I202"/>
-      <c r="J202"/>
-      <c r="K202"/>
-      <c r="L202">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>283</v>
-      </c>
-      <c r="B203" t="s">
-        <v>284</v>
-      </c>
-      <c r="C203" t="s">
-        <v>285</v>
-      </c>
-      <c r="D203">
-        <v>4000</v>
-      </c>
-      <c r="E203" t="s">
-        <v>286</v>
-      </c>
-      <c r="F203" s="2">
-        <v>46296.511597222219</v>
-      </c>
-      <c r="G203" t="s">
-        <v>244</v>
-      </c>
-      <c r="H203" t="s">
-        <v>287</v>
-      </c>
-      <c r="I203">
-        <v>4000</v>
-      </c>
-      <c r="J203"/>
-      <c r="K203"/>
-      <c r="L203">
         <v>423</v>
       </c>
     </row>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="R105108b30e4941d6"/>
+    <sheet name="Inventarios" sheetId="1" r:id="Re46a20c497da4756"/>
   </sheets>
 </workbook>
 </file>
@@ -61,19 +61,175 @@
     <t>DO</t>
   </si>
   <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110317</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110402</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>110316</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>114365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2152388</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>VT41</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>2114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+  </si>
+  <si>
+    <t>2114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
+    <t>VT42</t>
+  </si>
+  <si>
+    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VT49</t>
+  </si>
+  <si>
+    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
+  </si>
+  <si>
     <t>112268</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>VT1</t>
-  </si>
-  <si>
-    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>HU</t>
+    <t>VT52</t>
+  </si>
+  <si>
+    <t>TAT BOGOTA - VT52</t>
   </si>
   <si>
     <t>112357</t>
@@ -88,55 +244,10 @@
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>2110327</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2110427</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2152388</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>VT2</t>
-  </si>
-  <si>
-    <t>TAT CALI - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>152382</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>2010102</t>
@@ -145,165 +256,69 @@
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
   </si>
   <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110317</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2112207</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110402</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>110316</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
-  </si>
-  <si>
-    <t>VT36</t>
-  </si>
-  <si>
-    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>114365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>110480</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE CAJA X 360 CON ETIQUETA</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
-    <t>2114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
-  </si>
-  <si>
-    <t>2114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
-    <t>VT41</t>
-  </si>
-  <si>
-    <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT42</t>
-  </si>
-  <si>
-    <t>TAT SANTAMARTA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT49</t>
-  </si>
-  <si>
-    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>VT52</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT52</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
     <t>VT59</t>
   </si>
   <si>
     <t>TAT BOGOTA - VT59</t>
   </si>
   <si>
+    <t>VT6</t>
+  </si>
+  <si>
+    <t>TAT PASTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>EECA006</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X300 EMPAQUE PET</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMBA025</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
+  </si>
+  <si>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
     <t>142111</t>
   </si>
   <si>
@@ -337,6 +352,75 @@
     <t>KIKES - EGIPTO - INVENTARIO TRANSITO</t>
   </si>
   <si>
+    <t>VTBC</t>
+  </si>
+  <si>
+    <t>EMPAQUES BELLAVISTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBO003</t>
+  </si>
+  <si>
+    <t>BOLSA POLIETILENO TRANSPARENTE 55X76CMS CALIBRE 2.5</t>
+  </si>
+  <si>
+    <t>EMCA019</t>
+  </si>
+  <si>
+    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EMET014</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
+  </si>
+  <si>
+    <t>EMET02</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO L X 30 - K</t>
+  </si>
+  <si>
+    <t>EMLA001</t>
+  </si>
+  <si>
+    <t>LAMINA DE CARTON CORRUGADO 88 X 119 CM</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
+  </si>
+  <si>
+    <t>MAAM033</t>
+  </si>
+  <si>
+    <t>AMARRES PLASTICOS DE 8"</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>VTBE</t>
+  </si>
+  <si>
+    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>13358</t>
   </si>
   <si>
@@ -355,12 +439,6 @@
     <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
   </si>
   <si>
-    <t>2010401</t>
-  </si>
-  <si>
-    <t>HUEVO A X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
     <t>VTBQ</t>
   </si>
   <si>
@@ -379,16 +457,220 @@
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
+    <t>VTDOTH</t>
+  </si>
+  <si>
+    <t>BODEGA DOTACION TH TRANSITO</t>
+  </si>
+  <si>
+    <t>DOTA050</t>
+  </si>
+  <si>
+    <t>TOALLA BLANCA 1.20X0.60X320</t>
+  </si>
+  <si>
+    <t>EMES001</t>
+  </si>
+  <si>
+    <t>ESQUINEROS DE CARTON  90X14 CM</t>
+  </si>
+  <si>
+    <t>VTEM03</t>
+  </si>
+  <si>
+    <t>EMPAQUES MEDELLIN TRANSITO</t>
+  </si>
+  <si>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
+  </si>
+  <si>
+    <t>EMET019</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
+  </si>
+  <si>
+    <t>VTEMBO</t>
+  </si>
+  <si>
+    <t>EMPAQUES BOGOTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMET050</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
+  </si>
+  <si>
+    <t>VTEMMO</t>
+  </si>
+  <si>
+    <t>EMPAQUES MONTERIA TRANSITO</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>DOCL001</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA S</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>DOCL003</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOCL005</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ002</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 30</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>DOPJ004</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 34</t>
+  </si>
+  <si>
+    <t>DOPJ005</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 36</t>
+  </si>
+  <si>
+    <t>DOPJ006</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 38</t>
+  </si>
+  <si>
+    <t>EMCA016</t>
+  </si>
+  <si>
+    <t>CAJA ESTÁNDAR NEUTRA</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
+  </si>
+  <si>
+    <t>VTEMT52</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
+  </si>
+  <si>
+    <t>PTET04</t>
+  </si>
+  <si>
+    <t>ETIQUETA PET X 30 L - ACEBRI</t>
+  </si>
+  <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>273001</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO X 30 BANDEJA GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
     <t>13324</t>
   </si>
   <si>
     <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
   </si>
   <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
   </si>
   <si>
     <t>13420</t>
@@ -397,415 +679,133 @@
     <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
   </si>
   <si>
-    <t>VTDOTH</t>
-  </si>
-  <si>
-    <t>BODEGA DOTACION TH TRANSITO</t>
-  </si>
-  <si>
-    <t>DOTA050</t>
-  </si>
-  <si>
-    <t>TOALLA BLANCA 1.20X0.60X320</t>
-  </si>
-  <si>
-    <t>EMES001</t>
-  </si>
-  <si>
-    <t>ESQUINEROS DE CARTON  90X14 CM</t>
-  </si>
-  <si>
-    <t>VTEM03</t>
-  </si>
-  <si>
-    <t>EMPAQUES MEDELLIN TRANSITO</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
-    <t>EMET019</t>
-  </si>
-  <si>
-    <t>ETIQUETA BARRA HUEVO A  X 30 ALKOSTO</t>
-  </si>
-  <si>
-    <t>VTEMBO</t>
-  </si>
-  <si>
-    <t>EMPAQUES BOGOTA TRANSITO</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+    <t>VTLZEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES LANZA TRANSITO</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>PTEM049</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM051</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM052</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>VTME</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTMO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTPALM</t>
+  </si>
+  <si>
+    <t>EGIPTO - INVENTARIO TRANSITO PALMA</t>
+  </si>
+  <si>
+    <t>MA0041</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA AMERICANA</t>
+  </si>
+  <si>
+    <t>VTPBU</t>
+  </si>
+  <si>
+    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>MA0043</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA BOLIVIANA</t>
+  </si>
+  <si>
+    <t>MA0056</t>
+  </si>
+  <si>
+    <t>FRIJOL SOYA AMERICANO CRUDO</t>
+  </si>
+  <si>
+    <t>MI0502</t>
+  </si>
+  <si>
+    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
+  </si>
+  <si>
+    <t>MDKU059</t>
+  </si>
+  <si>
+    <t>KUHL 8864 ELECTROVALVULA 1/2" PARA ENJUAGUE</t>
+  </si>
+  <si>
+    <t>VTPL01</t>
+  </si>
+  <si>
+    <t>ALMACEN - PALMAS TRANSITO</t>
+  </si>
+  <si>
+    <t>MDNU001</t>
+  </si>
+  <si>
+    <t>VIDEOJET NUCLEO DE TINTA PARA IMPRESORA 1620</t>
+  </si>
+  <si>
+    <t>MDSE066</t>
+  </si>
+  <si>
+    <t>CLS-SNV   Z206036  SENS. CABLE M12 90° FEMALE 3P PNP 2LED   Z204970</t>
+  </si>
+  <si>
+    <t>MDZU082</t>
+  </si>
+  <si>
+    <t>13013612 Conjunto rodillo tensor D90 C/eje y pasador A1102</t>
+  </si>
+  <si>
+    <t>VTPL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES PALMAS TRANSITO</t>
   </si>
   <si>
     <t>EMBA006</t>
   </si>
   <si>
     <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
-  </si>
-  <si>
-    <t>EMET015</t>
-  </si>
-  <si>
-    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
-  </si>
-  <si>
-    <t>EMET050</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
-  </si>
-  <si>
-    <t>EMET124</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - FS</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>DOCL001</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA S</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>DOCL003</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOCL005</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA XXL</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ002</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 30</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>DOPJ004</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 34</t>
-  </si>
-  <si>
-    <t>DOPJ005</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 36</t>
-  </si>
-  <si>
-    <t>DOPJ006</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 38</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMCA016</t>
-  </si>
-  <si>
-    <t>CAJA ESTÁNDAR NEUTRA</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>EECA006</t>
-  </si>
-  <si>
-    <t>CAJA REGULAR X300 EMPAQUE PET</t>
-  </si>
-  <si>
-    <t>VTEMT52</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>PTET04</t>
-  </si>
-  <si>
-    <t>ETIQUETA PET X 30 L - ACEBRI</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>273001</t>
-  </si>
-  <si>
-    <t>HUEVO PICADO X 30 BANDEJA GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>VTLZEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES LANZA TRANSITO</t>
-  </si>
-  <si>
-    <t>PTEM029</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>PTEM049</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM051</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM052</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
-  </si>
-  <si>
-    <t>VTME</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VTMO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>MA0041</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA AMERICANA</t>
-  </si>
-  <si>
-    <t>VTPBU</t>
-  </si>
-  <si>
-    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>MA0043</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA BOLIVIANA</t>
-  </si>
-  <si>
-    <t>MA0056</t>
-  </si>
-  <si>
-    <t>FRIJOL SOYA AMERICANO CRUDO</t>
-  </si>
-  <si>
-    <t>MI0502</t>
-  </si>
-  <si>
-    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
-  </si>
-  <si>
-    <t>EPGU006</t>
-  </si>
-  <si>
-    <t>GUANTE VAQUETA TIPO INGENIERO REFORZADO</t>
-  </si>
-  <si>
-    <t>VTPL01</t>
-  </si>
-  <si>
-    <t>ALMACEN - PALMAS TRANSITO</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>EP</t>
-  </si>
-  <si>
-    <t>MDKU059</t>
-  </si>
-  <si>
-    <t>KUHL 8864 ELECTROVALVULA 1/2" PARA ENJUAGUE</t>
-  </si>
-  <si>
-    <t>MDMI010</t>
-  </si>
-  <si>
-    <t>CLS-399180 MODULO IMPRESOR 70 MICRAS</t>
-  </si>
-  <si>
-    <t>MDMO04</t>
-  </si>
-  <si>
-    <t>MODULO DE VÁLVULAS IMPRESORA 1620 REF. 399181</t>
-  </si>
-  <si>
-    <t>MDNU001</t>
-  </si>
-  <si>
-    <t>VIDEOJET NUCLEO DE TINTA PARA IMPRESORA 1620</t>
-  </si>
-  <si>
-    <t>MDSE066</t>
-  </si>
-  <si>
-    <t>CLS-SNV   Z206036  SENS. CABLE M12 90° FEMALE 3P PNP 2LED   Z204970</t>
-  </si>
-  <si>
-    <t>MDTA042</t>
-  </si>
-  <si>
-    <t>TARJETA CPU IMPRESORA 1620 REF. SP392415</t>
-  </si>
-  <si>
-    <t>MDZU082</t>
-  </si>
-  <si>
-    <t>13013612 Conjunto rodillo tensor D90 C/eje y pasador A1102</t>
   </si>
   <si>
     <t>VTPSM</t>
@@ -977,13 +977,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -995,7 +995,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>2533</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="4">
@@ -1009,13 +1009,13 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>1500</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.5458912037</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1027,7 +1027,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1717</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5">
@@ -1041,13 +1041,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>3000</v>
+        <v>1080</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.5458912037</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1059,7 +1059,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>2843</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6">
@@ -1073,13 +1073,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1800</v>
+        <v>6300</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="2">
-        <v>46298.948877314811</v>
+        <v>46299.5458912037</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1091,7 +1091,7 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>1437</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="7">
@@ -1105,13 +1105,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>57600</v>
+        <v>274320</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1123,7 +1123,7 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>885</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="8">
@@ -1137,13 +1137,13 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>23040</v>
+        <v>10560</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -1155,7 +1155,7 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>887</v>
+        <v>861</v>
       </c>
     </row>
     <row r="9">
@@ -1169,13 +1169,13 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>900</v>
+        <v>84480</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1187,7 +1187,7 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>465</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="10">
@@ -1201,93 +1201,91 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>341</v>
+        <v>3960</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2514</v>
+        <v>877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>15840</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="2">
-        <v>46298.984074074069</v>
+        <v>46299.833564814813</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>1759</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>6000</v>
+        <v>2306</v>
       </c>
       <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46300.44798611111</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="2">
-        <v>46299.901064814811</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12"/>
+      <c r="I12">
+        <v>440</v>
+      </c>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>2199</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="13">
@@ -1298,28 +1296,30 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>30000</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46300.44798611111</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="2">
-        <v>46299.901064814811</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13"/>
+      <c r="I13">
+        <v>250</v>
+      </c>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>509</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="14">
@@ -1330,28 +1330,30 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>14769</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46299.833564814813</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="2">
-        <v>46299.901064814811</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14"/>
+      <c r="I14">
+        <v>250</v>
+      </c>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>1471</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="15">
@@ -1362,48 +1364,50 @@
         <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>104940</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2">
-        <v>46299.901064814811</v>
+        <v>46299.76326388889</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15"/>
+        <v>47</v>
+      </c>
+      <c r="I15">
+        <v>5000</v>
+      </c>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2285</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D16">
-        <v>148560</v>
+        <v>6000</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2">
-        <v>46299.902175925927</v>
+        <v>46298.6159375</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -1415,27 +1419,27 @@
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>2082</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
       <c r="D17">
-        <v>3960</v>
+        <v>600</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2">
-        <v>46299.901064814811</v>
+        <v>46295.691284722219</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1447,27 +1451,27 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>823</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>600</v>
+      </c>
+      <c r="E18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>3960</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
-      </c>
       <c r="F18" s="2">
-        <v>46299.901064814811</v>
+        <v>46295.69253472222</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1479,27 +1483,27 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D19">
-        <v>3960</v>
+        <v>126240</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2">
-        <v>46299.901064814811</v>
+        <v>46300.601099537038</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1511,101 +1515,99 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>423</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D20">
-        <v>1392</v>
+        <v>11880</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2">
-        <v>46299.902175925927</v>
+        <v>46299.676678240736</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>3341</v>
+        <v>528</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D21">
-        <v>83</v>
+        <v>592</v>
       </c>
       <c r="E21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46300.601099537038</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="2">
-        <v>46299.901064814811</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
-        <v>36</v>
-      </c>
       <c r="I21">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>2894</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
       <c r="D22">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="2">
+        <v>46300.601099537038</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
         <v>40</v>
-      </c>
-      <c r="F22" s="2">
-        <v>46299.901064814811</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>36</v>
       </c>
       <c r="I22">
         <v>250</v>
@@ -1613,91 +1615,95 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>342</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23">
-        <v>6000</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
       <c r="F23" s="2">
-        <v>46299.833564814813</v>
+        <v>46300.601099537038</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23"/>
+        <v>40</v>
+      </c>
+      <c r="I23">
+        <v>250</v>
+      </c>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>1145</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24">
-        <v>1500</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F24" s="2">
-        <v>46299.5458912037</v>
+        <v>46299.741620370369</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24"/>
+        <v>47</v>
+      </c>
+      <c r="I24">
+        <v>5000</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>1107</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" s="2">
-        <v>46299.5458912037</v>
+        <v>46298.721979166665</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1709,7 +1715,7 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>393</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="26">
@@ -1720,16 +1726,16 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>6300</v>
+        <v>1500</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F26" s="2">
-        <v>46299.5458912037</v>
+        <v>46298.721979166665</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1741,27 +1747,27 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>1082</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27">
-        <v>274320</v>
+        <v>52800</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" s="2">
-        <v>46299.833564814813</v>
+        <v>46298.720150462963</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1773,27 +1779,27 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>2963</v>
+        <v>807</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28">
-        <v>10560</v>
+        <v>307200</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F28" s="2">
-        <v>46299.833564814813</v>
+        <v>46300.578321759254</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -1805,27 +1811,27 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>861</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29">
-        <v>84480</v>
+        <v>11340</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" s="2">
-        <v>46299.833564814813</v>
+        <v>46298.72111111111</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1837,27 +1843,27 @@
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>2437</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D30">
-        <v>3960</v>
+        <v>2448</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" s="2">
-        <v>46299.833564814813</v>
+        <v>46298.72111111111</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1869,27 +1875,27 @@
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>877</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s">
         <v>65</v>
       </c>
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31">
-        <v>15840</v>
+        <v>24840</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F31" s="2">
-        <v>46299.833564814813</v>
+        <v>46298.72111111111</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1901,101 +1907,99 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>1659</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>2052</v>
+        <v>3960</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" s="2">
-        <v>46299.833564814813</v>
+        <v>46300.572638888887</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>4303</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D33">
-        <v>101</v>
+        <v>1740</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33" s="2">
-        <v>46299.833564814813</v>
+        <v>46300.578321759254</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I33">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>3745</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D34">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" s="2">
-        <v>46299.833564814813</v>
+        <v>46300.578321759254</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I34">
         <v>250</v>
@@ -2003,93 +2007,95 @@
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>2543</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D35">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F35" s="2">
-        <v>46299.76326388889</v>
+        <v>46300.578321759254</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="I35">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>2553</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D36">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F36" s="2">
-        <v>46298.6159375</v>
+        <v>46296.614837962959</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36"/>
+        <v>47</v>
+      </c>
+      <c r="I36">
+        <v>5000</v>
+      </c>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>710</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D37">
-        <v>600</v>
+        <v>3960</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F37" s="2">
-        <v>46295.691284722219</v>
+        <v>46298.895787037036</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -2101,27 +2107,27 @@
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D38">
-        <v>600</v>
+        <v>1008</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F38" s="2">
-        <v>46295.69253472222</v>
+        <v>46298.895787037036</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -2133,27 +2139,27 @@
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D39">
-        <v>32760</v>
+        <v>5580</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F39" s="2">
-        <v>46299.46539351852</v>
+        <v>46298.895787037036</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
@@ -2165,59 +2171,61 @@
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>191</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D40">
-        <v>3600</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F40" s="2">
-        <v>46299.381273148145</v>
+        <v>46300.578506944439</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40"/>
+        <v>40</v>
+      </c>
+      <c r="I40">
+        <v>440</v>
+      </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>1350</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D41">
-        <v>1800</v>
+        <v>52800</v>
       </c>
       <c r="E41" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F41" s="2">
-        <v>46299.46539351852</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -2229,27 +2237,27 @@
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>249</v>
+        <v>467</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D42">
-        <v>52800</v>
+        <v>246960</v>
       </c>
       <c r="E42" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F42" s="2">
-        <v>46299.676678240736</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2261,27 +2269,27 @@
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>2108</v>
+        <v>950</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D43">
-        <v>3960</v>
+        <v>900</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F43" s="2">
-        <v>46299.46539351852</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
@@ -2293,155 +2301,163 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>467</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D44">
-        <v>288000</v>
+        <v>1254</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F44" s="2">
-        <v>46299.741620370369</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44"/>
+        <v>40</v>
+      </c>
+      <c r="I44">
+        <v>440</v>
+      </c>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>2808</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D45">
-        <v>3780</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F45" s="2">
-        <v>46299.382152777776</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45"/>
+        <v>40</v>
+      </c>
+      <c r="I45">
+        <v>250</v>
+      </c>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>81</v>
+        <v>892</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D46">
-        <v>1296</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F46" s="2">
-        <v>46299.382152777776</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46"/>
+        <v>40</v>
+      </c>
+      <c r="I46">
+        <v>250</v>
+      </c>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>81</v>
+        <v>677</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D47">
-        <v>9180</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F47" s="2">
-        <v>46299.382152777776</v>
+        <v>46299.781226851846</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47"/>
+        <v>47</v>
+      </c>
+      <c r="I47">
+        <v>5000</v>
+      </c>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>79</v>
+        <v>564</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D48">
-        <v>11880</v>
+        <v>9300</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F48" s="2">
-        <v>46299.676678240736</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
@@ -2453,163 +2469,155 @@
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>528</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D49">
-        <v>1599</v>
+        <v>2400</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F49" s="2">
-        <v>46299.741620370369</v>
+        <v>46299.880509259259</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>3566</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D50">
-        <v>175</v>
+        <v>24000</v>
       </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F50" s="2">
-        <v>46299.741620370369</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>2792</v>
+        <v>4775</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D51">
-        <v>87</v>
+        <v>27000</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F51" s="2">
-        <v>46299.741620370369</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I51">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I51"/>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>2121</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D52">
-        <v>68</v>
+        <v>2894</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F52" s="2">
-        <v>46299.741620370369</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>69</v>
-      </c>
-      <c r="I52">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>2181</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D53">
-        <v>1200</v>
+        <v>52800</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F53" s="2">
-        <v>46298.721979166665</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2621,27 +2629,27 @@
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>1043</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D54">
-        <v>1500</v>
+        <v>21120</v>
       </c>
       <c r="E54" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F54" s="2">
-        <v>46298.721979166665</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
@@ -2653,27 +2661,27 @@
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>1056</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D55">
-        <v>52800</v>
+        <v>7920</v>
       </c>
       <c r="E55" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F55" s="2">
-        <v>46298.720150462963</v>
+        <v>46299.880509259259</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -2685,27 +2693,27 @@
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>807</v>
+        <v>869</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D56">
-        <v>704640</v>
+        <v>10560</v>
       </c>
       <c r="E56" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F56" s="2">
-        <v>46298.720150462963</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
@@ -2717,123 +2725,129 @@
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>3249</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C57" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D57">
-        <v>11340</v>
+        <v>641</v>
       </c>
       <c r="E57" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2">
-        <v>46298.72111111111</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57"/>
+        <v>40</v>
+      </c>
+      <c r="I57">
+        <v>440</v>
+      </c>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>71</v>
+        <v>5561</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D58">
-        <v>2448</v>
+        <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F58" s="2">
-        <v>46298.72111111111</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58"/>
+        <v>40</v>
+      </c>
+      <c r="I58">
+        <v>250</v>
+      </c>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>59</v>
+        <v>4838</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D59">
-        <v>24840</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F59" s="2">
-        <v>46298.72111111111</v>
+        <v>46300.065335648149</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59"/>
+        <v>40</v>
+      </c>
+      <c r="I59">
+        <v>250</v>
+      </c>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>67</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D60">
-        <v>19800</v>
+        <v>1200</v>
       </c>
       <c r="E60" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F60" s="2">
-        <v>46298.720150462963</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -2845,163 +2859,155 @@
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>340</v>
+        <v>841</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D61">
-        <v>3484</v>
+        <v>23760</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F61" s="2">
-        <v>46298.72111111111</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>36</v>
-      </c>
-      <c r="I61">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>4091</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D62">
-        <v>184</v>
+        <v>15840</v>
       </c>
       <c r="E62" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F62" s="2">
-        <v>46298.720150462963</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>3162</v>
+        <v>697</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D63">
-        <v>92</v>
+        <v>10560</v>
       </c>
       <c r="E63" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F63" s="2">
-        <v>46298.720150462963</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>1808</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F64" s="2">
-        <v>46296.614837962959</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>69</v>
-      </c>
-      <c r="I64">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>2153</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D65">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F65" s="2">
-        <v>46298.843263888884</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3013,155 +3019,163 @@
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>596</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D66">
-        <v>600</v>
+        <v>314</v>
       </c>
       <c r="E66" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F66" s="2">
-        <v>46298.843263888884</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66"/>
+        <v>40</v>
+      </c>
+      <c r="I66">
+        <v>440</v>
+      </c>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>333</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D67">
-        <v>6000</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F67" s="2">
-        <v>46298.843263888884</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67"/>
+        <v>40</v>
+      </c>
+      <c r="I67">
+        <v>250</v>
+      </c>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>603</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D68">
-        <v>34560</v>
+        <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F68" s="2">
-        <v>46299.706041666665</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>21</v>
-      </c>
-      <c r="I68"/>
+        <v>40</v>
+      </c>
+      <c r="I68">
+        <v>250</v>
+      </c>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>1123</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D69">
-        <v>211920</v>
+        <v>32</v>
       </c>
       <c r="E69" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F69" s="2">
-        <v>46299.706041666665</v>
+        <v>46299.649583333332</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69"/>
+        <v>47</v>
+      </c>
+      <c r="I69">
+        <v>5000</v>
+      </c>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>1778</v>
+        <v>753</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D70">
-        <v>3960</v>
+        <v>39600</v>
       </c>
       <c r="E70" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F70" s="2">
-        <v>46298.895787037036</v>
+        <v>46300.628067129626</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
@@ -3173,1239 +3187,1273 @@
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>67</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D71">
-        <v>1008</v>
+        <v>220</v>
       </c>
       <c r="E71" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F71" s="2">
-        <v>46298.895787037036</v>
+        <v>46300.628067129626</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71"/>
+        <v>40</v>
+      </c>
+      <c r="I71">
+        <v>440</v>
+      </c>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>51</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" t="s">
         <v>84</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
         <v>85</v>
       </c>
-      <c r="C72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D72">
-        <v>5580</v>
-      </c>
-      <c r="E72" t="s">
-        <v>89</v>
-      </c>
       <c r="F72" s="2">
-        <v>46298.895787037036</v>
+        <v>46300.628067129626</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72"/>
+        <v>40</v>
+      </c>
+      <c r="I72">
+        <v>250</v>
+      </c>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>67</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D73">
-        <v>1087</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F73" s="2">
-        <v>46299.706041666665</v>
+        <v>46300.628067129626</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I73">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>2127</v>
+        <v>405</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D74">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F74" s="2">
-        <v>46299.706041666665</v>
+        <v>46300.628067129626</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I74">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>1760</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75">
+        <v>1000</v>
+      </c>
+      <c r="E75" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="2">
+        <v>46300.341631944444</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
         <v>90</v>
       </c>
-      <c r="D75">
-        <v>52800</v>
-      </c>
-      <c r="E75" t="s">
-        <v>91</v>
-      </c>
-      <c r="F75" s="2">
-        <v>46299.781226851846</v>
-      </c>
-      <c r="G75" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75"/>
+      <c r="I75">
+        <v>350</v>
+      </c>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>467</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D76">
-        <v>246960</v>
+        <v>40320</v>
       </c>
       <c r="E76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F76" s="2">
-        <v>46299.781226851846</v>
+        <v>46300.411122685182</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76"/>
+        <v>93</v>
+      </c>
+      <c r="I76">
+        <v>46340</v>
+      </c>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>950</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D77">
-        <v>900</v>
+        <v>7680</v>
       </c>
       <c r="E77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F77" s="2">
-        <v>46299.781226851846</v>
+        <v>46300.411122685182</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77"/>
+        <v>93</v>
+      </c>
+      <c r="I77">
+        <v>7680</v>
+      </c>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>111</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D78">
-        <v>1254</v>
+        <v>4480</v>
       </c>
       <c r="E78" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F78" s="2">
-        <v>46299.781226851846</v>
+        <v>46300.411122685182</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I78">
-        <v>440</v>
+        <v>14700</v>
       </c>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>1056</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C79" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D79">
-        <v>60</v>
+        <v>4200</v>
       </c>
       <c r="E79" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F79" s="2">
-        <v>46299.781226851846</v>
+        <v>46300.411122685182</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I79">
-        <v>250</v>
+        <v>33600</v>
       </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>892</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F80" s="2">
-        <v>46299.781226851846</v>
+        <v>46300.341631944444</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="H80" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I80">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>677</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D81">
-        <v>32</v>
+        <v>480</v>
       </c>
       <c r="E81" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F81" s="2">
-        <v>46299.781226851846</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>69</v>
-      </c>
-      <c r="I81">
-        <v>5000</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>564</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="C82" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D82">
-        <v>9300</v>
+        <v>480</v>
       </c>
       <c r="E82" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F82" s="2">
-        <v>46300.065335648149</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>3767</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D83">
-        <v>2400</v>
+        <v>720</v>
       </c>
       <c r="E83" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F83" s="2">
-        <v>46299.880509259259</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>2437</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C84" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D84">
-        <v>24000</v>
+        <v>384</v>
       </c>
       <c r="E84" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F84" s="2">
-        <v>46300.065335648149</v>
+        <v>46300.638854166667</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>21</v>
-      </c>
-      <c r="I84"/>
+        <v>40</v>
+      </c>
+      <c r="I84">
+        <v>440</v>
+      </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>4775</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="C85" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D85">
-        <v>27000</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="F85" s="2">
-        <v>46300.065335648149</v>
+        <v>46300.638854166667</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85"/>
+        <v>40</v>
+      </c>
+      <c r="I85">
+        <v>250</v>
+      </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>2184</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D86">
-        <v>2894</v>
+        <v>10500</v>
       </c>
       <c r="E86" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="2">
+        <v>46300.637824074074</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
         <v>93</v>
       </c>
-      <c r="F86" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G86" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" t="s">
-        <v>21</v>
-      </c>
-      <c r="I86"/>
+      <c r="I86">
+        <v>46340</v>
+      </c>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>1663</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C87" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D87">
-        <v>52800</v>
+        <v>7680</v>
       </c>
       <c r="E87" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" s="2">
+        <v>46300.637824074074</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
         <v>93</v>
       </c>
-      <c r="F87" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G87" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87"/>
+      <c r="I87">
+        <v>7680</v>
+      </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>1243</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B88" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D88">
-        <v>21120</v>
+        <v>14700</v>
       </c>
       <c r="E88" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" s="2">
+        <v>46300.637824074074</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
         <v>93</v>
       </c>
-      <c r="F88" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G88" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88"/>
+      <c r="I88">
+        <v>14700</v>
+      </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>2889</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D89">
-        <v>7920</v>
+        <v>21000</v>
       </c>
       <c r="E89" t="s">
+        <v>115</v>
+      </c>
+      <c r="F89" s="2">
+        <v>46300.637824074074</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
         <v>93</v>
       </c>
-      <c r="F89" s="2">
-        <v>46299.880509259259</v>
-      </c>
-      <c r="G89" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89"/>
+      <c r="I89">
+        <v>33600</v>
+      </c>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>869</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C90" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D90">
-        <v>10560</v>
+        <v>100</v>
       </c>
       <c r="E90" t="s">
+        <v>115</v>
+      </c>
+      <c r="F90" s="2">
+        <v>46300.480439814812</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
         <v>93</v>
       </c>
-      <c r="F90" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G90" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90"/>
+      <c r="I90">
+        <v>2000</v>
+      </c>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>1149</v>
+        <v>810</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C91" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D91">
-        <v>641</v>
+        <v>600</v>
       </c>
       <c r="E91" t="s">
+        <v>115</v>
+      </c>
+      <c r="F91" s="2">
+        <v>46300.480439814812</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
         <v>93</v>
       </c>
-      <c r="F91" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G91" t="s">
-        <v>15</v>
-      </c>
-      <c r="H91" t="s">
-        <v>36</v>
-      </c>
       <c r="I91">
-        <v>440</v>
+        <v>244</v>
       </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>5561</v>
+        <v>337</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="C92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D92">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E92" t="s">
+        <v>115</v>
+      </c>
+      <c r="F92" s="2">
+        <v>46300.593298611107</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
         <v>93</v>
       </c>
-      <c r="F92" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G92" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" t="s">
-        <v>36</v>
-      </c>
       <c r="I92">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>4838</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D93">
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="E93" t="s">
+        <v>115</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46300.480439814812</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
         <v>93</v>
       </c>
-      <c r="F93" s="2">
-        <v>46300.065335648149</v>
-      </c>
-      <c r="G93" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" t="s">
-        <v>36</v>
-      </c>
       <c r="I93">
-        <v>250</v>
+        <v>100000</v>
       </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>2753</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D94">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E94" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F94" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.480439814812</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94"/>
+        <v>93</v>
+      </c>
+      <c r="I94">
+        <v>20000</v>
+      </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>841</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D95">
-        <v>23760</v>
+        <v>200</v>
       </c>
       <c r="E95" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F95" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.480439814812</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95"/>
+        <v>93</v>
+      </c>
+      <c r="I95">
+        <v>133</v>
+      </c>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>1203</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D96">
-        <v>15840</v>
+        <v>200</v>
       </c>
       <c r="E96" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F96" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.480439814812</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96"/>
+        <v>93</v>
+      </c>
+      <c r="I96">
+        <v>359</v>
+      </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>697</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="B97" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D97">
-        <v>10560</v>
+        <v>12880</v>
       </c>
       <c r="E97" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F97" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.637824074074</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97"/>
+        <v>93</v>
+      </c>
+      <c r="I97">
+        <v>12880</v>
+      </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>1019</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D98">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F98" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.480439814812</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98"/>
+        <v>134</v>
+      </c>
+      <c r="I98">
+        <v>400</v>
+      </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>431</v>
+        <v>932</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B99" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C99" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D99">
-        <v>1200</v>
+        <v>4565</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="F99" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.401076388887</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99"/>
+        <v>40</v>
+      </c>
+      <c r="I99">
+        <v>440</v>
+      </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>525</v>
+        <v>4398</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="D100">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="E100" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="F100" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.401076388887</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I100">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>1437</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D101">
-        <v>16</v>
+        <v>146304</v>
       </c>
       <c r="E101" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F101" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.372060185182</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>36</v>
-      </c>
-      <c r="I101">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>1147</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="B102" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="C102" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>314400</v>
       </c>
       <c r="E102" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F102" s="2">
-        <v>46299.649583333332</v>
+        <v>46299.651423611111</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>36</v>
-      </c>
-      <c r="I102">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>743</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C103" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D103">
-        <v>32</v>
+        <v>1310</v>
       </c>
       <c r="E103" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F103" s="2">
-        <v>46299.649583333332</v>
+        <v>46300.372060185182</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="I103">
-        <v>5000</v>
+        <v>440</v>
       </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>753</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D104">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="E104" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F104" s="2">
-        <v>46297.4564699074</v>
+        <v>46300.372060185182</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>102</v>
-      </c>
-      <c r="I104"/>
+        <v>40</v>
+      </c>
+      <c r="I104">
+        <v>250</v>
+      </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>6</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D105">
-        <v>480</v>
+        <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F105" s="2">
-        <v>46297.4564699074</v>
+        <v>46299.651423611111</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>102</v>
-      </c>
-      <c r="I105"/>
+        <v>40</v>
+      </c>
+      <c r="I105">
+        <v>250</v>
+      </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>5</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C106" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D106">
-        <v>720</v>
+        <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="F106" s="2">
-        <v>46297.4564699074</v>
+        <v>46300.372060185182</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>102</v>
-      </c>
-      <c r="I106"/>
+        <v>47</v>
+      </c>
+      <c r="I106">
+        <v>5000</v>
+      </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>5</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="D107">
-        <v>128</v>
+        <v>4200</v>
       </c>
       <c r="E107" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F107" s="2">
-        <v>46298.676087962958</v>
+        <v>46296</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>36</v>
-      </c>
-      <c r="I107">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I107"/>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>5775</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D108">
-        <v>219456</v>
+        <v>5400</v>
       </c>
       <c r="E108" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F108" s="2">
-        <v>46299.699629629627</v>
+        <v>46296</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
@@ -4417,27 +4465,27 @@
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>1590</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D109">
-        <v>314400</v>
+        <v>1800</v>
       </c>
       <c r="E109" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F109" s="2">
-        <v>46299.651423611111</v>
+        <v>46298</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
@@ -4449,27 +4497,27 @@
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>1843</v>
+        <v>297</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D110">
-        <v>34775</v>
+        <v>480</v>
       </c>
       <c r="E110" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F110" s="2">
-        <v>46298.790439814809</v>
+        <v>46298</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
@@ -4481,163 +4529,155 @@
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>2705</v>
+        <v>275</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C111" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D111">
-        <v>1455</v>
+        <v>1200</v>
       </c>
       <c r="E111" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F111" s="2">
-        <v>46299.651423611111</v>
+        <v>46296</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>36</v>
-      </c>
-      <c r="I111">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I111"/>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>4442</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C112" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D112">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="E112" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F112" s="2">
-        <v>46299.699629629627</v>
+        <v>46298</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>36</v>
-      </c>
-      <c r="I112">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>4127</v>
+        <v>307</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="C113" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D113">
-        <v>18</v>
+        <v>182304</v>
       </c>
       <c r="E113" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F113" s="2">
-        <v>46299.651423611111</v>
+        <v>46299.643287037034</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>36</v>
-      </c>
-      <c r="I113">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>1488</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="B114" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D114">
-        <v>38</v>
+        <v>274560</v>
       </c>
       <c r="E114" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="F114" s="2">
-        <v>46299.651423611111</v>
+        <v>46299.670335648145</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>69</v>
-      </c>
-      <c r="I114">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I114"/>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>2600</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="C115" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D115">
-        <v>4200</v>
+        <v>583148</v>
       </c>
       <c r="E115" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F115" s="2">
-        <v>46296</v>
+        <v>46299.891226851847</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
@@ -4649,27 +4689,27 @@
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>1364</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B116" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D116">
-        <v>5400</v>
+        <v>47905</v>
       </c>
       <c r="E116" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F116" s="2">
-        <v>46296</v>
+        <v>46299.892199074071</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
@@ -4681,27 +4721,27 @@
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>1370</v>
+        <v>998</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="B117" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="C117" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D117">
-        <v>1800</v>
+        <v>126960</v>
       </c>
       <c r="E117" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F117" s="2">
-        <v>46298</v>
+        <v>46298.854942129627</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
@@ -4713,515 +4753,537 @@
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>297</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B118" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C118" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D118">
-        <v>480</v>
+        <v>4303</v>
       </c>
       <c r="E118" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F118" s="2">
-        <v>46298</v>
+        <v>46299.892199074071</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>21</v>
-      </c>
-      <c r="I118"/>
+        <v>40</v>
+      </c>
+      <c r="I118">
+        <v>440</v>
+      </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>275</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C119" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D119">
-        <v>1200</v>
+        <v>198</v>
       </c>
       <c r="E119" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F119" s="2">
-        <v>46296</v>
+        <v>46299.891226851847</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>21</v>
-      </c>
-      <c r="I119"/>
+        <v>40</v>
+      </c>
+      <c r="I119">
+        <v>250</v>
+      </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>13</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B120" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C120" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D120">
-        <v>900</v>
+        <v>97</v>
       </c>
       <c r="E120" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F120" s="2">
-        <v>46298</v>
+        <v>46299.891226851847</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>21</v>
-      </c>
-      <c r="I120"/>
+        <v>40</v>
+      </c>
+      <c r="I120">
+        <v>250</v>
+      </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>307</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="D121">
-        <v>182304</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="F121" s="2">
-        <v>46299.643287037034</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>21</v>
-      </c>
-      <c r="I121"/>
+        <v>16</v>
+      </c>
+      <c r="I121">
+        <v>130</v>
+      </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>1874</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="B122" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="D122">
-        <v>274560</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="F122" s="2">
-        <v>46299.670335648145</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>21</v>
-      </c>
-      <c r="I122"/>
+        <v>16</v>
+      </c>
+      <c r="I122">
+        <v>200</v>
+      </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>1387</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="C123" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="D123">
-        <v>583148</v>
+        <v>600</v>
       </c>
       <c r="E123" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F123" s="2">
-        <v>46299.891226851847</v>
+        <v>46287.95758101852</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>21</v>
-      </c>
-      <c r="I123"/>
+        <v>93</v>
+      </c>
+      <c r="I123">
+        <v>660</v>
+      </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>5250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="B124" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="C124" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="D124">
-        <v>47905</v>
+        <v>3920</v>
       </c>
       <c r="E124" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F124" s="2">
-        <v>46299.892199074071</v>
+        <v>46300.103761574072</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>21</v>
-      </c>
-      <c r="I124"/>
+        <v>93</v>
+      </c>
+      <c r="I124">
+        <v>28000</v>
+      </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>998</v>
+        <v>655</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="D125">
-        <v>126960</v>
+        <v>850</v>
       </c>
       <c r="E125" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="F125" s="2">
-        <v>46298.854942129627</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>21</v>
-      </c>
-      <c r="I125"/>
+        <v>163</v>
+      </c>
+      <c r="I125">
+        <v>5000</v>
+      </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>155</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="D126">
-        <v>4303</v>
+        <v>980</v>
       </c>
       <c r="E126" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F126" s="2">
-        <v>46299.892199074071</v>
+        <v>46300.594560185185</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I126">
-        <v>440</v>
+        <v>46340</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>9264</v>
+        <v>930</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="D127">
-        <v>198</v>
+        <v>16000</v>
       </c>
       <c r="E127" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="F127" s="2">
-        <v>46299.891226851847</v>
+        <v>46300.340590277774</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I127">
-        <v>250</v>
+        <v>50000</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>6520</v>
+        <v>43</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="B128" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="C128" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="D128">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="E128" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="F128" s="2">
-        <v>46299.891226851847</v>
+        <v>46299.792754629627</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I128">
-        <v>250</v>
+        <v>660</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>5286</v>
+        <v>180</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D129">
-        <v>900</v>
+        <v>352</v>
       </c>
       <c r="E129" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="F129" s="2">
-        <v>46299.76829861111</v>
+        <v>46299.792754629627</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>21</v>
-      </c>
-      <c r="I129"/>
+        <v>93</v>
+      </c>
+      <c r="I129">
+        <v>359</v>
+      </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>1047</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D130">
-        <v>1152</v>
+        <v>2599</v>
       </c>
       <c r="E130" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="F130" s="2">
-        <v>46299.76829861111</v>
+        <v>46299.792754629627</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>21</v>
-      </c>
-      <c r="I130"/>
+        <v>93</v>
+      </c>
+      <c r="I130">
+        <v>12880</v>
+      </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>1170</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="C131" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D131">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="E131" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="F131" s="2">
-        <v>46300.213819444441</v>
+        <v>46299.792754629627</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>21</v>
-      </c>
-      <c r="I131"/>
+        <v>93</v>
+      </c>
+      <c r="I131">
+        <v>28000</v>
+      </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>1499</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="C132" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="D132">
-        <v>9</v>
+        <v>400</v>
       </c>
       <c r="E132" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="F132" s="2">
-        <v>46290.555405092593</v>
+        <v>45185</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="I132">
-        <v>130</v>
+        <v>359</v>
       </c>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="C133" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D133">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="F133" s="2">
-        <v>46290.555405092593</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
@@ -5230,542 +5292,542 @@
         <v>16</v>
       </c>
       <c r="I133">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="C134" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="D134">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="F134" s="2">
-        <v>46287.95758101852</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I134">
-        <v>660</v>
+        <v>50</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>160</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="C135" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="D135">
-        <v>3920</v>
+        <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="F135" s="2">
-        <v>46300.103761574072</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I135">
-        <v>4480</v>
+        <v>36</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>655</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C136" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="D136">
-        <v>850</v>
+        <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F136" s="2">
-        <v>46295.8800462963</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="I136">
-        <v>5000</v>
+        <v>8</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="C137" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D137">
-        <v>2380</v>
+        <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F137" s="2">
-        <v>46300.3178587963</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I137">
-        <v>32480</v>
+        <v>43</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>929</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="B138" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="C138" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D138">
-        <v>2800</v>
+        <v>2</v>
       </c>
       <c r="E138" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F138" s="2">
-        <v>46300.3178587963</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I138">
-        <v>17920</v>
+        <v>22</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>282</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="C139" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D139">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F139" s="2">
-        <v>46300.3178587963</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I139">
-        <v>1440</v>
+        <v>15</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>183</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="B140" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D140">
-        <v>20000</v>
+        <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F140" s="2">
-        <v>46298.270462962959</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I140">
-        <v>90000</v>
+        <v>22</v>
       </c>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>140</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C141" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D141">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F141" s="2">
-        <v>46300.340590277774</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I141">
-        <v>50000</v>
+        <v>5</v>
       </c>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="C142" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="D142">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="F142" s="2">
-        <v>46298.004571759258</v>
+        <v>46273.306030092594</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="I142">
-        <v>10000</v>
+        <v>4</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="B143" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="C143" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D143">
-        <v>200</v>
+        <v>4340</v>
       </c>
       <c r="E143" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F143" s="2">
-        <v>46299.792754629627</v>
+        <v>46297.862581018519</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="I143">
-        <v>660</v>
+        <v>14700</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>180</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D144">
-        <v>352</v>
+        <v>120</v>
       </c>
       <c r="E144" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F144" s="2">
-        <v>46299.792754629627</v>
+        <v>46293</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="I144">
-        <v>359</v>
+        <v>5000</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="B145" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="C145" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D145">
-        <v>2599</v>
+        <v>600</v>
       </c>
       <c r="E145" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F145" s="2">
-        <v>46299.792754629627</v>
+        <v>46293</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="I145">
-        <v>8960</v>
+        <v>8000</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>267</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="B146" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C146" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D146">
-        <v>1400</v>
+        <v>30000</v>
       </c>
       <c r="E146" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F146" s="2">
-        <v>46299.792754629627</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="I146">
-        <v>4480</v>
+        <v>220000</v>
       </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>155</v>
+        <v>102</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D147">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E147" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="F147" s="2">
-        <v>45185</v>
+        <v>46297.650706018518</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I147">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="B148" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="C148" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="E148" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="F148" s="2">
-        <v>46273.306030092594</v>
+        <v>46298.789583333331</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="I148">
-        <v>25</v>
+        <v>200000</v>
       </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C149" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F149" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
@@ -5779,27 +5841,27 @@
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B150" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F150" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
@@ -5808,32 +5870,32 @@
         <v>16</v>
       </c>
       <c r="I150">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B151" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C151" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F151" s="2">
-        <v>46273.306030092594</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
@@ -5842,276 +5904,274 @@
         <v>16</v>
       </c>
       <c r="I151">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="B152" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="C152" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>2280</v>
       </c>
       <c r="E152" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F152" s="2">
-        <v>46273.306030092594</v>
+        <v>46298</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>16</v>
-      </c>
-      <c r="I152">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I152"/>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>7151</v>
       </c>
       <c r="E153" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F153" s="2">
-        <v>46273.306030092594</v>
+        <v>46300.417303240742</v>
       </c>
       <c r="G153" t="s">
         <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I153">
-        <v>2</v>
+        <v>440</v>
       </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>16</v>
+        <v>11329</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="B154" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="E154" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F154" s="2">
-        <v>46273.306030092594</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I154">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="B155" t="s">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="C155" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="E155" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F155" s="2">
-        <v>46273.306030092594</v>
+        <v>46300.417303240742</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I155">
-        <v>88</v>
+        <v>250</v>
       </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>21</v>
+        <v>8975</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="B156" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E156" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F156" s="2">
-        <v>46273.306030092594</v>
+        <v>46300.417303240742</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I156">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>20</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="E157" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F157" s="2">
-        <v>46273.306030092594</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
+        <v>214</v>
+      </c>
+      <c r="I157">
         <v>16</v>
-      </c>
-      <c r="I157">
-        <v>2</v>
       </c>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="B158" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C158" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D158">
-        <v>4340</v>
+        <v>55</v>
       </c>
       <c r="E158" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F158" s="2">
-        <v>46297.862581018519</v>
+        <v>44426</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="I158">
-        <v>44800</v>
+        <v>2</v>
       </c>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>259</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B159" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="C159" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="D159">
-        <v>120</v>
+        <v>519</v>
       </c>
       <c r="E159" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F159" s="2">
-        <v>46293</v>
+        <v>46297.423749999994</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="I159">
         <v>5000</v>
@@ -6119,499 +6179,493 @@
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>168</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B160" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C160" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="D160">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E160" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="F160" s="2">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>137</v>
-      </c>
-      <c r="I160">
-        <v>8000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I160"/>
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>196</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="B161" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C161" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="D161">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="E161" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="F161" s="2">
-        <v>46280.943472222221</v>
+        <v>46298.78020833333</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
       </c>
       <c r="H161" t="s">
-        <v>137</v>
-      </c>
-      <c r="I161">
-        <v>100000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I161"/>
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>102</v>
+        <v>573</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="B162" t="s">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c r="C162" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="D162">
-        <v>300</v>
+        <v>665</v>
       </c>
       <c r="E162" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F162" s="2">
-        <v>46297.650706018518</v>
+        <v>46298.761041666665</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
       </c>
       <c r="H162" t="s">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="I162">
-        <v>875</v>
+        <v>440</v>
       </c>
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>28</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="B163" t="s">
-        <v>203</v>
+        <v>42</v>
       </c>
       <c r="C163" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="D163">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E163" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F163" s="2">
-        <v>46298.789583333331</v>
+        <v>46297.765023148146</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="I163">
-        <v>200000</v>
+        <v>250</v>
       </c>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>171</v>
+        <v>45</v>
       </c>
       <c r="B164" t="s">
-        <v>172</v>
+        <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E164" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F164" s="2">
-        <v>46265.788981481477</v>
+        <v>46297.7596412037</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I164">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>14</v>
+        <v>61</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="B165" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="C165" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>35840</v>
       </c>
       <c r="E165" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F165" s="2">
-        <v>46265.776967592588</v>
+        <v>46300.637245370366</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="I165">
-        <v>43</v>
+        <v>46340</v>
       </c>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>11</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="B166" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="C166" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>12600</v>
       </c>
       <c r="E166" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F166" s="2">
-        <v>46265.788981481477</v>
+        <v>46300.637245370366</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
       </c>
       <c r="H166" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="I166">
-        <v>15</v>
+        <v>33600</v>
       </c>
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>19</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="B167" t="s">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="C167" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D167">
-        <v>2280</v>
+        <v>1380</v>
       </c>
       <c r="E167" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F167" s="2">
-        <v>46298</v>
+        <v>46300.329861111109</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
       </c>
       <c r="H167" t="s">
-        <v>21</v>
-      </c>
-      <c r="I167"/>
+        <v>93</v>
+      </c>
+      <c r="I167">
+        <v>660</v>
+      </c>
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>83</v>
+        <v>27</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="C168" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D168">
-        <v>1322</v>
+        <v>400</v>
       </c>
       <c r="E168" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F168" s="2">
-        <v>46298.924513888887</v>
+        <v>46300.34469907407</v>
       </c>
       <c r="G168" t="s">
         <v>15</v>
       </c>
       <c r="H168" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I168">
-        <v>440</v>
+        <v>50000</v>
       </c>
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>11325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B169" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C169" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D169">
-        <v>186</v>
+        <v>20000</v>
       </c>
       <c r="E169" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F169" s="2">
-        <v>44946.553055555552</v>
+        <v>46300.667465277773</v>
       </c>
       <c r="G169" t="s">
         <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I169">
-        <v>20</v>
+        <v>220000</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>2</v>
+        <v>999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B170" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C170" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D170">
-        <v>93</v>
+        <v>4800</v>
       </c>
       <c r="E170" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F170" s="2">
-        <v>45777.752291666664</v>
+        <v>46300.34469907407</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="I170">
-        <v>16</v>
+        <v>57600</v>
       </c>
       <c r="J170"/>
       <c r="K170"/>
       <c r="L170">
-        <v>7</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B171" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C171" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D171">
-        <v>55</v>
+        <v>6000</v>
       </c>
       <c r="E171" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F171" s="2">
-        <v>44426</v>
+        <v>46300.34469907407</v>
       </c>
       <c r="G171" t="s">
         <v>15</v>
       </c>
       <c r="H171" t="s">
-        <v>69</v>
-      </c>
-      <c r="I171">
-        <v>2</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="I171"/>
       <c r="J171"/>
       <c r="K171"/>
       <c r="L171">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>67</v>
+        <v>230</v>
       </c>
       <c r="B172" t="s">
-        <v>68</v>
+        <v>231</v>
       </c>
       <c r="C172" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D172">
-        <v>519</v>
+        <v>4800</v>
       </c>
       <c r="E172" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F172" s="2">
-        <v>46297.423749999994</v>
+        <v>46300.34469907407</v>
       </c>
       <c r="G172" t="s">
         <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>69</v>
-      </c>
-      <c r="I172">
-        <v>5000</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="I172"/>
       <c r="J172"/>
       <c r="K172"/>
       <c r="L172">
-        <v>2519</v>
+        <v>156</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="B173" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
       <c r="C173" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D173">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E173" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F173" s="2">
-        <v>46298</v>
+        <v>46300.34469907407</v>
       </c>
       <c r="G173" t="s">
         <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="I173"/>
       <c r="J173"/>
       <c r="K173"/>
       <c r="L173">
-        <v>450</v>
+        <v>95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="B174" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C174" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D174">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="E174" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F174" s="2">
-        <v>46298.78020833333</v>
+        <v>46298.447638888887</v>
       </c>
       <c r="G174" t="s">
         <v>15</v>
@@ -6623,495 +6677,501 @@
       <c r="J174"/>
       <c r="K174"/>
       <c r="L174">
-        <v>573</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="B175" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="C175" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D175">
-        <v>665</v>
+        <v>182880</v>
       </c>
       <c r="E175" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F175" s="2">
-        <v>46298.761041666665</v>
+        <v>46300.102696759255</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>36</v>
-      </c>
-      <c r="I175">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I175"/>
       <c r="J175"/>
       <c r="K175"/>
       <c r="L175">
-        <v>175</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="C176" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D176">
-        <v>37</v>
+        <v>134400</v>
       </c>
       <c r="E176" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F176" s="2">
-        <v>46297.765023148146</v>
+        <v>46300.050983796296</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>36</v>
-      </c>
-      <c r="I176">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I176"/>
       <c r="J176"/>
       <c r="K176"/>
       <c r="L176">
-        <v>104</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="B177" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="C177" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D177">
-        <v>22</v>
+        <v>282240</v>
       </c>
       <c r="E177" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F177" s="2">
-        <v>46297.7596412037</v>
+        <v>46300.102696759255</v>
       </c>
       <c r="G177" t="s">
         <v>15</v>
       </c>
       <c r="H177" t="s">
-        <v>69</v>
-      </c>
-      <c r="I177">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I177"/>
       <c r="J177"/>
       <c r="K177"/>
       <c r="L177">
-        <v>61</v>
+        <v>293</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="B178" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="C178" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D178">
-        <v>1380</v>
+        <v>1736</v>
       </c>
       <c r="E178" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F178" s="2">
-        <v>46300.329861111109</v>
+        <v>46300.102696759255</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
       </c>
       <c r="H178" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="I178">
-        <v>660</v>
+        <v>440</v>
       </c>
       <c r="J178"/>
       <c r="K178"/>
       <c r="L178">
-        <v>27</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="B179" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D179">
-        <v>400</v>
+        <v>109</v>
       </c>
       <c r="E179" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F179" s="2">
-        <v>46300.34469907407</v>
+        <v>46300.102696759255</v>
       </c>
       <c r="G179" t="s">
         <v>15</v>
       </c>
       <c r="H179" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="I179">
-        <v>50000</v>
+        <v>250</v>
       </c>
       <c r="J179"/>
       <c r="K179"/>
       <c r="L179">
-        <v>335</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="B180" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="C180" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D180">
-        <v>4800</v>
+        <v>42</v>
       </c>
       <c r="E180" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F180" s="2">
-        <v>46300.34469907407</v>
+        <v>46300.050983796296</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
       </c>
       <c r="H180" t="s">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="I180">
-        <v>57600</v>
+        <v>250</v>
       </c>
       <c r="J180"/>
       <c r="K180"/>
       <c r="L180">
-        <v>1222</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>224</v>
+        <v>45</v>
       </c>
       <c r="B181" t="s">
-        <v>225</v>
+        <v>46</v>
       </c>
       <c r="C181" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D181">
-        <v>6000</v>
+        <v>168</v>
       </c>
       <c r="E181" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F181" s="2">
-        <v>46300.34469907407</v>
+        <v>46300.050983796296</v>
       </c>
       <c r="G181" t="s">
         <v>15</v>
       </c>
       <c r="H181" t="s">
-        <v>223</v>
-      </c>
-      <c r="I181"/>
+        <v>47</v>
+      </c>
+      <c r="I181">
+        <v>5000</v>
+      </c>
       <c r="J181"/>
       <c r="K181"/>
       <c r="L181">
-        <v>151</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>226</v>
+        <v>147</v>
       </c>
       <c r="B182" t="s">
-        <v>227</v>
+        <v>148</v>
       </c>
       <c r="C182" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D182">
-        <v>4800</v>
+        <v>98400</v>
       </c>
       <c r="E182" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F182" s="2">
-        <v>46300.34469907407</v>
+        <v>46299.782349537032</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
       </c>
       <c r="H182" t="s">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="I182"/>
       <c r="J182"/>
       <c r="K182"/>
       <c r="L182">
-        <v>156</v>
+        <v>67</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="B183" t="s">
-        <v>229</v>
+        <v>39</v>
       </c>
       <c r="C183" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D183">
-        <v>900</v>
+        <v>410</v>
       </c>
       <c r="E183" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F183" s="2">
-        <v>46300.34469907407</v>
+        <v>46299.782349537032</v>
       </c>
       <c r="G183" t="s">
         <v>15</v>
       </c>
       <c r="H183" t="s">
-        <v>223</v>
-      </c>
-      <c r="I183"/>
+        <v>40</v>
+      </c>
+      <c r="I183">
+        <v>440</v>
+      </c>
       <c r="J183"/>
       <c r="K183"/>
       <c r="L183">
-        <v>95</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B184" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C184" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D184">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E184" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F184" s="2">
-        <v>46298.447638888887</v>
+        <v>46299.782349537032</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
       </c>
       <c r="H184" t="s">
-        <v>21</v>
-      </c>
-      <c r="I184"/>
+        <v>40</v>
+      </c>
+      <c r="I184">
+        <v>250</v>
+      </c>
       <c r="J184"/>
       <c r="K184"/>
       <c r="L184">
-        <v>1691</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="B185" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="C185" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D185">
-        <v>182880</v>
+        <v>8</v>
       </c>
       <c r="E185" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F185" s="2">
-        <v>46300.102696759255</v>
+        <v>46299.782349537032</v>
       </c>
       <c r="G185" t="s">
         <v>15</v>
       </c>
       <c r="H185" t="s">
-        <v>21</v>
-      </c>
-      <c r="I185"/>
+        <v>40</v>
+      </c>
+      <c r="I185">
+        <v>250</v>
+      </c>
       <c r="J185"/>
       <c r="K185"/>
       <c r="L185">
-        <v>2449</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="B186" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="C186" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D186">
-        <v>134400</v>
+        <v>32</v>
       </c>
       <c r="E186" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F186" s="2">
-        <v>46300.050983796296</v>
+        <v>46299.782349537032</v>
       </c>
       <c r="G186" t="s">
         <v>15</v>
       </c>
       <c r="H186" t="s">
-        <v>21</v>
-      </c>
-      <c r="I186"/>
+        <v>47</v>
+      </c>
+      <c r="I186">
+        <v>5000</v>
+      </c>
       <c r="J186"/>
       <c r="K186"/>
       <c r="L186">
-        <v>1861</v>
+        <v>780</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="B187" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="C187" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D187">
-        <v>282240</v>
+        <v>3556</v>
       </c>
       <c r="E187" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F187" s="2">
-        <v>46300.102696759255</v>
+        <v>46300.398298611108</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
       </c>
       <c r="H187" t="s">
-        <v>21</v>
-      </c>
-      <c r="I187"/>
+        <v>40</v>
+      </c>
+      <c r="I187">
+        <v>440</v>
+      </c>
       <c r="J187"/>
       <c r="K187"/>
       <c r="L187">
-        <v>293</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D188">
-        <v>1736</v>
+        <v>156</v>
       </c>
       <c r="E188" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F188" s="2">
-        <v>46300.102696759255</v>
+        <v>46300.398298611108</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
       </c>
       <c r="H188" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I188">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J188"/>
       <c r="K188"/>
       <c r="L188">
-        <v>5110</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C189" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D189">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E189" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F189" s="2">
-        <v>46300.102696759255</v>
+        <v>46300.398298611108</v>
       </c>
       <c r="G189" t="s">
         <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I189">
         <v>250</v>
@@ -7119,659 +7179,661 @@
       <c r="J189"/>
       <c r="K189"/>
       <c r="L189">
-        <v>4506</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="C190" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D190">
-        <v>42</v>
+        <v>2439100</v>
       </c>
       <c r="E190" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F190" s="2">
-        <v>46300.050983796296</v>
+        <v>46266</v>
       </c>
       <c r="G190" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="H190" t="s">
-        <v>36</v>
+        <v>245</v>
       </c>
       <c r="I190">
-        <v>250</v>
+        <v>950000</v>
       </c>
       <c r="J190"/>
       <c r="K190"/>
       <c r="L190">
-        <v>2574</v>
+        <v>56</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>67</v>
+        <v>246</v>
       </c>
       <c r="B191" t="s">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="C191" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D191">
-        <v>168</v>
+        <v>2530000</v>
       </c>
       <c r="E191" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F191" s="2">
-        <v>46300.050983796296</v>
+        <v>46266</v>
       </c>
       <c r="G191" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="H191" t="s">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c r="I191">
-        <v>5000</v>
+        <v>1265000</v>
       </c>
       <c r="J191"/>
       <c r="K191"/>
       <c r="L191">
-        <v>2661</v>
+        <v>48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="B192" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="C192" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D192">
-        <v>98400</v>
+        <v>750000</v>
       </c>
       <c r="E192" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F192" s="2">
-        <v>46299.782349537032</v>
+        <v>46266</v>
       </c>
       <c r="G192" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="H192" t="s">
-        <v>21</v>
-      </c>
-      <c r="I192"/>
+        <v>245</v>
+      </c>
+      <c r="I192">
+        <v>750000</v>
+      </c>
       <c r="J192"/>
       <c r="K192"/>
       <c r="L192">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>34</v>
+        <v>250</v>
       </c>
       <c r="B193" t="s">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="C193" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D193">
-        <v>410</v>
+        <v>52000</v>
       </c>
       <c r="E193" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F193" s="2">
-        <v>46299.782349537032</v>
+        <v>46294</v>
       </c>
       <c r="G193" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="H193" t="s">
-        <v>36</v>
+        <v>245</v>
       </c>
       <c r="I193">
-        <v>440</v>
+        <v>26000</v>
       </c>
       <c r="J193"/>
       <c r="K193"/>
       <c r="L193">
-        <v>1618</v>
+        <v>56</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="B194" t="s">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="C194" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D194">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="F194" s="2">
-        <v>46299.782349537032</v>
+        <v>46293.599965277775</v>
       </c>
       <c r="G194" t="s">
         <v>15</v>
       </c>
       <c r="H194" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I194">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="J194"/>
       <c r="K194"/>
       <c r="L194">
-        <v>1186</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>53</v>
+        <v>256</v>
       </c>
       <c r="B195" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
       <c r="C195" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D195">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="F195" s="2">
-        <v>46299.782349537032</v>
+        <v>46297.708645833329</v>
       </c>
       <c r="G195" t="s">
         <v>15</v>
       </c>
       <c r="H195" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I195">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="J195"/>
       <c r="K195"/>
       <c r="L195">
-        <v>1057</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="B196" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D196">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="F196" s="2">
-        <v>46299.782349537032</v>
+        <v>46297.708645833329</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="I196">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="J196"/>
       <c r="K196"/>
       <c r="L196">
-        <v>780</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B197" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C197" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D197">
-        <v>2439100</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F197" s="2">
-        <v>46266</v>
+        <v>46293.594282407408</v>
       </c>
       <c r="G197" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="H197" t="s">
-        <v>239</v>
+        <v>47</v>
       </c>
       <c r="I197">
-        <v>950000</v>
+        <v>16</v>
       </c>
       <c r="J197"/>
       <c r="K197"/>
       <c r="L197">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>240</v>
+        <v>91</v>
       </c>
       <c r="B198" t="s">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="C198" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="D198">
-        <v>2530000</v>
+        <v>13440</v>
       </c>
       <c r="E198" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="F198" s="2">
-        <v>46266</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G198" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="H198" t="s">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="I198">
-        <v>1265000</v>
+        <v>46340</v>
       </c>
       <c r="J198"/>
       <c r="K198"/>
       <c r="L198">
-        <v>48</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="B199" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C199" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="D199">
-        <v>750000</v>
+        <v>13440</v>
       </c>
       <c r="E199" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="F199" s="2">
-        <v>46266</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G199" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="H199" t="s">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="I199">
-        <v>750000</v>
+        <v>3920</v>
       </c>
       <c r="J199"/>
       <c r="K199"/>
       <c r="L199">
-        <v>45</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="B200" t="s">
-        <v>245</v>
+        <v>95</v>
       </c>
       <c r="C200" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="D200">
-        <v>52000</v>
+        <v>7680</v>
       </c>
       <c r="E200" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="F200" s="2">
-        <v>46294</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G200" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="H200" t="s">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="I200">
-        <v>26000</v>
+        <v>7680</v>
       </c>
       <c r="J200"/>
       <c r="K200"/>
       <c r="L200">
-        <v>56</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>246</v>
+        <v>96</v>
       </c>
       <c r="B201" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="C201" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D201">
-        <v>50</v>
+        <v>4480</v>
       </c>
       <c r="E201" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F201" s="2">
-        <v>46295.485300925924</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G201" t="s">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="H201" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="I201">
-        <v>50</v>
+        <v>14700</v>
       </c>
       <c r="J201"/>
       <c r="K201"/>
       <c r="L201">
-        <v>1</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>252</v>
+        <v>98</v>
       </c>
       <c r="B202" t="s">
-        <v>253</v>
+        <v>99</v>
       </c>
       <c r="C202" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>12600</v>
       </c>
       <c r="E202" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F202" s="2">
-        <v>46293.599965277775</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G202" t="s">
         <v>15</v>
       </c>
       <c r="H202" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I202">
-        <v>1</v>
+        <v>33600</v>
       </c>
       <c r="J202"/>
       <c r="K202"/>
       <c r="L202">
-        <v>1</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>254</v>
+        <v>118</v>
       </c>
       <c r="B203" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="C203" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D203">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="E203" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F203" s="2">
-        <v>46293.600868055553</v>
+        <v>46300.399675925924</v>
       </c>
       <c r="G203" t="s">
         <v>15</v>
       </c>
       <c r="H203" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I203">
-        <v>2</v>
+        <v>244</v>
       </c>
       <c r="J203"/>
       <c r="K203"/>
       <c r="L203">
-        <v>2</v>
+        <v>362</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="B204" t="s">
-        <v>257</v>
+        <v>123</v>
       </c>
       <c r="C204" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>15000</v>
       </c>
       <c r="E204" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F204" s="2">
-        <v>46293.600868055553</v>
+        <v>46300.399675925924</v>
       </c>
       <c r="G204" t="s">
         <v>15</v>
       </c>
       <c r="H204" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I204">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="J204"/>
       <c r="K204"/>
       <c r="L204">
-        <v>1</v>
+        <v>976</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="B205" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
       <c r="C205" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>50000</v>
       </c>
       <c r="E205" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F205" s="2">
-        <v>46297.708645833329</v>
+        <v>46300.399675925924</v>
       </c>
       <c r="G205" t="s">
         <v>15</v>
       </c>
       <c r="H205" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I205">
-        <v>1</v>
+        <v>220000</v>
       </c>
       <c r="J205"/>
       <c r="K205"/>
       <c r="L205">
-        <v>1</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="B206" t="s">
-        <v>261</v>
+        <v>131</v>
       </c>
       <c r="C206" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>4480</v>
       </c>
       <c r="E206" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F206" s="2">
-        <v>46297.708645833329</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G206" t="s">
         <v>15</v>
       </c>
       <c r="H206" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I206">
-        <v>1</v>
+        <v>12880</v>
       </c>
       <c r="J206"/>
       <c r="K206"/>
       <c r="L206">
-        <v>1</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
+        <v>157</v>
+      </c>
+      <c r="B207" t="s">
+        <v>158</v>
+      </c>
+      <c r="C207" t="s">
         <v>262</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207">
+        <v>4480</v>
+      </c>
+      <c r="E207" t="s">
         <v>263</v>
       </c>
-      <c r="C207" t="s">
-        <v>248</v>
-      </c>
-      <c r="D207">
-        <v>1</v>
-      </c>
-      <c r="E207" t="s">
-        <v>249</v>
-      </c>
       <c r="F207" s="2">
-        <v>46293.600868055553</v>
+        <v>46300.414583333331</v>
       </c>
       <c r="G207" t="s">
         <v>15</v>
       </c>
       <c r="H207" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I207">
-        <v>1</v>
+        <v>28000</v>
       </c>
       <c r="J207"/>
       <c r="K207"/>
       <c r="L207">
-        <v>1</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="B208" t="s">
-        <v>265</v>
+        <v>101</v>
       </c>
       <c r="C208" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E208" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F208" s="2">
-        <v>46293.594282407408</v>
+        <v>46300.399675925924</v>
       </c>
       <c r="G208" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="H208" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I208">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="J208"/>
       <c r="K208"/>
       <c r="L208">
-        <v>1</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B209" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C209" t="s">
         <v>266</v>
@@ -7786,10 +7848,10 @@
         <v>46266</v>
       </c>
       <c r="G209" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H209" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="I209">
         <v>26000</v>
@@ -7852,7 +7914,7 @@
         <v>46296.511597222219</v>
       </c>
       <c r="G211" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H211" t="s">
         <v>276</v>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="Re28694263e944667"/>
+    <sheet name="Inventarios" sheetId="1" r:id="Rd99dc67ee8334c4f"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="282" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -61,6 +61,96 @@
     <t>DO</t>
   </si>
   <si>
+    <t>110303</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE AMARRADO</t>
+  </si>
+  <si>
+    <t>VT1</t>
+  </si>
+  <si>
+    <t>TAT BUCARAMANGA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>112357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>13459</t>
+  </si>
+  <si>
+    <t>HUEVO A X 300 BANDEJA GRIS ALAT CAJA AMARRADO</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>2110327</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>2110427</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>VT2</t>
+  </si>
+  <si>
+    <t>TAT CALI - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>114357</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>112268</t>
   </si>
   <si>
@@ -73,39 +163,12 @@
     <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>HU</t>
-  </si>
-  <si>
     <t>112271</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
     <t>2010102</t>
   </si>
   <si>
@@ -130,6 +193,57 @@
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>110316</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
+    <t>152281</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PAGUE 14 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152381</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PAGUE 11 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>152382</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PAGUE 28 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>VT4</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>2110317</t>
   </si>
   <si>
@@ -142,82 +256,40 @@
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>VT4</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>112357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
-    <t>2110403</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
     <t>2152388</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
     <t>VT41</t>
   </si>
   <si>
     <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
   </si>
   <si>
+    <t>112365</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>13561</t>
+  </si>
+  <si>
+    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
+  </si>
+  <si>
     <t>2110303</t>
   </si>
   <si>
     <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>VT49</t>
-  </si>
-  <si>
-    <t>MONTERIA - INVENTARIO EN TRANSITO OPERADOR</t>
-  </si>
-  <si>
-    <t>10601</t>
-  </si>
-  <si>
-    <t>HUEVO C X30 CARTON GRIS</t>
+    <t>110472</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE CAJA  X 60</t>
   </si>
   <si>
     <t>VT52</t>
@@ -226,22 +298,10 @@
     <t>TAT BOGOTA - VT52</t>
   </si>
   <si>
-    <t>2013421</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 CARTON GRIS AMARRADO ALKOSTO CANASTA</t>
-  </si>
-  <si>
-    <t>2112207</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>VT59</t>
-  </si>
-  <si>
-    <t>TAT BOGOTA - VT59</t>
+    <t>VT55</t>
+  </si>
+  <si>
+    <t>TAT VILLAVICENCIO - INVENTARIO TRANSITO</t>
   </si>
   <si>
     <t>VT6</t>
@@ -250,16 +310,43 @@
     <t>TAT PASTO - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>2013322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT CANASTA</t>
-  </si>
-  <si>
-    <t>VT7</t>
-  </si>
-  <si>
-    <t>TAT CUCUTA - INVENTARIO TRANSITO</t>
+    <t>EECA006</t>
+  </si>
+  <si>
+    <t>CAJA REGULAR X300 EMPAQUE PET</t>
+  </si>
+  <si>
+    <t>VTAL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 1 TRANSITO</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>PTEM029</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>VTALBKA2</t>
+  </si>
+  <si>
+    <t>EMPAQUES ALKA 2 TRANSITO</t>
+  </si>
+  <si>
+    <t>EMES005</t>
+  </si>
+  <si>
+    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+  </si>
+  <si>
+    <t>EM</t>
   </si>
   <si>
     <t>PTEM049</t>
@@ -268,19 +355,16 @@
     <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
   </si>
   <si>
-    <t>VTAL06</t>
-  </si>
-  <si>
-    <t>EMPAQUES ALKA 1 TRANSITO</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>PTET043</t>
-  </si>
-  <si>
-    <t>ETIQUETA PET X 15 L</t>
+    <t>PTEM051</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>PTEM054</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L ETIQUETADO</t>
   </si>
   <si>
     <t>142111</t>
@@ -310,22 +394,25 @@
     <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
   </si>
   <si>
-    <t>PTEM029</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 UNIDADES BASE ACEBRI</t>
-  </si>
-  <si>
-    <t>VTALKA2</t>
-  </si>
-  <si>
-    <t>EGIPTO - INVENTARIO TRANSITO ALKA2</t>
-  </si>
-  <si>
-    <t>VTBE</t>
-  </si>
-  <si>
-    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>EMET015</t>
+  </si>
+  <si>
+    <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
+  </si>
+  <si>
+    <t>VTBC</t>
+  </si>
+  <si>
+    <t>EMPAQUES BELLAVISTA TRANSITO</t>
   </si>
   <si>
     <t>13358</t>
@@ -358,30 +445,18 @@
     <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
-    <t>13322</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT.</t>
-  </si>
-  <si>
-    <t>13469</t>
-  </si>
-  <si>
-    <t>HUEVO A X 300 BAND GRIS CAJA AMARR EXITO.</t>
-  </si>
-  <si>
     <t>2010501</t>
   </si>
   <si>
     <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
   </si>
   <si>
+    <t>VTCA</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>VTDOTH</t>
   </si>
   <si>
@@ -394,10 +469,22 @@
     <t>TOALLA BLANCA 1.20X0.60X320</t>
   </si>
   <si>
-    <t>EMES005</t>
-  </si>
-  <si>
-    <t>ESQUINERO DE CARTON 85 X 14 CM</t>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>VTEM02</t>
+  </si>
+  <si>
+    <t>EMPAQUES CALI TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
   </si>
   <si>
     <t>VTEM03</t>
@@ -406,9 +493,6 @@
     <t>EMPAQUES MEDELLIN TRANSITO</t>
   </si>
   <si>
-    <t>EM</t>
-  </si>
-  <si>
     <t>EMTB002</t>
   </si>
   <si>
@@ -430,289 +514,283 @@
     <t>EV</t>
   </si>
   <si>
+    <t>VTEMBQ</t>
+  </si>
+  <si>
+    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>VTEMMO</t>
+  </si>
+  <si>
+    <t>EMPAQUES MONTERIA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>VTEMT3</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>VTEMT41</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>EMCA016</t>
+  </si>
+  <si>
+    <t>CAJA ESTÁNDAR NEUTRA</t>
+  </si>
+  <si>
+    <t>EMET01</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
+  </si>
+  <si>
+    <t>DOPJ001</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 28</t>
+  </si>
+  <si>
+    <t>VTEMT52</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
+  </si>
+  <si>
+    <t>PTET04</t>
+  </si>
+  <si>
+    <t>ETIQUETA PET X 30 L - ACEBRI</t>
+  </si>
+  <si>
+    <t>DOCL002</t>
+  </si>
+  <si>
+    <t>CAMISETA LANILLA VERDE TALLA M</t>
+  </si>
+  <si>
+    <t>VTEMT6</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT PASTO</t>
+  </si>
+  <si>
+    <t>DOCP003</t>
+  </si>
+  <si>
+    <t>CAMISETA POLO VERDE TALLA L</t>
+  </si>
+  <si>
+    <t>DOPJ003</t>
+  </si>
+  <si>
+    <t>PANTALON JEAN CABALLERO TALLA 32</t>
+  </si>
+  <si>
+    <t>EMBA008</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
+  </si>
+  <si>
+    <t>VTEMT7</t>
+  </si>
+  <si>
+    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>EMPA007</t>
+  </si>
+  <si>
+    <t>PLASTICO SUPER STRECH 45X10X450 MT SIN CONO</t>
+  </si>
+  <si>
+    <t>143230</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>143241</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 6 CAJA X 72</t>
+  </si>
+  <si>
+    <t>AFES00</t>
+  </si>
+  <si>
+    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
+  </si>
+  <si>
+    <t>ENES014</t>
+  </si>
+  <si>
+    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>MDES002</t>
+  </si>
+  <si>
+    <t>ESTIBAS PLASTICAS</t>
+  </si>
+  <si>
+    <t>13324</t>
+  </si>
+  <si>
+    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
+  </si>
+  <si>
     <t>EMES001</t>
   </si>
   <si>
     <t>ESQUINEROS DE CARTON  90X14 CM</t>
   </si>
   <si>
-    <t>VTEMBQ</t>
-  </si>
-  <si>
-    <t>EMPAQUES BARRANQUILLA TRANSITO</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMTB001</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS</t>
-  </si>
-  <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
-  </si>
-  <si>
-    <t>VTEMT1</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT BUCARAMANGA</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
-  </si>
-  <si>
-    <t>EMET01</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
-  </si>
-  <si>
-    <t>VTEMT23</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT POPAYAN</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
-    <t>VTEMT3</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>VTEMT41</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>EMCA016</t>
-  </si>
-  <si>
-    <t>CAJA ESTÁNDAR NEUTRA</t>
-  </si>
-  <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
-    <t>DOPJ001</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 28</t>
-  </si>
-  <si>
-    <t>VTEMT52</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT BOGOTA NORTE</t>
-  </si>
-  <si>
-    <t>EECA006</t>
-  </si>
-  <si>
-    <t>CAJA REGULAR X300 EMPAQUE PET</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>PTET04</t>
-  </si>
-  <si>
-    <t>ETIQUETA PET X 30 L - ACEBRI</t>
-  </si>
-  <si>
-    <t>DOCL002</t>
-  </si>
-  <si>
-    <t>CAMISETA LANILLA VERDE TALLA M</t>
-  </si>
-  <si>
-    <t>VTEMT6</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT PASTO</t>
-  </si>
-  <si>
-    <t>DOCP003</t>
-  </si>
-  <si>
-    <t>CAMISETA POLO VERDE TALLA L</t>
-  </si>
-  <si>
-    <t>DOPJ003</t>
-  </si>
-  <si>
-    <t>PANTALON JEAN CABALLERO TALLA 32</t>
-  </si>
-  <si>
-    <t>EMBA008</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 EXTRA VERDE</t>
-  </si>
-  <si>
-    <t>VTEMT7</t>
-  </si>
-  <si>
-    <t>VIRTUAL EMPAQUE TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>143230</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18</t>
-  </si>
-  <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>143241</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 6 CAJA X 72</t>
-  </si>
-  <si>
-    <t>AFES00</t>
-  </si>
-  <si>
-    <t>ESTIBA DE MADERA 120 CM X100 CM   X 9 TACOS</t>
-  </si>
-  <si>
-    <t>ENES014</t>
-  </si>
-  <si>
-    <t>ESTIBA TIPO EXPORTACION 120 CMS X 100CMS</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>MDES002</t>
-  </si>
-  <si>
-    <t>ESTIBAS PLASTICAS</t>
-  </si>
-  <si>
-    <t>13324</t>
-  </si>
-  <si>
-    <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
-  </si>
-  <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
-    <t>13524</t>
-  </si>
-  <si>
-    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
-  </si>
-  <si>
-    <t>13561</t>
-  </si>
-  <si>
-    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
     <t>VTLZEM</t>
   </si>
   <si>
     <t>EMPAQUES LANZA TRANSITO</t>
   </si>
   <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>EMBA025</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
-  </si>
-  <si>
-    <t>EMCA019</t>
-  </si>
-  <si>
-    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
-  </si>
-  <si>
-    <t>EMCI001</t>
-  </si>
-  <si>
-    <t>CINTA CAJA  ROLLO X 1000 MTS</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>EMET014</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD  BARRA HUEVO A ROJO X 30 D1</t>
-  </si>
-  <si>
-    <t>EMET03</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD DE BARRA HUEVO XL X 30 - K</t>
-  </si>
-  <si>
-    <t>EMET050</t>
-  </si>
-  <si>
-    <t>ETIQUETA COD BARRA HUEVO B X 30 - BUENASOS</t>
-  </si>
-  <si>
-    <t>EMTA006</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
-  </si>
-  <si>
-    <t>EMZU004</t>
-  </si>
-  <si>
-    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
-  </si>
-  <si>
-    <t>PTEM051</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 30 L ETIQUETADO</t>
+    <t>VTME</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTMO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>MA0041</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA AMERICANA</t>
+  </si>
+  <si>
+    <t>VTPBU</t>
+  </si>
+  <si>
+    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>MA0043</t>
+  </si>
+  <si>
+    <t>TORTA DE SOYA BOLIVIANA</t>
+  </si>
+  <si>
+    <t>MA0056</t>
+  </si>
+  <si>
+    <t>FRIJOL SOYA AMERICANO CRUDO</t>
+  </si>
+  <si>
+    <t>MI0502</t>
+  </si>
+  <si>
+    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
+  </si>
+  <si>
+    <t>MDKI038</t>
+  </si>
+  <si>
+    <t>VJ 393760 KIT BOMBA DE VACIO VJ1000 FG 399393</t>
+  </si>
+  <si>
+    <t>VTPL01</t>
+  </si>
+  <si>
+    <t>ALMACEN - PALMAS TRANSITO</t>
+  </si>
+  <si>
+    <t>MDLA032</t>
+  </si>
+  <si>
+    <t>CLS Z38000091 TUV PL - LAMPARA UV 55W ANT Z200301</t>
+  </si>
+  <si>
+    <t>MDZU092</t>
+  </si>
+  <si>
+    <t>13001198 Conjunto chapa protectora cinta -Jaula A-</t>
+  </si>
+  <si>
+    <t>MDZU120</t>
+  </si>
+  <si>
+    <t>13001241 Conjunto rodillo presión MT A1262.</t>
+  </si>
+  <si>
+    <t>MDZU670</t>
+  </si>
+  <si>
+    <t>13002339 TAPA DEPOSITO AGUA.</t>
+  </si>
+  <si>
+    <t>VTPL06</t>
+  </si>
+  <si>
+    <t>EMPAQUES PALMAS TRANSITO</t>
+  </si>
+  <si>
+    <t>PTEM050</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
   </si>
   <si>
     <t>PTEM052</t>
@@ -721,96 +799,6 @@
     <t>EMPAQUE PET X 12 L ETIQUETADO</t>
   </si>
   <si>
-    <t>VTME</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VTMO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>MA0041</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA AMERICANA</t>
-  </si>
-  <si>
-    <t>VTPBU</t>
-  </si>
-  <si>
-    <t>TRANSITO VIRTUAL PUERTO BUENAVENTURA</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>MA0043</t>
-  </si>
-  <si>
-    <t>TORTA DE SOYA BOLIVIANA</t>
-  </si>
-  <si>
-    <t>MA0056</t>
-  </si>
-  <si>
-    <t>FRIJOL SOYA AMERICANO CRUDO</t>
-  </si>
-  <si>
-    <t>MI0502</t>
-  </si>
-  <si>
-    <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
-  </si>
-  <si>
-    <t>MDKI038</t>
-  </si>
-  <si>
-    <t>VJ 393760 KIT BOMBA DE VACIO VJ1000 FG 399393</t>
-  </si>
-  <si>
-    <t>VTPL01</t>
-  </si>
-  <si>
-    <t>ALMACEN - PALMAS TRANSITO</t>
-  </si>
-  <si>
-    <t>MDLA032</t>
-  </si>
-  <si>
-    <t>CLS Z38000091 TUV PL - LAMPARA UV 55W ANT Z200301</t>
-  </si>
-  <si>
-    <t>MDZU092</t>
-  </si>
-  <si>
-    <t>13001198 Conjunto chapa protectora cinta -Jaula A-</t>
-  </si>
-  <si>
-    <t>MDZU120</t>
-  </si>
-  <si>
-    <t>13001241 Conjunto rodillo presión MT A1262.</t>
-  </si>
-  <si>
-    <t>MDZU670</t>
-  </si>
-  <si>
-    <t>13002339 TAPA DEPOSITO AGUA.</t>
-  </si>
-  <si>
-    <t>VTPL06</t>
-  </si>
-  <si>
-    <t>EMPAQUES PALMAS TRANSITO</t>
-  </si>
-  <si>
     <t>VTPSM</t>
   </si>
   <si>
@@ -827,12 +815,6 @@
   </si>
   <si>
     <t>BODEGA TRANSITO HUEVO ROTO PARA PULVERIZADO</t>
-  </si>
-  <si>
-    <t>79111</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO ZF - SANTANDER</t>
   </si>
   <si>
     <t>81151</t>
@@ -992,13 +974,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15000</v>
+        <v>10410</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>46303.729201388887</v>
+        <v>46308.347997685181</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1010,7 +992,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>2971</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4">
@@ -1024,13 +1006,13 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>11100</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="2">
-        <v>46303.789224537039</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1042,7 +1024,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1152</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>27000</v>
+        <v>3000</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="2">
-        <v>46303.952337962961</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1074,7 +1056,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>2745</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="6">
@@ -1088,13 +1070,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>600</v>
+        <v>9300</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="2">
-        <v>46303.907268518517</v>
+        <v>46308.347997685181</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1106,7 +1088,7 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>1111</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7">
@@ -1120,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>2400</v>
+        <v>3300</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>46303.907268518517</v>
+        <v>46308.347997685181</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1138,7 +1120,7 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>1086</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="8">
@@ -1152,13 +1134,13 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>6000</v>
+        <v>46080</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="2">
-        <v>46303.952337962961</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -1170,7 +1152,7 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>1667</v>
+        <v>895</v>
       </c>
     </row>
     <row r="9">
@@ -1184,13 +1166,13 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>4226</v>
+        <v>23040</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="2">
-        <v>46303.952928240738</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1202,7 +1184,7 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>559</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10">
@@ -1216,77 +1198,81 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>50760</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="2">
-        <v>46303.065023148149</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10"/>
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>440</v>
+      </c>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2977</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11">
-        <v>13200</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="2">
-        <v>46303.9584837963</v>
+        <v>46306.396504629629</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11"/>
+        <v>36</v>
+      </c>
+      <c r="I11">
+        <v>250</v>
+      </c>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>869</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D12">
-        <v>124800</v>
+        <v>3300</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F12" s="2">
-        <v>46303.789224537039</v>
+        <v>46307.789201388885</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1298,27 +1284,27 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>2444</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
       <c r="D13">
-        <v>6480</v>
+        <v>840</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2">
-        <v>46303.789224537039</v>
+        <v>46307.789201388885</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1330,27 +1316,27 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>880</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14">
+        <v>6900</v>
+      </c>
+      <c r="E14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14">
-        <v>30960</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
       <c r="F14" s="2">
-        <v>46303.729201388887</v>
+        <v>46307.789201388885</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1362,129 +1348,123 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>1666</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>1367</v>
+        <v>6000</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>46303.9584837963</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>4330</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D16">
-        <v>36</v>
+        <v>4200</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>46303.9584837963</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>3774</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17">
+        <v>18000</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17">
-        <v>34</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
-      </c>
       <c r="F17" s="2">
-        <v>46303.9584837963</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>2563</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D18">
-        <v>3000</v>
+        <v>4800</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>46303</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1496,27 +1476,27 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>657</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19">
-        <v>120</v>
+        <v>9600</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>46303</v>
+        <v>46307.844988425924</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1528,27 +1508,27 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>407</v>
+        <v>563</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D20">
-        <v>9000</v>
+        <v>160560</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F20" s="2">
-        <v>46303</v>
+        <v>46308.160625</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1560,27 +1540,27 @@
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>635</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21">
-        <v>26400</v>
+        <v>18480</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>46304.362013888887</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
@@ -1592,27 +1572,27 @@
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>2120</v>
+        <v>875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D22">
-        <v>11880</v>
+        <v>84480</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>46304.362013888887</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1624,259 +1604,259 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>474</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>181380</v>
+        <v>1732</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2">
-        <v>46304.362013888887</v>
+        <v>46308.160625</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23"/>
+        <v>36</v>
+      </c>
+      <c r="I23">
+        <v>440</v>
+      </c>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>2819</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>3960</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>46303</v>
+        <v>46308.160625</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24"/>
+        <v>36</v>
+      </c>
+      <c r="I24">
+        <v>250</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>697</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D25">
-        <v>15840</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>46304.362013888887</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25"/>
+        <v>36</v>
+      </c>
+      <c r="I25">
+        <v>250</v>
+      </c>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>534</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D26">
-        <v>1042</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>46304.362013888887</v>
+        <v>46308.160625</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I26">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>3589</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D27">
-        <v>147</v>
+        <v>12000</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F27" s="2">
-        <v>46304.362013888887</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>2811</v>
+        <v>714</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D28">
-        <v>74</v>
+        <v>480</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F28" s="2">
-        <v>46304.362013888887</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>2137</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D29">
-        <v>209</v>
+        <v>2100</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2">
-        <v>46303</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
-      </c>
-      <c r="I29">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>2188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D30">
-        <v>7500</v>
+        <v>360</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2">
-        <v>46302</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1888,27 +1868,27 @@
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>821</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D31">
-        <v>1080</v>
+        <v>6000</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F31" s="2">
-        <v>46302</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1920,27 +1900,27 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>359</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D32">
-        <v>12000</v>
+        <v>600</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F32" s="2">
-        <v>46302</v>
+        <v>46307.56690972222</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -1952,27 +1932,27 @@
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>1203</v>
+        <v>661</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D33">
-        <v>21120</v>
+        <v>900</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F33" s="2">
-        <v>46304.199872685182</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -1984,27 +1964,27 @@
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>813</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D34">
-        <v>5940</v>
+        <v>265920</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F34" s="2">
-        <v>46302</v>
+        <v>46307.754907407405</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -2016,27 +1996,27 @@
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>519</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D35">
-        <v>334800</v>
+        <v>5940</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2">
-        <v>46304.21130787037</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2048,27 +2028,27 @@
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>3259</v>
+        <v>481</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D36">
-        <v>7920</v>
+        <v>113280</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F36" s="2">
-        <v>46302</v>
+        <v>46308.263935185183</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2080,101 +2060,99 @@
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>345</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D37">
-        <v>1560</v>
+        <v>7920</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F37" s="2">
-        <v>46304.21130787037</v>
+        <v>46306.768437499995</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>46</v>
-      </c>
-      <c r="I37">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>4104</v>
+        <v>538</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D38">
-        <v>80</v>
+        <v>1662</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F38" s="2">
-        <v>46304.21130787037</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I38">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>3172</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D39">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F39" s="2">
-        <v>46302</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I39">
         <v>250</v>
@@ -2182,93 +2160,95 @@
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>1814</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2">
-        <v>46304.21130787037</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="I40">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D41">
-        <v>1200</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F41" s="2">
-        <v>46303.7289699074</v>
+        <v>46307.656215277777</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41"/>
+        <v>65</v>
+      </c>
+      <c r="I41">
+        <v>5000</v>
+      </c>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>333</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D42">
-        <v>240</v>
+        <v>3000</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F42" s="2">
-        <v>46303.7289699074</v>
+        <v>46307.514803240738</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2280,27 +2260,27 @@
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>235</v>
+        <v>825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D43">
-        <v>4800</v>
+        <v>720</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F43" s="2">
-        <v>46303.7289699074</v>
+        <v>46307.514803240738</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
@@ -2312,27 +2292,27 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>325</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D44">
-        <v>63360</v>
+        <v>600</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F44" s="2">
-        <v>46302.988182870366</v>
+        <v>46306.686631944445</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2344,27 +2324,27 @@
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>469</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D45">
-        <v>96720</v>
+        <v>18000</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F45" s="2">
-        <v>46302.988182870366</v>
+        <v>46307.514803240738</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
@@ -2376,27 +2356,27 @@
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>952</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D46">
-        <v>3240</v>
+        <v>2400</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F46" s="2">
-        <v>46302.988182870366</v>
+        <v>46306.679768518516</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
@@ -2408,163 +2388,155 @@
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>113</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
-        <v>45</v>
-      </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D47">
-        <v>685</v>
+        <v>1200</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F47" s="2">
-        <v>46302.988182870366</v>
+        <v>46306.679768518516</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>1062</v>
+        <v>632</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D48">
-        <v>47</v>
+        <v>10500</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F48" s="2">
-        <v>46302.988182870366</v>
+        <v>46306.679768518516</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>46</v>
-      </c>
-      <c r="I48">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>898</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D49">
-        <v>23</v>
+        <v>133800</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F49" s="2">
-        <v>46302.988182870366</v>
+        <v>46308.062245370369</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>679</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D50">
-        <v>92</v>
+        <v>84480</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F50" s="2">
-        <v>46302.988182870366</v>
+        <v>46307.731412037036</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>51</v>
-      </c>
-      <c r="I50">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>566</v>
+        <v>817</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D51">
-        <v>270</v>
+        <v>6000</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F51" s="2">
-        <v>46304.662928240738</v>
+        <v>46307.514803240738</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2572,33 +2544,31 @@
       <c r="H51" t="s">
         <v>21</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
+      <c r="I51"/>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>89</v>
+        <v>523</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D52">
-        <v>21000</v>
+        <v>655704</v>
       </c>
       <c r="E52" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F52" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
@@ -2610,27 +2580,27 @@
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>3778</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D53">
-        <v>12000</v>
+        <v>15840</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F53" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.731412037036</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2642,155 +2612,163 @@
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>1069</v>
+        <v>349</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D54">
-        <v>1200</v>
+        <v>3207</v>
       </c>
       <c r="E54" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F54" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54"/>
+        <v>36</v>
+      </c>
+      <c r="I54">
+        <v>440</v>
+      </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>2449</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D55">
-        <v>54000</v>
+        <v>132</v>
       </c>
       <c r="E55" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F55" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55"/>
+        <v>36</v>
+      </c>
+      <c r="I55">
+        <v>250</v>
+      </c>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>4789</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D56">
-        <v>19200</v>
+        <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F56" s="2">
-        <v>46304.4972337963</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56"/>
+        <v>36</v>
+      </c>
+      <c r="I56">
+        <v>250</v>
+      </c>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>1850</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D57">
-        <v>6000</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F57" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57"/>
+        <v>65</v>
+      </c>
+      <c r="I57">
+        <v>5000</v>
+      </c>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>2195</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D58">
-        <v>3260</v>
+        <v>9600</v>
       </c>
       <c r="E58" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F58" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.723865740736</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
@@ -2802,27 +2780,27 @@
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>1671</v>
+        <v>961</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D59">
-        <v>72000</v>
+        <v>1080</v>
       </c>
       <c r="E59" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F59" s="2">
-        <v>46304.577708333331</v>
+        <v>46307.733067129629</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
@@ -2834,27 +2812,27 @@
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>11</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D60">
-        <v>1440</v>
+        <v>600</v>
       </c>
       <c r="E60" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F60" s="2">
-        <v>46304.499606481477</v>
+        <v>46307.733067129629</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -2866,225 +2844,227 @@
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>221</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D61">
-        <v>694</v>
+        <v>3600</v>
       </c>
       <c r="E61" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F61" s="2">
-        <v>46304.577708333331</v>
+        <v>46307.724537037036</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>46</v>
-      </c>
-      <c r="I61">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>5585</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D62">
-        <v>80</v>
+        <v>126720</v>
       </c>
       <c r="E62" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F62" s="2">
-        <v>46304.57540509259</v>
+        <v>46308.170590277776</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>46</v>
-      </c>
-      <c r="I62">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>4855</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D63">
-        <v>38</v>
+        <v>1177</v>
       </c>
       <c r="E63" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F63" s="2">
-        <v>46304.499606481477</v>
+        <v>46308.170590277776</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I63">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>2763</v>
+        <v>5606</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64">
         <v>34</v>
       </c>
-      <c r="B64" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64">
-        <v>23760</v>
-      </c>
       <c r="E64" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F64" s="2">
-        <v>46304.387395833328</v>
+        <v>46308.169803240737</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>21</v>
-      </c>
-      <c r="I64"/>
+        <v>36</v>
+      </c>
+      <c r="I64">
+        <v>250</v>
+      </c>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>1211</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" s="2">
+        <v>46307.715439814812</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
         <v>36</v>
       </c>
-      <c r="B65" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" t="s">
-        <v>76</v>
-      </c>
-      <c r="D65">
-        <v>7920</v>
-      </c>
-      <c r="E65" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65" s="2">
-        <v>46304.385798611111</v>
-      </c>
-      <c r="G65" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" t="s">
-        <v>21</v>
-      </c>
-      <c r="I65"/>
+      <c r="I65">
+        <v>250</v>
+      </c>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>705</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D66">
-        <v>21120</v>
+        <v>32</v>
       </c>
       <c r="E66" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F66" s="2">
-        <v>46304.385798611111</v>
+        <v>46308.169803240737</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66"/>
+        <v>65</v>
+      </c>
+      <c r="I66">
+        <v>5000</v>
+      </c>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>1027</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C67" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D67">
-        <v>2400</v>
+        <v>69120</v>
       </c>
       <c r="E67" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F67" s="2">
-        <v>46304.385798611111</v>
+        <v>46305.832569444443</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
@@ -3096,554 +3076,558 @@
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>533</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D68">
-        <v>360</v>
+        <v>288</v>
       </c>
       <c r="E68" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F68" s="2">
-        <v>46303.863946759258</v>
+        <v>46305.832569444443</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>21</v>
-      </c>
-      <c r="I68"/>
+        <v>36</v>
+      </c>
+      <c r="I68">
+        <v>440</v>
+      </c>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>165</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C69" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D69">
-        <v>1080</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F69" s="2">
-        <v>46304.385798611111</v>
+        <v>46305.832569444443</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69"/>
+        <v>36</v>
+      </c>
+      <c r="I69">
+        <v>250</v>
+      </c>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>195</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D70">
-        <v>304</v>
+        <v>255360</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F70" s="2">
-        <v>46304.387395833328</v>
+        <v>46306.44899305555</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>46</v>
-      </c>
-      <c r="I70">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>1447</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D71">
-        <v>14</v>
+        <v>5580</v>
       </c>
       <c r="E71" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F71" s="2">
-        <v>46304.387395833328</v>
+        <v>46306.448460648149</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>46</v>
-      </c>
-      <c r="I71">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>1157</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>1095</v>
       </c>
       <c r="E72" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F72" s="2">
-        <v>46304.387395833328</v>
+        <v>46306.44899305555</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I72">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>753</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73">
         <v>50</v>
       </c>
-      <c r="C73" t="s">
-        <v>76</v>
-      </c>
-      <c r="D73">
-        <v>21</v>
-      </c>
       <c r="E73" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F73" s="2">
-        <v>46304.387395833328</v>
+        <v>46306.44899305555</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="I73">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>763</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D74">
-        <v>1080</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F74" s="2">
-        <v>46304.513645833329</v>
+        <v>46306.44899305555</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74"/>
+        <v>36</v>
+      </c>
+      <c r="I74">
+        <v>250</v>
+      </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>159</v>
+        <v>415</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C75" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D75">
-        <v>102480</v>
+        <v>42</v>
       </c>
       <c r="E75" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="F75" s="2">
-        <v>46304.513645833329</v>
+        <v>46306.44899305555</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75"/>
+        <v>65</v>
+      </c>
+      <c r="I75">
+        <v>5000</v>
+      </c>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>2900</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C76" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="D76">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E76" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F76" s="2">
-        <v>46304.513645833329</v>
+        <v>46308.326608796291</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76"/>
+        <v>104</v>
+      </c>
+      <c r="I76">
+        <v>236</v>
+      </c>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>819</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="D77">
-        <v>441</v>
+        <v>2497</v>
       </c>
       <c r="E77" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F77" s="2">
-        <v>46304.513645833329</v>
+        <v>46305.42895833333</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I77">
-        <v>440</v>
+        <v>32000</v>
       </c>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>3167</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="B78" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D78">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="E78" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F78" s="2">
-        <v>46304.513645833329</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="I78">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>2871</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C79" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D79">
-        <v>84240</v>
+        <v>850</v>
       </c>
       <c r="E79" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="F79" s="2">
-        <v>46304.662627314814</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79"/>
+        <v>112</v>
+      </c>
+      <c r="I79">
+        <v>1550</v>
+      </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>259</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B80" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D80">
-        <v>468</v>
+        <v>3840</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="F80" s="2">
-        <v>46304.662627314814</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I80">
-        <v>440</v>
+        <v>32000</v>
       </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>2385</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D81">
-        <v>20</v>
+        <v>4800</v>
       </c>
       <c r="E81" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="F81" s="2">
-        <v>46304.662627314814</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>46</v>
-      </c>
-      <c r="I81">
-        <v>250</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>1947</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D82">
-        <v>400</v>
+        <v>3840</v>
       </c>
       <c r="E82" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="F82" s="2">
-        <v>46303.591041666667</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D83">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="E83" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="F83" s="2">
-        <v>46303.338136574072</v>
+        <v>46308.327928240738</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>88</v>
-      </c>
-      <c r="I83">
-        <v>10000</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D84">
         <v>288</v>
       </c>
       <c r="E84" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F84" s="2">
         <v>46301.62263888889</v>
@@ -3652,7 +3636,7 @@
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="I84"/>
       <c r="J84"/>
@@ -3663,19 +3647,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D85">
         <v>480</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F85" s="2">
         <v>46297.4564699074</v>
@@ -3684,7 +3668,7 @@
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="I85"/>
       <c r="J85"/>
@@ -3695,19 +3679,19 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D86">
         <v>720</v>
       </c>
       <c r="E86" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F86" s="2">
         <v>46297.4564699074</v>
@@ -3716,7 +3700,7 @@
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="I86"/>
       <c r="J86"/>
@@ -3727,264 +3711,260 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D87">
-        <v>2497</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F87" s="2">
-        <v>46301.643206018518</v>
+        <v>46305.61546296296</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="H87" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="I87">
-        <v>32000</v>
+        <v>40</v>
       </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>476</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="B88" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="D88">
-        <v>4352</v>
+        <v>2000</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F88" s="2">
-        <v>46304.390462962961</v>
+        <v>46305.498599537037</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="I88">
-        <v>440</v>
+        <v>10000</v>
       </c>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>2811</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D89">
-        <v>187</v>
+        <v>73152</v>
       </c>
       <c r="E89" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="F89" s="2">
-        <v>46304.390462962961</v>
+        <v>46307.609467592592</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>46</v>
-      </c>
-      <c r="I89">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>2625</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D90">
-        <v>44</v>
+        <v>57600</v>
       </c>
       <c r="E90" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="F90" s="2">
-        <v>46304.390462962961</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>46</v>
-      </c>
-      <c r="I90">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>1065</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D91">
-        <v>230</v>
+        <v>704640</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="F91" s="2">
-        <v>46304.390462962961</v>
+        <v>46307.609467592592</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>51</v>
-      </c>
-      <c r="I91">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>1115</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D92">
-        <v>30</v>
+        <v>3176</v>
       </c>
       <c r="E92" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="F92" s="2">
-        <v>46303.739386574074</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92"/>
+        <v>36</v>
+      </c>
+      <c r="I92">
+        <v>440</v>
+      </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>258</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B93" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D93">
-        <v>4642</v>
+        <v>172</v>
       </c>
       <c r="E93" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="F93" s="2">
-        <v>46303.394409722219</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I93">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>4412</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B94" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D94">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="E94" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="F94" s="2">
-        <v>46303.394409722219</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I94">
         <v>250</v>
@@ -3992,61 +3972,61 @@
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>4237</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C95" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D95">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E95" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="F95" s="2">
-        <v>46303.394409722219</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I95">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>2378</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D96">
-        <v>109728</v>
+        <v>300</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>46303.918564814812</v>
+        <v>46306.963043981479</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
@@ -4058,27 +4038,27 @@
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>1607</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="C97" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D97">
-        <v>149601</v>
+        <v>4200</v>
       </c>
       <c r="E97" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F97" s="2">
-        <v>46304.652592592589</v>
+        <v>46304</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
@@ -4090,27 +4070,27 @@
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>1858</v>
+        <v>301</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="C98" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D98">
-        <v>219360</v>
+        <v>3360</v>
       </c>
       <c r="E98" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F98" s="2">
-        <v>46304.651898148149</v>
+        <v>46304</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
@@ -4122,163 +4102,155 @@
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C99" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D99">
-        <v>1538</v>
+        <v>13200</v>
       </c>
       <c r="E99" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F99" s="2">
-        <v>46304.652592592589</v>
+        <v>46304</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>46</v>
-      </c>
-      <c r="I99">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>4466</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D100">
-        <v>92</v>
+        <v>66816</v>
       </c>
       <c r="E100" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F100" s="2">
-        <v>46304.652592592589</v>
+        <v>46308.303368055553</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>46</v>
-      </c>
-      <c r="I100">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>4148</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D101">
-        <v>37</v>
+        <v>105600</v>
       </c>
       <c r="E101" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F101" s="2">
-        <v>46304.652592592589</v>
+        <v>46307.81627314815</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>46</v>
-      </c>
-      <c r="I101">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>1498</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D102">
-        <v>111</v>
+        <v>642500</v>
       </c>
       <c r="E102" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="F102" s="2">
-        <v>46304.385104166664</v>
+        <v>46307.987523148149</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>51</v>
-      </c>
-      <c r="I102">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>2615</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D103">
-        <v>900</v>
+        <v>136800</v>
       </c>
       <c r="E103" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F103" s="2">
-        <v>46304.218726851846</v>
+        <v>46307.991168981476</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
@@ -4290,155 +4262,163 @@
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>1368</v>
+        <v>179</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D104">
-        <v>240</v>
+        <v>3688</v>
       </c>
       <c r="E104" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F104" s="2">
-        <v>46302.271099537036</v>
+        <v>46307.991168981476</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104"/>
+        <v>36</v>
+      </c>
+      <c r="I104">
+        <v>440</v>
+      </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>917</v>
+        <v>9343</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C105" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D105">
-        <v>300</v>
+        <v>148</v>
       </c>
       <c r="E105" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F105" s="2">
-        <v>46304.218726851846</v>
+        <v>46308.303368055553</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105"/>
+        <v>36</v>
+      </c>
+      <c r="I105">
+        <v>250</v>
+      </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>1372</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B106" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D106">
-        <v>900</v>
+        <v>68</v>
       </c>
       <c r="E106" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F106" s="2">
-        <v>46301.8950462963</v>
+        <v>46308.303368055553</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106"/>
+        <v>36</v>
+      </c>
+      <c r="I106">
+        <v>250</v>
+      </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>299</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="D107">
-        <v>3240</v>
+        <v>224</v>
       </c>
       <c r="E107" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F107" s="2">
-        <v>46304.202719907407</v>
+        <v>46307.987523148149</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>21</v>
-      </c>
-      <c r="I107"/>
+        <v>65</v>
+      </c>
+      <c r="I107">
+        <v>5000</v>
+      </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>278</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="D108">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="F108" s="2">
-        <v>46304.202719907407</v>
+        <v>46307.626539351848</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
@@ -4450,35 +4430,37 @@
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>310</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="D109">
-        <v>2160</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="F109" s="2">
-        <v>46301.892662037033</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>21</v>
-      </c>
-      <c r="I109"/>
+        <v>16</v>
+      </c>
+      <c r="I109">
+        <v>130</v>
+      </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
@@ -4487,1340 +4469,1334 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="C110" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="D110">
-        <v>72864</v>
+        <v>6</v>
       </c>
       <c r="E110" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="F110" s="2">
-        <v>46304.305381944439</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>21</v>
-      </c>
-      <c r="I110"/>
+        <v>16</v>
+      </c>
+      <c r="I110">
+        <v>200</v>
+      </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>1885</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="C111" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D111">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="E111" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F111" s="2">
-        <v>46304.218726851846</v>
+        <v>46306.83394675926</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>21</v>
-      </c>
-      <c r="I111"/>
+        <v>112</v>
+      </c>
+      <c r="I111">
+        <v>31360</v>
+      </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>251</v>
+        <v>410</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="C112" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D112">
-        <v>295608</v>
+        <v>2100</v>
       </c>
       <c r="E112" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="F112" s="2">
-        <v>46303</v>
+        <v>46306.872395833328</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>21</v>
-      </c>
-      <c r="I112"/>
+        <v>112</v>
+      </c>
+      <c r="I112">
+        <v>42420</v>
+      </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>1405</v>
+        <v>890</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C113" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D113">
-        <v>637645</v>
+        <v>3920</v>
       </c>
       <c r="E113" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="F113" s="2">
-        <v>46304.305381944439</v>
+        <v>46305.130706018514</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>21</v>
-      </c>
-      <c r="I113"/>
+        <v>112</v>
+      </c>
+      <c r="I113">
+        <v>6160</v>
+      </c>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>5282</v>
+        <v>669</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C114" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="D114">
-        <v>587280</v>
+        <v>850</v>
       </c>
       <c r="E114" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="F114" s="2">
-        <v>46303.954039351847</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>21</v>
-      </c>
-      <c r="I114"/>
+        <v>167</v>
+      </c>
+      <c r="I114">
+        <v>5000</v>
+      </c>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>166</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C115" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="D115">
-        <v>6336</v>
+        <v>1000</v>
       </c>
       <c r="E115" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="F115" s="2">
-        <v>46304.305381944439</v>
+        <v>46306.912569444445</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="I115">
-        <v>440</v>
+        <v>1550</v>
       </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>9309</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D116">
-        <v>191</v>
+        <v>1260</v>
       </c>
       <c r="E116" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="F116" s="2">
-        <v>46304.305381944439</v>
+        <v>46306.975057870368</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="I116">
-        <v>250</v>
+        <v>5880</v>
       </c>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>6550</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C117" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D117">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="E117" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="F117" s="2">
-        <v>46304.305381944439</v>
+        <v>46306.975057870368</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="I117">
-        <v>250</v>
+        <v>1550</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>5310</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="C118" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="D118">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="E118" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="F118" s="2">
-        <v>46303.952731481477</v>
+        <v>45185</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="I118">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>3038</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="C119" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="D119">
-        <v>9</v>
+        <v>3780</v>
       </c>
       <c r="E119" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="F119" s="2">
-        <v>46290.555405092593</v>
+        <v>46307.517488425925</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="I119">
-        <v>130</v>
+        <v>31360</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>11</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="C120" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="D120">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="E120" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="F120" s="2">
-        <v>46290.555405092593</v>
+        <v>46304.581412037034</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="I120">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>20</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="C121" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="D121">
         <v>600</v>
       </c>
       <c r="E121" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="F121" s="2">
-        <v>46304.224398148144</v>
+        <v>46307.517488425925</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I121">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>438</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="B122" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="C122" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="D122">
-        <v>7560</v>
+        <v>30000</v>
       </c>
       <c r="E122" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="F122" s="2">
-        <v>46303.962557870371</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I122">
-        <v>30100</v>
+        <v>190000</v>
       </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>667</v>
+        <v>102</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="C123" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="D123">
-        <v>850</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="F123" s="2">
-        <v>46295.8800462963</v>
+        <v>46303.692881944444</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="I123">
-        <v>5000</v>
+        <v>14</v>
       </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="B124" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="D124">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E124" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="F124" s="2">
-        <v>46304.319710648146</v>
+        <v>46297.650706018518</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="I124">
-        <v>660</v>
+        <v>236</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="D125">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E125" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="F125" s="2">
-        <v>46304.349722222221</v>
+        <v>46298.789583333331</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I125">
-        <v>1000</v>
+        <v>200000</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>190</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="C126" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="D126">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="F126" s="2">
-        <v>46302.989849537036</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="I126">
-        <v>660</v>
+        <v>50</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>182</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="B127" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="C127" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="D127">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="F127" s="2">
-        <v>46302.989849537036</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="I127">
-        <v>1000</v>
+        <v>43</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>129</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="B128" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="C128" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="D128">
-        <v>4480</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="F128" s="2">
-        <v>46302.989849537036</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="I128">
-        <v>60060</v>
+        <v>15</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>269</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="B129" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="D129">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="E129" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="F129" s="2">
-        <v>46304.159039351849</v>
+        <v>46304.513993055552</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I129">
-        <v>22400</v>
+        <v>19200</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="C130" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="D130">
-        <v>840</v>
+        <v>400</v>
       </c>
       <c r="E130" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="F130" s="2">
-        <v>46304.159039351849</v>
+        <v>46306.64980324074</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I130">
-        <v>22400</v>
+        <v>1550</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>97</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="B131" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C131" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="D131">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="E131" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="F131" s="2">
-        <v>46304.159039351849</v>
+        <v>46306.64980324074</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="H131" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="I131">
-        <v>10000</v>
+        <v>120</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="B132" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="C132" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="D132">
-        <v>700</v>
+        <v>144</v>
       </c>
       <c r="E132" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="F132" s="2">
-        <v>46301.818715277775</v>
+        <v>46302.905416666668</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>132</v>
-      </c>
-      <c r="I132">
-        <v>22400</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I132"/>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>157</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="B133" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="C133" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="D133">
-        <v>400</v>
+        <v>72</v>
       </c>
       <c r="E133" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="F133" s="2">
-        <v>45185</v>
+        <v>46301</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>132</v>
-      </c>
-      <c r="I133">
-        <v>7000</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I133"/>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="B134" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="D134">
-        <v>3780</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="F134" s="2">
-        <v>46304.581412037034</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="I134">
-        <v>22400</v>
+        <v>20</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>263</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B135" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="D135">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="E135" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="F135" s="2">
-        <v>46304.581412037034</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="I135">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>171</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="B136" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="C136" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="D136">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="E136" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="F136" s="2">
-        <v>46293</v>
+        <v>44426</v>
       </c>
       <c r="G136" t="s">
         <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="I136">
-        <v>10000</v>
+        <v>2</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>196</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="B137" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="D137">
-        <v>30000</v>
+        <v>600</v>
       </c>
       <c r="E137" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="F137" s="2">
-        <v>46280.943472222221</v>
+        <v>46307.297361111108</v>
       </c>
       <c r="G137" t="s">
         <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>132</v>
-      </c>
-      <c r="I137">
-        <v>190000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I137"/>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>102</v>
+        <v>455</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="B138" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="C138" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>900</v>
       </c>
       <c r="E138" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="F138" s="2">
-        <v>46303.692881944444</v>
+        <v>46307.561365740738</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
-      </c>
-      <c r="I138">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I138"/>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>13</v>
+        <v>581</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="B139" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="C139" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="D139">
-        <v>300</v>
+        <v>1380</v>
       </c>
       <c r="E139" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="F139" s="2">
-        <v>46297.650706018518</v>
+        <v>46300.329861111109</v>
       </c>
       <c r="G139" t="s">
         <v>15</v>
       </c>
       <c r="H139" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="I139">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="B140" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="C140" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="D140">
-        <v>1500</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="F140" s="2">
-        <v>46298.789583333331</v>
+        <v>46303.877905092588</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>132</v>
-      </c>
-      <c r="I140">
-        <v>200000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I140"/>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="C141" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>86400</v>
       </c>
       <c r="E141" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="F141" s="2">
-        <v>46265.788981481477</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>16</v>
-      </c>
-      <c r="I141">
-        <v>50</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I141"/>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>14</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C142" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>278400</v>
       </c>
       <c r="E142" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="F142" s="2">
-        <v>46265.776967592588</v>
+        <v>46307.885034722218</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>16</v>
-      </c>
-      <c r="I142">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I142"/>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>11</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="B143" t="s">
-        <v>184</v>
+        <v>35</v>
       </c>
       <c r="C143" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>1520</v>
       </c>
       <c r="E143" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="F143" s="2">
-        <v>46265.788981481477</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="I143">
-        <v>15</v>
+        <v>440</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>19</v>
+        <v>5144</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="B144" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="C144" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="D144">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="E144" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="F144" s="2">
-        <v>46304.513993055552</v>
+        <v>46308.161539351851</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="I144">
-        <v>7680</v>
+        <v>250</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>58</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="B145" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="C145" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="D145">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="F145" s="2">
-        <v>46304.663726851853</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="I145">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>129</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C146" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="D146">
-        <v>200</v>
+        <v>84480</v>
       </c>
       <c r="E146" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="F146" s="2">
-        <v>46304.663726851853</v>
+        <v>46306.948807870365</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>132</v>
-      </c>
-      <c r="I146">
-        <v>7000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I146"/>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>71</v>
+        <v>379</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D147">
-        <v>144</v>
+        <v>248640</v>
       </c>
       <c r="E147" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F147" s="2">
-        <v>46302.905416666668</v>
+        <v>46306.948807870365</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I147"/>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="B148" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="C148" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D148">
-        <v>72</v>
+        <v>115200</v>
       </c>
       <c r="E148" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F148" s="2">
-        <v>46301</v>
+        <v>46308.275497685187</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I148"/>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D149">
-        <v>2835</v>
+        <v>1868</v>
       </c>
       <c r="E149" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F149" s="2">
-        <v>46304.39534722222</v>
+        <v>46308.275497685187</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I149">
         <v>440</v>
@@ -5828,67 +5804,67 @@
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>11349</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="B150" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="C150" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D150">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="E150" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F150" s="2">
-        <v>44946.553055555552</v>
+        <v>46308.275497685187</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I150">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>2</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B151" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D151">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E151" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F151" s="2">
-        <v>46304.39534722222</v>
+        <v>46308.275497685187</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I151">
         <v>250</v>
@@ -5896,2390 +5872,610 @@
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>8993</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="B152" t="s">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="C152" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D152">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E152" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="F152" s="2">
-        <v>45777.752291666664</v>
+        <v>46306.948807870365</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="I152">
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>7</v>
+        <v>786</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="B153" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="C153" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="D153">
-        <v>55</v>
+        <v>899100</v>
       </c>
       <c r="E153" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="F153" s="2">
-        <v>44426</v>
+        <v>46296</v>
       </c>
       <c r="G153" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H153" t="s">
-        <v>51</v>
+        <v>238</v>
       </c>
       <c r="I153">
-        <v>2</v>
+        <v>950000</v>
       </c>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="B154" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="C154" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D154">
-        <v>300</v>
+        <v>2530000</v>
       </c>
       <c r="E154" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F154" s="2">
-        <v>46304.466620370367</v>
+        <v>46266</v>
       </c>
       <c r="G154" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H154" t="s">
-        <v>21</v>
-      </c>
-      <c r="I154"/>
+        <v>238</v>
+      </c>
+      <c r="I154">
+        <v>1265000</v>
+      </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>452</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="B155" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D155">
-        <v>300</v>
+        <v>750000</v>
       </c>
       <c r="E155" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F155" s="2">
-        <v>46303.533715277779</v>
+        <v>46266</v>
       </c>
       <c r="G155" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H155" t="s">
-        <v>21</v>
-      </c>
-      <c r="I155"/>
+        <v>238</v>
+      </c>
+      <c r="I155">
+        <v>750000</v>
+      </c>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>577</v>
+        <v>45</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="B156" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="C156" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D156">
-        <v>240</v>
+        <v>52000</v>
       </c>
       <c r="E156" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F156" s="2">
-        <v>46302.966481481482</v>
+        <v>46294</v>
       </c>
       <c r="G156" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H156" t="s">
-        <v>21</v>
-      </c>
-      <c r="I156"/>
+        <v>238</v>
+      </c>
+      <c r="I156">
+        <v>26000</v>
+      </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>418</v>
+        <v>56</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="B157" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="C157" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="D157">
-        <v>1348</v>
+        <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="F157" s="2">
-        <v>46304.480347222219</v>
+        <v>46303.697349537033</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>21</v>
-      </c>
-      <c r="I157"/>
+        <v>65</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="B158" t="s">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="C158" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="D158">
-        <v>921</v>
+        <v>28</v>
       </c>
       <c r="E158" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="F158" s="2">
-        <v>46304.480347222219</v>
+        <v>46304.313263888886</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I158">
-        <v>440</v>
+        <v>28</v>
       </c>
       <c r="J158"/>
       <c r="K158"/>
       <c r="L158">
-        <v>181</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>47</v>
+        <v>251</v>
       </c>
       <c r="B159" t="s">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="C159" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="D159">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E159" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="F159" s="2">
-        <v>46303.397303240738</v>
+        <v>46303.34983796296</v>
       </c>
       <c r="G159" t="s">
         <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I159">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="J159"/>
       <c r="K159"/>
       <c r="L159">
-        <v>106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="B160" t="s">
-        <v>50</v>
+        <v>254</v>
       </c>
       <c r="C160" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="D160">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E160" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="F160" s="2">
-        <v>46303.397303240738</v>
+        <v>46304.302789351852</v>
       </c>
       <c r="G160" t="s">
         <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I160">
-        <v>5000</v>
+        <v>15</v>
       </c>
       <c r="J160"/>
       <c r="K160"/>
       <c r="L160">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="B161" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="C161" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="D161">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="F161" s="2">
-        <v>46304.496759259258</v>
+        <v>46304.316724537035</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
       </c>
       <c r="H161" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="I161">
-        <v>640</v>
+        <v>14</v>
       </c>
       <c r="J161"/>
       <c r="K161"/>
       <c r="L161">
-        <v>1660</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="B162" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="C162" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="D162">
-        <v>22400</v>
+        <v>500</v>
       </c>
       <c r="E162" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="F162" s="2">
-        <v>46304.54819444444</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
       </c>
       <c r="H162" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="I162">
-        <v>22400</v>
+        <v>236</v>
       </c>
       <c r="J162"/>
       <c r="K162"/>
       <c r="L162">
-        <v>3105</v>
+        <v>515</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="B163" t="s">
-        <v>215</v>
+        <v>114</v>
       </c>
       <c r="C163" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="D163">
-        <v>5600</v>
+        <v>3600</v>
       </c>
       <c r="E163" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="F163" s="2">
-        <v>46304.54819444444</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G163" t="s">
         <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>132</v>
-      </c>
-      <c r="I163">
-        <v>5600</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I163"/>
       <c r="J163"/>
       <c r="K163"/>
       <c r="L163">
-        <v>2545</v>
+        <v>65</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="B164" t="s">
-        <v>186</v>
+        <v>260</v>
       </c>
       <c r="C164" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="D164">
-        <v>7680</v>
+        <v>3600</v>
       </c>
       <c r="E164" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="F164" s="2">
-        <v>46304.54819444444</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G164" t="s">
         <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>132</v>
-      </c>
-      <c r="I164">
-        <v>7680</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I164"/>
       <c r="J164"/>
       <c r="K164"/>
       <c r="L164">
-        <v>2115</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="B165" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="C165" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="D165">
-        <v>22400</v>
+        <v>1800</v>
       </c>
       <c r="E165" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="F165" s="2">
-        <v>46304.54819444444</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G165" t="s">
         <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>132</v>
-      </c>
-      <c r="I165">
-        <v>22400</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="I165"/>
       <c r="J165"/>
       <c r="K165"/>
       <c r="L165">
-        <v>3153</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="B166" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C166" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="D166">
-        <v>14700</v>
+        <v>52000</v>
       </c>
       <c r="E166" t="s">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="F166" s="2">
-        <v>46304.54819444444</v>
+        <v>46296</v>
       </c>
       <c r="G166" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H166" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="I166">
-        <v>14700</v>
+        <v>26000</v>
       </c>
       <c r="J166"/>
       <c r="K166"/>
       <c r="L166">
-        <v>2737</v>
+        <v>50</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="C167" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="D167">
-        <v>300</v>
+        <v>49720</v>
       </c>
       <c r="E167" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="F167" s="2">
-        <v>46304.496759259258</v>
+        <v>46306</v>
       </c>
       <c r="G167" t="s">
         <v>15</v>
       </c>
       <c r="H167" t="s">
-        <v>132</v>
-      </c>
-      <c r="I167">
-        <v>180</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I167"/>
       <c r="J167"/>
       <c r="K167"/>
       <c r="L167">
-        <v>1000</v>
+        <v>596</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="B168" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="C168" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="D168">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="E168" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="F168" s="2">
-        <v>46304.496759259258</v>
+        <v>46301.290810185186</v>
       </c>
       <c r="G168" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H168" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="I168">
-        <v>244</v>
+        <v>520</v>
       </c>
       <c r="J168"/>
       <c r="K168"/>
       <c r="L168">
-        <v>454</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="B169" t="s">
-        <v>221</v>
+        <v>275</v>
       </c>
       <c r="C169" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>13000</v>
       </c>
       <c r="E169" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="F169" s="2">
-        <v>46304.496759259258</v>
+        <v>46302.52238425926</v>
       </c>
       <c r="G169" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H169" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="I169">
-        <v>60</v>
+        <v>4000</v>
       </c>
       <c r="J169"/>
       <c r="K169"/>
       <c r="L169">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>140</v>
-      </c>
-      <c r="B170" t="s">
-        <v>141</v>
-      </c>
-      <c r="C170" t="s">
-        <v>212</v>
-      </c>
-      <c r="D170">
-        <v>1380</v>
-      </c>
-      <c r="E170" t="s">
-        <v>213</v>
-      </c>
-      <c r="F170" s="2">
-        <v>46300.329861111109</v>
-      </c>
-      <c r="G170" t="s">
-        <v>15</v>
-      </c>
-      <c r="H170" t="s">
-        <v>132</v>
-      </c>
-      <c r="I170">
-        <v>660</v>
-      </c>
-      <c r="J170"/>
-      <c r="K170"/>
-      <c r="L170">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>128</v>
-      </c>
-      <c r="B171" t="s">
-        <v>129</v>
-      </c>
-      <c r="C171" t="s">
-        <v>212</v>
-      </c>
-      <c r="D171">
-        <v>780</v>
-      </c>
-      <c r="E171" t="s">
-        <v>213</v>
-      </c>
-      <c r="F171" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G171" t="s">
-        <v>15</v>
-      </c>
-      <c r="H171" t="s">
-        <v>132</v>
-      </c>
-      <c r="I171">
-        <v>1000</v>
-      </c>
-      <c r="J171"/>
-      <c r="K171"/>
-      <c r="L171">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>223</v>
-      </c>
-      <c r="B172" t="s">
-        <v>224</v>
-      </c>
-      <c r="C172" t="s">
-        <v>212</v>
-      </c>
-      <c r="D172">
-        <v>2000</v>
-      </c>
-      <c r="E172" t="s">
-        <v>213</v>
-      </c>
-      <c r="F172" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G172" t="s">
-        <v>15</v>
-      </c>
-      <c r="H172" t="s">
-        <v>132</v>
-      </c>
-      <c r="I172">
-        <v>100000</v>
-      </c>
-      <c r="J172"/>
-      <c r="K172"/>
-      <c r="L172">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>225</v>
-      </c>
-      <c r="B173" t="s">
-        <v>226</v>
-      </c>
-      <c r="C173" t="s">
-        <v>212</v>
-      </c>
-      <c r="D173">
-        <v>2000</v>
-      </c>
-      <c r="E173" t="s">
-        <v>213</v>
-      </c>
-      <c r="F173" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G173" t="s">
-        <v>15</v>
-      </c>
-      <c r="H173" t="s">
-        <v>132</v>
-      </c>
-      <c r="I173">
-        <v>30000</v>
-      </c>
-      <c r="J173"/>
-      <c r="K173"/>
-      <c r="L173">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>227</v>
-      </c>
-      <c r="B174" t="s">
-        <v>228</v>
-      </c>
-      <c r="C174" t="s">
-        <v>212</v>
-      </c>
-      <c r="D174">
-        <v>10000</v>
-      </c>
-      <c r="E174" t="s">
-        <v>213</v>
-      </c>
-      <c r="F174" s="2">
-        <v>46302.655300925922</v>
-      </c>
-      <c r="G174" t="s">
-        <v>15</v>
-      </c>
-      <c r="H174" t="s">
-        <v>132</v>
-      </c>
-      <c r="I174">
-        <v>50000</v>
-      </c>
-      <c r="J174"/>
-      <c r="K174"/>
-      <c r="L174">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>158</v>
-      </c>
-      <c r="B175" t="s">
-        <v>159</v>
-      </c>
-      <c r="C175" t="s">
-        <v>212</v>
-      </c>
-      <c r="D175">
-        <v>300</v>
-      </c>
-      <c r="E175" t="s">
-        <v>213</v>
-      </c>
-      <c r="F175" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G175" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" t="s">
-        <v>132</v>
-      </c>
-      <c r="I175">
-        <v>7000</v>
-      </c>
-      <c r="J175"/>
-      <c r="K175"/>
-      <c r="L175">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>166</v>
-      </c>
-      <c r="B176" t="s">
-        <v>167</v>
-      </c>
-      <c r="C176" t="s">
-        <v>212</v>
-      </c>
-      <c r="D176">
-        <v>10000</v>
-      </c>
-      <c r="E176" t="s">
-        <v>213</v>
-      </c>
-      <c r="F176" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G176" t="s">
-        <v>15</v>
-      </c>
-      <c r="H176" t="s">
-        <v>132</v>
-      </c>
-      <c r="I176">
-        <v>190000</v>
-      </c>
-      <c r="J176"/>
-      <c r="K176"/>
-      <c r="L176">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>229</v>
-      </c>
-      <c r="B177" t="s">
-        <v>230</v>
-      </c>
-      <c r="C177" t="s">
-        <v>212</v>
-      </c>
-      <c r="D177">
-        <v>3920</v>
-      </c>
-      <c r="E177" t="s">
-        <v>213</v>
-      </c>
-      <c r="F177" s="2">
-        <v>46304.54819444444</v>
-      </c>
-      <c r="G177" t="s">
-        <v>15</v>
-      </c>
-      <c r="H177" t="s">
-        <v>132</v>
-      </c>
-      <c r="I177">
-        <v>3920</v>
-      </c>
-      <c r="J177"/>
-      <c r="K177"/>
-      <c r="L177">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>146</v>
-      </c>
-      <c r="B178" t="s">
-        <v>147</v>
-      </c>
-      <c r="C178" t="s">
-        <v>212</v>
-      </c>
-      <c r="D178">
-        <v>13440</v>
-      </c>
-      <c r="E178" t="s">
-        <v>213</v>
-      </c>
-      <c r="F178" s="2">
-        <v>46304.54819444444</v>
-      </c>
-      <c r="G178" t="s">
-        <v>15</v>
-      </c>
-      <c r="H178" t="s">
-        <v>132</v>
-      </c>
-      <c r="I178">
-        <v>60060</v>
-      </c>
-      <c r="J178"/>
-      <c r="K178"/>
-      <c r="L178">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>133</v>
-      </c>
-      <c r="B179" t="s">
-        <v>134</v>
-      </c>
-      <c r="C179" t="s">
-        <v>212</v>
-      </c>
-      <c r="D179">
-        <v>4480</v>
-      </c>
-      <c r="E179" t="s">
-        <v>213</v>
-      </c>
-      <c r="F179" s="2">
-        <v>46304.54819444444</v>
-      </c>
-      <c r="G179" t="s">
-        <v>15</v>
-      </c>
-      <c r="H179" t="s">
-        <v>132</v>
-      </c>
-      <c r="I179">
-        <v>30100</v>
-      </c>
-      <c r="J179"/>
-      <c r="K179"/>
-      <c r="L179">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>231</v>
-      </c>
-      <c r="B180" t="s">
-        <v>232</v>
-      </c>
-      <c r="C180" t="s">
-        <v>212</v>
-      </c>
-      <c r="D180">
-        <v>2</v>
-      </c>
-      <c r="E180" t="s">
-        <v>213</v>
-      </c>
-      <c r="F180" s="2">
-        <v>46304.496759259258</v>
-      </c>
-      <c r="G180" t="s">
-        <v>222</v>
-      </c>
-      <c r="H180" t="s">
-        <v>132</v>
-      </c>
-      <c r="I180">
-        <v>40</v>
-      </c>
-      <c r="J180"/>
-      <c r="K180"/>
-      <c r="L180">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>100</v>
-      </c>
-      <c r="B181" t="s">
-        <v>101</v>
-      </c>
-      <c r="C181" t="s">
-        <v>212</v>
-      </c>
-      <c r="D181">
-        <v>4000</v>
-      </c>
-      <c r="E181" t="s">
-        <v>213</v>
-      </c>
-      <c r="F181" s="2">
-        <v>46304.349004629628</v>
-      </c>
-      <c r="G181" t="s">
-        <v>15</v>
-      </c>
-      <c r="H181" t="s">
-        <v>88</v>
-      </c>
-      <c r="I181">
-        <v>32000</v>
-      </c>
-      <c r="J181"/>
-      <c r="K181"/>
-      <c r="L181">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>84</v>
-      </c>
-      <c r="B182" t="s">
-        <v>85</v>
-      </c>
-      <c r="C182" t="s">
-        <v>212</v>
-      </c>
-      <c r="D182">
-        <v>3000</v>
-      </c>
-      <c r="E182" t="s">
-        <v>213</v>
-      </c>
-      <c r="F182" s="2">
-        <v>46304.349004629628</v>
-      </c>
-      <c r="G182" t="s">
-        <v>15</v>
-      </c>
-      <c r="H182" t="s">
-        <v>88</v>
-      </c>
-      <c r="I182"/>
-      <c r="J182"/>
-      <c r="K182"/>
-      <c r="L182">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>233</v>
-      </c>
-      <c r="B183" t="s">
-        <v>234</v>
-      </c>
-      <c r="C183" t="s">
-        <v>212</v>
-      </c>
-      <c r="D183">
-        <v>4800</v>
-      </c>
-      <c r="E183" t="s">
-        <v>213</v>
-      </c>
-      <c r="F183" s="2">
-        <v>46304.349004629628</v>
-      </c>
-      <c r="G183" t="s">
-        <v>15</v>
-      </c>
-      <c r="H183" t="s">
-        <v>88</v>
-      </c>
-      <c r="I183"/>
-      <c r="J183"/>
-      <c r="K183"/>
-      <c r="L183">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>235</v>
-      </c>
-      <c r="B184" t="s">
-        <v>236</v>
-      </c>
-      <c r="C184" t="s">
-        <v>212</v>
-      </c>
-      <c r="D184">
-        <v>1200</v>
-      </c>
-      <c r="E184" t="s">
-        <v>213</v>
-      </c>
-      <c r="F184" s="2">
-        <v>46304.349004629628</v>
-      </c>
-      <c r="G184" t="s">
-        <v>15</v>
-      </c>
-      <c r="H184" t="s">
-        <v>88</v>
-      </c>
-      <c r="I184"/>
-      <c r="J184"/>
-      <c r="K184"/>
-      <c r="L184">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>54</v>
-      </c>
-      <c r="B185" t="s">
-        <v>55</v>
-      </c>
-      <c r="C185" t="s">
-        <v>237</v>
-      </c>
-      <c r="D185">
-        <v>36</v>
-      </c>
-      <c r="E185" t="s">
-        <v>238</v>
-      </c>
-      <c r="F185" s="2">
-        <v>46303.877905092588</v>
-      </c>
-      <c r="G185" t="s">
-        <v>15</v>
-      </c>
-      <c r="H185" t="s">
-        <v>21</v>
-      </c>
-      <c r="I185"/>
-      <c r="J185"/>
-      <c r="K185"/>
-      <c r="L185">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>106</v>
-      </c>
-      <c r="B186" t="s">
-        <v>107</v>
-      </c>
-      <c r="C186" t="s">
-        <v>237</v>
-      </c>
-      <c r="D186">
-        <v>73152</v>
-      </c>
-      <c r="E186" t="s">
-        <v>238</v>
-      </c>
-      <c r="F186" s="2">
-        <v>46304.223634259259</v>
-      </c>
-      <c r="G186" t="s">
-        <v>15</v>
-      </c>
-      <c r="H186" t="s">
-        <v>21</v>
-      </c>
-      <c r="I186"/>
-      <c r="J186"/>
-      <c r="K186"/>
-      <c r="L186">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>110</v>
-      </c>
-      <c r="B187" t="s">
-        <v>111</v>
-      </c>
-      <c r="C187" t="s">
-        <v>237</v>
-      </c>
-      <c r="D187">
-        <v>287520</v>
-      </c>
-      <c r="E187" t="s">
-        <v>238</v>
-      </c>
-      <c r="F187" s="2">
-        <v>46304.667048611111</v>
-      </c>
-      <c r="G187" t="s">
-        <v>15</v>
-      </c>
-      <c r="H187" t="s">
-        <v>21</v>
-      </c>
-      <c r="I187"/>
-      <c r="J187"/>
-      <c r="K187"/>
-      <c r="L187">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>112</v>
-      </c>
-      <c r="B188" t="s">
-        <v>113</v>
-      </c>
-      <c r="C188" t="s">
-        <v>237</v>
-      </c>
-      <c r="D188">
-        <v>360000</v>
-      </c>
-      <c r="E188" t="s">
-        <v>238</v>
-      </c>
-      <c r="F188" s="2">
-        <v>46303.959907407407</v>
-      </c>
-      <c r="G188" t="s">
-        <v>15</v>
-      </c>
-      <c r="H188" t="s">
-        <v>21</v>
-      </c>
-      <c r="I188"/>
-      <c r="J188"/>
-      <c r="K188"/>
-      <c r="L188">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>44</v>
-      </c>
-      <c r="B189" t="s">
-        <v>45</v>
-      </c>
-      <c r="C189" t="s">
-        <v>237</v>
-      </c>
-      <c r="D189">
-        <v>2698</v>
-      </c>
-      <c r="E189" t="s">
-        <v>238</v>
-      </c>
-      <c r="F189" s="2">
-        <v>46304.667048611111</v>
-      </c>
-      <c r="G189" t="s">
-        <v>15</v>
-      </c>
-      <c r="H189" t="s">
-        <v>46</v>
-      </c>
-      <c r="I189">
-        <v>440</v>
-      </c>
-      <c r="J189"/>
-      <c r="K189"/>
-      <c r="L189">
-        <v>5124</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>47</v>
-      </c>
-      <c r="B190" t="s">
-        <v>48</v>
-      </c>
-      <c r="C190" t="s">
-        <v>237</v>
-      </c>
-      <c r="D190">
-        <v>145</v>
-      </c>
-      <c r="E190" t="s">
-        <v>238</v>
-      </c>
-      <c r="F190" s="2">
-        <v>46304.667048611111</v>
-      </c>
-      <c r="G190" t="s">
-        <v>15</v>
-      </c>
-      <c r="H190" t="s">
-        <v>46</v>
-      </c>
-      <c r="I190">
-        <v>250</v>
-      </c>
-      <c r="J190"/>
-      <c r="K190"/>
-      <c r="L190">
-        <v>4522</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>60</v>
-      </c>
-      <c r="B191" t="s">
-        <v>61</v>
-      </c>
-      <c r="C191" t="s">
-        <v>237</v>
-      </c>
-      <c r="D191">
-        <v>52</v>
-      </c>
-      <c r="E191" t="s">
-        <v>238</v>
-      </c>
-      <c r="F191" s="2">
-        <v>46303.950300925921</v>
-      </c>
-      <c r="G191" t="s">
-        <v>15</v>
-      </c>
-      <c r="H191" t="s">
-        <v>46</v>
-      </c>
-      <c r="I191">
-        <v>250</v>
-      </c>
-      <c r="J191"/>
-      <c r="K191"/>
-      <c r="L191">
-        <v>2583</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>49</v>
-      </c>
-      <c r="B192" t="s">
-        <v>50</v>
-      </c>
-      <c r="C192" t="s">
-        <v>237</v>
-      </c>
-      <c r="D192">
-        <v>195</v>
-      </c>
-      <c r="E192" t="s">
-        <v>238</v>
-      </c>
-      <c r="F192" s="2">
-        <v>46304.667048611111</v>
-      </c>
-      <c r="G192" t="s">
-        <v>15</v>
-      </c>
-      <c r="H192" t="s">
-        <v>51</v>
-      </c>
-      <c r="I192">
-        <v>5000</v>
-      </c>
-      <c r="J192"/>
-      <c r="K192"/>
-      <c r="L192">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>122</v>
-      </c>
-      <c r="B193" t="s">
-        <v>123</v>
-      </c>
-      <c r="C193" t="s">
-        <v>239</v>
-      </c>
-      <c r="D193">
-        <v>338640</v>
-      </c>
-      <c r="E193" t="s">
-        <v>240</v>
-      </c>
-      <c r="F193" s="2">
-        <v>46303.730902777774</v>
-      </c>
-      <c r="G193" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" t="s">
-        <v>21</v>
-      </c>
-      <c r="I193"/>
-      <c r="J193"/>
-      <c r="K193"/>
-      <c r="L193">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>112</v>
-      </c>
-      <c r="B194" t="s">
-        <v>113</v>
-      </c>
-      <c r="C194" t="s">
-        <v>239</v>
-      </c>
-      <c r="D194">
-        <v>138240</v>
-      </c>
-      <c r="E194" t="s">
-        <v>240</v>
-      </c>
-      <c r="F194" s="2">
-        <v>46303.730902777774</v>
-      </c>
-      <c r="G194" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" t="s">
-        <v>21</v>
-      </c>
-      <c r="I194"/>
-      <c r="J194"/>
-      <c r="K194"/>
-      <c r="L194">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>44</v>
-      </c>
-      <c r="B195" t="s">
-        <v>45</v>
-      </c>
-      <c r="C195" t="s">
-        <v>239</v>
-      </c>
-      <c r="D195">
-        <v>1987</v>
-      </c>
-      <c r="E195" t="s">
-        <v>240</v>
-      </c>
-      <c r="F195" s="2">
-        <v>46303.730902777774</v>
-      </c>
-      <c r="G195" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" t="s">
-        <v>46</v>
-      </c>
-      <c r="I195">
-        <v>440</v>
-      </c>
-      <c r="J195"/>
-      <c r="K195"/>
-      <c r="L195">
-        <v>1623</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>47</v>
-      </c>
-      <c r="B196" t="s">
-        <v>48</v>
-      </c>
-      <c r="C196" t="s">
-        <v>239</v>
-      </c>
-      <c r="D196">
-        <v>74</v>
-      </c>
-      <c r="E196" t="s">
-        <v>240</v>
-      </c>
-      <c r="F196" s="2">
-        <v>46303.730902777774</v>
-      </c>
-      <c r="G196" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" t="s">
-        <v>46</v>
-      </c>
-      <c r="I196">
-        <v>250</v>
-      </c>
-      <c r="J196"/>
-      <c r="K196"/>
-      <c r="L196">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>60</v>
-      </c>
-      <c r="B197" t="s">
-        <v>61</v>
-      </c>
-      <c r="C197" t="s">
-        <v>239</v>
-      </c>
-      <c r="D197">
-        <v>27</v>
-      </c>
-      <c r="E197" t="s">
-        <v>240</v>
-      </c>
-      <c r="F197" s="2">
-        <v>46303.730902777774</v>
-      </c>
-      <c r="G197" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" t="s">
-        <v>46</v>
-      </c>
-      <c r="I197">
-        <v>250</v>
-      </c>
-      <c r="J197"/>
-      <c r="K197"/>
-      <c r="L197">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>49</v>
-      </c>
-      <c r="B198" t="s">
-        <v>50</v>
-      </c>
-      <c r="C198" t="s">
-        <v>239</v>
-      </c>
-      <c r="D198">
-        <v>41</v>
-      </c>
-      <c r="E198" t="s">
-        <v>240</v>
-      </c>
-      <c r="F198" s="2">
-        <v>46302</v>
-      </c>
-      <c r="G198" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" t="s">
-        <v>51</v>
-      </c>
-      <c r="I198">
-        <v>5000</v>
-      </c>
-      <c r="J198"/>
-      <c r="K198"/>
-      <c r="L198">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>241</v>
-      </c>
-      <c r="B199" t="s">
-        <v>242</v>
-      </c>
-      <c r="C199" t="s">
-        <v>243</v>
-      </c>
-      <c r="D199">
-        <v>899100</v>
-      </c>
-      <c r="E199" t="s">
-        <v>244</v>
-      </c>
-      <c r="F199" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G199" t="s">
-        <v>245</v>
-      </c>
-      <c r="H199" t="s">
-        <v>246</v>
-      </c>
-      <c r="I199">
-        <v>950000</v>
-      </c>
-      <c r="J199"/>
-      <c r="K199"/>
-      <c r="L199">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>247</v>
-      </c>
-      <c r="B200" t="s">
-        <v>248</v>
-      </c>
-      <c r="C200" t="s">
-        <v>243</v>
-      </c>
-      <c r="D200">
-        <v>2530000</v>
-      </c>
-      <c r="E200" t="s">
-        <v>244</v>
-      </c>
-      <c r="F200" s="2">
-        <v>46266</v>
-      </c>
-      <c r="G200" t="s">
-        <v>245</v>
-      </c>
-      <c r="H200" t="s">
-        <v>246</v>
-      </c>
-      <c r="I200">
-        <v>1265000</v>
-      </c>
-      <c r="J200"/>
-      <c r="K200"/>
-      <c r="L200">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>249</v>
-      </c>
-      <c r="B201" t="s">
-        <v>250</v>
-      </c>
-      <c r="C201" t="s">
-        <v>243</v>
-      </c>
-      <c r="D201">
-        <v>750000</v>
-      </c>
-      <c r="E201" t="s">
-        <v>244</v>
-      </c>
-      <c r="F201" s="2">
-        <v>46266</v>
-      </c>
-      <c r="G201" t="s">
-        <v>245</v>
-      </c>
-      <c r="H201" t="s">
-        <v>246</v>
-      </c>
-      <c r="I201">
-        <v>750000</v>
-      </c>
-      <c r="J201"/>
-      <c r="K201"/>
-      <c r="L201">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>251</v>
-      </c>
-      <c r="B202" t="s">
-        <v>252</v>
-      </c>
-      <c r="C202" t="s">
-        <v>243</v>
-      </c>
-      <c r="D202">
-        <v>52000</v>
-      </c>
-      <c r="E202" t="s">
-        <v>244</v>
-      </c>
-      <c r="F202" s="2">
-        <v>46294</v>
-      </c>
-      <c r="G202" t="s">
-        <v>245</v>
-      </c>
-      <c r="H202" t="s">
-        <v>246</v>
-      </c>
-      <c r="I202">
-        <v>26000</v>
-      </c>
-      <c r="J202"/>
-      <c r="K202"/>
-      <c r="L202">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>253</v>
-      </c>
-      <c r="B203" t="s">
-        <v>254</v>
-      </c>
-      <c r="C203" t="s">
-        <v>255</v>
-      </c>
-      <c r="D203">
-        <v>2</v>
-      </c>
-      <c r="E203" t="s">
-        <v>256</v>
-      </c>
-      <c r="F203" s="2">
-        <v>46303.697349537033</v>
-      </c>
-      <c r="G203" t="s">
-        <v>15</v>
-      </c>
-      <c r="H203" t="s">
-        <v>51</v>
-      </c>
-      <c r="I203">
-        <v>1</v>
-      </c>
-      <c r="J203"/>
-      <c r="K203"/>
-      <c r="L203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s">
-        <v>257</v>
-      </c>
-      <c r="B204" t="s">
-        <v>258</v>
-      </c>
-      <c r="C204" t="s">
-        <v>255</v>
-      </c>
-      <c r="D204">
-        <v>28</v>
-      </c>
-      <c r="E204" t="s">
-        <v>256</v>
-      </c>
-      <c r="F204" s="2">
-        <v>46304.313263888886</v>
-      </c>
-      <c r="G204" t="s">
-        <v>15</v>
-      </c>
-      <c r="H204" t="s">
-        <v>51</v>
-      </c>
-      <c r="I204">
-        <v>28</v>
-      </c>
-      <c r="J204"/>
-      <c r="K204"/>
-      <c r="L204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>259</v>
-      </c>
-      <c r="B205" t="s">
-        <v>260</v>
-      </c>
-      <c r="C205" t="s">
-        <v>255</v>
-      </c>
-      <c r="D205">
-        <v>10</v>
-      </c>
-      <c r="E205" t="s">
-        <v>256</v>
-      </c>
-      <c r="F205" s="2">
-        <v>46303.34983796296</v>
-      </c>
-      <c r="G205" t="s">
-        <v>15</v>
-      </c>
-      <c r="H205" t="s">
-        <v>51</v>
-      </c>
-      <c r="I205">
-        <v>10</v>
-      </c>
-      <c r="J205"/>
-      <c r="K205"/>
-      <c r="L205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s">
-        <v>261</v>
-      </c>
-      <c r="B206" t="s">
-        <v>262</v>
-      </c>
-      <c r="C206" t="s">
-        <v>255</v>
-      </c>
-      <c r="D206">
-        <v>4</v>
-      </c>
-      <c r="E206" t="s">
-        <v>256</v>
-      </c>
-      <c r="F206" s="2">
-        <v>46304.302789351852</v>
-      </c>
-      <c r="G206" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" t="s">
-        <v>51</v>
-      </c>
-      <c r="I206">
-        <v>15</v>
-      </c>
-      <c r="J206"/>
-      <c r="K206"/>
-      <c r="L206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>263</v>
-      </c>
-      <c r="B207" t="s">
-        <v>264</v>
-      </c>
-      <c r="C207" t="s">
-        <v>255</v>
-      </c>
-      <c r="D207">
-        <v>4</v>
-      </c>
-      <c r="E207" t="s">
-        <v>256</v>
-      </c>
-      <c r="F207" s="2">
-        <v>46304.316724537035</v>
-      </c>
-      <c r="G207" t="s">
-        <v>15</v>
-      </c>
-      <c r="H207" t="s">
-        <v>51</v>
-      </c>
-      <c r="I207">
-        <v>14</v>
-      </c>
-      <c r="J207"/>
-      <c r="K207"/>
-      <c r="L207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s">
-        <v>148</v>
-      </c>
-      <c r="B208" t="s">
-        <v>149</v>
-      </c>
-      <c r="C208" t="s">
-        <v>265</v>
-      </c>
-      <c r="D208">
-        <v>17920</v>
-      </c>
-      <c r="E208" t="s">
-        <v>266</v>
-      </c>
-      <c r="F208" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G208" t="s">
-        <v>15</v>
-      </c>
-      <c r="H208" t="s">
-        <v>132</v>
-      </c>
-      <c r="I208">
-        <v>22400</v>
-      </c>
-      <c r="J208"/>
-      <c r="K208"/>
-      <c r="L208">
-        <v>3660</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s">
-        <v>214</v>
-      </c>
-      <c r="B209" t="s">
-        <v>215</v>
-      </c>
-      <c r="C209" t="s">
-        <v>265</v>
-      </c>
-      <c r="D209">
-        <v>8960</v>
-      </c>
-      <c r="E209" t="s">
-        <v>266</v>
-      </c>
-      <c r="F209" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G209" t="s">
-        <v>15</v>
-      </c>
-      <c r="H209" t="s">
-        <v>132</v>
-      </c>
-      <c r="I209">
-        <v>5600</v>
-      </c>
-      <c r="J209"/>
-      <c r="K209"/>
-      <c r="L209">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>185</v>
-      </c>
-      <c r="B210" t="s">
-        <v>186</v>
-      </c>
-      <c r="C210" t="s">
-        <v>265</v>
-      </c>
-      <c r="D210">
-        <v>7680</v>
-      </c>
-      <c r="E210" t="s">
-        <v>266</v>
-      </c>
-      <c r="F210" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G210" t="s">
-        <v>15</v>
-      </c>
-      <c r="H210" t="s">
-        <v>132</v>
-      </c>
-      <c r="I210">
-        <v>7680</v>
-      </c>
-      <c r="J210"/>
-      <c r="K210"/>
-      <c r="L210">
-        <v>2405</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>152</v>
-      </c>
-      <c r="B211" t="s">
-        <v>153</v>
-      </c>
-      <c r="C211" t="s">
-        <v>265</v>
-      </c>
-      <c r="D211">
-        <v>13440</v>
-      </c>
-      <c r="E211" t="s">
-        <v>266</v>
-      </c>
-      <c r="F211" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G211" t="s">
-        <v>15</v>
-      </c>
-      <c r="H211" t="s">
-        <v>132</v>
-      </c>
-      <c r="I211">
-        <v>22400</v>
-      </c>
-      <c r="J211"/>
-      <c r="K211"/>
-      <c r="L211">
-        <v>3081</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>216</v>
-      </c>
-      <c r="B212" t="s">
-        <v>217</v>
-      </c>
-      <c r="C212" t="s">
-        <v>265</v>
-      </c>
-      <c r="D212">
-        <v>4200</v>
-      </c>
-      <c r="E212" t="s">
-        <v>266</v>
-      </c>
-      <c r="F212" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G212" t="s">
-        <v>15</v>
-      </c>
-      <c r="H212" t="s">
-        <v>132</v>
-      </c>
-      <c r="I212">
-        <v>14700</v>
-      </c>
-      <c r="J212"/>
-      <c r="K212"/>
-      <c r="L212">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>218</v>
-      </c>
-      <c r="B213" t="s">
-        <v>219</v>
-      </c>
-      <c r="C213" t="s">
-        <v>265</v>
-      </c>
-      <c r="D213">
-        <v>500</v>
-      </c>
-      <c r="E213" t="s">
-        <v>266</v>
-      </c>
-      <c r="F213" s="2">
-        <v>46304.3387037037</v>
-      </c>
-      <c r="G213" t="s">
-        <v>15</v>
-      </c>
-      <c r="H213" t="s">
-        <v>132</v>
-      </c>
-      <c r="I213">
-        <v>244</v>
-      </c>
-      <c r="J213"/>
-      <c r="K213"/>
-      <c r="L213">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>223</v>
-      </c>
-      <c r="B214" t="s">
-        <v>224</v>
-      </c>
-      <c r="C214" t="s">
-        <v>265</v>
-      </c>
-      <c r="D214">
-        <v>15000</v>
-      </c>
-      <c r="E214" t="s">
-        <v>266</v>
-      </c>
-      <c r="F214" s="2">
-        <v>46304.3387037037</v>
-      </c>
-      <c r="G214" t="s">
-        <v>15</v>
-      </c>
-      <c r="H214" t="s">
-        <v>132</v>
-      </c>
-      <c r="I214">
-        <v>100000</v>
-      </c>
-      <c r="J214"/>
-      <c r="K214"/>
-      <c r="L214">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>158</v>
-      </c>
-      <c r="B215" t="s">
-        <v>159</v>
-      </c>
-      <c r="C215" t="s">
-        <v>265</v>
-      </c>
-      <c r="D215">
-        <v>1000</v>
-      </c>
-      <c r="E215" t="s">
-        <v>266</v>
-      </c>
-      <c r="F215" s="2">
-        <v>46304.3387037037</v>
-      </c>
-      <c r="G215" t="s">
-        <v>15</v>
-      </c>
-      <c r="H215" t="s">
-        <v>132</v>
-      </c>
-      <c r="I215">
-        <v>7000</v>
-      </c>
-      <c r="J215"/>
-      <c r="K215"/>
-      <c r="L215">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>146</v>
-      </c>
-      <c r="B216" t="s">
-        <v>147</v>
-      </c>
-      <c r="C216" t="s">
-        <v>265</v>
-      </c>
-      <c r="D216">
-        <v>4480</v>
-      </c>
-      <c r="E216" t="s">
-        <v>266</v>
-      </c>
-      <c r="F216" s="2">
-        <v>46304.405636574069</v>
-      </c>
-      <c r="G216" t="s">
-        <v>15</v>
-      </c>
-      <c r="H216" t="s">
-        <v>132</v>
-      </c>
-      <c r="I216">
-        <v>60060</v>
-      </c>
-      <c r="J216"/>
-      <c r="K216"/>
-      <c r="L216">
-        <v>2777</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>231</v>
-      </c>
-      <c r="B217" t="s">
-        <v>232</v>
-      </c>
-      <c r="C217" t="s">
-        <v>265</v>
-      </c>
-      <c r="D217">
-        <v>6</v>
-      </c>
-      <c r="E217" t="s">
-        <v>266</v>
-      </c>
-      <c r="F217" s="2">
-        <v>46304.3387037037</v>
-      </c>
-      <c r="G217" t="s">
-        <v>222</v>
-      </c>
-      <c r="H217" t="s">
-        <v>132</v>
-      </c>
-      <c r="I217">
-        <v>40</v>
-      </c>
-      <c r="J217"/>
-      <c r="K217"/>
-      <c r="L217">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>251</v>
-      </c>
-      <c r="B218" t="s">
-        <v>252</v>
-      </c>
-      <c r="C218" t="s">
-        <v>267</v>
-      </c>
-      <c r="D218">
-        <v>52000</v>
-      </c>
-      <c r="E218" t="s">
-        <v>268</v>
-      </c>
-      <c r="F218" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G218" t="s">
-        <v>245</v>
-      </c>
-      <c r="H218" t="s">
-        <v>246</v>
-      </c>
-      <c r="I218">
-        <v>26000</v>
-      </c>
-      <c r="J218"/>
-      <c r="K218"/>
-      <c r="L218">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>269</v>
-      </c>
-      <c r="B219" t="s">
-        <v>270</v>
-      </c>
-      <c r="C219" t="s">
-        <v>271</v>
-      </c>
-      <c r="D219">
-        <v>173920</v>
-      </c>
-      <c r="E219" t="s">
-        <v>272</v>
-      </c>
-      <c r="F219" s="2">
-        <v>46303</v>
-      </c>
-      <c r="G219" t="s">
-        <v>15</v>
-      </c>
-      <c r="H219" t="s">
-        <v>21</v>
-      </c>
-      <c r="I219"/>
-      <c r="J219"/>
-      <c r="K219"/>
-      <c r="L219">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>273</v>
-      </c>
-      <c r="B220" t="s">
-        <v>274</v>
-      </c>
-      <c r="C220" t="s">
-        <v>271</v>
-      </c>
-      <c r="D220">
-        <v>22500</v>
-      </c>
-      <c r="E220" t="s">
-        <v>272</v>
-      </c>
-      <c r="F220" s="2">
-        <v>46303</v>
-      </c>
-      <c r="G220" t="s">
-        <v>15</v>
-      </c>
-      <c r="H220" t="s">
-        <v>21</v>
-      </c>
-      <c r="I220"/>
-      <c r="J220"/>
-      <c r="K220"/>
-      <c r="L220">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>275</v>
-      </c>
-      <c r="B221" t="s">
-        <v>276</v>
-      </c>
-      <c r="C221" t="s">
-        <v>277</v>
-      </c>
-      <c r="D221">
-        <v>520</v>
-      </c>
-      <c r="E221" t="s">
-        <v>278</v>
-      </c>
-      <c r="F221" s="2">
-        <v>46301.290810185186</v>
-      </c>
-      <c r="G221" t="s">
-        <v>245</v>
-      </c>
-      <c r="H221" t="s">
-        <v>279</v>
-      </c>
-      <c r="I221">
-        <v>520</v>
-      </c>
-      <c r="J221"/>
-      <c r="K221"/>
-      <c r="L221">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>280</v>
-      </c>
-      <c r="B222" t="s">
-        <v>281</v>
-      </c>
-      <c r="C222" t="s">
-        <v>277</v>
-      </c>
-      <c r="D222">
-        <v>13000</v>
-      </c>
-      <c r="E222" t="s">
-        <v>278</v>
-      </c>
-      <c r="F222" s="2">
-        <v>46302.52238425926</v>
-      </c>
-      <c r="G222" t="s">
-        <v>245</v>
-      </c>
-      <c r="H222" t="s">
-        <v>279</v>
-      </c>
-      <c r="I222">
-        <v>4000</v>
-      </c>
-      <c r="J222"/>
-      <c r="K222"/>
-      <c r="L222">
         <v>425</v>
       </c>
     </row>

--- a/Inventarios.xlsx
+++ b/Inventarios.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="Inventarios" sheetId="1" r:id="Rd99dc67ee8334c4f"/>
+    <sheet name="Inventarios" sheetId="1" r:id="R059235cbd33e483b"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276" xml:space="preserve">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271" xml:space="preserve">
   <si>
     <t>codigo_articulo</t>
   </si>
@@ -61,10 +61,10 @@
     <t>DO</t>
   </si>
   <si>
-    <t>110303</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE AMARRADO</t>
+    <t>114268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>VT1</t>
@@ -76,150 +76,114 @@
     <t>HU</t>
   </si>
   <si>
+    <t>114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>112268</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>VT3</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>112271</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>112379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>152384</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>2010102</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
+  </si>
+  <si>
+    <t>2110202</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2110217</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>2110302</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>AFCA022</t>
+  </si>
+  <si>
+    <t>CANASTA KIKES 63  X 32 X  23</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AFES013</t>
+  </si>
+  <si>
+    <t>ESTIBAS OVOID 124CM X 65CM</t>
+  </si>
+  <si>
+    <t>AFSE003</t>
+  </si>
+  <si>
+    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
+  </si>
+  <si>
+    <t>MDGA105</t>
+  </si>
+  <si>
+    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>110316</t>
+  </si>
+  <si>
+    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
+  </si>
+  <si>
+    <t>VT36</t>
+  </si>
+  <si>
+    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
+  </si>
+  <si>
     <t>112357</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
-    <t>112379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>13459</t>
-  </si>
-  <si>
-    <t>HUEVO A X 300 BANDEJA GRIS ALAT CAJA AMARRADO</t>
-  </si>
-  <si>
-    <t>152384</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>2110327</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>2110427</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BGA</t>
-  </si>
-  <si>
-    <t>AFCA022</t>
-  </si>
-  <si>
-    <t>CANASTA KIKES 63  X 32 X  23</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>AFES013</t>
-  </si>
-  <si>
-    <t>ESTIBAS OVOID 124CM X 65CM</t>
-  </si>
-  <si>
-    <t>114268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>VT2</t>
-  </si>
-  <si>
-    <t>TAT CALI - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>114357</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
-    <t>114379</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>112268</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>VT3</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>112271</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
-    <t>2010102</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA.</t>
-  </si>
-  <si>
-    <t>2110202</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2110217</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO CON ETIQUETA CANASTA</t>
-  </si>
-  <si>
-    <t>2110302</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>AFSE003</t>
-  </si>
-  <si>
-    <t>SEPARADORES OVOID DE 124CM X 66CM</t>
-  </si>
-  <si>
-    <t>MDGA105</t>
-  </si>
-  <si>
-    <t>GANGHO METÁLICO LAMINA CAL14 COLD ROLLED BRAZOS 5.2CM P/CANASTA OVOID</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>110316</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE CON ETIQUETA</t>
-  </si>
-  <si>
-    <t>VT36</t>
-  </si>
-  <si>
-    <t>PEREIRA - INVENTARIO TRANSITO OPERADOR</t>
-  </si>
-  <si>
     <t>152281</t>
   </si>
   <si>
@@ -262,30 +226,18 @@
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
+    <t>13561</t>
+  </si>
+  <si>
+    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
+  </si>
+  <si>
     <t>VT41</t>
   </si>
   <si>
     <t>TAT CARTAGENA - INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>112365</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>13561</t>
-  </si>
-  <si>
-    <t>HUEVO B X 30 BAND GRIS AMARRADO - OLIMPICA</t>
-  </si>
-  <si>
-    <t>2110303</t>
-  </si>
-  <si>
-    <t>HUEVO L X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
     <t>110472</t>
   </si>
   <si>
@@ -298,18 +250,6 @@
     <t>TAT BOGOTA - VT52</t>
   </si>
   <si>
-    <t>VT55</t>
-  </si>
-  <si>
-    <t>TAT VILLAVICENCIO - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VT6</t>
-  </si>
-  <si>
-    <t>TAT PASTO - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>EECA006</t>
   </si>
   <si>
@@ -325,6 +265,45 @@
     <t>EE</t>
   </si>
   <si>
+    <t>EMBA001</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>EMBA006</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
+  </si>
+  <si>
+    <t>EMBA010</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+  </si>
+  <si>
+    <t>EMBA025</t>
+  </si>
+  <si>
+    <t>BANDEJA HUEVO 12 GRIS SOL NACIENTE</t>
+  </si>
+  <si>
+    <t>EMLA002</t>
+  </si>
+  <si>
+    <t>LAMINA CARTON 60X90</t>
+  </si>
+  <si>
+    <t>EMTA006</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS DISENO KIKES</t>
+  </si>
+  <si>
     <t>PTEM029</t>
   </si>
   <si>
@@ -334,10 +313,70 @@
     <t>PT</t>
   </si>
   <si>
-    <t>VTALBKA2</t>
-  </si>
-  <si>
-    <t>EMPAQUES ALKA 2 TRANSITO</t>
+    <t>142111</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
+  </si>
+  <si>
+    <t>VTALEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES CALOTO TRANSITO</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>142121</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12 CAJA X 48</t>
+  </si>
+  <si>
+    <t>143231</t>
+  </si>
+  <si>
+    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
+  </si>
+  <si>
+    <t>EMZU004</t>
+  </si>
+  <si>
+    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>VTALKA</t>
+  </si>
+  <si>
+    <t>KIKES - EGIPTO - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>VTALKA2</t>
+  </si>
+  <si>
+    <t>EGIPTO - INVENTARIO TRANSITO ALKA2</t>
+  </si>
+  <si>
+    <t>EMBO003</t>
+  </si>
+  <si>
+    <t>BOLSA POLIETILENO TRANSPARENTE 55X76CMS CALIBRE 2.5</t>
+  </si>
+  <si>
+    <t>VTBC</t>
+  </si>
+  <si>
+    <t>EMPAQUES BELLAVISTA TRANSITO</t>
+  </si>
+  <si>
+    <t>EMCA019</t>
+  </si>
+  <si>
+    <t>CAJA DOCENERA SOL NACIENTE NEGRA</t>
   </si>
   <si>
     <t>EMES005</t>
@@ -346,7 +385,25 @@
     <t>ESQUINERO DE CARTON 85 X 14 CM</t>
   </si>
   <si>
-    <t>EM</t>
+    <t>EMET010</t>
+  </si>
+  <si>
+    <t>ETIQUETA COD BARRA HUEVO A ROJO X 30 ALAT</t>
+  </si>
+  <si>
+    <t>EMSU001</t>
+  </si>
+  <si>
+    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
+  </si>
+  <si>
+    <t>MAAM033</t>
+  </si>
+  <si>
+    <t>AMARRES PLASTICOS DE 8"</t>
+  </si>
+  <si>
+    <t>MA</t>
   </si>
   <si>
     <t>PTEM049</t>
@@ -355,52 +412,76 @@
     <t>EMPAQUE PET X 15 XL ETIQUETADO</t>
   </si>
   <si>
+    <t>PTEM050</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
+  </si>
+  <si>
     <t>PTEM051</t>
   </si>
   <si>
     <t>EMPAQUE PET X 30 L ETIQUETADO</t>
   </si>
   <si>
-    <t>PTEM054</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 L ETIQUETADO</t>
-  </si>
-  <si>
-    <t>142111</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 4 CAJA X 48</t>
-  </si>
-  <si>
-    <t>VTALEM</t>
-  </si>
-  <si>
-    <t>EMPAQUES CALOTO TRANSITO</t>
-  </si>
-  <si>
-    <t>BP</t>
-  </si>
-  <si>
-    <t>142121</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 50 GR ARANDANO DISPLAY X 12 CAJA X 48</t>
-  </si>
-  <si>
-    <t>143231</t>
-  </si>
-  <si>
-    <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18 CAJA X 72</t>
-  </si>
-  <si>
-    <t>EMZU004</t>
-  </si>
-  <si>
-    <t>ZUNCHO ANCHO 5 MM 7.500 MTS</t>
-  </si>
-  <si>
-    <t>RL</t>
+    <t>PTEM052</t>
+  </si>
+  <si>
+    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
+  </si>
+  <si>
+    <t>VTBE</t>
+  </si>
+  <si>
+    <t>BODEGA BELLAVISTA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>13358</t>
+  </si>
+  <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>VTBO</t>
+  </si>
+  <si>
+    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010301</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>2410401</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>VTBQ</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
+    <t>2010501</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
+  </si>
+  <si>
+    <t>VTDOTH</t>
+  </si>
+  <si>
+    <t>BODEGA DOTACION TH TRANSITO</t>
+  </si>
+  <si>
+    <t>DOTA050</t>
+  </si>
+  <si>
+    <t>TOALLA BLANCA 1.20X0.60X320</t>
   </si>
   <si>
     <t>EMET015</t>
@@ -409,70 +490,10 @@
     <t>ETIQUETA HUEVO B ROJO X 30- ALAT</t>
   </si>
   <si>
-    <t>VTBC</t>
-  </si>
-  <si>
-    <t>EMPAQUES BELLAVISTA TRANSITO</t>
-  </si>
-  <si>
-    <t>13358</t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>VTBO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES BOGOTA -INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010301</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>2410401</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>VTBQ</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>2010501</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS CANASTA.</t>
-  </si>
-  <si>
-    <t>VTCA</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES CALI-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
-    <t>VTDOTH</t>
-  </si>
-  <si>
-    <t>BODEGA DOTACION TH TRANSITO</t>
-  </si>
-  <si>
-    <t>DOTA050</t>
-  </si>
-  <si>
-    <t>TOALLA BLANCA 1.20X0.60X320</t>
-  </si>
-  <si>
-    <t>EMBA010</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO VERDE</t>
+    <t>VTEM</t>
+  </si>
+  <si>
+    <t>EMPAQUES BUCARAMANGA TRANSITO</t>
   </si>
   <si>
     <t>VTEM02</t>
@@ -481,10 +502,10 @@
     <t>EMPAQUES CALI TRANSITO</t>
   </si>
   <si>
-    <t>EMBA001</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SPCCO GRIS</t>
+    <t>EMTB002</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA VERDE KIKES</t>
   </si>
   <si>
     <t>VTEM03</t>
@@ -493,12 +514,6 @@
     <t>EMPAQUES MEDELLIN TRANSITO</t>
   </si>
   <si>
-    <t>EMTB002</t>
-  </si>
-  <si>
-    <t>TAPA PARA BANDEJA VERDE KIKES</t>
-  </si>
-  <si>
     <t>EMET019</t>
   </si>
   <si>
@@ -520,24 +535,6 @@
     <t>EMPAQUES BARRANQUILLA TRANSITO</t>
   </si>
   <si>
-    <t>EMBA006</t>
-  </si>
-  <si>
-    <t>BANDEJA HUEVO X 30 SUPERIOR O UNIVERSAL GRIS</t>
-  </si>
-  <si>
-    <t>VTEMMO</t>
-  </si>
-  <si>
-    <t>EMPAQUES MONTERIA TRANSITO</t>
-  </si>
-  <si>
-    <t>EMLA002</t>
-  </si>
-  <si>
-    <t>LAMINA CARTON 60X90</t>
-  </si>
-  <si>
     <t>VTEMT3</t>
   </si>
   <si>
@@ -562,12 +559,6 @@
     <t>ETIQUETA COD DE BARRA HUEVO M X 30 - K</t>
   </si>
   <si>
-    <t>EMSU001</t>
-  </si>
-  <si>
-    <t>SUJETADOR PLASTIFLECHA 8MM NYLON DOBLE TT CAJA X 10.000 UNID</t>
-  </si>
-  <si>
     <t>DOPJ001</t>
   </si>
   <si>
@@ -628,24 +619,36 @@
     <t>PLASTICO SUPER STRECH 45X10X450 MT SIN CONO</t>
   </si>
   <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
+  </si>
+  <si>
+    <t>VTKI</t>
+  </si>
+  <si>
+    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
+  </si>
+  <si>
     <t>143230</t>
   </si>
   <si>
     <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 18</t>
   </si>
   <si>
-    <t>VTKI</t>
-  </si>
-  <si>
-    <t>BODEGA KIKES - INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>143241</t>
   </si>
   <si>
     <t>BARRA DE PROTEINA 30 GR CHOCOLATE DISPLAY X 6 CAJA X 72</t>
   </si>
   <si>
+    <t>2114379</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
     <t>AFES00</t>
   </si>
   <si>
@@ -667,24 +670,24 @@
     <t>ESTIBAS PLASTICAS</t>
   </si>
   <si>
+    <t>10601</t>
+  </si>
+  <si>
+    <t>HUEVO C X30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>VTKIGT</t>
+  </si>
+  <si>
+    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
+  </si>
+  <si>
     <t>13324</t>
   </si>
   <si>
     <t>HUEVO AA X 30 BAND GRIS AMARRADO TAPA VERDE ALAT - ESTIBADO</t>
   </si>
   <si>
-    <t>VTKIGT</t>
-  </si>
-  <si>
-    <t>BODEGA EVENTUALIDAD ALMACENAMIENTO- INVENTARIO TRA</t>
-  </si>
-  <si>
-    <t>13420</t>
-  </si>
-  <si>
-    <t>HUEVO A X 30 BAND GRIS AMARRADO SOL NACIENTE - ESTIBADO</t>
-  </si>
-  <si>
     <t>EMES001</t>
   </si>
   <si>
@@ -697,18 +700,18 @@
     <t>EMPAQUES LANZA TRANSITO</t>
   </si>
   <si>
+    <t>EMET017</t>
+  </si>
+  <si>
+    <t>ETIQUETA BARRA HUEVO A  X 30 INSUPERABLE EXITO</t>
+  </si>
+  <si>
     <t>VTME</t>
   </si>
   <si>
     <t>CENTRO DE EMPAQUES MEDELLIN -INVENTARIO TRANSITO</t>
   </si>
   <si>
-    <t>VTMO</t>
-  </si>
-  <si>
-    <t>CENTRO DE EMPAQUES MONTERIA-INVENTARIO TRANSITO</t>
-  </si>
-  <si>
     <t>MA0041</t>
   </si>
   <si>
@@ -745,10 +748,10 @@
     <t>FOSFATO MONOCALCICO MCP PHOSPHEA</t>
   </si>
   <si>
-    <t>MDKI038</t>
-  </si>
-  <si>
-    <t>VJ 393760 KIT BOMBA DE VACIO VJ1000 FG 399393</t>
+    <t>MDZU092</t>
+  </si>
+  <si>
+    <t>13001198 Conjunto chapa protectora cinta -Jaula A-</t>
   </si>
   <si>
     <t>VTPL01</t>
@@ -757,18 +760,6 @@
     <t>ALMACEN - PALMAS TRANSITO</t>
   </si>
   <si>
-    <t>MDLA032</t>
-  </si>
-  <si>
-    <t>CLS Z38000091 TUV PL - LAMPARA UV 55W ANT Z200301</t>
-  </si>
-  <si>
-    <t>MDZU092</t>
-  </si>
-  <si>
-    <t>13001198 Conjunto chapa protectora cinta -Jaula A-</t>
-  </si>
-  <si>
     <t>MDZU120</t>
   </si>
   <si>
@@ -787,16 +778,10 @@
     <t>EMPAQUES PALMAS TRANSITO</t>
   </si>
   <si>
-    <t>PTEM050</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 15 L PAGUE 14 ETIQUETADO</t>
-  </si>
-  <si>
-    <t>PTEM052</t>
-  </si>
-  <si>
-    <t>EMPAQUE PET X 12 L ETIQUETADO</t>
+    <t>EMTB001</t>
+  </si>
+  <si>
+    <t>TAPA PARA BANDEJA GRIS</t>
   </si>
   <si>
     <t>VTPSM</t>
@@ -974,13 +959,13 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10410</v>
+        <v>1200</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>46308.347997685181</v>
+        <v>46308.605787037035</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -992,7 +977,7 @@
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3">
-        <v>507</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="4">
@@ -1006,13 +991,13 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>2700</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="2">
-        <v>46306.396504629629</v>
+        <v>46308.605787037035</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1024,7 +1009,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4">
-        <v>1729</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="5">
@@ -1035,16 +1020,16 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2">
-        <v>46306.396504629629</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1056,27 +1041,27 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5">
-        <v>2855</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6">
+        <v>4200</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>9300</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
       <c r="F6" s="2">
-        <v>46308.347997685181</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1088,27 +1073,27 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6">
-        <v>321</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>3300</v>
+        <v>18000</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2">
-        <v>46308.347997685181</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1120,27 +1105,27 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7">
-        <v>1048</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>46080</v>
+        <v>4800</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>46306.396504629629</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -1152,27 +1137,27 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8">
-        <v>895</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>23040</v>
+        <v>9600</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2">
-        <v>46306.396504629629</v>
+        <v>46307.844988425924</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1184,95 +1169,91 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9">
-        <v>899</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>288</v>
+        <v>160560</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F10" s="2">
-        <v>46306.396504629629</v>
+        <v>46308.160625</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10">
-        <v>2534</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>18480</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F11" s="2">
-        <v>46306.396504629629</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11">
-        <v>1771</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>3300</v>
+        <v>84480</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F12" s="2">
-        <v>46307.789201388885</v>
+        <v>46307.992731481478</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1284,39 +1265,41 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12">
-        <v>711</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>1732</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46308.160625</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13">
-        <v>840</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="2">
-        <v>46307.789201388885</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13"/>
+      <c r="I13">
+        <v>440</v>
+      </c>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13">
-        <v>261</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="14">
@@ -1327,28 +1310,30 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D14">
-        <v>6900</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F14" s="2">
-        <v>46307.789201388885</v>
+        <v>46308.160625</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14"/>
+        <v>44</v>
+      </c>
+      <c r="I14">
+        <v>250</v>
+      </c>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14">
-        <v>1092</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="15">
@@ -1359,13 +1344,13 @@
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D15">
-        <v>6000</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2">
         <v>46307.992731481478</v>
@@ -1374,65 +1359,69 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15"/>
+        <v>44</v>
+      </c>
+      <c r="I15">
+        <v>250</v>
+      </c>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15">
-        <v>2975</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46308.160625</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16">
-        <v>4200</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="2">
-        <v>46307.992731481478</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16"/>
+      <c r="I16">
+        <v>5000</v>
+      </c>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16">
-        <v>1159</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F17" s="2">
-        <v>46307.992731481478</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1444,27 +1433,27 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17">
-        <v>2753</v>
+        <v>714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18">
-        <v>4800</v>
+        <v>480</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F18" s="2">
-        <v>46307.992731481478</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1476,27 +1465,27 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18">
-        <v>1673</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
         <v>54</v>
       </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
       <c r="D19">
-        <v>9600</v>
+        <v>2100</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2">
-        <v>46307.844988425924</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1508,27 +1497,27 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19">
-        <v>563</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20">
+        <v>360</v>
+      </c>
+      <c r="E20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20">
-        <v>160560</v>
-      </c>
-      <c r="E20" t="s">
-        <v>50</v>
-      </c>
       <c r="F20" s="2">
-        <v>46308.160625</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1540,27 +1529,27 @@
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20">
-        <v>2989</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D21">
-        <v>18480</v>
+        <v>6000</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2">
-        <v>46307.992731481478</v>
+        <v>46305.703425925924</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
@@ -1572,27 +1561,27 @@
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21">
-        <v>875</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D22">
-        <v>84480</v>
+        <v>600</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2">
-        <v>46307.992731481478</v>
+        <v>46307.56690972222</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1604,163 +1593,155 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22">
-        <v>2454</v>
+        <v>661</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D23">
-        <v>1732</v>
+        <v>900</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2">
-        <v>46308.160625</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23">
-        <v>440</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23">
-        <v>4347</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D24">
-        <v>72</v>
+        <v>139200</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F24" s="2">
-        <v>46308.160625</v>
+        <v>46308.474710648145</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24">
-        <v>3790</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D25">
-        <v>34</v>
+        <v>5940</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F25" s="2">
-        <v>46307.992731481478</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25">
-        <v>2571</v>
+        <v>481</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
         <v>64</v>
       </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
       <c r="D26">
-        <v>30</v>
+        <v>46080</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F26" s="2">
-        <v>46308.160625</v>
+        <v>46308.623483796291</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26">
-        <v>2575</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D27">
-        <v>12000</v>
+        <v>7920</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2">
-        <v>46305.703425925924</v>
+        <v>46306.768437499995</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1772,123 +1753,129 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="L27">
-        <v>714</v>
+        <v>538</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D28">
-        <v>480</v>
+        <v>854</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2">
-        <v>46305.703425925924</v>
+        <v>46308.623483796291</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28"/>
+        <v>44</v>
+      </c>
+      <c r="I28">
+        <v>440</v>
+      </c>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28">
-        <v>395</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D29">
-        <v>2100</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F29" s="2">
-        <v>46305.703425925924</v>
+        <v>46308.623483796291</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29"/>
+        <v>44</v>
+      </c>
+      <c r="I29">
+        <v>250</v>
+      </c>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29">
-        <v>189</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D30">
-        <v>360</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2">
-        <v>46305.703425925924</v>
+        <v>46308.265844907408</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30"/>
+        <v>44</v>
+      </c>
+      <c r="I30">
+        <v>250</v>
+      </c>
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30">
-        <v>41</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31">
+        <v>133800</v>
+      </c>
+      <c r="E31" t="s">
         <v>75</v>
       </c>
-      <c r="C31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31">
-        <v>6000</v>
-      </c>
-      <c r="E31" t="s">
-        <v>69</v>
-      </c>
       <c r="F31" s="2">
-        <v>46305.703425925924</v>
+        <v>46308.062245370369</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1900,27 +1887,27 @@
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31">
-        <v>237</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D32">
-        <v>600</v>
+        <v>84480</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F32" s="2">
-        <v>46307.56690972222</v>
+        <v>46307.731412037036</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -1932,27 +1919,27 @@
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32">
-        <v>661</v>
+        <v>817</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D33">
-        <v>900</v>
+        <v>538104</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F33" s="2">
-        <v>46308.265844907408</v>
+        <v>46308.595717592594</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -1964,27 +1951,27 @@
       <c r="J33"/>
       <c r="K33"/>
       <c r="L33">
-        <v>255</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34">
-        <v>265920</v>
+        <v>15840</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F34" s="2">
-        <v>46307.754907407405</v>
+        <v>46307.731412037036</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1996,259 +1983,259 @@
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34">
-        <v>2125</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D35">
-        <v>5940</v>
+        <v>2683</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2">
-        <v>46308.265844907408</v>
+        <v>46308.595717592594</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35"/>
+        <v>44</v>
+      </c>
+      <c r="I35">
+        <v>440</v>
+      </c>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35">
-        <v>481</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D36">
-        <v>113280</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F36" s="2">
-        <v>46308.263935185183</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36"/>
+        <v>44</v>
+      </c>
+      <c r="I36">
+        <v>250</v>
+      </c>
       <c r="J36"/>
       <c r="K36"/>
       <c r="L36">
-        <v>2827</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D37">
-        <v>7920</v>
+        <v>66</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F37" s="2">
-        <v>46306.768437499995</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37"/>
+        <v>44</v>
+      </c>
+      <c r="I37">
+        <v>250</v>
+      </c>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37">
-        <v>538</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D38">
-        <v>1662</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F38" s="2">
-        <v>46308.265844907408</v>
+        <v>46307.975046296291</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I38">
-        <v>440</v>
+        <v>5000</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38">
-        <v>3612</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D39">
-        <v>100</v>
+        <v>9600</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F39" s="2">
-        <v>46308.265844907408</v>
+        <v>46307.723865740736</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I39"/>
       <c r="J39"/>
       <c r="K39"/>
       <c r="L39">
-        <v>2829</v>
+        <v>961</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D40">
-        <v>34</v>
+        <v>1080</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F40" s="2">
-        <v>46308.265844907408</v>
+        <v>46307.733067129629</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40">
-        <v>250</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40">
-        <v>2154</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D41">
-        <v>49</v>
+        <v>600</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F41" s="2">
-        <v>46307.656215277777</v>
+        <v>46307.733067129629</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41">
-        <v>5000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41">
-        <v>2196</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D42">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F42" s="2">
-        <v>46307.514803240738</v>
+        <v>46307.724537037036</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2260,27 +2247,27 @@
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42">
-        <v>825</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D43">
-        <v>720</v>
+        <v>126720</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F43" s="2">
-        <v>46307.514803240738</v>
+        <v>46308.170590277776</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
@@ -2292,231 +2279,245 @@
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43">
-        <v>363</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D44">
-        <v>600</v>
+        <v>197</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F44" s="2">
-        <v>46306.686631944445</v>
+        <v>46308.490995370368</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44"/>
+        <v>44</v>
+      </c>
+      <c r="I44">
+        <v>440</v>
+      </c>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44">
-        <v>1</v>
+        <v>5607</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D45">
-        <v>18000</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F45" s="2">
-        <v>46307.514803240738</v>
+        <v>46308.490995370368</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45"/>
+        <v>44</v>
+      </c>
+      <c r="I45">
+        <v>250</v>
+      </c>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45">
-        <v>1207</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D46">
-        <v>2400</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F46" s="2">
-        <v>46306.679768518516</v>
+        <v>46307.715439814812</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46"/>
+        <v>44</v>
+      </c>
+      <c r="I46">
+        <v>250</v>
+      </c>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46">
-        <v>1050</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D47">
-        <v>1200</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F47" s="2">
-        <v>46306.679768518516</v>
+        <v>46308.169803240737</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47"/>
+        <v>51</v>
+      </c>
+      <c r="I47">
+        <v>5000</v>
+      </c>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47">
-        <v>632</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48">
+        <v>1000</v>
+      </c>
+      <c r="E48" t="s">
+        <v>83</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46308.326608796291</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
         <v>84</v>
       </c>
-      <c r="D48">
-        <v>10500</v>
-      </c>
-      <c r="E48" t="s">
-        <v>85</v>
-      </c>
-      <c r="F48" s="2">
-        <v>46306.679768518516</v>
-      </c>
-      <c r="G48" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48"/>
+      <c r="I48">
+        <v>236</v>
+      </c>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48">
-        <v>1064</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D49">
-        <v>133800</v>
+        <v>35840</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F49" s="2">
-        <v>46308.062245370369</v>
+        <v>46308.427141203705</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49"/>
+        <v>87</v>
+      </c>
+      <c r="I49">
+        <v>4060</v>
+      </c>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49">
-        <v>79</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D50">
-        <v>84480</v>
+        <v>4480</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F50" s="2">
-        <v>46307.731412037036</v>
+        <v>46308.427141203705</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50"/>
+        <v>87</v>
+      </c>
+      <c r="I50">
+        <v>4060</v>
+      </c>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50">
-        <v>817</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="51">
@@ -2527,324 +2528,330 @@
         <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D51">
-        <v>6000</v>
+        <v>8960</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F51" s="2">
-        <v>46307.514803240738</v>
+        <v>46308.427141203705</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51"/>
+        <v>87</v>
+      </c>
+      <c r="I51">
+        <v>31360</v>
+      </c>
       <c r="J51"/>
       <c r="K51"/>
       <c r="L51">
-        <v>523</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D52">
-        <v>655704</v>
+        <v>8400</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F52" s="2">
-        <v>46307.975046296291</v>
+        <v>46308.427141203705</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52"/>
+        <v>87</v>
+      </c>
+      <c r="I52">
+        <v>16800</v>
+      </c>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52">
-        <v>3268</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" t="s">
         <v>82</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53">
+        <v>1000</v>
+      </c>
+      <c r="E53" t="s">
         <v>83</v>
       </c>
-      <c r="C53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53">
-        <v>15840</v>
-      </c>
-      <c r="E53" t="s">
-        <v>85</v>
-      </c>
       <c r="F53" s="2">
-        <v>46307.731412037036</v>
+        <v>46308.485023148147</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53"/>
+        <v>87</v>
+      </c>
+      <c r="I53">
+        <v>7000</v>
+      </c>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53">
-        <v>349</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D54">
-        <v>3207</v>
+        <v>3920</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F54" s="2">
-        <v>46307.975046296291</v>
+        <v>46308.427141203705</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I54">
-        <v>440</v>
+        <v>42000</v>
       </c>
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54">
-        <v>4115</v>
+        <v>604</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55">
-        <v>132</v>
+        <v>2497</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F55" s="2">
-        <v>46307.975046296291</v>
+        <v>46305.42895833333</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I55">
-        <v>250</v>
+        <v>32000</v>
       </c>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55">
-        <v>3180</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D56">
-        <v>66</v>
+        <v>288</v>
       </c>
       <c r="E56" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F56" s="2">
-        <v>46307.975046296291</v>
+        <v>46301.62263888889</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
-      </c>
-      <c r="I56">
-        <v>250</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56">
-        <v>1822</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D57">
-        <v>182</v>
+        <v>480</v>
       </c>
       <c r="E57" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F57" s="2">
-        <v>46307.975046296291</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>65</v>
-      </c>
-      <c r="I57">
-        <v>5000</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
       <c r="L57">
-        <v>2159</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D58">
-        <v>9600</v>
+        <v>720</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F58" s="2">
-        <v>46307.723865740736</v>
+        <v>46297.4564699074</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58">
-        <v>961</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D59">
-        <v>1080</v>
+        <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F59" s="2">
-        <v>46307.733067129629</v>
+        <v>46305.61546296296</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59"/>
+        <v>87</v>
+      </c>
+      <c r="I59">
+        <v>60</v>
+      </c>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59">
-        <v>2454</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D60">
-        <v>600</v>
+        <v>4325</v>
       </c>
       <c r="E60" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F60" s="2">
-        <v>46307.733067129629</v>
+        <v>46308.4419212963</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
-      </c>
-      <c r="I60"/>
+        <v>44</v>
+      </c>
+      <c r="I60">
+        <v>440</v>
+      </c>
       <c r="J60"/>
       <c r="K60"/>
       <c r="L60">
-        <v>4791</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="61">
@@ -2855,86 +2862,90 @@
         <v>46</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D61">
-        <v>3600</v>
+        <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F61" s="2">
-        <v>46307.724537037036</v>
+        <v>46308.4419212963</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61"/>
+        <v>44</v>
+      </c>
+      <c r="I61">
+        <v>250</v>
+      </c>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61">
-        <v>1854</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D62">
-        <v>126720</v>
+        <v>105</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F62" s="2">
-        <v>46308.170590277776</v>
+        <v>46308.4419212963</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62"/>
+        <v>44</v>
+      </c>
+      <c r="I62">
+        <v>250</v>
+      </c>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62">
-        <v>3818</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D63">
-        <v>1177</v>
+        <v>1920</v>
       </c>
       <c r="E63" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="F63" s="2">
-        <v>46308.170590277776</v>
+        <v>46308.442824074074</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I63">
         <v>440</v>
@@ -2942,33 +2953,33 @@
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63">
-        <v>5606</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D64">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E64" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="F64" s="2">
-        <v>46308.169803240737</v>
+        <v>46308.442824074074</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I64">
         <v>250</v>
@@ -2976,825 +2987,827 @@
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64">
-        <v>4868</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F65" s="2">
-        <v>46307.715439814812</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I65">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65">
-        <v>2771</v>
+        <v>816</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D66">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="E66" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F66" s="2">
-        <v>46308.169803240737</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="I66">
-        <v>5000</v>
+        <v>244</v>
       </c>
       <c r="J66"/>
       <c r="K66"/>
       <c r="L66">
-        <v>3683</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D67">
-        <v>69120</v>
+        <v>390</v>
       </c>
       <c r="E67" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F67" s="2">
-        <v>46305.832569444443</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67"/>
+        <v>87</v>
+      </c>
+      <c r="I67">
+        <v>1550</v>
+      </c>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67">
-        <v>185</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D68">
-        <v>288</v>
+        <v>2000</v>
       </c>
       <c r="E68" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F68" s="2">
-        <v>46305.832569444443</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I68">
-        <v>440</v>
+        <v>30000</v>
       </c>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D69">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F69" s="2">
-        <v>46305.832569444443</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I69">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="J69"/>
       <c r="K69"/>
       <c r="L69">
-        <v>131</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D70">
-        <v>255360</v>
+        <v>10000</v>
       </c>
       <c r="E70" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F70" s="2">
-        <v>46306.44899305555</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70"/>
+        <v>87</v>
+      </c>
+      <c r="I70">
+        <v>100000</v>
+      </c>
       <c r="J70"/>
       <c r="K70"/>
       <c r="L70">
-        <v>2908</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D71">
-        <v>5580</v>
+        <v>3920</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F71" s="2">
-        <v>46306.448460648149</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71"/>
+        <v>87</v>
+      </c>
+      <c r="I71">
+        <v>42000</v>
+      </c>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71">
-        <v>233</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D72">
-        <v>1095</v>
+        <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F72" s="2">
-        <v>46306.44899305555</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="H72" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I72">
-        <v>440</v>
+        <v>60</v>
       </c>
       <c r="J72"/>
       <c r="K72"/>
       <c r="L72">
-        <v>3174</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F73" s="2">
-        <v>46306.44899305555</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="I73">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73">
-        <v>2878</v>
+        <v>940</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D74">
-        <v>14</v>
+        <v>1600</v>
       </c>
       <c r="E74" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F74" s="2">
-        <v>46306.44899305555</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G74" t="s">
         <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I74">
-        <v>250</v>
+        <v>32000</v>
       </c>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74">
-        <v>415</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D75">
-        <v>42</v>
+        <v>2000</v>
       </c>
       <c r="E75" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="F75" s="2">
-        <v>46306.44899305555</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>65</v>
-      </c>
-      <c r="I75">
-        <v>5000</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
       <c r="L75">
-        <v>2037</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
+        <v>119</v>
+      </c>
+      <c r="D76">
+        <v>1400</v>
+      </c>
+      <c r="E76" t="s">
+        <v>120</v>
+      </c>
+      <c r="F76" s="2">
+        <v>46308.511898148143</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
         <v>100</v>
       </c>
-      <c r="B76" t="s">
-        <v>101</v>
-      </c>
-      <c r="C76" t="s">
-        <v>102</v>
-      </c>
-      <c r="D76">
-        <v>1000</v>
-      </c>
-      <c r="E76" t="s">
-        <v>103</v>
-      </c>
-      <c r="F76" s="2">
-        <v>46308.326608796291</v>
-      </c>
-      <c r="G76" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" t="s">
-        <v>104</v>
-      </c>
-      <c r="I76">
-        <v>236</v>
-      </c>
+      <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76">
-        <v>1916</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D77">
-        <v>2497</v>
+        <v>1600</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F77" s="2">
-        <v>46305.42895833333</v>
+        <v>46308.511898148143</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>107</v>
-      </c>
-      <c r="I77">
-        <v>32000</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77">
-        <v>1890</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>138</v>
+      </c>
+      <c r="B78" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78">
+        <v>900</v>
+      </c>
+      <c r="E78" t="s">
+        <v>120</v>
+      </c>
+      <c r="F78" s="2">
+        <v>46308.511898148143</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
         <v>100</v>
       </c>
-      <c r="B78" t="s">
-        <v>101</v>
-      </c>
-      <c r="C78" t="s">
-        <v>108</v>
-      </c>
-      <c r="D78">
-        <v>500</v>
-      </c>
-      <c r="E78" t="s">
-        <v>109</v>
-      </c>
-      <c r="F78" s="2">
-        <v>46308.327928240738</v>
-      </c>
-      <c r="G78" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" t="s">
-        <v>104</v>
-      </c>
-      <c r="I78">
-        <v>236</v>
-      </c>
+      <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
       <c r="L78">
-        <v>1199</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="C79" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D79">
-        <v>850</v>
+        <v>2240</v>
       </c>
       <c r="E79" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="F79" s="2">
-        <v>46308.327928240738</v>
+        <v>46308.444699074069</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="I79">
-        <v>1550</v>
+        <v>440</v>
       </c>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79">
-        <v>99</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D80">
-        <v>3840</v>
+        <v>154</v>
       </c>
       <c r="E80" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="F80" s="2">
-        <v>46308.327928240738</v>
+        <v>46308.444699074069</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="I80">
-        <v>32000</v>
+        <v>250</v>
       </c>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80">
-        <v>1316</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C81" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="D81">
-        <v>4800</v>
+        <v>73152</v>
       </c>
       <c r="E81" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="F81" s="2">
-        <v>46308.327928240738</v>
+        <v>46307.609467592592</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
       <c r="L81">
-        <v>85</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="D82">
-        <v>3840</v>
+        <v>57600</v>
       </c>
       <c r="E82" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="F82" s="2">
-        <v>46308.327928240738</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82">
-        <v>73</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="D83">
-        <v>1000</v>
+        <v>288000</v>
       </c>
       <c r="E83" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="F83" s="2">
-        <v>46308.327928240738</v>
+        <v>46308.468726851846</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83">
-        <v>49</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D84">
-        <v>288</v>
+        <v>1440</v>
       </c>
       <c r="E84" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F84" s="2">
-        <v>46301.62263888889</v>
+        <v>46308.468726851846</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>123</v>
-      </c>
-      <c r="I84"/>
+        <v>44</v>
+      </c>
+      <c r="I84">
+        <v>440</v>
+      </c>
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84">
-        <v>7</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="C85" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D85">
-        <v>480</v>
+        <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F85" s="2">
-        <v>46297.4564699074</v>
+        <v>46308.468726851846</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>123</v>
-      </c>
-      <c r="I85"/>
+        <v>44</v>
+      </c>
+      <c r="I85">
+        <v>250</v>
+      </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85">
-        <v>5</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="B86" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="C86" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D86">
-        <v>720</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F86" s="2">
-        <v>46297.4564699074</v>
+        <v>46308.468726851846</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>123</v>
-      </c>
-      <c r="I86"/>
+        <v>44</v>
+      </c>
+      <c r="I86">
+        <v>250</v>
+      </c>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86">
-        <v>5</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="E87" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F87" s="2">
-        <v>46305.61546296296</v>
+        <v>46307.77579861111</v>
       </c>
       <c r="G87" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="I87">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="J87"/>
       <c r="K87"/>
       <c r="L87">
-        <v>9</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D88">
-        <v>2000</v>
+        <v>105600</v>
       </c>
       <c r="E88" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="F88" s="2">
-        <v>46305.498599537037</v>
+        <v>46307.81627314815</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>112</v>
-      </c>
-      <c r="I88">
-        <v>10000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88">
-        <v>48</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B89" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D89">
-        <v>73152</v>
+        <v>544580</v>
       </c>
       <c r="E89" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F89" s="2">
-        <v>46307.609467592592</v>
+        <v>46308.404780092591</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
@@ -3806,27 +3819,27 @@
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89">
-        <v>1634</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D90">
-        <v>57600</v>
+        <v>720</v>
       </c>
       <c r="E90" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F90" s="2">
-        <v>46307.77579861111</v>
+        <v>46308.61824074074</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
@@ -3838,99 +3851,101 @@
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90">
-        <v>1867</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="C91" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D91">
-        <v>704640</v>
+        <v>2713</v>
       </c>
       <c r="E91" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F91" s="2">
-        <v>46307.609467592592</v>
+        <v>46308.61824074074</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91"/>
+        <v>44</v>
+      </c>
+      <c r="I91">
+        <v>440</v>
+      </c>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91">
-        <v>294</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C92" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D92">
-        <v>3176</v>
+        <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F92" s="2">
-        <v>46307.77579861111</v>
+        <v>46308.619456018518</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I92">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92">
-        <v>4479</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C93" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D93">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="E93" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F93" s="2">
-        <v>46307.77579861111</v>
+        <v>46308.404780092591</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I93">
         <v>250</v>
@@ -3938,553 +3953,571 @@
       <c r="J93"/>
       <c r="K93"/>
       <c r="L93">
-        <v>4166</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D94">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="E94" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F94" s="2">
-        <v>46307.77579861111</v>
+        <v>46307.987523148149</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I94">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94">
-        <v>1506</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D95">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F95" s="2">
-        <v>46307.77579861111</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="I95">
-        <v>5000</v>
+        <v>130</v>
       </c>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95">
-        <v>2624</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D96">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="E96" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F96" s="2">
-        <v>46306.963043981479</v>
+        <v>46290.555405092593</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96"/>
+        <v>16</v>
+      </c>
+      <c r="I96">
+        <v>200</v>
+      </c>
       <c r="J96"/>
       <c r="K96"/>
       <c r="L96">
-        <v>1374</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D97">
-        <v>4200</v>
+        <v>500</v>
       </c>
       <c r="E97" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="F97" s="2">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97"/>
+        <v>87</v>
+      </c>
+      <c r="I97">
+        <v>10000</v>
+      </c>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97">
-        <v>301</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D98">
-        <v>3360</v>
+        <v>840</v>
       </c>
       <c r="E98" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F98" s="2">
-        <v>46304</v>
+        <v>46306.83394675926</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98"/>
+        <v>87</v>
+      </c>
+      <c r="I98">
+        <v>31360</v>
+      </c>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98">
-        <v>281</v>
+        <v>410</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="C99" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D99">
-        <v>13200</v>
+        <v>3920</v>
       </c>
       <c r="E99" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="F99" s="2">
-        <v>46304</v>
+        <v>46305.130706018514</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99"/>
+        <v>87</v>
+      </c>
+      <c r="I99">
+        <v>20020</v>
+      </c>
       <c r="J99"/>
       <c r="K99"/>
       <c r="L99">
-        <v>313</v>
+        <v>669</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="B100" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="C100" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D100">
-        <v>66816</v>
+        <v>850</v>
       </c>
       <c r="E100" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F100" s="2">
-        <v>46308.303368055553</v>
+        <v>46295.8800462963</v>
       </c>
       <c r="G100" t="s">
         <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100"/>
+        <v>172</v>
+      </c>
+      <c r="I100">
+        <v>5000</v>
+      </c>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100">
-        <v>1894</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="D101">
-        <v>105600</v>
+        <v>1000</v>
       </c>
       <c r="E101" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="F101" s="2">
-        <v>46307.81627314815</v>
+        <v>46306.912569444445</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101"/>
+        <v>87</v>
+      </c>
+      <c r="I101">
+        <v>1550</v>
+      </c>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101">
-        <v>1413</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="B102" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="C102" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="D102">
-        <v>642500</v>
+        <v>400</v>
       </c>
       <c r="E102" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F102" s="2">
-        <v>46307.987523148149</v>
+        <v>45185</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102"/>
+        <v>87</v>
+      </c>
+      <c r="I102">
+        <v>7000</v>
+      </c>
       <c r="J102"/>
       <c r="K102"/>
       <c r="L102">
-        <v>5304</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D103">
-        <v>136800</v>
+        <v>3780</v>
       </c>
       <c r="E103" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="F103" s="2">
-        <v>46307.991168981476</v>
+        <v>46307.517488425925</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103"/>
+        <v>87</v>
+      </c>
+      <c r="I103">
+        <v>31360</v>
+      </c>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103">
-        <v>179</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="C104" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D104">
-        <v>3688</v>
+        <v>160</v>
       </c>
       <c r="E104" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="F104" s="2">
-        <v>46307.991168981476</v>
+        <v>46304.581412037034</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I104">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104">
-        <v>9343</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="C105" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D105">
-        <v>148</v>
+        <v>600</v>
       </c>
       <c r="E105" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="F105" s="2">
-        <v>46308.303368055553</v>
+        <v>46307.517488425925</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I105">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="J105"/>
       <c r="K105"/>
       <c r="L105">
-        <v>6577</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="B106" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D106">
-        <v>68</v>
+        <v>30000</v>
       </c>
       <c r="E106" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="F106" s="2">
-        <v>46308.303368055553</v>
+        <v>46280.943472222221</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I106">
-        <v>250</v>
+        <v>100000</v>
       </c>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106">
-        <v>5333</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="B107" t="s">
-        <v>64</v>
+        <v>184</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="D107">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="E107" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="F107" s="2">
-        <v>46307.987523148149</v>
+        <v>46303.692881944444</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="I107">
-        <v>5000</v>
+        <v>14</v>
       </c>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107">
-        <v>3055</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="C108" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="D108">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="E108" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F108" s="2">
-        <v>46307.626539351848</v>
+        <v>46297.650706018518</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>21</v>
-      </c>
-      <c r="I108"/>
+        <v>84</v>
+      </c>
+      <c r="I108">
+        <v>236</v>
+      </c>
       <c r="J108"/>
       <c r="K108"/>
       <c r="L108">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="D109">
-        <v>9</v>
+        <v>1500</v>
       </c>
       <c r="E109" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="F109" s="2">
-        <v>46290.555405092593</v>
+        <v>46298.789583333331</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="I109">
-        <v>130</v>
+        <v>200000</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="B110" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="C110" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="F110" s="2">
-        <v>46290.555405092593</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
@@ -4493,1989 +4526,1583 @@
         <v>16</v>
       </c>
       <c r="I110">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="B111" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="D111">
-        <v>840</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>46306.83394675926</v>
+        <v>46265.776967592588</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="I111">
-        <v>31360</v>
+        <v>43</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
       <c r="L111">
-        <v>410</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="C112" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="D112">
-        <v>2100</v>
+        <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="F112" s="2">
-        <v>46306.872395833328</v>
+        <v>46265.788981481477</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="I112">
-        <v>42420</v>
+        <v>15</v>
       </c>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112">
-        <v>890</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="B113" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="D113">
-        <v>3920</v>
+        <v>480</v>
       </c>
       <c r="E113" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="F113" s="2">
-        <v>46305.130706018514</v>
+        <v>46304.513993055552</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I113">
-        <v>6160</v>
+        <v>11520</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113">
-        <v>669</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="B114" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="C114" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="D114">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="E114" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="F114" s="2">
-        <v>46295.8800462963</v>
+        <v>46306.64980324074</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="I114">
-        <v>5000</v>
+        <v>1550</v>
       </c>
       <c r="J114"/>
       <c r="K114"/>
       <c r="L114">
-        <v>1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="C115" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="D115">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="E115" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="F115" s="2">
-        <v>46306.912569444445</v>
+        <v>46306.64980324074</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="H115" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I115">
-        <v>1550</v>
+        <v>100</v>
       </c>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115">
-        <v>192</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="B116" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="D116">
-        <v>1260</v>
+        <v>360</v>
       </c>
       <c r="E116" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="F116" s="2">
-        <v>46306.975057870368</v>
+        <v>46308.511782407404</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>112</v>
-      </c>
-      <c r="I116">
-        <v>5880</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I116"/>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116">
-        <v>60</v>
+        <v>722</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>208</v>
       </c>
       <c r="C117" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="D117">
-        <v>600</v>
+        <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="F117" s="2">
-        <v>46306.975057870368</v>
+        <v>46302.905416666668</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>112</v>
-      </c>
-      <c r="I117">
-        <v>1550</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="I117"/>
       <c r="J117"/>
       <c r="K117"/>
       <c r="L117">
-        <v>133</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="C118" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="D118">
-        <v>400</v>
+        <v>72</v>
       </c>
       <c r="E118" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="F118" s="2">
-        <v>45185</v>
+        <v>46301</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>112</v>
-      </c>
-      <c r="I118">
-        <v>7000</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="I118"/>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="B119" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="C119" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D119">
-        <v>3780</v>
+        <v>7440</v>
       </c>
       <c r="E119" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="F119" s="2">
-        <v>46307.517488425925</v>
+        <v>46308.456273148149</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>112</v>
-      </c>
-      <c r="I119">
-        <v>31360</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I119"/>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119">
-        <v>265</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" t="s">
+        <v>212</v>
+      </c>
+      <c r="C120" t="s">
+        <v>205</v>
+      </c>
+      <c r="D120">
         <v>180</v>
       </c>
-      <c r="B120" t="s">
-        <v>181</v>
-      </c>
-      <c r="C120" t="s">
-        <v>178</v>
-      </c>
-      <c r="D120">
-        <v>160</v>
-      </c>
       <c r="E120" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="F120" s="2">
-        <v>46304.581412037034</v>
+        <v>46308.457407407404</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>112</v>
-      </c>
-      <c r="I120">
-        <v>180</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I120"/>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120">
-        <v>171</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="B121" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C121" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D121">
-        <v>600</v>
+        <v>186</v>
       </c>
       <c r="E121" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="F121" s="2">
-        <v>46307.517488425925</v>
+        <v>44946.553055555552</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="I121">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="J121"/>
       <c r="K121"/>
       <c r="L121">
-        <v>198</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="B122" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="C122" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D122">
-        <v>30000</v>
+        <v>93</v>
       </c>
       <c r="E122" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="F122" s="2">
-        <v>46280.943472222221</v>
+        <v>45777.752291666664</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="I122">
-        <v>190000</v>
+        <v>16</v>
       </c>
       <c r="J122"/>
       <c r="K122"/>
       <c r="L122">
-        <v>102</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="B123" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="C123" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="E123" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F123" s="2">
-        <v>46303.692881944444</v>
+        <v>44426</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I123">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="B124" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="C124" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D124">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E124" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F124" s="2">
-        <v>46297.650706018518</v>
+        <v>46308.4506712963</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="I124">
-        <v>236</v>
+        <v>5000</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124">
-        <v>28</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="B125" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C125" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D125">
-        <v>1500</v>
+        <v>34560</v>
       </c>
       <c r="E125" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="F125" s="2">
-        <v>46298.789583333331</v>
+        <v>46308.679942129631</v>
       </c>
       <c r="G125" t="s">
         <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="I125">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
       <c r="L125">
-        <v>7</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="B126" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="C126" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="E126" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="F126" s="2">
-        <v>46265.788981481477</v>
+        <v>46308.508506944439</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>16</v>
-      </c>
-      <c r="I126">
-        <v>50</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I126"/>
       <c r="J126"/>
       <c r="K126"/>
       <c r="L126">
-        <v>14</v>
+        <v>456</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B127" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C127" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="E127" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="F127" s="2">
-        <v>46265.776967592588</v>
+        <v>46308.509652777779</v>
       </c>
       <c r="G127" t="s">
         <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>16</v>
-      </c>
-      <c r="I127">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I127"/>
       <c r="J127"/>
       <c r="K127"/>
       <c r="L127">
-        <v>11</v>
+        <v>583</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="B128" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C128" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>1380</v>
       </c>
       <c r="E128" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="F128" s="2">
-        <v>46265.788981481477</v>
+        <v>46300.329861111109</v>
       </c>
       <c r="G128" t="s">
         <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="I128">
-        <v>15</v>
+        <v>660</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
       <c r="L128">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="B129" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="C129" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="D129">
-        <v>480</v>
+        <v>4000</v>
       </c>
       <c r="E129" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="F129" s="2">
-        <v>46304.513993055552</v>
+        <v>46308.67555555555</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="I129">
-        <v>19200</v>
+        <v>5000</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
       <c r="L129">
-        <v>58</v>
+        <v>265</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C130" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="D130">
         <v>400</v>
       </c>
       <c r="E130" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="F130" s="2">
-        <v>46306.64980324074</v>
+        <v>46308.450289351851</v>
       </c>
       <c r="G130" t="s">
         <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I130">
-        <v>1550</v>
+        <v>7000</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
       <c r="L130">
-        <v>133</v>
+        <v>711</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="B131" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="C131" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>86400</v>
       </c>
       <c r="E131" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="F131" s="2">
-        <v>46306.64980324074</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G131" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>112</v>
-      </c>
-      <c r="I131">
-        <v>120</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I131"/>
       <c r="J131"/>
       <c r="K131"/>
       <c r="L131">
-        <v>55</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C132" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D132">
-        <v>144</v>
+        <v>278400</v>
       </c>
       <c r="E132" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F132" s="2">
-        <v>46302.905416666668</v>
+        <v>46307.885034722218</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="I132"/>
       <c r="J132"/>
       <c r="K132"/>
       <c r="L132">
-        <v>26</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>210</v>
+        <v>42</v>
       </c>
       <c r="B133" t="s">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c r="C133" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D133">
-        <v>72</v>
+        <v>1520</v>
       </c>
       <c r="E133" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F133" s="2">
-        <v>46301</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>123</v>
-      </c>
-      <c r="I133"/>
+        <v>44</v>
+      </c>
+      <c r="I133">
+        <v>440</v>
+      </c>
       <c r="J133"/>
       <c r="K133"/>
       <c r="L133">
-        <v>18</v>
+        <v>5144</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>213</v>
+        <v>46</v>
       </c>
       <c r="C134" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D134">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="E134" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F134" s="2">
-        <v>44946.553055555552</v>
+        <v>46308.161539351851</v>
       </c>
       <c r="G134" t="s">
         <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I134">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
       <c r="L134">
-        <v>2</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D135">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F135" s="2">
-        <v>45777.752291666664</v>
+        <v>46308.115034722221</v>
       </c>
       <c r="G135" t="s">
         <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>216</v>
+        <v>44</v>
       </c>
       <c r="I135">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
       <c r="L135">
-        <v>7</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C136" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="D136">
-        <v>55</v>
+        <v>899100</v>
       </c>
       <c r="E136" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="F136" s="2">
-        <v>44426</v>
+        <v>46296</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="H136" t="s">
-        <v>65</v>
+        <v>239</v>
       </c>
       <c r="I136">
-        <v>2</v>
+        <v>950000</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
       <c r="L136">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B137" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C137" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D137">
-        <v>600</v>
+        <v>2530000</v>
       </c>
       <c r="E137" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="F137" s="2">
-        <v>46307.297361111108</v>
+        <v>46266</v>
       </c>
       <c r="G137" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="H137" t="s">
-        <v>21</v>
-      </c>
-      <c r="I137"/>
+        <v>239</v>
+      </c>
+      <c r="I137">
+        <v>1265000</v>
+      </c>
       <c r="J137"/>
       <c r="K137"/>
       <c r="L137">
-        <v>455</v>
+        <v>48</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C138" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D138">
-        <v>900</v>
+        <v>750000</v>
       </c>
       <c r="E138" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="F138" s="2">
-        <v>46307.561365740738</v>
+        <v>46266</v>
       </c>
       <c r="G138" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="H138" t="s">
-        <v>21</v>
-      </c>
-      <c r="I138"/>
+        <v>239</v>
+      </c>
+      <c r="I138">
+        <v>750000</v>
+      </c>
       <c r="J138"/>
       <c r="K138"/>
       <c r="L138">
-        <v>581</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="B139" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C139" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D139">
-        <v>1380</v>
+        <v>52000</v>
       </c>
       <c r="E139" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F139" s="2">
-        <v>46300.329861111109</v>
+        <v>46294</v>
       </c>
       <c r="G139" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="H139" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="I139">
-        <v>660</v>
+        <v>26000</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
       <c r="L139">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="B140" t="s">
-        <v>23</v>
+        <v>247</v>
       </c>
       <c r="C140" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="D140">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E140" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="F140" s="2">
-        <v>46303.877905092588</v>
+        <v>46303.34983796296</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>21</v>
-      </c>
-      <c r="I140"/>
+        <v>51</v>
+      </c>
+      <c r="I140">
+        <v>10</v>
+      </c>
       <c r="J140"/>
       <c r="K140"/>
       <c r="L140">
-        <v>176</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>251</v>
       </c>
       <c r="C141" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="D141">
-        <v>86400</v>
+        <v>4</v>
       </c>
       <c r="E141" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="F141" s="2">
-        <v>46308.115034722221</v>
+        <v>46304.302789351852</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
       <c r="H141" t="s">
-        <v>21</v>
-      </c>
-      <c r="I141"/>
+        <v>51</v>
+      </c>
+      <c r="I141">
+        <v>15</v>
+      </c>
       <c r="J141"/>
       <c r="K141"/>
       <c r="L141">
-        <v>1883</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="C142" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="D142">
-        <v>278400</v>
+        <v>4</v>
       </c>
       <c r="E142" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="F142" s="2">
-        <v>46307.885034722218</v>
+        <v>46304.316724537035</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>21</v>
-      </c>
-      <c r="I142"/>
+        <v>51</v>
+      </c>
+      <c r="I142">
+        <v>14</v>
+      </c>
       <c r="J142"/>
       <c r="K142"/>
       <c r="L142">
-        <v>313</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="B143" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="C143" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D143">
-        <v>1520</v>
+        <v>500</v>
       </c>
       <c r="E143" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="F143" s="2">
-        <v>46308.115034722221</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I143">
-        <v>440</v>
+        <v>236</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
       <c r="L143">
-        <v>5144</v>
+        <v>515</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="B144" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C144" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D144">
-        <v>82</v>
+        <v>22400</v>
       </c>
       <c r="E144" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="F144" s="2">
-        <v>46308.161539351851</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I144">
-        <v>250</v>
+        <v>4060</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="L144">
-        <v>4547</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B145" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C145" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D145">
-        <v>38</v>
+        <v>4480</v>
       </c>
       <c r="E145" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="F145" s="2">
-        <v>46308.115034722221</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I145">
-        <v>250</v>
+        <v>4060</v>
       </c>
       <c r="J145"/>
       <c r="K145"/>
       <c r="L145">
-        <v>2596</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="B146" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C146" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D146">
-        <v>84480</v>
+        <v>7680</v>
       </c>
       <c r="E146" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F146" s="2">
-        <v>46306.948807870365</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>21</v>
-      </c>
-      <c r="I146"/>
+        <v>87</v>
+      </c>
+      <c r="I146">
+        <v>11520</v>
+      </c>
       <c r="J146"/>
       <c r="K146"/>
       <c r="L146">
-        <v>379</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D147">
-        <v>248640</v>
+        <v>13440</v>
       </c>
       <c r="E147" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F147" s="2">
-        <v>46306.948807870365</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>21</v>
-      </c>
-      <c r="I147"/>
+        <v>87</v>
+      </c>
+      <c r="I147">
+        <v>31360</v>
+      </c>
       <c r="J147"/>
       <c r="K147"/>
       <c r="L147">
-        <v>33</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="B148" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D148">
-        <v>115200</v>
+        <v>4200</v>
       </c>
       <c r="E148" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F148" s="2">
-        <v>46308.275497685187</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G148" t="s">
         <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>21</v>
-      </c>
-      <c r="I148"/>
+        <v>87</v>
+      </c>
+      <c r="I148">
+        <v>16800</v>
+      </c>
       <c r="J148"/>
       <c r="K148"/>
       <c r="L148">
-        <v>73</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="C149" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D149">
-        <v>1868</v>
+        <v>4480</v>
       </c>
       <c r="E149" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F149" s="2">
-        <v>46308.275497685187</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I149">
-        <v>440</v>
+        <v>15960</v>
       </c>
       <c r="J149"/>
       <c r="K149"/>
       <c r="L149">
-        <v>1632</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>37</v>
+        <v>164</v>
       </c>
       <c r="B150" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C150" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D150">
-        <v>88</v>
+        <v>4480</v>
       </c>
       <c r="E150" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F150" s="2">
-        <v>46308.275497685187</v>
+        <v>46308.436608796292</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I150">
-        <v>250</v>
+        <v>20020</v>
       </c>
       <c r="J150"/>
       <c r="K150"/>
       <c r="L150">
-        <v>1198</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="B151" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C151" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D151">
-        <v>42</v>
+        <v>3600</v>
       </c>
       <c r="E151" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F151" s="2">
-        <v>46308.275497685187</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>36</v>
-      </c>
-      <c r="I151">
-        <v>250</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I151"/>
       <c r="J151"/>
       <c r="K151"/>
       <c r="L151">
-        <v>1065</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B152" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="C152" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="D152">
-        <v>88</v>
+        <v>3600</v>
       </c>
       <c r="E152" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="F152" s="2">
-        <v>46306.948807870365</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>65</v>
-      </c>
-      <c r="I152">
-        <v>5000</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I152"/>
       <c r="J152"/>
       <c r="K152"/>
       <c r="L152">
-        <v>786</v>
+        <v>55</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>233</v>
+        <v>138</v>
       </c>
       <c r="B153" t="s">
-        <v>234</v>
+        <v>139</v>
       </c>
       <c r="C153" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="D153">
-        <v>899100</v>
+        <v>1800</v>
       </c>
       <c r="E153" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="F153" s="2">
-        <v>46296</v>
+        <v>46308.346365740741</v>
       </c>
       <c r="G153" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>238</v>
-      </c>
-      <c r="I153">
-        <v>950000</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I153"/>
       <c r="J153"/>
       <c r="K153"/>
       <c r="L153">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
+        <v>244</v>
+      </c>
+      <c r="B154" t="s">
+        <v>245</v>
+      </c>
+      <c r="C154" t="s">
+        <v>258</v>
+      </c>
+      <c r="D154">
+        <v>52000</v>
+      </c>
+      <c r="E154" t="s">
+        <v>259</v>
+      </c>
+      <c r="F154" s="2">
+        <v>46296</v>
+      </c>
+      <c r="G154" t="s">
+        <v>238</v>
+      </c>
+      <c r="H154" t="s">
         <v>239</v>
       </c>
-      <c r="B154" t="s">
-        <v>240</v>
-      </c>
-      <c r="C154" t="s">
-        <v>235</v>
-      </c>
-      <c r="D154">
-        <v>2530000</v>
-      </c>
-      <c r="E154" t="s">
-        <v>236</v>
-      </c>
-      <c r="F154" s="2">
-        <v>46266</v>
-      </c>
-      <c r="G154" t="s">
-        <v>237</v>
-      </c>
-      <c r="H154" t="s">
-        <v>238</v>
-      </c>
       <c r="I154">
-        <v>1265000</v>
+        <v>26000</v>
       </c>
       <c r="J154"/>
       <c r="K154"/>
       <c r="L154">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="B155" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C155" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="D155">
-        <v>750000</v>
+        <v>49720</v>
       </c>
       <c r="E155" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="F155" s="2">
-        <v>46266</v>
+        <v>46306</v>
       </c>
       <c r="G155" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>238</v>
-      </c>
-      <c r="I155">
-        <v>750000</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I155"/>
       <c r="J155"/>
       <c r="K155"/>
       <c r="L155">
-        <v>45</v>
+        <v>596</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C156" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="D156">
-        <v>52000</v>
+        <v>520</v>
       </c>
       <c r="E156" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="F156" s="2">
-        <v>46294</v>
+        <v>46301.290810185186</v>
       </c>
       <c r="G156" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H156" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="I156">
-        <v>26000</v>
+        <v>520</v>
       </c>
       <c r="J156"/>
       <c r="K156"/>
       <c r="L156">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B157" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="C157" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>13000</v>
       </c>
       <c r="E157" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="F157" s="2">
-        <v>46303.697349537033</v>
+        <v>46302.52238425926</v>
       </c>
       <c r="G157" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="H157" t="s">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="I157">
-        <v>1</v>
+        <v>4000</v>
       </c>
       <c r="J157"/>
       <c r="K157"/>
       <c r="L157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>249</v>
-      </c>
-      <c r="B158" t="s">
-        <v>250</v>
-      </c>
-      <c r="C158" t="s">
-        <v>247</v>
-      </c>
-      <c r="D158">
-        <v>28</v>
-      </c>
-      <c r="E158" t="s">
-        <v>248</v>
-      </c>
-      <c r="F158" s="2">
-        <v>46304.313263888886</v>
-      </c>
-      <c r="G158" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" t="s">
-        <v>65</v>
-      </c>
-      <c r="I158">
-        <v>28</v>
-      </c>
-      <c r="J158"/>
-      <c r="K158"/>
-      <c r="L158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>251</v>
-      </c>
-      <c r="B159" t="s">
-        <v>252</v>
-      </c>
-      <c r="C159" t="s">
-        <v>247</v>
-      </c>
-      <c r="D159">
-        <v>10</v>
-      </c>
-      <c r="E159" t="s">
-        <v>248</v>
-      </c>
-      <c r="F159" s="2">
-        <v>46303.34983796296</v>
-      </c>
-      <c r="G159" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" t="s">
-        <v>65</v>
-      </c>
-      <c r="I159">
-        <v>10</v>
-      </c>
-      <c r="J159"/>
-      <c r="K159"/>
-      <c r="L159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>253</v>
-      </c>
-      <c r="B160" t="s">
-        <v>254</v>
-      </c>
-      <c r="C160" t="s">
-        <v>247</v>
-      </c>
-      <c r="D160">
-        <v>4</v>
-      </c>
-      <c r="E160" t="s">
-        <v>248</v>
-      </c>
-      <c r="F160" s="2">
-        <v>46304.302789351852</v>
-      </c>
-      <c r="G160" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" t="s">
-        <v>65</v>
-      </c>
-      <c r="I160">
-        <v>15</v>
-      </c>
-      <c r="J160"/>
-      <c r="K160"/>
-      <c r="L160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>255</v>
-      </c>
-      <c r="B161" t="s">
-        <v>256</v>
-      </c>
-      <c r="C161" t="s">
-        <v>247</v>
-      </c>
-      <c r="D161">
-        <v>4</v>
-      </c>
-      <c r="E161" t="s">
-        <v>248</v>
-      </c>
-      <c r="F161" s="2">
-        <v>46304.316724537035</v>
-      </c>
-      <c r="G161" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" t="s">
-        <v>65</v>
-      </c>
-      <c r="I161">
-        <v>14</v>
-      </c>
-      <c r="J161"/>
-      <c r="K161"/>
-      <c r="L161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>100</v>
-      </c>
-      <c r="B162" t="s">
-        <v>101</v>
-      </c>
-      <c r="C162" t="s">
-        <v>257</v>
-      </c>
-      <c r="D162">
-        <v>500</v>
-      </c>
-      <c r="E162" t="s">
-        <v>258</v>
-      </c>
-      <c r="F162" s="2">
-        <v>46308.346365740741</v>
-      </c>
-      <c r="G162" t="s">
-        <v>15</v>
-      </c>
-      <c r="H162" t="s">
-        <v>104</v>
-      </c>
-      <c r="I162">
-        <v>236</v>
-      </c>
-      <c r="J162"/>
-      <c r="K162"/>
-      <c r="L162">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>113</v>
-      </c>
-      <c r="B163" t="s">
-        <v>114</v>
-      </c>
-      <c r="C163" t="s">
-        <v>257</v>
-      </c>
-      <c r="D163">
-        <v>3600</v>
-      </c>
-      <c r="E163" t="s">
-        <v>258</v>
-      </c>
-      <c r="F163" s="2">
-        <v>46308.346365740741</v>
-      </c>
-      <c r="G163" t="s">
-        <v>15</v>
-      </c>
-      <c r="H163" t="s">
-        <v>107</v>
-      </c>
-      <c r="I163"/>
-      <c r="J163"/>
-      <c r="K163"/>
-      <c r="L163">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>259</v>
-      </c>
-      <c r="B164" t="s">
-        <v>260</v>
-      </c>
-      <c r="C164" t="s">
-        <v>257</v>
-      </c>
-      <c r="D164">
-        <v>3600</v>
-      </c>
-      <c r="E164" t="s">
-        <v>258</v>
-      </c>
-      <c r="F164" s="2">
-        <v>46308.346365740741</v>
-      </c>
-      <c r="G164" t="s">
-        <v>15</v>
-      </c>
-      <c r="H164" t="s">
-        <v>107</v>
-      </c>
-      <c r="I164"/>
-      <c r="J164"/>
-      <c r="K164"/>
-      <c r="L164">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>261</v>
-      </c>
-      <c r="B165" t="s">
-        <v>262</v>
-      </c>
-      <c r="C165" t="s">
-        <v>257</v>
-      </c>
-      <c r="D165">
-        <v>1800</v>
-      </c>
-      <c r="E165" t="s">
-        <v>258</v>
-      </c>
-      <c r="F165" s="2">
-        <v>46308.346365740741</v>
-      </c>
-      <c r="G165" t="s">
-        <v>15</v>
-      </c>
-      <c r="H165" t="s">
-        <v>107</v>
-      </c>
-      <c r="I165"/>
-      <c r="J165"/>
-      <c r="K165"/>
-      <c r="L165">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>243</v>
-      </c>
-      <c r="B166" t="s">
-        <v>244</v>
-      </c>
-      <c r="C166" t="s">
-        <v>263</v>
-      </c>
-      <c r="D166">
-        <v>52000</v>
-      </c>
-      <c r="E166" t="s">
-        <v>264</v>
-      </c>
-      <c r="F166" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G166" t="s">
-        <v>237</v>
-      </c>
-      <c r="H166" t="s">
-        <v>238</v>
-      </c>
-      <c r="I166">
-        <v>26000</v>
-      </c>
-      <c r="J166"/>
-      <c r="K166"/>
-      <c r="L166">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>265</v>
-      </c>
-      <c r="B167" t="s">
-        <v>266</v>
-      </c>
-      <c r="C167" t="s">
-        <v>267</v>
-      </c>
-      <c r="D167">
-        <v>49720</v>
-      </c>
-      <c r="E167" t="s">
-        <v>268</v>
-      </c>
-      <c r="F167" s="2">
-        <v>46306</v>
-      </c>
-      <c r="G167" t="s">
-        <v>15</v>
-      </c>
-      <c r="H167" t="s">
-        <v>21</v>
-      </c>
-      <c r="I167"/>
-      <c r="J167"/>
-      <c r="K167"/>
-      <c r="L167">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>269</v>
-      </c>
-      <c r="B168" t="s">
-        <v>270</v>
-      </c>
-      <c r="C168" t="s">
-        <v>271</v>
-      </c>
-      <c r="D168">
-        <v>520</v>
-      </c>
-      <c r="E168" t="s">
-        <v>272</v>
-      </c>
-      <c r="F168" s="2">
-        <v>46301.290810185186</v>
-      </c>
-      <c r="G168" t="s">
-        <v>237</v>
-      </c>
-      <c r="H168" t="s">
-        <v>273</v>
-      </c>
-      <c r="I168">
-        <v>520</v>
-      </c>
-      <c r="J168"/>
-      <c r="K168"/>
-      <c r="L168">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>274</v>
-      </c>
-      <c r="B169" t="s">
-        <v>275</v>
-      </c>
-      <c r="C169" t="s">
-        <v>271</v>
-      </c>
-      <c r="D169">
-        <v>13000</v>
-      </c>
-      <c r="E169" t="s">
-        <v>272</v>
-      </c>
-      <c r="F169" s="2">
-        <v>46302.52238425926</v>
-      </c>
-      <c r="G169" t="s">
-        <v>237</v>
-      </c>
-      <c r="H169" t="s">
-        <v>273</v>
-      </c>
-      <c r="I169">
-        <v>4000</v>
-      </c>
-      <c r="J169"/>
-      <c r="K169"/>
-      <c r="L169">
         <v>425</v>
       </c>
     </row>
